--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3078" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB51178B-E852-4776-9DF7-67E5D25EF38A}"/>
+  <xr:revisionPtr revIDLastSave="3082" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{492A131A-B193-4B70-9CA8-A81BF70380B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={53E2F897-EFE6-436F-9FD1-B2E222A81956}</author>
+    <author>tc={657E6C82-E276-4F4D-A851-59EA509D8885}</author>
   </authors>
   <commentList>
-    <comment ref="JK1" authorId="0" shapeId="0" xr:uid="{53E2F897-EFE6-436F-9FD1-B2E222A81956}">
+    <comment ref="JK1" authorId="0" shapeId="0" xr:uid="{657E6C82-E276-4F4D-A851-59EA509D8885}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -269,7 +269,7 @@
     Should be the same for C and T, to check!</t>
       </text>
     </comment>
-    <comment ref="F382" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
+    <comment ref="F389" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
       <text>
         <r>
           <rPr>
@@ -283,7 +283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F387" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
+    <comment ref="F394" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
       <text>
         <r>
           <rPr>
@@ -297,7 +297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F500" authorId="7" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+    <comment ref="F507" authorId="7" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -305,7 +305,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F503" authorId="8" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+    <comment ref="F510" authorId="8" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -313,7 +313,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F506" authorId="9" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+    <comment ref="F513" authorId="9" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -321,7 +321,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F509" authorId="10" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+    <comment ref="F516" authorId="10" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6533" uniqueCount="1655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6537" uniqueCount="1652">
   <si>
     <t>Example</t>
   </si>
@@ -11077,15 +11077,6 @@
     <t>pler_value_calc</t>
   </si>
   <si>
-    <t>pler_var_value_calc</t>
-  </si>
-  <si>
-    <t>ler_value_total_calc</t>
-  </si>
-  <si>
-    <t>ler_var_value_total_calc</t>
-  </si>
-  <si>
     <t>out_cv_grouping_method</t>
   </si>
   <si>
@@ -11132,7 +11123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11547,6 +11538,12 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="64">
@@ -12117,7 +12114,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12381,9 +12378,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12438,6 +12436,48 @@
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -12511,48 +12551,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -12573,21 +12571,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:LK2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:LK2" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}"/>
-  <tableColumns count="323">
-    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="title" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:LO2" insertRow="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:LO2" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}"/>
+  <tableColumns count="327">
+    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="title" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{2E8FEB31-CDE6-4F6E-9CE5-1A215D75D367}" name="year"/>
     <tableColumn id="6" xr3:uid="{6E81B9F5-7064-4F0E-B712-65740CB351D8}" name="journal"/>
     <tableColumn id="7" xr3:uid="{E0947224-5770-4E2B-A4A7-C0A71900C8BD}" name="doi"/>
     <tableColumn id="8" xr3:uid="{24D0318B-34D8-47C8-8CAB-44EBE0F157F2}" name="country"/>
     <tableColumn id="9" xr3:uid="{F42035FC-2860-44A3-A333-068FD694F5D9}" name="country_ISO"/>
     <tableColumn id="10" xr3:uid="{9D9C9B5B-5264-4FC9-B626-FF4756D7E80B}" name="C_country"/>
-    <tableColumn id="11" xr3:uid="{A2FF4D11-FAEC-4095-AC4E-A0B304B43F81}" name="C_site_type"/>
-    <tableColumn id="12" xr3:uid="{7010382C-3B13-4266-8425-96EF8CEB6CDE}" name="C_site_id"/>
+    <tableColumn id="11" xr3:uid="{A2FF4D11-FAEC-4095-AC4E-A0B304B43F81}" name="C_site_id"/>
+    <tableColumn id="12" xr3:uid="{7010382C-3B13-4266-8425-96EF8CEB6CDE}" name="C_site_type"/>
     <tableColumn id="13" xr3:uid="{1F12B971-6FD7-4CCB-9416-BEB6F73713C9}" name="C_site_admin"/>
     <tableColumn id="14" xr3:uid="{93FBA520-D0A6-47FB-A38F-43951180DF21}" name="C_site_agg"/>
     <tableColumn id="15" xr3:uid="{95216E25-B7A3-4E7E-85F4-DC656823804C}" name="C_site_latlong_type"/>
@@ -12596,8 +12594,8 @@
     <tableColumn id="18" xr3:uid="{1131EF97-EBDF-4799-A105-944062EB38E3}" name="C_site_buffer"/>
     <tableColumn id="19" xr3:uid="{9DD0D856-4914-4F9D-BB5D-8148B83A9DA3}" name="C_site_key"/>
     <tableColumn id="20" xr3:uid="{8D8F13D7-93D8-4D4B-947B-71FF74E57F39}" name="T_country"/>
-    <tableColumn id="21" xr3:uid="{8635811E-F7F4-4AC3-A968-BB714EB48044}" name="T_site_type"/>
-    <tableColumn id="22" xr3:uid="{DA85B61B-BDA9-403F-B185-FE3BC1716A51}" name="T_site_id"/>
+    <tableColumn id="21" xr3:uid="{8635811E-F7F4-4AC3-A968-BB714EB48044}" name="T_site_id"/>
+    <tableColumn id="22" xr3:uid="{DA85B61B-BDA9-403F-B185-FE3BC1716A51}" name="T_site_type"/>
     <tableColumn id="23" xr3:uid="{8E032AC2-1332-4BD2-A98E-8B163F2F00BD}" name="T_site_admin"/>
     <tableColumn id="24" xr3:uid="{B56FE6DE-D16A-4B29-B388-10727769EBEF}" name="T_site_agg"/>
     <tableColumn id="25" xr3:uid="{C13BF501-DC09-43E7-AACF-2150DCFD76C8}" name="T_site_latlong_type"/>
@@ -12896,9 +12894,13 @@
     <tableColumn id="317" xr3:uid="{03E22C1A-A0CB-419A-97A1-1A5437CBDBA3}" name="out_effect_size_yi"/>
     <tableColumn id="318" xr3:uid="{F6128811-4C02-4340-8918-5870F4B4990E}" name="out_effect_size_vi"/>
     <tableColumn id="319" xr3:uid="{B3722C44-77A9-4F9D-9D00-EB9D511F432C}" name="pler_value_calc"/>
-    <tableColumn id="320" xr3:uid="{B3B429FE-8A8E-483D-ABDC-7B69A939B427}" name="pler_var_value_calc"/>
-    <tableColumn id="321" xr3:uid="{A2C32C60-27F7-4BE0-9388-F075EEC7F517}" name="ler_value_total_calc"/>
-    <tableColumn id="322" xr3:uid="{143C2FD6-95A3-4DBA-9D9D-7A600806C124}" name="ler_var_value_total_calc"/>
+    <tableColumn id="320" xr3:uid="{B3B429FE-8A8E-483D-ABDC-7B69A939B427}" name="pler_var_calc"/>
+    <tableColumn id="321" xr3:uid="{A2C32C60-27F7-4BE0-9388-F075EEC7F517}" name="ler_value_calc"/>
+    <tableColumn id="322" xr3:uid="{143C2FD6-95A3-4DBA-9D9D-7A600806C124}" name="ler_sd_calc"/>
+    <tableColumn id="324" xr3:uid="{1C7CA45A-7884-414D-A122-8AFFBB5A3404}" name="ler_product"/>
+    <tableColumn id="325" xr3:uid="{C67338DB-8264-49EE-BC03-363E12B6331A}" name="ler_effect_size_type"/>
+    <tableColumn id="326" xr3:uid="{0C7A2316-2462-45E6-AF49-7444C43812A7}" name="ler_effect_size_yi"/>
+    <tableColumn id="327" xr3:uid="{E6B961C5-BEFB-43E0-A72F-065D4D2D9F2B}" name="ler_effect_size_vi"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13221,7 +13223,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="JK1" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{53E2F897-EFE6-436F-9FD1-B2E222A81956}">
+  <threadedComment ref="JK1" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{657E6C82-E276-4F4D-A851-59EA509D8885}">
     <text>Should be the same for C and T, to check!</text>
   </threadedComment>
 </ThreadedComments>
@@ -13279,16 +13281,16 @@
   <threadedComment ref="D272" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{EAB21104-13DB-406F-AB06-2D8E16F65555}">
     <text>Should be the same for C and T, to check!</text>
   </threadedComment>
-  <threadedComment ref="F500" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+  <threadedComment ref="F507" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F503" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+  <threadedComment ref="F510" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F506" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+  <threadedComment ref="F513" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F509" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+  <threadedComment ref="F516" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
     <text>Not sure what is this</text>
   </threadedComment>
 </ThreadedComments>
@@ -13358,10 +13360,10 @@
         <v>1381</v>
       </c>
       <c r="K1" s="115" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L1" s="115" t="s">
         <v>1382</v>
-      </c>
-      <c r="L1" s="115" t="s">
-        <v>1383</v>
       </c>
       <c r="M1" s="115" t="s">
         <v>1384</v>
@@ -13388,10 +13390,10 @@
         <v>1390</v>
       </c>
       <c r="U1" s="115" t="s">
+        <v>1392</v>
+      </c>
+      <c r="V1" s="115" t="s">
         <v>1391</v>
-      </c>
-      <c r="V1" s="115" t="s">
-        <v>1392</v>
       </c>
       <c r="W1" s="115" t="s">
         <v>1393</v>
@@ -14072,13 +14074,13 @@
         <v>1000</v>
       </c>
       <c r="IO1" s="78" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="IP1" s="78" t="s">
         <v>1591</v>
       </c>
       <c r="IQ1" s="78" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="IR1" s="78" t="s">
         <v>1590</v>
@@ -14207,7 +14209,7 @@
         <v>623</v>
       </c>
       <c r="KH1" s="83" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="KI1" s="152" t="s">
         <v>1633</v>
@@ -14221,7 +14223,7 @@
       <c r="KL1" s="152" t="s">
         <v>1636</v>
       </c>
-      <c r="KM1" s="154" t="s">
+      <c r="KM1" s="153" t="s">
         <v>1631</v>
       </c>
       <c r="KN1" s="24" t="s">
@@ -14272,34 +14274,42 @@
       <c r="LC1" s="137" t="s">
         <v>1557</v>
       </c>
-      <c r="LD1" s="155" t="s">
+      <c r="LD1" s="154" t="s">
+        <v>1638</v>
+      </c>
+      <c r="LE1" s="154" t="s">
+        <v>1639</v>
+      </c>
+      <c r="LF1" s="154" t="s">
+        <v>1640</v>
+      </c>
+      <c r="LG1" s="154" t="s">
         <v>1641</v>
-      </c>
-      <c r="LE1" s="155" t="s">
-        <v>1642</v>
-      </c>
-      <c r="LF1" s="155" t="s">
-        <v>1643</v>
-      </c>
-      <c r="LG1" s="155" t="s">
-        <v>1644</v>
       </c>
       <c r="LH1" s="152" t="s">
         <v>1637</v>
       </c>
       <c r="LI1" s="152" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="LJ1" s="152" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="LK1" s="152" t="s">
-        <v>1640</v>
-      </c>
-      <c r="LL1" s="139"/>
-      <c r="LM1" s="139"/>
-      <c r="LN1" s="139"/>
-      <c r="LO1" s="139"/>
+        <v>1645</v>
+      </c>
+      <c r="LL1" s="153" t="s">
+        <v>1651</v>
+      </c>
+      <c r="LM1" s="153" t="s">
+        <v>1650</v>
+      </c>
+      <c r="LN1" s="153" t="s">
+        <v>1648</v>
+      </c>
+      <c r="LO1" s="153" t="s">
+        <v>1649</v>
+      </c>
       <c r="LP1" s="138"/>
       <c r="LQ1" s="138"/>
       <c r="LR1" s="138"/>
@@ -31686,13 +31696,13 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="156" t="s">
+      <c r="O544" s="157" t="s">
         <v>35</v>
       </c>
-      <c r="P544" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q544" s="158" t="s">
+      <c r="P544" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q544" s="159" t="s">
         <v>36</v>
       </c>
       <c r="R544" s="3" t="s">
@@ -31714,9 +31724,9 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="156"/>
-      <c r="P545" s="157"/>
-      <c r="Q545" s="158"/>
+      <c r="O545" s="157"/>
+      <c r="P545" s="158"/>
+      <c r="Q545" s="159"/>
       <c r="R545" s="3" t="s">
         <v>38</v>
       </c>
@@ -31764,13 +31774,13 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="159" t="s">
+      <c r="O548" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="P548" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q548" s="158" t="s">
+      <c r="P548" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q548" s="159" t="s">
         <v>43</v>
       </c>
       <c r="R548" s="3">
@@ -31792,9 +31802,9 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="159"/>
-      <c r="P549" s="157"/>
-      <c r="Q549" s="158"/>
+      <c r="O549" s="160"/>
+      <c r="P549" s="158"/>
+      <c r="Q549" s="159"/>
       <c r="R549" s="3" t="s">
         <v>44</v>
       </c>
@@ -31814,13 +31824,13 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="156" t="s">
+      <c r="O550" s="157" t="s">
         <v>45</v>
       </c>
-      <c r="P550" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q550" s="158" t="s">
+      <c r="P550" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q550" s="159" t="s">
         <v>46</v>
       </c>
       <c r="R550" s="3" t="s">
@@ -31842,9 +31852,9 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="156"/>
-      <c r="P551" s="157"/>
-      <c r="Q551" s="158"/>
+      <c r="O551" s="157"/>
+      <c r="P551" s="158"/>
+      <c r="Q551" s="159"/>
       <c r="R551" s="3" t="s">
         <v>48</v>
       </c>
@@ -31892,13 +31902,13 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="159" t="s">
+      <c r="O554" s="160" t="s">
         <v>52</v>
       </c>
-      <c r="P554" s="157" t="s">
+      <c r="P554" s="158" t="s">
         <v>2</v>
       </c>
-      <c r="Q554" s="158" t="s">
+      <c r="Q554" s="159" t="s">
         <v>53</v>
       </c>
       <c r="R554" s="3">
@@ -31920,9 +31930,9 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="159"/>
-      <c r="P555" s="157"/>
-      <c r="Q555" s="158"/>
+      <c r="O555" s="160"/>
+      <c r="P555" s="158"/>
+      <c r="Q555" s="159"/>
       <c r="R555" s="3" t="s">
         <v>44</v>
       </c>
@@ -31942,13 +31952,13 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="156" t="s">
+      <c r="O556" s="157" t="s">
         <v>54</v>
       </c>
-      <c r="P556" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q556" s="158" t="s">
+      <c r="P556" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q556" s="159" t="s">
         <v>55</v>
       </c>
       <c r="R556" s="3" t="s">
@@ -31970,9 +31980,9 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="156"/>
-      <c r="P557" s="157"/>
-      <c r="Q557" s="158"/>
+      <c r="O557" s="157"/>
+      <c r="P557" s="158"/>
+      <c r="Q557" s="159"/>
       <c r="R557" s="3" t="s">
         <v>57</v>
       </c>
@@ -31992,13 +32002,13 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="156" t="s">
+      <c r="O558" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="P558" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q558" s="158" t="s">
+      <c r="P558" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q558" s="159" t="s">
         <v>59</v>
       </c>
       <c r="R558" s="3" t="s">
@@ -32020,9 +32030,9 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="156"/>
-      <c r="P559" s="157"/>
-      <c r="Q559" s="158"/>
+      <c r="O559" s="157"/>
+      <c r="P559" s="158"/>
+      <c r="Q559" s="159"/>
       <c r="R559" s="3" t="s">
         <v>61</v>
       </c>
@@ -32042,13 +32052,13 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="156" t="s">
+      <c r="O560" s="157" t="s">
         <v>62</v>
       </c>
-      <c r="P560" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q560" s="158" t="s">
+      <c r="P560" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q560" s="159" t="s">
         <v>63</v>
       </c>
       <c r="R560" s="3" t="s">
@@ -32070,9 +32080,9 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="156"/>
-      <c r="P561" s="157"/>
-      <c r="Q561" s="158"/>
+      <c r="O561" s="157"/>
+      <c r="P561" s="158"/>
+      <c r="Q561" s="159"/>
       <c r="R561" s="3" t="s">
         <v>65</v>
       </c>
@@ -32202,13 +32212,13 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="159" t="s">
+      <c r="O566" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="P566" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q566" s="158" t="s">
+      <c r="P566" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q566" s="159" t="s">
         <v>87</v>
       </c>
       <c r="R566" s="3" t="s">
@@ -32230,9 +32240,9 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="159"/>
-      <c r="P567" s="157"/>
-      <c r="Q567" s="158"/>
+      <c r="O567" s="160"/>
+      <c r="P567" s="158"/>
+      <c r="Q567" s="159"/>
       <c r="R567" s="3" t="s">
         <v>89</v>
       </c>
@@ -32252,9 +32262,9 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="159"/>
-      <c r="P568" s="157"/>
-      <c r="Q568" s="158"/>
+      <c r="O568" s="160"/>
+      <c r="P568" s="158"/>
+      <c r="Q568" s="159"/>
       <c r="R568" s="3" t="s">
         <v>90</v>
       </c>
@@ -32274,13 +32284,13 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="159" t="s">
+      <c r="O569" s="160" t="s">
         <v>91</v>
       </c>
-      <c r="P569" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q569" s="158" t="s">
+      <c r="P569" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q569" s="159" t="s">
         <v>92</v>
       </c>
       <c r="R569" s="3" t="s">
@@ -32302,9 +32312,9 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="159"/>
-      <c r="P570" s="157"/>
-      <c r="Q570" s="158"/>
+      <c r="O570" s="160"/>
+      <c r="P570" s="158"/>
+      <c r="Q570" s="159"/>
       <c r="R570" s="3" t="s">
         <v>89</v>
       </c>
@@ -32324,9 +32334,9 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="159"/>
-      <c r="P571" s="157"/>
-      <c r="Q571" s="158"/>
+      <c r="O571" s="160"/>
+      <c r="P571" s="158"/>
+      <c r="Q571" s="159"/>
       <c r="R571" s="3" t="s">
         <v>90</v>
       </c>
@@ -33132,7 +33142,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
-  <dimension ref="A1:H626"/>
+  <dimension ref="A1:H633"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="32.81640625" customWidth="1"/>
@@ -38098,7 +38108,7 @@
         <v>1002</v>
       </c>
       <c r="D250" s="78" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>4</v>
@@ -38131,7 +38141,7 @@
         <v>1002</v>
       </c>
       <c r="D252" s="78" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="F252" s="150"/>
     </row>
@@ -38822,7 +38832,7 @@
         <v>1008</v>
       </c>
       <c r="D295" s="83" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="E295" s="3"/>
       <c r="F295" s="14"/>
@@ -38902,7 +38912,7 @@
       <c r="C300" s="84" t="s">
         <v>1630</v>
       </c>
-      <c r="D300" s="154" t="s">
+      <c r="D300" s="153" t="s">
         <v>1631</v>
       </c>
       <c r="E300" s="3" t="s">
@@ -39168,8 +39178,8 @@
       <c r="C317" s="137" t="s">
         <v>1552</v>
       </c>
-      <c r="D317" s="155" t="s">
-        <v>1641</v>
+      <c r="D317" s="154" t="s">
+        <v>1638</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>1553</v>
@@ -39181,8 +39191,8 @@
       <c r="C318" s="137" t="s">
         <v>1552</v>
       </c>
-      <c r="D318" s="155" t="s">
-        <v>1642</v>
+      <c r="D318" s="154" t="s">
+        <v>1639</v>
       </c>
       <c r="F318" s="10" t="s">
         <v>1573</v>
@@ -39194,8 +39204,8 @@
       <c r="C319" s="137" t="s">
         <v>1552</v>
       </c>
-      <c r="D319" s="155" t="s">
-        <v>1643</v>
+      <c r="D319" s="154" t="s">
+        <v>1640</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -39204,11 +39214,11 @@
       <c r="C320" s="137" t="s">
         <v>1552</v>
       </c>
-      <c r="D320" s="155" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
+      <c r="D320" s="154" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="84" t="s">
@@ -39221,214 +39231,158 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:5">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="84" t="s">
         <v>1630</v>
       </c>
       <c r="D322" s="152" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:5">
       <c r="C323" s="84" t="s">
         <v>1630</v>
       </c>
       <c r="D323" s="152" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:5">
       <c r="C324" s="84" t="s">
         <v>1630</v>
       </c>
       <c r="D324" s="152" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:5">
       <c r="C325" s="84" t="s">
         <v>1630</v>
       </c>
-      <c r="D325" s="154" t="s">
-        <v>1654</v>
+      <c r="D325" s="153" t="s">
+        <v>1651</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:5">
       <c r="C326" s="84" t="s">
         <v>1630</v>
       </c>
-      <c r="D326" s="154" t="s">
-        <v>1653</v>
+      <c r="D326" s="153" t="s">
+        <v>1650</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:5">
       <c r="C327" s="84" t="s">
         <v>1630</v>
       </c>
-      <c r="D327" s="154" t="s">
-        <v>1651</v>
+      <c r="D327" s="153" t="s">
+        <v>1648</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:5">
       <c r="C328" s="84" t="s">
         <v>1630</v>
       </c>
-      <c r="D328" s="154" t="s">
-        <v>1652</v>
+      <c r="D328" s="153" t="s">
+        <v>1649</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
-      <c r="C329" s="153"/>
-      <c r="D329" s="154"/>
+    <row r="329" spans="1:5">
+      <c r="C329" s="155"/>
+      <c r="D329" s="156"/>
       <c r="E329" s="3"/>
     </row>
-    <row r="330" spans="1:7">
-      <c r="C330" s="153"/>
-      <c r="D330" s="154"/>
+    <row r="330" spans="1:5">
+      <c r="C330" s="155"/>
+      <c r="D330" s="156"/>
       <c r="E330" s="3"/>
     </row>
-    <row r="331" spans="1:7">
-      <c r="C331" s="29" t="s">
+    <row r="331" spans="1:5">
+      <c r="C331" s="155"/>
+      <c r="D331" s="156"/>
+      <c r="E331" s="3"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="C332" s="155"/>
+      <c r="D332" s="156"/>
+      <c r="E332" s="3"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="C333" s="155"/>
+      <c r="D333" s="156"/>
+      <c r="E333" s="3"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="C334" s="155"/>
+      <c r="D334" s="156"/>
+      <c r="E334" s="3"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="C335" s="155"/>
+      <c r="D335" s="156"/>
+      <c r="E335" s="3"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="C336" s="155"/>
+      <c r="D336" s="156"/>
+      <c r="E336" s="3"/>
+    </row>
+    <row r="337" spans="3:7">
+      <c r="C337" s="155"/>
+      <c r="D337" s="156"/>
+      <c r="E337" s="3"/>
+    </row>
+    <row r="338" spans="3:7">
+      <c r="C338" s="29" t="s">
         <v>1027</v>
       </c>
-      <c r="D331" s="29" t="s">
+      <c r="D338" s="29" t="s">
         <v>1027</v>
       </c>
-      <c r="E331" s="29" t="s">
+      <c r="E338" s="29" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="332" spans="1:7">
-      <c r="C332" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D332" t="s">
-        <v>1618</v>
-      </c>
-      <c r="E332" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7">
-      <c r="C333" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D333" s="59" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E333" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F333" s="3"/>
-      <c r="G333" s="3"/>
-    </row>
-    <row r="334" spans="1:7">
-      <c r="C334" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D334" s="59" t="s">
-        <v>1596</v>
-      </c>
-      <c r="E334" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F334" s="3"/>
-      <c r="G334" s="3"/>
-    </row>
-    <row r="335" spans="1:7">
-      <c r="C335" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D335" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E335" t="s">
-        <v>4</v>
-      </c>
-      <c r="F335" s="3"/>
-      <c r="G335" s="3"/>
-    </row>
-    <row r="336" spans="1:7">
-      <c r="C336" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D336" s="59" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E336" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F336" s="3"/>
-      <c r="G336" s="3"/>
-    </row>
-    <row r="337" spans="3:7">
-      <c r="C337" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D337" s="59" t="s">
-        <v>1595</v>
-      </c>
-      <c r="E337" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F337" s="3"/>
-      <c r="G337" s="3"/>
-    </row>
-    <row r="338" spans="3:7">
-      <c r="C338" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D338" t="s">
-        <v>1620</v>
-      </c>
-      <c r="E338" t="s">
-        <v>4</v>
-      </c>
-      <c r="F338" s="3"/>
-      <c r="G338" s="3"/>
     </row>
     <row r="339" spans="3:7">
       <c r="C339" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D339" s="59" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E339" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F339" s="3"/>
-      <c r="G339" s="3"/>
+      <c r="D339" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E339" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="340" spans="3:7">
       <c r="C340" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D340" s="59" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>2</v>
@@ -39440,10 +39394,12 @@
       <c r="C341" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D341" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E341" s="3"/>
+      <c r="D341" s="59" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E341" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3"/>
     </row>
@@ -39451,11 +39407,11 @@
       <c r="C342" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D342" s="59" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E342" s="3" t="s">
-        <v>2</v>
+      <c r="D342" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E342" t="s">
+        <v>4</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3"/>
@@ -39465,7 +39421,7 @@
         <v>765</v>
       </c>
       <c r="D343" s="59" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>2</v>
@@ -39478,7 +39434,7 @@
         <v>765</v>
       </c>
       <c r="D344" s="59" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>2</v>
@@ -39490,11 +39446,11 @@
       <c r="C345" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D345" s="59" t="s">
-        <v>1601</v>
-      </c>
-      <c r="E345" s="3" t="s">
-        <v>2</v>
+      <c r="D345" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E345" t="s">
+        <v>4</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3"/>
@@ -39504,7 +39460,7 @@
         <v>765</v>
       </c>
       <c r="D346" s="59" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>2</v>
@@ -39517,7 +39473,7 @@
         <v>765</v>
       </c>
       <c r="D347" s="59" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>2</v>
@@ -39529,12 +39485,10 @@
       <c r="C348" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D348" s="59" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E348" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D348" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E348" s="3"/>
       <c r="F348" s="3"/>
       <c r="G348" s="3"/>
     </row>
@@ -39543,7 +39497,7 @@
         <v>765</v>
       </c>
       <c r="D349" s="59" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>2</v>
@@ -39556,7 +39510,7 @@
         <v>765</v>
       </c>
       <c r="D350" s="59" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>2</v>
@@ -39569,7 +39523,7 @@
         <v>765</v>
       </c>
       <c r="D351" s="59" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>2</v>
@@ -39582,7 +39536,7 @@
         <v>765</v>
       </c>
       <c r="D352" s="59" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>2</v>
@@ -39595,7 +39549,7 @@
         <v>765</v>
       </c>
       <c r="D353" s="59" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>2</v>
@@ -39608,7 +39562,7 @@
         <v>765</v>
       </c>
       <c r="D354" s="59" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>2</v>
@@ -39621,7 +39575,7 @@
         <v>765</v>
       </c>
       <c r="D355" s="59" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>2</v>
@@ -39630,151 +39584,123 @@
       <c r="G355" s="3"/>
     </row>
     <row r="356" spans="1:7">
-      <c r="C356" s="14"/>
-      <c r="D356" s="59"/>
-      <c r="E356" s="3"/>
+      <c r="C356" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D356" s="59" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3"/>
     </row>
     <row r="357" spans="1:7">
-      <c r="C357" s="14"/>
-      <c r="D357" s="59"/>
-      <c r="E357" s="3"/>
+      <c r="C357" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D357" s="59" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3"/>
     </row>
     <row r="358" spans="1:7">
-      <c r="C358" s="14"/>
-      <c r="D358" s="59"/>
-      <c r="E358" s="3"/>
+      <c r="C358" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D358" s="59" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3"/>
     </row>
     <row r="359" spans="1:7">
-      <c r="C359" s="14"/>
-      <c r="D359" s="59"/>
-      <c r="E359" s="3"/>
+      <c r="C359" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D359" s="59" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3"/>
     </row>
     <row r="360" spans="1:7">
-      <c r="A360" s="14"/>
-      <c r="B360" s="14"/>
       <c r="C360" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D360" s="36" t="s">
-        <v>644</v>
-      </c>
-      <c r="E360" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G360" s="14"/>
+      <c r="D360" s="59" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F360" s="3"/>
+      <c r="G360" s="3"/>
     </row>
     <row r="361" spans="1:7">
-      <c r="A361" s="14"/>
-      <c r="B361" s="14"/>
       <c r="C361" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D361" s="36" t="s">
-        <v>645</v>
-      </c>
-      <c r="E361" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F361" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G361" s="14"/>
+      <c r="D361" s="59" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F361" s="3"/>
+      <c r="G361" s="3"/>
     </row>
     <row r="362" spans="1:7">
-      <c r="A362" s="14"/>
-      <c r="B362" s="14"/>
       <c r="C362" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D362" s="36" t="s">
-        <v>646</v>
-      </c>
-      <c r="E362" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F362" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G362" s="14"/>
+      <c r="D362" s="59" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F362" s="3"/>
+      <c r="G362" s="3"/>
     </row>
     <row r="363" spans="1:7">
-      <c r="A363" s="14"/>
-      <c r="B363" s="14"/>
-      <c r="C363" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D363" s="36" t="s">
-        <v>647</v>
-      </c>
-      <c r="E363" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F363" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G363" s="14"/>
+      <c r="C363" s="14"/>
+      <c r="D363" s="59"/>
+      <c r="E363" s="3"/>
+      <c r="F363" s="3"/>
+      <c r="G363" s="3"/>
     </row>
     <row r="364" spans="1:7">
-      <c r="A364" s="14"/>
-      <c r="B364" s="14"/>
-      <c r="C364" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D364" s="16" t="s">
-        <v>1621</v>
-      </c>
-      <c r="E364" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F364" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G364" s="14"/>
+      <c r="C364" s="14"/>
+      <c r="D364" s="59"/>
+      <c r="E364" s="3"/>
+      <c r="F364" s="3"/>
+      <c r="G364" s="3"/>
     </row>
     <row r="365" spans="1:7">
-      <c r="A365" s="14"/>
-      <c r="B365" s="14"/>
-      <c r="C365" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D365" s="16" t="s">
-        <v>1622</v>
-      </c>
-      <c r="E365" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F365" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G365" s="14"/>
+      <c r="C365" s="14"/>
+      <c r="D365" s="59"/>
+      <c r="E365" s="3"/>
+      <c r="F365" s="3"/>
+      <c r="G365" s="3"/>
     </row>
     <row r="366" spans="1:7">
-      <c r="A366" s="14"/>
-      <c r="B366" s="14"/>
-      <c r="C366" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D366" s="16" t="s">
-        <v>661</v>
-      </c>
-      <c r="E366" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F366" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G366" s="14"/>
+      <c r="C366" s="14"/>
+      <c r="D366" s="59"/>
+      <c r="E366" s="3"/>
+      <c r="F366" s="3"/>
+      <c r="G366" s="3"/>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" s="14"/>
@@ -39782,14 +39708,14 @@
       <c r="C367" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D367" s="16" t="s">
-        <v>663</v>
-      </c>
-      <c r="E367" s="3" t="s">
+      <c r="D367" s="36" t="s">
+        <v>644</v>
+      </c>
+      <c r="E367" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G367" s="14"/>
     </row>
@@ -39799,14 +39725,14 @@
       <c r="C368" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D368" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="E368" s="3" t="s">
+      <c r="D368" s="36" t="s">
+        <v>645</v>
+      </c>
+      <c r="E368" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G368" s="14"/>
     </row>
@@ -39816,14 +39742,14 @@
       <c r="C369" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D369" s="16" t="s">
-        <v>664</v>
-      </c>
-      <c r="E369" s="3" t="s">
+      <c r="D369" s="36" t="s">
+        <v>646</v>
+      </c>
+      <c r="E369" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="G369" s="14"/>
     </row>
@@ -39833,14 +39759,14 @@
       <c r="C370" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D370" s="16" t="s">
-        <v>665</v>
-      </c>
-      <c r="E370" s="3" t="s">
+      <c r="D370" s="36" t="s">
+        <v>647</v>
+      </c>
+      <c r="E370" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G370" s="14"/>
     </row>
@@ -39851,13 +39777,13 @@
         <v>765</v>
       </c>
       <c r="D371" s="16" t="s">
-        <v>666</v>
+        <v>1621</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G371" s="14"/>
     </row>
@@ -39868,13 +39794,13 @@
         <v>765</v>
       </c>
       <c r="D372" s="16" t="s">
-        <v>667</v>
+        <v>1622</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G372" s="14"/>
     </row>
@@ -39885,13 +39811,13 @@
         <v>765</v>
       </c>
       <c r="D373" s="16" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G373" s="14"/>
     </row>
@@ -39902,13 +39828,13 @@
         <v>765</v>
       </c>
       <c r="D374" s="16" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G374" s="14"/>
     </row>
@@ -39919,13 +39845,13 @@
         <v>765</v>
       </c>
       <c r="D375" s="16" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G375" s="14"/>
     </row>
@@ -39935,14 +39861,14 @@
       <c r="C376" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D376" s="34" t="s">
-        <v>671</v>
+      <c r="D376" s="16" t="s">
+        <v>664</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G376" s="14"/>
     </row>
@@ -39952,14 +39878,14 @@
       <c r="C377" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D377" s="34" t="s">
-        <v>672</v>
+      <c r="D377" s="16" t="s">
+        <v>665</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G377" s="14"/>
     </row>
@@ -39969,14 +39895,14 @@
       <c r="C378" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D378" s="34" t="s">
-        <v>673</v>
+      <c r="D378" s="16" t="s">
+        <v>666</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G378" s="14"/>
     </row>
@@ -39986,14 +39912,14 @@
       <c r="C379" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D379" s="34" t="s">
-        <v>674</v>
+      <c r="D379" s="16" t="s">
+        <v>667</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="G379" s="14"/>
     </row>
@@ -40003,18 +39929,16 @@
       <c r="C380" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D380" s="20" t="s">
-        <v>675</v>
+      <c r="D380" s="16" t="s">
+        <v>668</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F380" t="s">
-        <v>325</v>
-      </c>
-      <c r="G380" s="31" t="s">
-        <v>326</v>
-      </c>
+      <c r="F380" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G380" s="14"/>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" s="14"/>
@@ -40022,18 +39946,16 @@
       <c r="C381" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D381" s="20" t="s">
-        <v>676</v>
+      <c r="D381" s="16" t="s">
+        <v>669</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F381" t="s">
-        <v>327</v>
-      </c>
-      <c r="G381" s="31" t="s">
-        <v>328</v>
-      </c>
+      <c r="F381" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G381" s="14"/>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" s="14"/>
@@ -40041,18 +39963,16 @@
       <c r="C382" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D382" s="20" t="s">
-        <v>677</v>
+      <c r="D382" s="16" t="s">
+        <v>670</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F382" t="s">
-        <v>329</v>
-      </c>
-      <c r="G382" s="31" t="s">
-        <v>330</v>
-      </c>
+      <c r="F382" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G382" s="14"/>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" s="14"/>
@@ -40060,37 +39980,33 @@
       <c r="C383" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D383" s="20" t="s">
-        <v>678</v>
+      <c r="D383" s="34" t="s">
+        <v>671</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F383" t="s">
-        <v>331</v>
-      </c>
-      <c r="G383" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" ht="15.5">
+      <c r="F383" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G383" s="14"/>
+    </row>
+    <row r="384" spans="1:7">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D384" s="20" t="s">
-        <v>679</v>
+      <c r="D384" s="34" t="s">
+        <v>672</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F384" t="s">
-        <v>332</v>
-      </c>
-      <c r="G384" s="5">
-        <v>2</v>
-      </c>
+      <c r="F384" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G384" s="14"/>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" s="14"/>
@@ -40098,18 +40014,16 @@
       <c r="C385" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D385" s="20" t="s">
-        <v>680</v>
+      <c r="D385" s="34" t="s">
+        <v>673</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F385" t="s">
-        <v>325</v>
-      </c>
-      <c r="G385" s="31" t="s">
-        <v>326</v>
-      </c>
+      <c r="F385" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G385" s="14"/>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" s="14"/>
@@ -40117,18 +40031,16 @@
       <c r="C386" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D386" s="20" t="s">
-        <v>681</v>
+      <c r="D386" s="34" t="s">
+        <v>674</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F386" t="s">
-        <v>327</v>
-      </c>
-      <c r="G386" s="31" t="s">
-        <v>328</v>
-      </c>
+      <c r="F386" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G386" s="14"/>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" s="14"/>
@@ -40137,16 +40049,16 @@
         <v>765</v>
       </c>
       <c r="D387" s="20" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F387" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G387" s="31" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -40156,35 +40068,35 @@
         <v>765</v>
       </c>
       <c r="D388" s="20" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F388" t="s">
-        <v>331</v>
-      </c>
-      <c r="G388" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7" ht="15.5">
+        <v>327</v>
+      </c>
+      <c r="G388" s="31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
       <c r="A389" s="14"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D389" s="20" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F389" t="s">
-        <v>332</v>
-      </c>
-      <c r="G389" s="5">
-        <v>2</v>
+        <v>329</v>
+      </c>
+      <c r="G389" s="31" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -40193,14 +40105,17 @@
       <c r="C390" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D390" s="24" t="s">
-        <v>685</v>
+      <c r="D390" s="20" t="s">
+        <v>678</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F390" t="s">
-        <v>342</v>
+        <v>331</v>
+      </c>
+      <c r="G390" s="31">
+        <v>20</v>
       </c>
     </row>
     <row r="391" spans="1:7" ht="15.5">
@@ -40209,16 +40124,18 @@
       <c r="C391" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D391" s="24" t="s">
-        <v>686</v>
+      <c r="D391" s="20" t="s">
+        <v>679</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F391" t="s">
-        <v>344</v>
-      </c>
-      <c r="G391" s="5"/>
+        <v>332</v>
+      </c>
+      <c r="G391" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" s="14"/>
@@ -40226,17 +40143,17 @@
       <c r="C392" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D392" s="24" t="s">
-        <v>687</v>
+      <c r="D392" s="20" t="s">
+        <v>680</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F392" t="s">
-        <v>603</v>
+        <v>325</v>
       </c>
       <c r="G392" s="31" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -40245,32 +40162,37 @@
       <c r="C393" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D393" s="24" t="s">
-        <v>688</v>
+      <c r="D393" s="20" t="s">
+        <v>681</v>
       </c>
       <c r="E393" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F393" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" ht="15.5">
+        <v>327</v>
+      </c>
+      <c r="G393" s="31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D394" s="24" t="s">
-        <v>689</v>
+      <c r="D394" s="20" t="s">
+        <v>682</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F394" t="s">
-        <v>344</v>
-      </c>
-      <c r="G394" s="5"/>
+        <v>329</v>
+      </c>
+      <c r="G394" s="31" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="14"/>
@@ -40278,36 +40200,36 @@
       <c r="C395" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D395" s="24" t="s">
-        <v>690</v>
+      <c r="D395" s="20" t="s">
+        <v>683</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F395" t="s">
-        <v>603</v>
-      </c>
-      <c r="G395" s="31" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7">
+        <v>331</v>
+      </c>
+      <c r="G395" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" ht="15.5">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D396" s="23" t="s">
-        <v>691</v>
+      <c r="D396" s="20" t="s">
+        <v>684</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F396" t="s">
-        <v>350</v>
-      </c>
-      <c r="G396" s="31" t="s">
-        <v>352</v>
+        <v>332</v>
+      </c>
+      <c r="G396" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -40316,17 +40238,14 @@
       <c r="C397" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D397" s="23" t="s">
-        <v>692</v>
+      <c r="D397" s="24" t="s">
+        <v>685</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F397" t="s">
-        <v>351</v>
-      </c>
-      <c r="G397" s="31" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="398" spans="1:7" ht="15.5">
@@ -40335,14 +40254,14 @@
       <c r="C398" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D398" s="23" t="s">
-        <v>693</v>
+      <c r="D398" s="24" t="s">
+        <v>686</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F398" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="G398" s="5"/>
     </row>
@@ -40352,17 +40271,17 @@
       <c r="C399" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D399" s="23" t="s">
-        <v>694</v>
+      <c r="D399" s="24" t="s">
+        <v>687</v>
       </c>
       <c r="E399" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F399" t="s">
-        <v>356</v>
+        <v>603</v>
       </c>
       <c r="G399" s="31" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -40371,362 +40290,355 @@
       <c r="C400" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D400" s="23" t="s">
-        <v>695</v>
+      <c r="D400" s="24" t="s">
+        <v>688</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F400" t="s">
-        <v>350</v>
-      </c>
-      <c r="G400" s="31" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" ht="15.5">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D401" s="23" t="s">
-        <v>696</v>
+      <c r="D401" s="24" t="s">
+        <v>689</v>
       </c>
       <c r="E401" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F401" t="s">
-        <v>351</v>
-      </c>
-      <c r="G401" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7" ht="15.5">
+        <v>344</v>
+      </c>
+      <c r="G401" s="5"/>
+    </row>
+    <row r="402" spans="1:7">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D402" s="23" t="s">
-        <v>697</v>
+      <c r="D402" s="24" t="s">
+        <v>690</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F402" t="s">
-        <v>355</v>
-      </c>
-      <c r="G402" s="5"/>
-    </row>
-    <row r="403" spans="1:7" ht="15" thickBot="1">
+        <v>603</v>
+      </c>
+      <c r="G402" s="31" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D403" s="23" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F403" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G403" s="31" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7" ht="15" thickBot="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D404" s="21" t="s">
-        <v>699</v>
+      <c r="D404" s="23" t="s">
+        <v>692</v>
       </c>
       <c r="E404" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F404" s="3"/>
-      <c r="G404" s="14"/>
-    </row>
-    <row r="405" spans="1:7" ht="15" thickBot="1">
+      <c r="F404" t="s">
+        <v>351</v>
+      </c>
+      <c r="G404" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" ht="15.5">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D405" s="21" t="s">
-        <v>700</v>
+      <c r="D405" s="23" t="s">
+        <v>693</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F405" s="3"/>
-      <c r="G405" s="14"/>
-    </row>
-    <row r="406" spans="1:7" ht="15.5">
+      <c r="F405" t="s">
+        <v>355</v>
+      </c>
+      <c r="G405" s="5"/>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" s="14"/>
+      <c r="B406" s="14"/>
       <c r="C406" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D406" s="24" t="s">
-        <v>701</v>
+      <c r="D406" s="23" t="s">
+        <v>694</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F406" t="s">
-        <v>397</v>
-      </c>
-      <c r="G406" s="5" t="s">
-        <v>382</v>
+        <v>356</v>
+      </c>
+      <c r="G406" s="31" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="407" spans="1:7">
+      <c r="A407" s="14"/>
+      <c r="B407" s="14"/>
       <c r="C407" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D407" s="24" t="s">
-        <v>702</v>
+      <c r="D407" s="23" t="s">
+        <v>695</v>
       </c>
       <c r="E407" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F407" t="s">
-        <v>399</v>
-      </c>
-      <c r="G407" t="s">
-        <v>597</v>
+        <v>350</v>
+      </c>
+      <c r="G407" s="31" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="408" spans="1:7">
+      <c r="A408" s="14"/>
+      <c r="B408" s="14"/>
       <c r="C408" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D408" s="24" t="s">
-        <v>703</v>
+      <c r="D408" s="23" t="s">
+        <v>696</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F408" t="s">
-        <v>400</v>
-      </c>
-      <c r="G408" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7">
+        <v>351</v>
+      </c>
+      <c r="G408" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" ht="15.5">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D409" s="24" t="s">
-        <v>704</v>
+      <c r="D409" s="23" t="s">
+        <v>697</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F409" t="s">
-        <v>401</v>
-      </c>
-      <c r="G409" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7" ht="15.5">
+        <v>355</v>
+      </c>
+      <c r="G409" s="5"/>
+    </row>
+    <row r="410" spans="1:7" ht="15" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D410" s="24" t="s">
-        <v>705</v>
+      <c r="D410" s="23" t="s">
+        <v>698</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F410" t="s">
-        <v>397</v>
-      </c>
-      <c r="G410" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="411" spans="1:7">
+        <v>356</v>
+      </c>
+      <c r="G410" s="31" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" ht="15" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D411" s="24" t="s">
-        <v>706</v>
+      <c r="D411" s="21" t="s">
+        <v>699</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F411" t="s">
-        <v>399</v>
-      </c>
-      <c r="G411" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7">
+      <c r="F411" s="3"/>
+      <c r="G411" s="14"/>
+    </row>
+    <row r="412" spans="1:7" ht="15" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D412" s="24" t="s">
-        <v>707</v>
+      <c r="D412" s="21" t="s">
+        <v>700</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F412" t="s">
-        <v>400</v>
-      </c>
-      <c r="G412" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7" ht="15" thickBot="1">
-      <c r="A413" s="14"/>
-      <c r="B413" s="14"/>
+      <c r="F412" s="3"/>
+      <c r="G412" s="14"/>
+    </row>
+    <row r="413" spans="1:7" ht="15.5">
       <c r="C413" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D413" s="24" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F413" t="s">
-        <v>401</v>
-      </c>
-      <c r="G413" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" ht="15" thickBot="1">
-      <c r="A414" s="14"/>
-      <c r="B414" s="14"/>
+        <v>397</v>
+      </c>
+      <c r="G413" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
       <c r="C414" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D414" s="21" t="s">
-        <v>709</v>
-      </c>
-      <c r="E414" s="17" t="s">
+      <c r="D414" s="24" t="s">
+        <v>702</v>
+      </c>
+      <c r="E414" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F414" t="s">
-        <v>431</v>
-      </c>
-      <c r="G414" s="38" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7" ht="15" thickBot="1">
-      <c r="A415" s="14"/>
-      <c r="B415" s="14"/>
+        <v>399</v>
+      </c>
+      <c r="G414" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
       <c r="C415" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D415" s="21" t="s">
-        <v>710</v>
-      </c>
-      <c r="E415" s="17" t="s">
+      <c r="D415" s="24" t="s">
+        <v>703</v>
+      </c>
+      <c r="E415" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F415" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="G415" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" ht="15" thickBot="1">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D416" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="E416" s="17" t="s">
+      <c r="D416" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="E416" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F416" t="s">
-        <v>434</v>
-      </c>
-      <c r="G416" s="39" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="417" spans="1:7" ht="15" thickBot="1">
+        <v>401</v>
+      </c>
+      <c r="G416" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" ht="15.5">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D417" s="21" t="s">
-        <v>712</v>
-      </c>
-      <c r="E417" s="17" t="s">
+      <c r="D417" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="E417" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F417" t="s">
-        <v>435</v>
-      </c>
-      <c r="G417" s="40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="418" spans="1:7" ht="15" thickBot="1">
+        <v>397</v>
+      </c>
+      <c r="G417" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D418" s="21" t="s">
-        <v>713</v>
-      </c>
-      <c r="E418" s="17" t="s">
-        <v>2</v>
+      <c r="D418" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="E418" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F418" t="s">
-        <v>714</v>
-      </c>
-      <c r="G418" s="32" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" ht="15" thickBot="1">
+        <v>399</v>
+      </c>
+      <c r="G418" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D419" s="21" t="s">
-        <v>715</v>
-      </c>
-      <c r="E419" s="17" t="s">
+      <c r="D419" s="24" t="s">
+        <v>707</v>
+      </c>
+      <c r="E419" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F419" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="G419" t="s">
-        <v>74</v>
+        <v>597</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="15" thickBot="1">
@@ -40735,17 +40647,17 @@
       <c r="C420" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D420" s="21" t="s">
-        <v>716</v>
-      </c>
-      <c r="E420" s="17" t="s">
-        <v>2</v>
+      <c r="D420" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="E420" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F420" t="s">
-        <v>717</v>
-      </c>
-      <c r="G420">
-        <v>120</v>
+        <v>401</v>
+      </c>
+      <c r="G420" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="15" thickBot="1">
@@ -40755,16 +40667,16 @@
         <v>765</v>
       </c>
       <c r="D421" s="21" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="E421" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F421" t="s">
-        <v>719</v>
-      </c>
-      <c r="G421">
-        <v>30</v>
+        <v>431</v>
+      </c>
+      <c r="G421" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="422" spans="1:7" ht="15" thickBot="1">
@@ -40774,16 +40686,16 @@
         <v>765</v>
       </c>
       <c r="D422" s="21" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="E422" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F422" t="s">
-        <v>721</v>
-      </c>
-      <c r="G422">
-        <v>60</v>
+        <v>433</v>
+      </c>
+      <c r="G422" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="423" spans="1:7" ht="15" thickBot="1">
@@ -40793,16 +40705,16 @@
         <v>765</v>
       </c>
       <c r="D423" s="21" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="E423" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F423" t="s">
-        <v>723</v>
-      </c>
-      <c r="G423">
-        <v>70</v>
+        <v>434</v>
+      </c>
+      <c r="G423" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="424" spans="1:7" ht="15" thickBot="1">
@@ -40812,16 +40724,16 @@
         <v>765</v>
       </c>
       <c r="D424" s="21" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="E424" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F424" t="s">
-        <v>725</v>
-      </c>
-      <c r="G424">
-        <v>90</v>
+        <v>435</v>
+      </c>
+      <c r="G424" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="425" spans="1:7" ht="15" thickBot="1">
@@ -40830,14 +40742,17 @@
       <c r="C425" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D425" s="20" t="s">
-        <v>726</v>
+      <c r="D425" s="21" t="s">
+        <v>713</v>
       </c>
       <c r="E425" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F425" t="s">
-        <v>443</v>
+        <v>714</v>
+      </c>
+      <c r="G425" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="15" thickBot="1">
@@ -40846,14 +40761,17 @@
       <c r="C426" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D426" s="20" t="s">
-        <v>727</v>
+      <c r="D426" s="21" t="s">
+        <v>715</v>
       </c>
       <c r="E426" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F426" t="s">
-        <v>444</v>
+        <v>437</v>
+      </c>
+      <c r="G426" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="427" spans="1:7" ht="15" thickBot="1">
@@ -40862,14 +40780,17 @@
       <c r="C427" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D427" s="20" t="s">
-        <v>728</v>
+      <c r="D427" s="21" t="s">
+        <v>716</v>
       </c>
       <c r="E427" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F427" t="s">
-        <v>447</v>
+        <v>717</v>
+      </c>
+      <c r="G427">
+        <v>120</v>
       </c>
     </row>
     <row r="428" spans="1:7" ht="15" thickBot="1">
@@ -40878,14 +40799,17 @@
       <c r="C428" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D428" s="20" t="s">
-        <v>729</v>
+      <c r="D428" s="21" t="s">
+        <v>718</v>
       </c>
       <c r="E428" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F428" t="s">
-        <v>730</v>
+        <v>719</v>
+      </c>
+      <c r="G428">
+        <v>30</v>
       </c>
     </row>
     <row r="429" spans="1:7" ht="15" thickBot="1">
@@ -40894,14 +40818,17 @@
       <c r="C429" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D429" s="20" t="s">
-        <v>731</v>
+      <c r="D429" s="21" t="s">
+        <v>720</v>
       </c>
       <c r="E429" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F429" t="s">
-        <v>448</v>
+        <v>721</v>
+      </c>
+      <c r="G429">
+        <v>60</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="15" thickBot="1">
@@ -40910,14 +40837,17 @@
       <c r="C430" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D430" s="20" t="s">
-        <v>732</v>
+      <c r="D430" s="21" t="s">
+        <v>722</v>
       </c>
       <c r="E430" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F430" t="s">
-        <v>449</v>
+        <v>723</v>
+      </c>
+      <c r="G430">
+        <v>70</v>
       </c>
     </row>
     <row r="431" spans="1:7" ht="15" thickBot="1">
@@ -40926,14 +40856,17 @@
       <c r="C431" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D431" s="20" t="s">
-        <v>733</v>
+      <c r="D431" s="21" t="s">
+        <v>724</v>
       </c>
       <c r="E431" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F431" t="s">
-        <v>450</v>
+        <v>725</v>
+      </c>
+      <c r="G431">
+        <v>90</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="15" thickBot="1">
@@ -40943,13 +40876,13 @@
         <v>765</v>
       </c>
       <c r="D432" s="20" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="E432" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F432" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="433" spans="1:7" ht="15" thickBot="1">
@@ -40959,15 +40892,14 @@
         <v>765</v>
       </c>
       <c r="D433" s="20" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="E433" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F433" t="s">
-        <v>453</v>
-      </c>
-      <c r="G433" s="41"/>
+        <v>444</v>
+      </c>
     </row>
     <row r="434" spans="1:7" ht="15" thickBot="1">
       <c r="A434" s="14"/>
@@ -40975,17 +40907,14 @@
       <c r="C434" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D434" s="21" t="s">
-        <v>736</v>
+      <c r="D434" s="20" t="s">
+        <v>728</v>
       </c>
       <c r="E434" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F434" t="s">
-        <v>431</v>
-      </c>
-      <c r="G434" s="38" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
     </row>
     <row r="435" spans="1:7" ht="15" thickBot="1">
@@ -40994,17 +40923,14 @@
       <c r="C435" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D435" s="21" t="s">
-        <v>737</v>
+      <c r="D435" s="20" t="s">
+        <v>729</v>
       </c>
       <c r="E435" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F435" t="s">
-        <v>433</v>
-      </c>
-      <c r="G435" t="s">
-        <v>419</v>
+        <v>730</v>
       </c>
     </row>
     <row r="436" spans="1:7" ht="15" thickBot="1">
@@ -41013,17 +40939,14 @@
       <c r="C436" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D436" s="21" t="s">
-        <v>738</v>
+      <c r="D436" s="20" t="s">
+        <v>731</v>
       </c>
       <c r="E436" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F436" t="s">
-        <v>434</v>
-      </c>
-      <c r="G436" s="39" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="437" spans="1:7" ht="15" thickBot="1">
@@ -41032,17 +40955,14 @@
       <c r="C437" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D437" s="21" t="s">
-        <v>739</v>
+      <c r="D437" s="20" t="s">
+        <v>732</v>
       </c>
       <c r="E437" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F437" t="s">
-        <v>435</v>
-      </c>
-      <c r="G437" s="40" t="s">
-        <v>74</v>
+        <v>449</v>
       </c>
     </row>
     <row r="438" spans="1:7" ht="15" thickBot="1">
@@ -41051,17 +40971,14 @@
       <c r="C438" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D438" s="21" t="s">
-        <v>740</v>
+      <c r="D438" s="20" t="s">
+        <v>733</v>
       </c>
       <c r="E438" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F438" t="s">
-        <v>741</v>
-      </c>
-      <c r="G438" s="32" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
     </row>
     <row r="439" spans="1:7" ht="15" thickBot="1">
@@ -41070,17 +40987,14 @@
       <c r="C439" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D439" s="21" t="s">
-        <v>742</v>
+      <c r="D439" s="20" t="s">
+        <v>734</v>
       </c>
       <c r="E439" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F439" t="s">
-        <v>437</v>
-      </c>
-      <c r="G439" t="s">
-        <v>74</v>
+        <v>451</v>
       </c>
     </row>
     <row r="440" spans="1:7" ht="15" thickBot="1">
@@ -41089,18 +41003,16 @@
       <c r="C440" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D440" s="21" t="s">
-        <v>743</v>
+      <c r="D440" s="20" t="s">
+        <v>735</v>
       </c>
       <c r="E440" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F440" t="s">
-        <v>744</v>
-      </c>
-      <c r="G440">
-        <v>120</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G440" s="41"/>
     </row>
     <row r="441" spans="1:7" ht="15" thickBot="1">
       <c r="A441" s="14"/>
@@ -41109,16 +41021,16 @@
         <v>765</v>
       </c>
       <c r="D441" s="21" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="E441" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F441" t="s">
-        <v>746</v>
-      </c>
-      <c r="G441">
-        <v>30</v>
+        <v>431</v>
+      </c>
+      <c r="G441" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="442" spans="1:7" ht="15" thickBot="1">
@@ -41128,16 +41040,16 @@
         <v>765</v>
       </c>
       <c r="D442" s="21" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="E442" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F442" t="s">
-        <v>748</v>
-      </c>
-      <c r="G442">
-        <v>60</v>
+        <v>433</v>
+      </c>
+      <c r="G442" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="15" thickBot="1">
@@ -41147,16 +41059,16 @@
         <v>765</v>
       </c>
       <c r="D443" s="21" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="E443" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F443" t="s">
-        <v>750</v>
-      </c>
-      <c r="G443">
-        <v>70</v>
+        <v>434</v>
+      </c>
+      <c r="G443" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="444" spans="1:7" ht="15" thickBot="1">
@@ -41166,16 +41078,16 @@
         <v>765</v>
       </c>
       <c r="D444" s="21" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="E444" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F444" t="s">
-        <v>752</v>
-      </c>
-      <c r="G444">
-        <v>90</v>
+        <v>435</v>
+      </c>
+      <c r="G444" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="445" spans="1:7" ht="15" thickBot="1">
@@ -41184,14 +41096,17 @@
       <c r="C445" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D445" s="20" t="s">
-        <v>753</v>
+      <c r="D445" s="21" t="s">
+        <v>740</v>
       </c>
       <c r="E445" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F445" t="s">
-        <v>443</v>
+        <v>741</v>
+      </c>
+      <c r="G445" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="446" spans="1:7" ht="15" thickBot="1">
@@ -41200,14 +41115,17 @@
       <c r="C446" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D446" s="20" t="s">
-        <v>754</v>
+      <c r="D446" s="21" t="s">
+        <v>742</v>
       </c>
       <c r="E446" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F446" t="s">
-        <v>444</v>
+        <v>437</v>
+      </c>
+      <c r="G446" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="447" spans="1:7" ht="15" thickBot="1">
@@ -41216,14 +41134,17 @@
       <c r="C447" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D447" s="20" t="s">
-        <v>755</v>
+      <c r="D447" s="21" t="s">
+        <v>743</v>
       </c>
       <c r="E447" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F447" t="s">
-        <v>447</v>
+        <v>744</v>
+      </c>
+      <c r="G447">
+        <v>120</v>
       </c>
     </row>
     <row r="448" spans="1:7" ht="15" thickBot="1">
@@ -41232,14 +41153,17 @@
       <c r="C448" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D448" s="20" t="s">
-        <v>756</v>
+      <c r="D448" s="21" t="s">
+        <v>745</v>
       </c>
       <c r="E448" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F448" t="s">
-        <v>757</v>
+        <v>746</v>
+      </c>
+      <c r="G448">
+        <v>30</v>
       </c>
     </row>
     <row r="449" spans="1:7" ht="15" thickBot="1">
@@ -41248,14 +41172,17 @@
       <c r="C449" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D449" s="20" t="s">
-        <v>758</v>
+      <c r="D449" s="21" t="s">
+        <v>747</v>
       </c>
       <c r="E449" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F449" t="s">
-        <v>448</v>
+        <v>748</v>
+      </c>
+      <c r="G449">
+        <v>60</v>
       </c>
     </row>
     <row r="450" spans="1:7" ht="15" thickBot="1">
@@ -41264,14 +41191,17 @@
       <c r="C450" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D450" s="20" t="s">
-        <v>759</v>
+      <c r="D450" s="21" t="s">
+        <v>749</v>
       </c>
       <c r="E450" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F450" t="s">
-        <v>449</v>
+        <v>750</v>
+      </c>
+      <c r="G450">
+        <v>70</v>
       </c>
     </row>
     <row r="451" spans="1:7" ht="15" thickBot="1">
@@ -41280,14 +41210,17 @@
       <c r="C451" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D451" s="20" t="s">
-        <v>760</v>
+      <c r="D451" s="21" t="s">
+        <v>751</v>
       </c>
       <c r="E451" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F451" t="s">
-        <v>450</v>
+        <v>752</v>
+      </c>
+      <c r="G451">
+        <v>90</v>
       </c>
     </row>
     <row r="452" spans="1:7" ht="15" thickBot="1">
@@ -41297,13 +41230,13 @@
         <v>765</v>
       </c>
       <c r="D452" s="20" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="E452" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F452" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="453" spans="1:7" ht="15" thickBot="1">
@@ -41313,15 +41246,14 @@
         <v>765</v>
       </c>
       <c r="D453" s="20" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="E453" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F453" t="s">
-        <v>453</v>
-      </c>
-      <c r="G453" s="41"/>
+        <v>444</v>
+      </c>
     </row>
     <row r="454" spans="1:7" ht="15" thickBot="1">
       <c r="A454" s="14"/>
@@ -41329,17 +41261,14 @@
       <c r="C454" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D454" s="21" t="s">
-        <v>763</v>
+      <c r="D454" s="20" t="s">
+        <v>755</v>
       </c>
       <c r="E454" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F454" t="s">
-        <v>485</v>
-      </c>
-      <c r="G454" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
     </row>
     <row r="455" spans="1:7" ht="15" thickBot="1">
@@ -41348,17 +41277,14 @@
       <c r="C455" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D455" s="21" t="s">
-        <v>764</v>
+      <c r="D455" s="20" t="s">
+        <v>756</v>
       </c>
       <c r="E455" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F455" t="s">
-        <v>486</v>
-      </c>
-      <c r="G455" t="s">
-        <v>483</v>
+        <v>757</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="15" thickBot="1">
@@ -41367,17 +41293,14 @@
       <c r="C456" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D456" s="21" t="s">
-        <v>766</v>
+      <c r="D456" s="20" t="s">
+        <v>758</v>
       </c>
       <c r="E456" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F456" t="s">
-        <v>485</v>
-      </c>
-      <c r="G456" t="s">
-        <v>484</v>
+        <v>448</v>
       </c>
     </row>
     <row r="457" spans="1:7" ht="15" thickBot="1">
@@ -41386,17 +41309,14 @@
       <c r="C457" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D457" s="21" t="s">
-        <v>767</v>
+      <c r="D457" s="20" t="s">
+        <v>759</v>
       </c>
       <c r="E457" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F457" t="s">
-        <v>486</v>
-      </c>
-      <c r="G457" t="s">
-        <v>483</v>
+        <v>449</v>
       </c>
     </row>
     <row r="458" spans="1:7" ht="15" thickBot="1">
@@ -41406,16 +41326,13 @@
         <v>765</v>
       </c>
       <c r="D458" s="20" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="E458" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F458" t="s">
-        <v>495</v>
-      </c>
-      <c r="G458" t="s">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="15" thickBot="1">
@@ -41425,16 +41342,13 @@
         <v>765</v>
       </c>
       <c r="D459" s="20" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="E459" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F459" t="s">
-        <v>496</v>
-      </c>
-      <c r="G459" t="s">
-        <v>497</v>
+        <v>451</v>
       </c>
     </row>
     <row r="460" spans="1:7" ht="15" thickBot="1">
@@ -41444,17 +41358,15 @@
         <v>765</v>
       </c>
       <c r="D460" s="20" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="E460" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F460" t="s">
-        <v>498</v>
-      </c>
-      <c r="G460" s="42" t="s">
-        <v>493</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G460" s="41"/>
     </row>
     <row r="461" spans="1:7" ht="15" thickBot="1">
       <c r="A461" s="14"/>
@@ -41462,17 +41374,17 @@
       <c r="C461" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D461" s="20" t="s">
-        <v>771</v>
+      <c r="D461" s="21" t="s">
+        <v>763</v>
       </c>
       <c r="E461" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F461" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="G461" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="462" spans="1:7" ht="15" thickBot="1">
@@ -41482,16 +41394,16 @@
         <v>765</v>
       </c>
       <c r="D462" s="21" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="E462" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F462" t="s">
-        <v>524</v>
-      </c>
-      <c r="G462" s="42" t="s">
-        <v>501</v>
+        <v>486</v>
+      </c>
+      <c r="G462" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="463" spans="1:7" ht="15" thickBot="1">
@@ -41501,13 +41413,16 @@
         <v>765</v>
       </c>
       <c r="D463" s="21" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="E463" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F463" t="s">
-        <v>525</v>
+        <v>485</v>
+      </c>
+      <c r="G463" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="464" spans="1:7" ht="15" thickBot="1">
@@ -41517,15 +41432,17 @@
         <v>765</v>
       </c>
       <c r="D464" s="21" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="E464" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F464" t="s">
-        <v>526</v>
-      </c>
-      <c r="G464" s="43"/>
+        <v>486</v>
+      </c>
+      <c r="G464" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="465" spans="1:7" ht="15" thickBot="1">
       <c r="A465" s="14"/>
@@ -41533,16 +41450,18 @@
       <c r="C465" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D465" s="21" t="s">
-        <v>775</v>
+      <c r="D465" s="20" t="s">
+        <v>768</v>
       </c>
       <c r="E465" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F465" t="s">
-        <v>527</v>
-      </c>
-      <c r="G465" s="44"/>
+        <v>495</v>
+      </c>
+      <c r="G465" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="466" spans="1:7" ht="15" thickBot="1">
       <c r="A466" s="14"/>
@@ -41550,16 +41469,18 @@
       <c r="C466" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D466" s="21" t="s">
-        <v>776</v>
+      <c r="D466" s="20" t="s">
+        <v>769</v>
       </c>
       <c r="E466" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F466" t="s">
-        <v>528</v>
-      </c>
-      <c r="G466" s="44"/>
+        <v>496</v>
+      </c>
+      <c r="G466" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="467" spans="1:7" ht="15" thickBot="1">
       <c r="A467" s="14"/>
@@ -41567,14 +41488,17 @@
       <c r="C467" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D467" s="21" t="s">
-        <v>777</v>
+      <c r="D467" s="20" t="s">
+        <v>770</v>
       </c>
       <c r="E467" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F467" t="s">
-        <v>529</v>
+        <v>498</v>
+      </c>
+      <c r="G467" s="42" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="468" spans="1:7" ht="15" thickBot="1">
@@ -41583,14 +41507,17 @@
       <c r="C468" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D468" s="21" t="s">
-        <v>778</v>
+      <c r="D468" s="20" t="s">
+        <v>771</v>
       </c>
       <c r="E468" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F468" t="s">
-        <v>530</v>
+        <v>499</v>
+      </c>
+      <c r="G468" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="469" spans="1:7" ht="15" thickBot="1">
@@ -41600,13 +41527,16 @@
         <v>765</v>
       </c>
       <c r="D469" s="21" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E469" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F469" t="s">
-        <v>531</v>
+        <v>524</v>
+      </c>
+      <c r="G469" s="42" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="470" spans="1:7" ht="15" thickBot="1">
@@ -41616,13 +41546,13 @@
         <v>765</v>
       </c>
       <c r="D470" s="21" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="E470" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F470" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="471" spans="1:7" ht="15" thickBot="1">
@@ -41632,17 +41562,15 @@
         <v>765</v>
       </c>
       <c r="D471" s="21" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="E471" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F471" t="s">
-        <v>533</v>
-      </c>
-      <c r="G471" t="s">
-        <v>522</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="G471" s="43"/>
     </row>
     <row r="472" spans="1:7" ht="15" thickBot="1">
       <c r="A472" s="14"/>
@@ -41651,17 +41579,15 @@
         <v>765</v>
       </c>
       <c r="D472" s="21" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="E472" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F472" t="s">
-        <v>534</v>
-      </c>
-      <c r="G472" s="43" t="s">
-        <v>520</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="G472" s="44"/>
     </row>
     <row r="473" spans="1:7" ht="15" thickBot="1">
       <c r="A473" s="14"/>
@@ -41670,14 +41596,15 @@
         <v>765</v>
       </c>
       <c r="D473" s="21" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="E473" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F473" t="s">
-        <v>525</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="G473" s="44"/>
     </row>
     <row r="474" spans="1:7" ht="15" thickBot="1">
       <c r="A474" s="14"/>
@@ -41686,16 +41613,13 @@
         <v>765</v>
       </c>
       <c r="D474" s="21" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="E474" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F474" t="s">
-        <v>535</v>
-      </c>
-      <c r="G474" s="43" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
     </row>
     <row r="475" spans="1:7" ht="15" thickBot="1">
@@ -41705,16 +41629,13 @@
         <v>765</v>
       </c>
       <c r="D475" s="21" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="E475" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F475" t="s">
-        <v>536</v>
-      </c>
-      <c r="G475" s="44" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
     </row>
     <row r="476" spans="1:7" ht="15" thickBot="1">
@@ -41724,16 +41645,13 @@
         <v>765</v>
       </c>
       <c r="D476" s="21" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="E476" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F476" t="s">
-        <v>537</v>
-      </c>
-      <c r="G476" s="44" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="477" spans="1:7" ht="15" thickBot="1">
@@ -41743,13 +41661,13 @@
         <v>765</v>
       </c>
       <c r="D477" s="21" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="E477" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F477" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="478" spans="1:7" ht="15" thickBot="1">
@@ -41759,16 +41677,16 @@
         <v>765</v>
       </c>
       <c r="D478" s="21" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="E478" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F478" t="s">
-        <v>538</v>
-      </c>
-      <c r="G478" s="45" t="s">
-        <v>521</v>
+        <v>533</v>
+      </c>
+      <c r="G478" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="479" spans="1:7" ht="15" thickBot="1">
@@ -41778,16 +41696,16 @@
         <v>765</v>
       </c>
       <c r="D479" s="21" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="E479" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F479" t="s">
-        <v>531</v>
-      </c>
-      <c r="G479" s="44" t="s">
-        <v>511</v>
+        <v>534</v>
+      </c>
+      <c r="G479" s="43" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="480" spans="1:7" ht="15" thickBot="1">
@@ -41797,16 +41715,13 @@
         <v>765</v>
       </c>
       <c r="D480" s="21" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="E480" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F480" t="s">
-        <v>539</v>
-      </c>
-      <c r="G480" s="44" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
     </row>
     <row r="481" spans="1:7" ht="15" thickBot="1">
@@ -41816,16 +41731,16 @@
         <v>765</v>
       </c>
       <c r="D481" s="21" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="E481" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F481" t="s">
-        <v>540</v>
-      </c>
-      <c r="G481" s="41" t="s">
-        <v>523</v>
+        <v>535</v>
+      </c>
+      <c r="G481" s="43" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="482" spans="1:7" ht="15" thickBot="1">
@@ -41834,17 +41749,17 @@
       <c r="C482" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D482" s="50" t="s">
-        <v>782</v>
+      <c r="D482" s="21" t="s">
+        <v>788</v>
       </c>
       <c r="E482" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F482" t="s">
-        <v>545</v>
-      </c>
-      <c r="G482" s="29" t="s">
-        <v>548</v>
+        <v>536</v>
+      </c>
+      <c r="G482" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="483" spans="1:7" ht="15" thickBot="1">
@@ -41853,17 +41768,17 @@
       <c r="C483" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D483" s="50" t="s">
-        <v>783</v>
+      <c r="D483" s="21" t="s">
+        <v>789</v>
       </c>
       <c r="E483" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F483" t="s">
-        <v>546</v>
-      </c>
-      <c r="G483" s="29" t="s">
-        <v>549</v>
+        <v>537</v>
+      </c>
+      <c r="G483" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="484" spans="1:7" ht="15" thickBot="1">
@@ -41872,17 +41787,14 @@
       <c r="C484" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D484" s="50" t="s">
-        <v>784</v>
+      <c r="D484" s="21" t="s">
+        <v>790</v>
       </c>
       <c r="E484" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F484" t="s">
-        <v>547</v>
-      </c>
-      <c r="G484" s="29" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
     </row>
     <row r="485" spans="1:7" ht="15" thickBot="1">
@@ -41891,17 +41803,17 @@
       <c r="C485" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D485" s="50" t="s">
-        <v>795</v>
+      <c r="D485" s="21" t="s">
+        <v>791</v>
       </c>
       <c r="E485" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F485" t="s">
-        <v>551</v>
-      </c>
-      <c r="G485" s="29" t="s">
-        <v>552</v>
+        <v>538</v>
+      </c>
+      <c r="G485" s="45" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="486" spans="1:7" ht="15" thickBot="1">
@@ -41910,17 +41822,17 @@
       <c r="C486" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D486" s="50" t="s">
-        <v>796</v>
+      <c r="D486" s="21" t="s">
+        <v>792</v>
       </c>
       <c r="E486" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F486" t="s">
-        <v>553</v>
-      </c>
-      <c r="G486" s="29" t="s">
-        <v>554</v>
+        <v>531</v>
+      </c>
+      <c r="G486" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="487" spans="1:7" ht="15" thickBot="1">
@@ -41929,17 +41841,17 @@
       <c r="C487" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D487" s="50" t="s">
-        <v>797</v>
+      <c r="D487" s="21" t="s">
+        <v>793</v>
       </c>
       <c r="E487" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F487" t="s">
-        <v>555</v>
-      </c>
-      <c r="G487" t="s">
-        <v>523</v>
+        <v>539</v>
+      </c>
+      <c r="G487" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="488" spans="1:7" ht="15" thickBot="1">
@@ -41948,14 +41860,17 @@
       <c r="C488" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D488" s="51" t="s">
-        <v>798</v>
+      <c r="D488" s="21" t="s">
+        <v>794</v>
       </c>
       <c r="E488" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F488" t="s">
-        <v>563</v>
+        <v>540</v>
+      </c>
+      <c r="G488" s="41" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="489" spans="1:7" ht="15" thickBot="1">
@@ -41964,17 +41879,17 @@
       <c r="C489" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D489" s="51" t="s">
-        <v>799</v>
+      <c r="D489" s="50" t="s">
+        <v>782</v>
       </c>
       <c r="E489" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F489" s="48" t="s">
-        <v>572</v>
-      </c>
-      <c r="G489" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F489" t="s">
+        <v>545</v>
+      </c>
+      <c r="G489" s="29" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="490" spans="1:7" ht="15" thickBot="1">
@@ -41983,17 +41898,17 @@
       <c r="C490" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D490" s="51" t="s">
-        <v>800</v>
+      <c r="D490" s="50" t="s">
+        <v>783</v>
       </c>
       <c r="E490" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F490" t="s">
-        <v>564</v>
-      </c>
-      <c r="G490" t="s">
-        <v>565</v>
+        <v>546</v>
+      </c>
+      <c r="G490" s="29" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="491" spans="1:7" ht="15" thickBot="1">
@@ -42002,17 +41917,17 @@
       <c r="C491" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D491" s="51" t="s">
-        <v>801</v>
+      <c r="D491" s="50" t="s">
+        <v>784</v>
       </c>
       <c r="E491" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F491" t="s">
-        <v>566</v>
-      </c>
-      <c r="G491" t="s">
-        <v>567</v>
+        <v>547</v>
+      </c>
+      <c r="G491" s="29" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="492" spans="1:7" ht="15" thickBot="1">
@@ -42021,14 +41936,17 @@
       <c r="C492" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D492" s="51" t="s">
-        <v>811</v>
+      <c r="D492" s="50" t="s">
+        <v>795</v>
       </c>
       <c r="E492" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F492" t="s">
-        <v>568</v>
+        <v>551</v>
+      </c>
+      <c r="G492" s="29" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="493" spans="1:7" ht="15" thickBot="1">
@@ -42037,17 +41955,17 @@
       <c r="C493" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D493" s="51" t="s">
-        <v>812</v>
+      <c r="D493" s="50" t="s">
+        <v>796</v>
       </c>
       <c r="E493" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F493" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="G493" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F493" t="s">
+        <v>553</v>
+      </c>
+      <c r="G493" s="29" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="494" spans="1:7" ht="15" thickBot="1">
@@ -42056,17 +41974,17 @@
       <c r="C494" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D494" s="51" t="s">
-        <v>813</v>
+      <c r="D494" s="50" t="s">
+        <v>797</v>
       </c>
       <c r="E494" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F494" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="G494" t="s">
-        <v>557</v>
+        <v>523</v>
       </c>
     </row>
     <row r="495" spans="1:7" ht="15" thickBot="1">
@@ -42076,13 +41994,13 @@
         <v>765</v>
       </c>
       <c r="D495" s="51" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="E495" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F495" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="496" spans="1:7" ht="15" thickBot="1">
@@ -42091,14 +42009,17 @@
       <c r="C496" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D496" s="52" t="s">
-        <v>802</v>
+      <c r="D496" s="51" t="s">
+        <v>799</v>
       </c>
       <c r="E496" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F496" t="s">
-        <v>585</v>
+        <v>7</v>
+      </c>
+      <c r="F496" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="G496" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="497" spans="1:7" ht="15" thickBot="1">
@@ -42107,14 +42028,17 @@
       <c r="C497" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D497" s="52" t="s">
-        <v>815</v>
+      <c r="D497" s="51" t="s">
+        <v>800</v>
       </c>
       <c r="E497" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F497" t="s">
-        <v>575</v>
+        <v>564</v>
+      </c>
+      <c r="G497" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="498" spans="1:7" ht="15" thickBot="1">
@@ -42123,14 +42047,17 @@
       <c r="C498" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D498" s="20" t="s">
-        <v>803</v>
+      <c r="D498" s="51" t="s">
+        <v>801</v>
       </c>
       <c r="E498" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F498" t="s">
-        <v>580</v>
+        <v>566</v>
+      </c>
+      <c r="G498" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="499" spans="1:7" ht="15" thickBot="1">
@@ -42139,17 +42066,14 @@
       <c r="C499" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D499" s="20" t="s">
-        <v>804</v>
+      <c r="D499" s="51" t="s">
+        <v>811</v>
       </c>
       <c r="E499" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F499" s="68" t="s">
-        <v>602</v>
-      </c>
-      <c r="G499" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F499" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="500" spans="1:7" ht="15" thickBot="1">
@@ -42158,14 +42082,17 @@
       <c r="C500" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D500" s="20" t="s">
-        <v>805</v>
-      </c>
-      <c r="E500" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F500" t="s">
-        <v>581</v>
+      <c r="D500" s="51" t="s">
+        <v>812</v>
+      </c>
+      <c r="E500" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F500" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="G500" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="501" spans="1:7" ht="15" thickBot="1">
@@ -42174,14 +42101,17 @@
       <c r="C501" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D501" s="20" t="s">
-        <v>816</v>
+      <c r="D501" s="51" t="s">
+        <v>813</v>
       </c>
       <c r="E501" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F501" t="s">
-        <v>582</v>
+        <v>569</v>
+      </c>
+      <c r="G501" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="502" spans="1:7" ht="15" thickBot="1">
@@ -42190,129 +42120,132 @@
       <c r="C502" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D502" s="20" t="s">
-        <v>817</v>
+      <c r="D502" s="51" t="s">
+        <v>814</v>
       </c>
       <c r="E502" s="17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F502" t="s">
-        <v>583</v>
-      </c>
-      <c r="G502" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="503" spans="1:7">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" ht="15" thickBot="1">
       <c r="A503" s="14"/>
       <c r="B503" s="14"/>
       <c r="C503" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D503" s="20" t="s">
-        <v>818</v>
-      </c>
-      <c r="E503" s="19" t="s">
-        <v>12</v>
+      <c r="D503" s="52" t="s">
+        <v>802</v>
+      </c>
+      <c r="E503" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F503" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="504" spans="1:7">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" ht="15" thickBot="1">
       <c r="A504" s="14"/>
       <c r="B504" s="14"/>
       <c r="C504" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D504" s="53" t="s">
-        <v>806</v>
-      </c>
-      <c r="E504" s="19" t="s">
+      <c r="D504" s="52" t="s">
+        <v>815</v>
+      </c>
+      <c r="E504" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F504" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="505" spans="1:7">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" ht="15" thickBot="1">
       <c r="A505" s="14"/>
       <c r="B505" s="14"/>
       <c r="C505" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D505" s="53" t="s">
-        <v>807</v>
-      </c>
-      <c r="E505" s="19" t="s">
-        <v>7</v>
+      <c r="D505" s="20" t="s">
+        <v>803</v>
+      </c>
+      <c r="E505" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F505" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="506" spans="1:7">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" ht="15" thickBot="1">
       <c r="A506" s="14"/>
       <c r="B506" s="14"/>
       <c r="C506" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D506" s="53" t="s">
-        <v>808</v>
-      </c>
-      <c r="E506" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F506" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="507" spans="1:7">
+      <c r="D506" s="20" t="s">
+        <v>804</v>
+      </c>
+      <c r="E506" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F506" s="68" t="s">
+        <v>602</v>
+      </c>
+      <c r="G506" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" ht="15" thickBot="1">
       <c r="A507" s="14"/>
       <c r="B507" s="14"/>
       <c r="C507" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D507" s="53" t="s">
-        <v>819</v>
+      <c r="D507" s="20" t="s">
+        <v>805</v>
       </c>
       <c r="E507" s="19" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F507" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="508" spans="1:7">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" ht="15" thickBot="1">
       <c r="A508" s="14"/>
       <c r="B508" s="14"/>
       <c r="C508" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D508" s="53" t="s">
-        <v>820</v>
-      </c>
-      <c r="E508" s="19" t="s">
-        <v>7</v>
+      <c r="D508" s="20" t="s">
+        <v>816</v>
+      </c>
+      <c r="E508" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F508" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="509" spans="1:7">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" ht="15" thickBot="1">
       <c r="A509" s="14"/>
       <c r="B509" s="14"/>
       <c r="C509" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D509" s="53" t="s">
-        <v>821</v>
-      </c>
-      <c r="E509" s="19" t="s">
-        <v>12</v>
+      <c r="D509" s="20" t="s">
+        <v>817</v>
+      </c>
+      <c r="E509" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="F509" t="s">
-        <v>591</v>
+        <v>583</v>
+      </c>
+      <c r="G509" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -42321,12 +42254,14 @@
       <c r="C510" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D510" s="36" t="s">
-        <v>809</v>
-      </c>
-      <c r="E510" s="19"/>
+      <c r="D510" s="20" t="s">
+        <v>818</v>
+      </c>
+      <c r="E510" s="19" t="s">
+        <v>12</v>
+      </c>
       <c r="F510" t="s">
-        <v>613</v>
+        <v>584</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -42335,12 +42270,14 @@
       <c r="C511" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D511" s="36" t="s">
-        <v>822</v>
-      </c>
-      <c r="E511" s="19"/>
+      <c r="D511" s="53" t="s">
+        <v>806</v>
+      </c>
+      <c r="E511" s="19" t="s">
+        <v>4</v>
+      </c>
       <c r="F511" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -42349,12 +42286,14 @@
       <c r="C512" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D512" s="36" t="s">
-        <v>810</v>
-      </c>
-      <c r="E512" s="19"/>
+      <c r="D512" s="53" t="s">
+        <v>807</v>
+      </c>
+      <c r="E512" s="19" t="s">
+        <v>7</v>
+      </c>
       <c r="F512" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -42363,12 +42302,14 @@
       <c r="C513" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D513" s="36" t="s">
-        <v>823</v>
-      </c>
-      <c r="E513" s="19"/>
+      <c r="D513" s="53" t="s">
+        <v>808</v>
+      </c>
+      <c r="E513" s="19" t="s">
+        <v>12</v>
+      </c>
       <c r="F513" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -42377,17 +42318,14 @@
       <c r="C514" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D514" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="E514" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F514" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G514" s="3" t="s">
-        <v>149</v>
+      <c r="D514" s="53" t="s">
+        <v>819</v>
+      </c>
+      <c r="E514" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F514" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -42396,17 +42334,14 @@
       <c r="C515" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D515" s="18" t="s">
-        <v>825</v>
-      </c>
-      <c r="E515" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F515" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G515" s="3" t="s">
-        <v>151</v>
+      <c r="D515" s="53" t="s">
+        <v>820</v>
+      </c>
+      <c r="E515" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F515" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -42415,17 +42350,14 @@
       <c r="C516" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D516" s="18" t="s">
-        <v>826</v>
-      </c>
-      <c r="E516" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F516" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G516" s="3" t="s">
-        <v>153</v>
+      <c r="D516" s="53" t="s">
+        <v>821</v>
+      </c>
+      <c r="E516" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F516" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -42434,17 +42366,12 @@
       <c r="C517" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D517" s="18" t="s">
-        <v>827</v>
-      </c>
-      <c r="E517" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F517" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G517" s="3" t="s">
-        <v>149</v>
+      <c r="D517" s="36" t="s">
+        <v>809</v>
+      </c>
+      <c r="E517" s="19"/>
+      <c r="F517" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -42453,17 +42380,12 @@
       <c r="C518" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D518" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="E518" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F518" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G518" s="3" t="s">
-        <v>149</v>
+      <c r="D518" s="36" t="s">
+        <v>822</v>
+      </c>
+      <c r="E518" s="19"/>
+      <c r="F518" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -42472,17 +42394,12 @@
       <c r="C519" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D519" s="18" t="s">
-        <v>829</v>
-      </c>
-      <c r="E519" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F519" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G519" s="3" t="s">
-        <v>151</v>
+      <c r="D519" s="36" t="s">
+        <v>810</v>
+      </c>
+      <c r="E519" s="19"/>
+      <c r="F519" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -42491,17 +42408,12 @@
       <c r="C520" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D520" s="18" t="s">
-        <v>830</v>
-      </c>
-      <c r="E520" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F520" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G520" s="3" t="s">
-        <v>153</v>
+      <c r="D520" s="36" t="s">
+        <v>823</v>
+      </c>
+      <c r="E520" s="19"/>
+      <c r="F520" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -42510,1110 +42422,1162 @@
       <c r="C521" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D521" s="18" t="s">
-        <v>831</v>
+      <c r="D521" s="1" t="s">
+        <v>824</v>
       </c>
       <c r="E521" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F521" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G521" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="15.5">
-      <c r="A522" s="1"/>
-      <c r="B522" s="1"/>
-      <c r="C522" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="D522" s="56" t="s">
-        <v>649</v>
+    <row r="522" spans="1:7">
+      <c r="A522" s="14"/>
+      <c r="B522" s="14"/>
+      <c r="C522" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D522" s="18" t="s">
+        <v>825</v>
       </c>
       <c r="E522" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F522" s="4"/>
-      <c r="G522" s="5"/>
+      <c r="F522" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G522" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="523" spans="1:7">
-      <c r="C523" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="D523" s="15" t="s">
-        <v>838</v>
+      <c r="A523" s="14"/>
+      <c r="B523" s="14"/>
+      <c r="C523" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D523" s="18" t="s">
+        <v>826</v>
       </c>
       <c r="E523" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F523" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G523" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" s="14"/>
       <c r="B524" s="14"/>
-      <c r="C524" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="D524" s="15" t="s">
-        <v>839</v>
+      <c r="C524" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D524" s="18" t="s">
+        <v>827</v>
       </c>
       <c r="E524" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F524" s="14"/>
-      <c r="G524" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="F524" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G524" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="525" spans="1:7">
       <c r="A525" s="14"/>
       <c r="B525" s="14"/>
-      <c r="C525" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="D525" s="15" t="s">
-        <v>650</v>
+      <c r="C525" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>828</v>
       </c>
       <c r="E525" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F525" s="14"/>
-      <c r="G525" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="F525" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G525" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" s="14"/>
       <c r="B526" s="14"/>
       <c r="C526" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D526" s="36" t="s">
-        <v>624</v>
-      </c>
-      <c r="E526" s="3"/>
-      <c r="F526" s="14"/>
-      <c r="G526" s="14"/>
+        <v>765</v>
+      </c>
+      <c r="D526" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="E526" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F526" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G526" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="527" spans="1:7">
       <c r="A527" s="14"/>
       <c r="B527" s="14"/>
       <c r="C527" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D527" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="E527" s="3"/>
-      <c r="F527" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G527" s="14"/>
+        <v>765</v>
+      </c>
+      <c r="D527" s="18" t="s">
+        <v>830</v>
+      </c>
+      <c r="E527" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F527" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G527" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" s="14"/>
       <c r="B528" s="14"/>
       <c r="C528" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D528" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="E528" s="3"/>
-      <c r="F528" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G528" s="14"/>
-    </row>
-    <row r="529" spans="1:7">
-      <c r="A529" s="14"/>
-      <c r="B529" s="14"/>
-      <c r="C529" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D529" s="36" t="s">
-        <v>651</v>
-      </c>
-      <c r="E529" s="3"/>
-      <c r="F529" s="13" t="s">
-        <v>655</v>
-      </c>
-      <c r="G529" s="14"/>
+        <v>765</v>
+      </c>
+      <c r="D528" s="18" t="s">
+        <v>831</v>
+      </c>
+      <c r="E528" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F528" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G528" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" ht="15.5">
+      <c r="A529" s="1"/>
+      <c r="B529" s="1"/>
+      <c r="C529" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D529" s="56" t="s">
+        <v>649</v>
+      </c>
+      <c r="E529" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F529" s="4"/>
+      <c r="G529" s="5"/>
     </row>
     <row r="530" spans="1:7">
-      <c r="A530" s="14"/>
-      <c r="B530" s="14"/>
-      <c r="C530" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D530" s="36" t="s">
-        <v>652</v>
-      </c>
-      <c r="E530" s="3"/>
-      <c r="F530" s="13" t="s">
-        <v>656</v>
-      </c>
-      <c r="G530" s="14"/>
+      <c r="C530" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D530" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="E530" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" s="14"/>
       <c r="B531" s="14"/>
-      <c r="C531" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D531" s="36" t="s">
-        <v>653</v>
-      </c>
-      <c r="E531" s="3"/>
-      <c r="F531" s="13" t="s">
-        <v>657</v>
-      </c>
+      <c r="C531" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D531" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="E531" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F531" s="14"/>
       <c r="G531" s="14"/>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" s="14"/>
       <c r="B532" s="14"/>
-      <c r="C532" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D532" s="36" t="s">
-        <v>654</v>
-      </c>
-      <c r="E532" s="3"/>
-      <c r="F532" s="13" t="s">
-        <v>658</v>
-      </c>
+      <c r="C532" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D532" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="E532" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F532" s="14"/>
       <c r="G532" s="14"/>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" s="14"/>
       <c r="B533" s="14"/>
-      <c r="C533" s="14"/>
-      <c r="D533" s="36"/>
+      <c r="C533" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D533" s="36" t="s">
+        <v>624</v>
+      </c>
       <c r="E533" s="3"/>
-      <c r="F533" s="13"/>
+      <c r="F533" s="14"/>
       <c r="G533" s="14"/>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" s="14"/>
       <c r="B534" s="14"/>
-      <c r="C534" s="14"/>
-      <c r="D534" s="36"/>
+      <c r="C534" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D534" s="36" t="s">
+        <v>276</v>
+      </c>
       <c r="E534" s="3"/>
-      <c r="F534" s="13"/>
+      <c r="F534" s="13" t="s">
+        <v>247</v>
+      </c>
       <c r="G534" s="14"/>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" s="14"/>
       <c r="B535" s="14"/>
-      <c r="C535" s="14"/>
-      <c r="D535" s="36"/>
+      <c r="C535" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D535" s="36" t="s">
+        <v>277</v>
+      </c>
       <c r="E535" s="3"/>
-      <c r="F535" s="13"/>
+      <c r="F535" s="13" t="s">
+        <v>246</v>
+      </c>
       <c r="G535" s="14"/>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
-      <c r="C536" s="14"/>
-      <c r="D536" s="36"/>
+      <c r="C536" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D536" s="36" t="s">
+        <v>651</v>
+      </c>
       <c r="E536" s="3"/>
-      <c r="F536" s="13"/>
+      <c r="F536" s="13" t="s">
+        <v>655</v>
+      </c>
       <c r="G536" s="14"/>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" s="14"/>
       <c r="B537" s="14"/>
-      <c r="C537" s="14"/>
-      <c r="D537" s="36"/>
+      <c r="C537" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D537" s="36" t="s">
+        <v>652</v>
+      </c>
       <c r="E537" s="3"/>
-      <c r="F537" s="13"/>
+      <c r="F537" s="13" t="s">
+        <v>656</v>
+      </c>
       <c r="G537" s="14"/>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" s="14"/>
       <c r="B538" s="14"/>
-      <c r="C538" s="14"/>
-      <c r="D538" s="36"/>
+      <c r="C538" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D538" s="36" t="s">
+        <v>653</v>
+      </c>
       <c r="E538" s="3"/>
-      <c r="F538" s="13"/>
+      <c r="F538" s="13" t="s">
+        <v>657</v>
+      </c>
       <c r="G538" s="14"/>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" s="14"/>
       <c r="B539" s="14"/>
-      <c r="C539" s="14"/>
-      <c r="D539" s="36"/>
+      <c r="C539" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D539" s="36" t="s">
+        <v>654</v>
+      </c>
       <c r="E539" s="3"/>
-      <c r="F539" s="13"/>
+      <c r="F539" s="13" t="s">
+        <v>658</v>
+      </c>
       <c r="G539" s="14"/>
     </row>
-    <row r="540" spans="1:7" ht="15.5">
-      <c r="A540" s="1"/>
-      <c r="B540" s="1"/>
-      <c r="C540" s="1"/>
-      <c r="D540" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E540" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F540" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G540" s="5"/>
-    </row>
-    <row r="541" spans="1:7" ht="15.5">
-      <c r="A541" s="1"/>
-      <c r="B541" s="1"/>
-      <c r="C541" s="1"/>
-      <c r="D541" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E541" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F541" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G541" s="5"/>
+    <row r="540" spans="1:7">
+      <c r="A540" s="14"/>
+      <c r="B540" s="14"/>
+      <c r="C540" s="14"/>
+      <c r="D540" s="36"/>
+      <c r="E540" s="3"/>
+      <c r="F540" s="13"/>
+      <c r="G540" s="14"/>
+    </row>
+    <row r="541" spans="1:7">
+      <c r="A541" s="14"/>
+      <c r="B541" s="14"/>
+      <c r="C541" s="14"/>
+      <c r="D541" s="36"/>
+      <c r="E541" s="3"/>
+      <c r="F541" s="13"/>
+      <c r="G541" s="14"/>
     </row>
     <row r="542" spans="1:7">
       <c r="A542" s="14"/>
       <c r="B542" s="14"/>
       <c r="C542" s="14"/>
-      <c r="D542" s="15"/>
+      <c r="D542" s="36"/>
       <c r="E542" s="3"/>
-      <c r="F542" s="14"/>
+      <c r="F542" s="13"/>
       <c r="G542" s="14"/>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" s="14"/>
       <c r="B543" s="14"/>
       <c r="C543" s="14"/>
-      <c r="D543" s="15"/>
+      <c r="D543" s="36"/>
       <c r="E543" s="3"/>
-      <c r="F543" s="14"/>
+      <c r="F543" s="13"/>
       <c r="G543" s="14"/>
     </row>
     <row r="544" spans="1:7">
-      <c r="A544" s="1"/>
-      <c r="B544" s="1"/>
-      <c r="C544" s="1"/>
-      <c r="D544" s="1"/>
+      <c r="A544" s="14"/>
+      <c r="B544" s="14"/>
+      <c r="C544" s="14"/>
+      <c r="D544" s="36"/>
       <c r="E544" s="3"/>
-      <c r="F544" s="4"/>
-      <c r="G544" s="3"/>
-    </row>
-    <row r="545" spans="1:7" ht="15.5">
-      <c r="A545" s="1"/>
-      <c r="B545" s="1"/>
-      <c r="C545" s="1"/>
-      <c r="D545" s="13"/>
+      <c r="F544" s="13"/>
+      <c r="G544" s="14"/>
+    </row>
+    <row r="545" spans="1:7">
+      <c r="A545" s="14"/>
+      <c r="B545" s="14"/>
+      <c r="C545" s="14"/>
+      <c r="D545" s="36"/>
       <c r="E545" s="3"/>
-      <c r="F545" s="4"/>
-      <c r="G545" s="5"/>
-    </row>
-    <row r="546" spans="1:7" ht="15.5">
-      <c r="A546" s="1"/>
-      <c r="B546" s="1"/>
-      <c r="C546" s="1"/>
-      <c r="D546" s="13"/>
+      <c r="F545" s="13"/>
+      <c r="G545" s="14"/>
+    </row>
+    <row r="546" spans="1:7">
+      <c r="A546" s="14"/>
+      <c r="B546" s="14"/>
+      <c r="C546" s="14"/>
+      <c r="D546" s="36"/>
       <c r="E546" s="3"/>
-      <c r="F546" s="4"/>
-      <c r="G546" s="5"/>
+      <c r="F546" s="13"/>
+      <c r="G546" s="14"/>
     </row>
     <row r="547" spans="1:7" ht="15.5">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
-      <c r="D547" s="13"/>
-      <c r="E547" s="3"/>
-      <c r="F547" s="4"/>
+      <c r="D547" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E547" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F547" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="G547" s="5"/>
     </row>
-    <row r="548" spans="1:7">
+    <row r="548" spans="1:7" ht="15.5">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
-      <c r="C548" s="6"/>
-      <c r="D548" s="11" t="s">
-        <v>19</v>
+      <c r="C548" s="1"/>
+      <c r="D548" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="E548" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F548" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G548" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G548" s="5"/>
     </row>
     <row r="549" spans="1:7">
-      <c r="A549" s="1"/>
-      <c r="B549" s="1"/>
-      <c r="C549" s="6"/>
-      <c r="D549" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E549" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F549" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G549" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A549" s="14"/>
+      <c r="B549" s="14"/>
+      <c r="C549" s="14"/>
+      <c r="D549" s="15"/>
+      <c r="E549" s="3"/>
+      <c r="F549" s="14"/>
+      <c r="G549" s="14"/>
     </row>
     <row r="550" spans="1:7">
-      <c r="A550" s="1"/>
-      <c r="B550" s="1"/>
-      <c r="C550" s="6"/>
-      <c r="D550" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E550" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F550" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G550" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A550" s="14"/>
+      <c r="B550" s="14"/>
+      <c r="C550" s="14"/>
+      <c r="D550" s="15"/>
+      <c r="E550" s="3"/>
+      <c r="F550" s="14"/>
+      <c r="G550" s="14"/>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
-      <c r="C551" s="6"/>
-      <c r="D551" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E551" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F551" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G551" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="552" spans="1:7" ht="26">
+      <c r="C551" s="1"/>
+      <c r="D551" s="1"/>
+      <c r="E551" s="3"/>
+      <c r="F551" s="4"/>
+      <c r="G551" s="3"/>
+    </row>
+    <row r="552" spans="1:7" ht="15.5">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
-      <c r="D552" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E552" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F552" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G552" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="553" spans="1:7" ht="26">
+      <c r="D552" s="13"/>
+      <c r="E552" s="3"/>
+      <c r="F552" s="4"/>
+      <c r="G552" s="5"/>
+    </row>
+    <row r="553" spans="1:7" ht="15.5">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
-      <c r="C553" s="7"/>
-      <c r="D553" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E553" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F553" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G553" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="554" spans="1:7">
-      <c r="A554" s="12"/>
-      <c r="B554" s="12"/>
-      <c r="C554" s="12"/>
-      <c r="D554" s="156" t="s">
-        <v>35</v>
-      </c>
-      <c r="E554" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F554" s="158" t="s">
-        <v>36</v>
-      </c>
-      <c r="G554" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="C553" s="1"/>
+      <c r="D553" s="13"/>
+      <c r="E553" s="3"/>
+      <c r="F553" s="4"/>
+      <c r="G553" s="5"/>
+    </row>
+    <row r="554" spans="1:7" ht="15.5">
+      <c r="A554" s="1"/>
+      <c r="B554" s="1"/>
+      <c r="C554" s="1"/>
+      <c r="D554" s="13"/>
+      <c r="E554" s="3"/>
+      <c r="F554" s="4"/>
+      <c r="G554" s="5"/>
     </row>
     <row r="555" spans="1:7">
-      <c r="A555" s="12"/>
-      <c r="B555" s="12"/>
-      <c r="C555" s="12"/>
-      <c r="D555" s="156"/>
-      <c r="E555" s="157"/>
-      <c r="F555" s="158"/>
+      <c r="A555" s="1"/>
+      <c r="B555" s="1"/>
+      <c r="C555" s="6"/>
+      <c r="D555" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E555" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F555" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G555" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7">
+      <c r="A556" s="1"/>
+      <c r="B556" s="1"/>
+      <c r="C556" s="6"/>
+      <c r="D556" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E556" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F556" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G556" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
-      <c r="C557" s="1"/>
-      <c r="D557" s="1" t="s">
-        <v>40</v>
+      <c r="C557" s="6"/>
+      <c r="D557" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E557" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F557" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G557" s="3">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="G557" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
-      <c r="C558" s="1"/>
-      <c r="D558" s="159" t="s">
-        <v>42</v>
-      </c>
-      <c r="E558" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F558" s="158" t="s">
-        <v>43</v>
-      </c>
-      <c r="G558" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="559" spans="1:7">
+      <c r="C558" s="6"/>
+      <c r="D558" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E558" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F558" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G558" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" ht="26">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
-      <c r="D559" s="159"/>
-      <c r="E559" s="157"/>
-      <c r="F559" s="158"/>
-      <c r="G559" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="560" spans="1:7">
-      <c r="A560" s="12"/>
-      <c r="B560" s="12"/>
-      <c r="C560" s="12"/>
-      <c r="D560" s="156" t="s">
-        <v>45</v>
-      </c>
-      <c r="E560" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F560" s="158" t="s">
-        <v>46</v>
-      </c>
-      <c r="G560" s="3" t="s">
-        <v>47</v>
+      <c r="D559" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E559" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F559" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G559" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" ht="26">
+      <c r="A560" s="1"/>
+      <c r="B560" s="1"/>
+      <c r="C560" s="7"/>
+      <c r="D560" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E560" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F560" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G560" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="561" spans="1:7">
       <c r="A561" s="12"/>
       <c r="B561" s="12"/>
       <c r="C561" s="12"/>
-      <c r="D561" s="156"/>
-      <c r="E561" s="157"/>
-      <c r="F561" s="158"/>
+      <c r="D561" s="157" t="s">
+        <v>35</v>
+      </c>
+      <c r="E561" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F561" s="159" t="s">
+        <v>36</v>
+      </c>
       <c r="G561" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="563" spans="1:7">
-      <c r="A563" s="1"/>
-      <c r="B563" s="1"/>
-      <c r="C563" s="1"/>
-      <c r="D563" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E563" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F563" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G563" s="3">
-        <v>80</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7">
+      <c r="A562" s="12"/>
+      <c r="B562" s="12"/>
+      <c r="C562" s="12"/>
+      <c r="D562" s="157"/>
+      <c r="E562" s="158"/>
+      <c r="F562" s="159"/>
+      <c r="G562" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="159" t="s">
-        <v>52</v>
-      </c>
-      <c r="E564" s="157" t="s">
-        <v>2</v>
-      </c>
-      <c r="F564" s="158" t="s">
-        <v>53</v>
+      <c r="D564" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E564" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="G564" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="159"/>
-      <c r="E565" s="157"/>
-      <c r="F565" s="158"/>
-      <c r="G565" s="3" t="s">
-        <v>44</v>
+      <c r="D565" s="160" t="s">
+        <v>42</v>
+      </c>
+      <c r="E565" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F565" s="159" t="s">
+        <v>43</v>
+      </c>
+      <c r="G565" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="156" t="s">
-        <v>54</v>
-      </c>
-      <c r="E566" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F566" s="158" t="s">
-        <v>55</v>
-      </c>
+      <c r="D566" s="160"/>
+      <c r="E566" s="158"/>
+      <c r="F566" s="159"/>
       <c r="G566" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="567" spans="1:7">
-      <c r="A567" s="1"/>
-      <c r="B567" s="1"/>
-      <c r="C567" s="1"/>
-      <c r="D567" s="156"/>
-      <c r="E567" s="157"/>
-      <c r="F567" s="158"/>
+      <c r="A567" s="12"/>
+      <c r="B567" s="12"/>
+      <c r="C567" s="12"/>
+      <c r="D567" s="157" t="s">
+        <v>45</v>
+      </c>
+      <c r="E567" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F567" s="159" t="s">
+        <v>46</v>
+      </c>
       <c r="G567" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="568" spans="1:7">
-      <c r="A568" s="1"/>
-      <c r="B568" s="1"/>
-      <c r="C568" s="1"/>
-      <c r="D568" s="156" t="s">
-        <v>58</v>
-      </c>
-      <c r="E568" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F568" s="158" t="s">
-        <v>59</v>
-      </c>
+      <c r="A568" s="12"/>
+      <c r="B568" s="12"/>
+      <c r="C568" s="12"/>
+      <c r="D568" s="157"/>
+      <c r="E568" s="158"/>
+      <c r="F568" s="159"/>
       <c r="G568" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="569" spans="1:7">
-      <c r="A569" s="1"/>
-      <c r="B569" s="1"/>
-      <c r="C569" s="1"/>
-      <c r="D569" s="156"/>
-      <c r="E569" s="157"/>
-      <c r="F569" s="158"/>
-      <c r="G569" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="156" t="s">
-        <v>62</v>
-      </c>
-      <c r="E570" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F570" s="158" t="s">
-        <v>63</v>
-      </c>
-      <c r="G570" s="3" t="s">
-        <v>64</v>
+      <c r="D570" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E570" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G570" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="571" spans="1:7">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
-      <c r="D571" s="156"/>
-      <c r="E571" s="157"/>
-      <c r="F571" s="158"/>
-      <c r="G571" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="572" spans="1:7" ht="63.5">
+      <c r="D571" s="160" t="s">
+        <v>52</v>
+      </c>
+      <c r="E571" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F571" s="159" t="s">
+        <v>53</v>
+      </c>
+      <c r="G571" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
-      <c r="D572" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E572" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F572" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G572" s="5"/>
-    </row>
-    <row r="573" spans="1:7" ht="26">
+      <c r="D572" s="160"/>
+      <c r="E572" s="158"/>
+      <c r="F572" s="159"/>
+      <c r="G572" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
-      <c r="D573" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E573" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F573" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G573" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="574" spans="1:7" ht="26">
+      <c r="D573" s="157" t="s">
+        <v>54</v>
+      </c>
+      <c r="E573" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F573" s="159" t="s">
+        <v>55</v>
+      </c>
+      <c r="G573" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
-      <c r="D574" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E574" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F574" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G574" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="575" spans="1:7" ht="38.5">
+      <c r="D574" s="157"/>
+      <c r="E574" s="158"/>
+      <c r="F574" s="159"/>
+      <c r="G574" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E575" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F575" s="4" t="s">
-        <v>84</v>
+      <c r="D575" s="157" t="s">
+        <v>58</v>
+      </c>
+      <c r="E575" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F575" s="159" t="s">
+        <v>59</v>
       </c>
       <c r="G575" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="159" t="s">
-        <v>86</v>
-      </c>
-      <c r="E576" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F576" s="158" t="s">
-        <v>87</v>
-      </c>
+      <c r="D576" s="157"/>
+      <c r="E576" s="158"/>
+      <c r="F576" s="159"/>
       <c r="G576" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="159"/>
-      <c r="E577" s="157"/>
-      <c r="F577" s="158"/>
+      <c r="D577" s="157" t="s">
+        <v>62</v>
+      </c>
+      <c r="E577" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F577" s="159" t="s">
+        <v>63</v>
+      </c>
       <c r="G577" s="3" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="159"/>
-      <c r="E578" s="157"/>
-      <c r="F578" s="158"/>
+      <c r="D578" s="157"/>
+      <c r="E578" s="158"/>
+      <c r="F578" s="159"/>
       <c r="G578" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="579" spans="1:7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" ht="63.5">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="159" t="s">
-        <v>91</v>
-      </c>
-      <c r="E579" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F579" s="158" t="s">
-        <v>92</v>
-      </c>
-      <c r="G579" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="580" spans="1:7">
+      <c r="D579" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E579" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G579" s="5"/>
+    </row>
+    <row r="580" spans="1:7" ht="26">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="159"/>
-      <c r="E580" s="157"/>
-      <c r="F580" s="158"/>
-      <c r="G580" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="581" spans="1:7">
+      <c r="D580" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E580" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G580" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" ht="26">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
-      <c r="D581" s="159"/>
-      <c r="E581" s="157"/>
-      <c r="F581" s="158"/>
-      <c r="G581" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="582" spans="1:7" ht="15.5">
+      <c r="D581" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E581" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G581" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" ht="38.5">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
       <c r="D582" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E582" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F582" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G582" s="5"/>
-    </row>
-    <row r="583" spans="1:7" ht="15.5">
+        <v>84</v>
+      </c>
+      <c r="G582" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
-      <c r="D583" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E583" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F583" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G583" s="5"/>
-    </row>
-    <row r="584" spans="1:7" ht="15.5">
+      <c r="D583" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="E583" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F583" s="159" t="s">
+        <v>87</v>
+      </c>
+      <c r="G583" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
-      <c r="D584" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E584" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F584" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G584" s="5"/>
-    </row>
-    <row r="585" spans="1:7" ht="15.5">
+      <c r="D584" s="160"/>
+      <c r="E584" s="158"/>
+      <c r="F584" s="159"/>
+      <c r="G584" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
-      <c r="D585" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E585" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F585" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G585" s="5"/>
-    </row>
-    <row r="586" spans="1:7" ht="15.5">
+      <c r="D585" s="160"/>
+      <c r="E585" s="158"/>
+      <c r="F585" s="159"/>
+      <c r="G585" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
-      <c r="D586" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E586" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F586" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G586" s="5"/>
-    </row>
-    <row r="587" spans="1:7" ht="15.5">
+      <c r="D586" s="160" t="s">
+        <v>91</v>
+      </c>
+      <c r="E586" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="F586" s="159" t="s">
+        <v>92</v>
+      </c>
+      <c r="G586" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
-      <c r="D587" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E587" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F587" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G587" s="5"/>
-    </row>
-    <row r="588" spans="1:7" ht="15.5">
+      <c r="D587" s="160"/>
+      <c r="E587" s="158"/>
+      <c r="F587" s="159"/>
+      <c r="G587" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
-      <c r="D588" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E588" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F588" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G588" s="5"/>
+      <c r="D588" s="160"/>
+      <c r="E588" s="158"/>
+      <c r="F588" s="159"/>
+      <c r="G588" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="589" spans="1:7" ht="15.5">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
       <c r="D589" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E589" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F589" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G589" s="5"/>
     </row>
-    <row r="591" spans="1:7">
+    <row r="590" spans="1:7" ht="15.5">
+      <c r="A590" s="1"/>
+      <c r="B590" s="1"/>
+      <c r="C590" s="1"/>
+      <c r="D590" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E590" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F590" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G590" s="5"/>
+    </row>
+    <row r="591" spans="1:7" ht="15.5">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
-      <c r="D591" s="1"/>
-      <c r="E591" s="3"/>
-      <c r="F591" s="4"/>
-      <c r="G591" s="3"/>
-    </row>
-    <row r="592" spans="1:7">
+      <c r="D591" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E591" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F591" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G591" s="5"/>
+    </row>
+    <row r="592" spans="1:7" ht="15.5">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
-      <c r="D592" s="1"/>
-      <c r="E592" s="3"/>
-      <c r="F592" s="4"/>
-      <c r="G592" s="3"/>
-    </row>
-    <row r="593" spans="1:7">
+      <c r="D592" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E592" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F592" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G592" s="5"/>
+    </row>
+    <row r="593" spans="1:7" ht="15.5">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
-      <c r="D593" s="1"/>
-      <c r="E593" s="3"/>
-      <c r="F593" s="4"/>
-      <c r="G593" s="3"/>
-    </row>
-    <row r="594" spans="1:7">
+      <c r="D593" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E593" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F593" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G593" s="5"/>
+    </row>
+    <row r="594" spans="1:7" ht="15.5">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
-      <c r="D594" s="1"/>
-      <c r="E594" s="3"/>
-      <c r="F594" s="4"/>
-      <c r="G594" s="3"/>
-    </row>
-    <row r="597" spans="1:7" ht="15.5">
-      <c r="A597" s="1"/>
-      <c r="B597" s="1"/>
-      <c r="C597" s="1"/>
-      <c r="D597" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E597" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F597" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G597" s="5"/>
-    </row>
-    <row r="598" spans="1:7" ht="15.5">
+      <c r="D594" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E594" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F594" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G594" s="5"/>
+    </row>
+    <row r="595" spans="1:7" ht="15.5">
+      <c r="A595" s="1"/>
+      <c r="B595" s="1"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E595" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F595" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G595" s="5"/>
+    </row>
+    <row r="596" spans="1:7" ht="15.5">
+      <c r="A596" s="1"/>
+      <c r="B596" s="1"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E596" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F596" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G596" s="5"/>
+    </row>
+    <row r="598" spans="1:7">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
-      <c r="D598" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E598" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F598" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G598" s="5"/>
-    </row>
-    <row r="599" spans="1:7" ht="15.5">
+      <c r="D598" s="1"/>
+      <c r="E598" s="3"/>
+      <c r="F598" s="4"/>
+      <c r="G598" s="3"/>
+    </row>
+    <row r="599" spans="1:7">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
-      <c r="D599" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E599" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F599" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G599" s="5"/>
-    </row>
-    <row r="602" spans="1:7" ht="15.5">
-      <c r="A602" s="1"/>
-      <c r="B602" s="1"/>
-      <c r="C602" s="1"/>
-      <c r="D602" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E602" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F602" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G602" s="5"/>
-    </row>
-    <row r="603" spans="1:7" ht="15.5">
-      <c r="A603" s="1"/>
-      <c r="B603" s="1"/>
-      <c r="C603" s="1"/>
-      <c r="D603" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E603" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F603" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G603" s="5"/>
+      <c r="D599" s="1"/>
+      <c r="E599" s="3"/>
+      <c r="F599" s="4"/>
+      <c r="G599" s="3"/>
+    </row>
+    <row r="600" spans="1:7">
+      <c r="A600" s="1"/>
+      <c r="B600" s="1"/>
+      <c r="C600" s="1"/>
+      <c r="D600" s="1"/>
+      <c r="E600" s="3"/>
+      <c r="F600" s="4"/>
+      <c r="G600" s="3"/>
+    </row>
+    <row r="601" spans="1:7">
+      <c r="A601" s="1"/>
+      <c r="B601" s="1"/>
+      <c r="C601" s="1"/>
+      <c r="D601" s="1"/>
+      <c r="E601" s="3"/>
+      <c r="F601" s="4"/>
+      <c r="G601" s="3"/>
     </row>
     <row r="604" spans="1:7" ht="15.5">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
       <c r="D604" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E604" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F604" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G604" s="5"/>
     </row>
-    <row r="606" spans="1:7">
+    <row r="605" spans="1:7" ht="15.5">
+      <c r="A605" s="1"/>
+      <c r="B605" s="1"/>
+      <c r="C605" s="1"/>
+      <c r="D605" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E605" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F605" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G605" s="5"/>
+    </row>
+    <row r="606" spans="1:7" ht="15.5">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
       <c r="D606" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E606" s="3" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F606" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G606" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="608" spans="1:7">
-      <c r="A608" s="1"/>
-      <c r="B608" s="1"/>
-      <c r="C608" s="1"/>
-      <c r="D608" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E608" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F608" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G608" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="609" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="G606" s="5"/>
+    </row>
+    <row r="609" spans="1:7" ht="15.5">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
       <c r="D609" s="1" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E609" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F609" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G609" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G609" s="5"/>
     </row>
     <row r="610" spans="1:7" ht="15.5">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
       <c r="D610" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E610" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F610" s="4" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="G610" s="5"/>
     </row>
@@ -43622,136 +43586,217 @@
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
       <c r="D611" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E611" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F611" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G611" s="5"/>
+    </row>
+    <row r="613" spans="1:7">
+      <c r="A613" s="1"/>
+      <c r="B613" s="1"/>
+      <c r="C613" s="1"/>
+      <c r="D613" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E613" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F613" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G613" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7">
+      <c r="A615" s="1"/>
+      <c r="B615" s="1"/>
+      <c r="C615" s="1"/>
+      <c r="D615" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E615" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F615" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G615" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7">
+      <c r="A616" s="1"/>
+      <c r="B616" s="1"/>
+      <c r="C616" s="1"/>
+      <c r="D616" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E616" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F616" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G616" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" ht="15.5">
+      <c r="A617" s="1"/>
+      <c r="B617" s="1"/>
+      <c r="C617" s="1"/>
+      <c r="D617" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F617" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G617" s="5"/>
+    </row>
+    <row r="618" spans="1:7" ht="15.5">
+      <c r="A618" s="1"/>
+      <c r="B618" s="1"/>
+      <c r="C618" s="1"/>
+      <c r="D618" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E611" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F611" s="4" t="s">
+      <c r="E618" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F618" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G611" s="5"/>
-    </row>
-    <row r="612" spans="1:7" ht="15.5">
-      <c r="A612" s="1"/>
-      <c r="B612" s="1"/>
-      <c r="C612" s="1"/>
-      <c r="D612" s="28"/>
-      <c r="E612" s="3"/>
-      <c r="F612" s="4"/>
-      <c r="G612" s="5"/>
-    </row>
-    <row r="613" spans="1:7" ht="26">
-      <c r="A613" s="27"/>
-      <c r="B613" s="27"/>
-      <c r="C613" s="27"/>
-      <c r="D613" s="28"/>
-      <c r="E613" s="3"/>
-      <c r="F613" s="4" t="s">
+      <c r="G618" s="5"/>
+    </row>
+    <row r="619" spans="1:7" ht="15.5">
+      <c r="A619" s="1"/>
+      <c r="B619" s="1"/>
+      <c r="C619" s="1"/>
+      <c r="D619" s="28"/>
+      <c r="E619" s="3"/>
+      <c r="F619" s="4"/>
+      <c r="G619" s="5"/>
+    </row>
+    <row r="620" spans="1:7" ht="26">
+      <c r="A620" s="27"/>
+      <c r="B620" s="27"/>
+      <c r="C620" s="27"/>
+      <c r="D620" s="28"/>
+      <c r="E620" s="3"/>
+      <c r="F620" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G613" s="3" t="s">
+      <c r="G620" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
-      <c r="A621" s="1"/>
-      <c r="B621" s="1"/>
-      <c r="C621" s="1"/>
-      <c r="D621" s="67" t="s">
+    <row r="628" spans="1:6">
+      <c r="A628" s="1"/>
+      <c r="B628" s="1"/>
+      <c r="C628" s="1"/>
+      <c r="D628" s="67" t="s">
         <v>279</v>
       </c>
-      <c r="E621" s="19"/>
-      <c r="F621" t="s">
+      <c r="E628" s="19"/>
+      <c r="F628" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="622" spans="1:7">
-      <c r="A622" s="1"/>
-      <c r="B622" s="1"/>
-      <c r="C622" s="1"/>
-      <c r="D622" s="67" t="s">
+    <row r="629" spans="1:6">
+      <c r="A629" s="1"/>
+      <c r="B629" s="1"/>
+      <c r="C629" s="1"/>
+      <c r="D629" s="67" t="s">
         <v>278</v>
       </c>
-      <c r="E622" s="19"/>
-      <c r="F622" t="s">
+      <c r="E629" s="19"/>
+      <c r="F629" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="623" spans="1:7">
-      <c r="A623" s="1"/>
-      <c r="B623" s="1"/>
-      <c r="C623" s="1"/>
-      <c r="D623" s="67" t="s">
+    <row r="630" spans="1:6">
+      <c r="A630" s="1"/>
+      <c r="B630" s="1"/>
+      <c r="C630" s="1"/>
+      <c r="D630" s="67" t="s">
         <v>592</v>
       </c>
-      <c r="E623" s="19"/>
-      <c r="F623" t="s">
+      <c r="E630" s="19"/>
+      <c r="F630" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="624" spans="1:7">
-      <c r="A624" s="1"/>
-      <c r="B624" s="1"/>
-      <c r="C624" s="1"/>
-      <c r="D624" s="67" t="s">
+    <row r="631" spans="1:6">
+      <c r="A631" s="1"/>
+      <c r="B631" s="1"/>
+      <c r="C631" s="1"/>
+      <c r="D631" s="67" t="s">
         <v>593</v>
       </c>
-      <c r="E624" s="19"/>
-      <c r="F624" t="s">
+      <c r="E631" s="19"/>
+      <c r="F631" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="625" spans="1:6">
-      <c r="A625" s="1"/>
-      <c r="B625" s="1"/>
-      <c r="C625" s="1"/>
-      <c r="D625" s="67" t="s">
+    <row r="632" spans="1:6">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="1"/>
+      <c r="D632" s="67" t="s">
         <v>840</v>
       </c>
-      <c r="E625" s="19"/>
-    </row>
-    <row r="626" spans="1:6">
-      <c r="A626" s="1"/>
-      <c r="B626" s="1"/>
-      <c r="C626" s="1"/>
-      <c r="D626" s="67" t="s">
+      <c r="E632" s="19"/>
+    </row>
+    <row r="633" spans="1:6">
+      <c r="A633" s="1"/>
+      <c r="B633" s="1"/>
+      <c r="C633" s="1"/>
+      <c r="D633" s="67" t="s">
         <v>845</v>
       </c>
-      <c r="E626" s="19"/>
-      <c r="F626" s="48" t="s">
+      <c r="E633" s="19"/>
+      <c r="F633" s="48" t="s">
         <v>609</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D579:D581"/>
-    <mergeCell ref="E579:E581"/>
-    <mergeCell ref="F579:F581"/>
-    <mergeCell ref="D570:D571"/>
-    <mergeCell ref="E570:E571"/>
-    <mergeCell ref="F570:F571"/>
-    <mergeCell ref="D576:D578"/>
-    <mergeCell ref="E576:E578"/>
-    <mergeCell ref="F576:F578"/>
-    <mergeCell ref="D566:D567"/>
-    <mergeCell ref="E566:E567"/>
-    <mergeCell ref="F566:F567"/>
-    <mergeCell ref="D568:D569"/>
-    <mergeCell ref="E568:E569"/>
-    <mergeCell ref="F568:F569"/>
-    <mergeCell ref="D560:D561"/>
-    <mergeCell ref="E560:E561"/>
-    <mergeCell ref="F560:F561"/>
-    <mergeCell ref="D564:D565"/>
-    <mergeCell ref="E564:E565"/>
-    <mergeCell ref="F564:F565"/>
-    <mergeCell ref="D554:D555"/>
-    <mergeCell ref="E554:E555"/>
-    <mergeCell ref="F554:F555"/>
-    <mergeCell ref="D558:D559"/>
-    <mergeCell ref="E558:E559"/>
-    <mergeCell ref="F558:F559"/>
+    <mergeCell ref="D586:D588"/>
+    <mergeCell ref="E586:E588"/>
+    <mergeCell ref="F586:F588"/>
+    <mergeCell ref="D577:D578"/>
+    <mergeCell ref="E577:E578"/>
+    <mergeCell ref="F577:F578"/>
+    <mergeCell ref="D583:D585"/>
+    <mergeCell ref="E583:E585"/>
+    <mergeCell ref="F583:F585"/>
+    <mergeCell ref="D573:D574"/>
+    <mergeCell ref="E573:E574"/>
+    <mergeCell ref="F573:F574"/>
+    <mergeCell ref="D575:D576"/>
+    <mergeCell ref="E575:E576"/>
+    <mergeCell ref="F575:F576"/>
+    <mergeCell ref="D567:D568"/>
+    <mergeCell ref="E567:E568"/>
+    <mergeCell ref="F567:F568"/>
+    <mergeCell ref="D571:D572"/>
+    <mergeCell ref="E571:E572"/>
+    <mergeCell ref="F571:F572"/>
+    <mergeCell ref="D561:D562"/>
+    <mergeCell ref="E561:E562"/>
+    <mergeCell ref="F561:F562"/>
+    <mergeCell ref="D565:D566"/>
+    <mergeCell ref="E565:E566"/>
+    <mergeCell ref="F565:F566"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3090" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE21BFF0-6B3C-489F-95C1-D879AAA1B82C}"/>
+  <xr:revisionPtr revIDLastSave="3109" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5739298E-DFE9-4E5D-9706-5FFD01608567}"/>
   <bookViews>
     <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9177" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="1654">
   <si>
     <t>Example</t>
   </si>
@@ -11264,12 +11264,15 @@
   <si>
     <t>ERA_harmonization_2026.09.14</t>
   </si>
+  <si>
+    <t>This column has a problem, years appear like this 1960.2 1961.2 1962.2 1963.2 1964.2 1965.2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="65">
+  <fonts count="64">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11684,12 +11687,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="64">
@@ -44101,14 +44098,18 @@
       <c r="B5" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C5" s="125"/>
+      <c r="C5" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D5" s="85" t="s">
         <v>615</v>
       </c>
       <c r="E5" s="62" t="s">
         <v>1331</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
@@ -44333,7 +44334,9 @@
       <c r="B16" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C16" s="125"/>
+      <c r="C16" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D16" s="35" t="s">
         <v>616</v>
       </c>
@@ -44533,7 +44536,9 @@
       <c r="B26" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C26" s="125"/>
+      <c r="C26" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D26" s="35" t="s">
         <v>616</v>
       </c>
@@ -44702,7 +44707,9 @@
       <c r="B34" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C34" s="125"/>
+      <c r="C34" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D34" s="34" t="s">
         <v>1038</v>
       </c>
@@ -44727,7 +44734,9 @@
       <c r="B35" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C35" s="125"/>
+      <c r="C35" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D35" s="34" t="s">
         <v>1038</v>
       </c>
@@ -44748,7 +44757,9 @@
     <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="D36" s="34" t="s">
         <v>1038</v>
       </c>
@@ -44769,7 +44780,9 @@
     <row r="37" spans="1:9" ht="15" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="C37" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D37" s="71" t="s">
         <v>1041</v>
       </c>
@@ -44786,7 +44799,9 @@
     <row r="38" spans="1:9" ht="15" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="D38" s="71" t="s">
         <v>1041</v>
       </c>
@@ -44803,7 +44818,9 @@
     <row r="39" spans="1:9" ht="15" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="9" t="s">
+        <v>1653</v>
+      </c>
       <c r="D39" s="71" t="s">
         <v>1041</v>
       </c>
@@ -44820,7 +44837,9 @@
     <row r="40" spans="1:9" ht="16" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="D40" s="71" t="s">
         <v>1041</v>
       </c>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3109" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5739298E-DFE9-4E5D-9706-5FFD01608567}"/>
+  <xr:revisionPtr revIDLastSave="3113" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34B523E-062A-4C0A-BD66-9380495BD5E8}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -477,7 +477,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="1654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9194" uniqueCount="1654">
   <si>
     <t>Example</t>
   </si>
@@ -11689,7 +11689,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="64">
+  <fills count="65">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12055,6 +12055,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -12257,7 +12263,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12531,6 +12537,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="64" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -13499,14 +13506,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487E46BC-52D3-4EF1-8B98-2DA697255E52}">
   <dimension ref="A1:PS2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="23.1796875" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="1" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:435" s="149" customFormat="1" ht="58.5" thickBot="1">
+    <row r="1" spans="1:435" s="149" customFormat="1" ht="60.75" thickBot="1">
       <c r="A1" s="62" t="s">
         <v>157</v>
       </c>
@@ -14597,7 +14604,7 @@
       <c r="PR1" s="144"/>
       <c r="PS1" s="144"/>
     </row>
-    <row r="2" spans="1:435" ht="15.5">
+    <row r="2" spans="1:435" ht="15.75">
       <c r="A2" s="60"/>
       <c r="B2" s="1"/>
       <c r="C2" s="60"/>
@@ -14616,19 +14623,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}">
   <dimension ref="A1:S616"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.453125" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
-    <col min="6" max="6" width="32.81640625" customWidth="1"/>
-    <col min="7" max="13" width="25.453125" customWidth="1"/>
-    <col min="14" max="14" width="20.54296875" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" customWidth="1"/>
+    <col min="7" max="13" width="25.42578125" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="121.81640625" style="10" customWidth="1"/>
+    <col min="17" max="17" width="121.85546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -14681,7 +14688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="25" customHeight="1">
+    <row r="2" spans="1:18" ht="24.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>902</v>
       </c>
@@ -14719,7 +14726,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.5">
+    <row r="3" spans="1:18" ht="15.75">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14824,7 +14831,7 @@
       <c r="Q5" s="46"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="15.5">
+    <row r="6" spans="1:18" ht="15.75">
       <c r="A6" s="3" t="s">
         <v>903</v>
       </c>
@@ -14898,7 +14905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.5">
+    <row r="8" spans="1:18" ht="15.75">
       <c r="A8" s="3" t="s">
         <v>905</v>
       </c>
@@ -14934,7 +14941,7 @@
       </c>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="16">
+    <row r="9" spans="1:18" ht="15.75">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -15200,7 +15207,7 @@
       </c>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="15.5">
+    <row r="16" spans="1:18" ht="15.75">
       <c r="A16" s="3" t="s">
         <v>909</v>
       </c>
@@ -15236,7 +15243,7 @@
       </c>
       <c r="R16" s="5"/>
     </row>
-    <row r="17" spans="1:19" ht="15.5">
+    <row r="17" spans="1:19" ht="15.75">
       <c r="A17" s="3" t="s">
         <v>910</v>
       </c>
@@ -15272,7 +15279,7 @@
       </c>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" spans="1:19" ht="15.5">
+    <row r="18" spans="1:19" ht="15.75">
       <c r="A18" s="3" t="s">
         <v>911</v>
       </c>
@@ -15383,7 +15390,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1">
       <c r="A21" s="3" t="s">
         <v>913</v>
       </c>
@@ -15418,7 +15425,7 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1">
+    <row r="22" spans="1:19" ht="15.75" thickBot="1">
       <c r="A22" s="75" t="s">
         <v>1003</v>
       </c>
@@ -15498,7 +15505,7 @@
       </c>
       <c r="S23" s="4"/>
     </row>
-    <row r="24" spans="1:19" ht="15" thickBot="1">
+    <row r="24" spans="1:19" ht="15.75" thickBot="1">
       <c r="A24" s="75" t="s">
         <v>1003</v>
       </c>
@@ -15537,7 +15544,7 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:19" ht="15" thickBot="1">
+    <row r="25" spans="1:19" ht="15.75" thickBot="1">
       <c r="A25" s="3" t="s">
         <v>915</v>
       </c>
@@ -15570,7 +15577,7 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19" ht="15" thickBot="1">
+    <row r="26" spans="1:19" ht="15.75" thickBot="1">
       <c r="A26" s="3" t="s">
         <v>916</v>
       </c>
@@ -15603,7 +15610,7 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:19" ht="16" thickBot="1">
+    <row r="27" spans="1:19" ht="16.5" thickBot="1">
       <c r="A27" t="s">
         <v>1044</v>
       </c>
@@ -15835,7 +15842,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="16">
+    <row r="33" spans="1:18" ht="15.75">
       <c r="A33" t="s">
         <v>1045</v>
       </c>
@@ -15979,7 +15986,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="16">
+    <row r="36" spans="1:18" ht="15.75">
       <c r="A36" t="s">
         <v>1046</v>
       </c>
@@ -16264,7 +16271,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="16">
+    <row r="43" spans="1:18" ht="15.75">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -16366,7 +16373,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="16">
+    <row r="46" spans="1:18" ht="15.75">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -16402,7 +16409,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" thickBot="1">
+    <row r="47" spans="1:18" ht="15.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -16434,7 +16441,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" thickBot="1">
+    <row r="48" spans="1:18" ht="15.75" thickBot="1">
       <c r="A48" s="3" t="s">
         <v>1062</v>
       </c>
@@ -16471,7 +16478,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="16">
+    <row r="49" spans="1:18" ht="15.75">
       <c r="A49" s="3"/>
       <c r="B49" s="87" t="s">
         <v>1070</v>
@@ -16625,7 +16632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="16" thickBot="1">
+    <row r="53" spans="1:18" ht="16.5" thickBot="1">
       <c r="A53" s="3" t="s">
         <v>1018</v>
       </c>
@@ -16663,7 +16670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="16" thickBot="1">
+    <row r="54" spans="1:18" ht="16.5" thickBot="1">
       <c r="A54" s="3" t="s">
         <v>1063</v>
       </c>
@@ -16701,7 +16708,7 @@
       </c>
       <c r="R54" s="5"/>
     </row>
-    <row r="55" spans="1:18" ht="16">
+    <row r="55" spans="1:18" ht="15.75">
       <c r="A55" s="3"/>
       <c r="B55" s="87" t="s">
         <v>1070</v>
@@ -16855,7 +16862,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15.5">
+    <row r="59" spans="1:18" ht="15.75">
       <c r="A59" s="3" t="s">
         <v>1022</v>
       </c>
@@ -16893,7 +16900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15.5">
+    <row r="60" spans="1:18" ht="15.75">
       <c r="A60" t="s">
         <v>1068</v>
       </c>
@@ -16958,7 +16965,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="16">
+    <row r="62" spans="1:18" ht="15.75">
       <c r="A62" t="s">
         <v>1066</v>
       </c>
@@ -17142,7 +17149,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="16">
+    <row r="67" spans="1:18" ht="15.75">
       <c r="A67" t="s">
         <v>1067</v>
       </c>
@@ -17360,7 +17367,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15.5">
+    <row r="73" spans="1:18" ht="15.75">
       <c r="A73" s="3" t="s">
         <v>1024</v>
       </c>
@@ -17458,7 +17465,7 @@
       <c r="Q75"/>
       <c r="R75" s="31"/>
     </row>
-    <row r="76" spans="1:18" ht="15.5">
+    <row r="76" spans="1:18" ht="15.75">
       <c r="A76" t="s">
         <v>1046</v>
       </c>
@@ -17492,7 +17499,7 @@
       </c>
       <c r="R76" s="5"/>
     </row>
-    <row r="77" spans="1:18" ht="15.5">
+    <row r="77" spans="1:18" ht="15.75">
       <c r="A77" s="3" t="s">
         <v>1025</v>
       </c>
@@ -17564,7 +17571,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15.5">
+    <row r="79" spans="1:18" ht="15.75">
       <c r="A79" s="3" t="s">
         <v>1061</v>
       </c>
@@ -17600,7 +17607,7 @@
       </c>
       <c r="R79" s="5"/>
     </row>
-    <row r="80" spans="1:18" ht="15.5">
+    <row r="80" spans="1:18" ht="15.75">
       <c r="A80" s="3"/>
       <c r="B80" s="93"/>
       <c r="C80" s="93"/>
@@ -17895,7 +17902,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15" thickBot="1">
+    <row r="89" spans="1:18" ht="15.75" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -17923,7 +17930,7 @@
       <c r="Q89"/>
       <c r="R89" s="31"/>
     </row>
-    <row r="90" spans="1:18" ht="15" thickBot="1">
+    <row r="90" spans="1:18" ht="15.75" thickBot="1">
       <c r="A90" t="s">
         <v>1084</v>
       </c>
@@ -17996,7 +18003,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15" thickBot="1">
+    <row r="92" spans="1:18" ht="15.75" thickBot="1">
       <c r="A92" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18033,7 +18040,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15" thickBot="1">
+    <row r="93" spans="1:18" ht="15.75" thickBot="1">
       <c r="A93" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18070,7 +18077,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15" thickBot="1">
+    <row r="94" spans="1:18" ht="15.75" thickBot="1">
       <c r="A94" s="3" t="s">
         <v>896</v>
       </c>
@@ -18105,7 +18112,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="16" thickBot="1">
+    <row r="95" spans="1:18" ht="16.5" thickBot="1">
       <c r="A95" t="s">
         <v>1086</v>
       </c>
@@ -18141,7 +18148,7 @@
       </c>
       <c r="R95" s="5"/>
     </row>
-    <row r="96" spans="1:18" ht="15" thickBot="1">
+    <row r="96" spans="1:18" ht="15.75" thickBot="1">
       <c r="A96" s="3" t="s">
         <v>895</v>
       </c>
@@ -18176,7 +18183,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15" thickBot="1">
+    <row r="97" spans="1:18" ht="15.75" thickBot="1">
       <c r="A97" t="s">
         <v>1085</v>
       </c>
@@ -18209,7 +18216,7 @@
       </c>
       <c r="Q97"/>
     </row>
-    <row r="98" spans="1:18" ht="16" thickBot="1">
+    <row r="98" spans="1:18" ht="16.5" thickBot="1">
       <c r="A98" s="3"/>
       <c r="B98" s="89" t="s">
         <v>1089</v>
@@ -18247,7 +18254,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15" thickBot="1">
+    <row r="99" spans="1:18" ht="15.75" thickBot="1">
       <c r="A99" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18287,7 +18294,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15" thickBot="1">
+    <row r="100" spans="1:18" ht="15.75" thickBot="1">
       <c r="A100" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18327,7 +18334,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="16" thickBot="1">
+    <row r="101" spans="1:18" ht="16.5" thickBot="1">
       <c r="A101" s="3" t="s">
         <v>894</v>
       </c>
@@ -18365,7 +18372,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="16" thickBot="1">
+    <row r="102" spans="1:18" ht="16.5" thickBot="1">
       <c r="A102" t="s">
         <v>1087</v>
       </c>
@@ -18403,7 +18410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15" thickBot="1">
+    <row r="103" spans="1:18" ht="15.75" thickBot="1">
       <c r="A103" s="3" t="s">
         <v>893</v>
       </c>
@@ -18472,7 +18479,7 @@
       <c r="P104" s="3"/>
       <c r="Q104"/>
     </row>
-    <row r="105" spans="1:18" ht="16">
+    <row r="105" spans="1:18" ht="15.75">
       <c r="A105" t="s">
         <v>1227</v>
       </c>
@@ -18512,7 +18519,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15.5">
+    <row r="106" spans="1:18" ht="15.75">
       <c r="A106" t="s">
         <v>1091</v>
       </c>
@@ -18548,7 +18555,7 @@
       </c>
       <c r="R106" s="5"/>
     </row>
-    <row r="107" spans="1:18" ht="15.5">
+    <row r="107" spans="1:18" ht="15.75">
       <c r="A107" t="s">
         <v>1093</v>
       </c>
@@ -18583,7 +18590,7 @@
       </c>
       <c r="R107" s="5"/>
     </row>
-    <row r="108" spans="1:18" ht="15.5">
+    <row r="108" spans="1:18" ht="15.75">
       <c r="A108" s="1"/>
       <c r="B108" s="97" t="s">
         <v>1232</v>
@@ -18619,7 +18626,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15.5">
+    <row r="109" spans="1:18" ht="15.75">
       <c r="A109" s="92" t="s">
         <v>891</v>
       </c>
@@ -18651,7 +18658,7 @@
       <c r="Q109"/>
       <c r="R109" s="5"/>
     </row>
-    <row r="110" spans="1:18" ht="16">
+    <row r="110" spans="1:18" ht="15.75">
       <c r="A110" t="s">
         <v>1227</v>
       </c>
@@ -18691,7 +18698,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15.5">
+    <row r="111" spans="1:18" ht="15.75">
       <c r="A111" t="s">
         <v>1092</v>
       </c>
@@ -18729,7 +18736,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15.5">
+    <row r="112" spans="1:18" ht="15.75">
       <c r="A112" t="s">
         <v>1094</v>
       </c>
@@ -18836,7 +18843,7 @@
       </c>
       <c r="Q114"/>
     </row>
-    <row r="115" spans="1:18" ht="16">
+    <row r="115" spans="1:18" ht="15.75">
       <c r="A115" s="1" t="s">
         <v>1301</v>
       </c>
@@ -19004,7 +19011,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15" thickBot="1">
+    <row r="119" spans="1:18" ht="15.75" thickBot="1">
       <c r="A119" s="1" t="s">
         <v>1237</v>
       </c>
@@ -19157,7 +19164,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15" thickBot="1">
+    <row r="123" spans="1:18" ht="15.75" thickBot="1">
       <c r="A123" s="75" t="s">
         <v>1003</v>
       </c>
@@ -19197,7 +19204,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15" thickBot="1">
+    <row r="124" spans="1:18" ht="15.75" thickBot="1">
       <c r="A124" t="s">
         <v>1257</v>
       </c>
@@ -19226,7 +19233,7 @@
       <c r="P124" s="3"/>
       <c r="Q124"/>
     </row>
-    <row r="125" spans="1:18" ht="15" thickBot="1">
+    <row r="125" spans="1:18" ht="15.75" thickBot="1">
       <c r="A125" s="1" t="s">
         <v>1298</v>
       </c>
@@ -19268,7 +19275,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" thickBot="1">
+    <row r="126" spans="1:18" ht="15.75" thickBot="1">
       <c r="A126" s="92" t="s">
         <v>1274</v>
       </c>
@@ -19308,7 +19315,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15" thickBot="1">
+    <row r="127" spans="1:18" ht="15.75" thickBot="1">
       <c r="A127" t="s">
         <v>1279</v>
       </c>
@@ -19346,7 +19353,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15" thickBot="1">
+    <row r="128" spans="1:18" ht="15.75" thickBot="1">
       <c r="A128" t="s">
         <v>1283</v>
       </c>
@@ -19384,7 +19391,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15" thickBot="1">
+    <row r="129" spans="1:18" ht="15.75" thickBot="1">
       <c r="A129" t="s">
         <v>1284</v>
       </c>
@@ -19422,7 +19429,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15" thickBot="1">
+    <row r="130" spans="1:18" ht="15.75" thickBot="1">
       <c r="A130" s="1" t="s">
         <v>881</v>
       </c>
@@ -19458,7 +19465,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15" thickBot="1">
+    <row r="131" spans="1:18" ht="15.75" thickBot="1">
       <c r="A131" t="s">
         <v>882</v>
       </c>
@@ -19494,7 +19501,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15" thickBot="1">
+    <row r="132" spans="1:18" ht="15.75" thickBot="1">
       <c r="A132" s="1" t="s">
         <v>883</v>
       </c>
@@ -19530,7 +19537,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15" thickBot="1">
+    <row r="133" spans="1:18" ht="15.75" thickBot="1">
       <c r="A133" s="1" t="s">
         <v>884</v>
       </c>
@@ -19566,7 +19573,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" thickBot="1">
+    <row r="134" spans="1:18" ht="15.75" thickBot="1">
       <c r="A134" s="1" t="s">
         <v>885</v>
       </c>
@@ -19602,7 +19609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15" thickBot="1">
+    <row r="135" spans="1:18" ht="15.75" thickBot="1">
       <c r="A135" t="s">
         <v>1269</v>
       </c>
@@ -19638,7 +19645,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15" thickBot="1">
+    <row r="136" spans="1:18" ht="15.75" thickBot="1">
       <c r="A136" s="92" t="s">
         <v>1274</v>
       </c>
@@ -19708,7 +19715,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15" thickBot="1">
+    <row r="138" spans="1:18" ht="15.75" thickBot="1">
       <c r="A138" t="s">
         <v>1283</v>
       </c>
@@ -19745,7 +19752,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15" thickBot="1">
+    <row r="139" spans="1:18" ht="15.75" thickBot="1">
       <c r="A139" t="s">
         <v>1284</v>
       </c>
@@ -19782,7 +19789,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15" thickBot="1">
+    <row r="140" spans="1:18" ht="15.75" thickBot="1">
       <c r="A140" t="s">
         <v>897</v>
       </c>
@@ -19815,7 +19822,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" thickBot="1">
+    <row r="141" spans="1:18" ht="15.75" thickBot="1">
       <c r="A141" s="92" t="s">
         <v>1259</v>
       </c>
@@ -19848,7 +19855,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" thickBot="1">
+    <row r="142" spans="1:18" ht="15.75" thickBot="1">
       <c r="A142" t="s">
         <v>1260</v>
       </c>
@@ -19881,7 +19888,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15" thickBot="1">
+    <row r="143" spans="1:18" ht="15.75" thickBot="1">
       <c r="A143" t="s">
         <v>1264</v>
       </c>
@@ -19914,7 +19921,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15" thickBot="1">
+    <row r="144" spans="1:18" ht="15.75" thickBot="1">
       <c r="A144" t="s">
         <v>1267</v>
       </c>
@@ -19948,7 +19955,7 @@
       </c>
       <c r="R144" s="41"/>
     </row>
-    <row r="145" spans="1:18" ht="15" thickBot="1">
+    <row r="145" spans="1:18" ht="15.75" thickBot="1">
       <c r="A145" t="s">
         <v>1258</v>
       </c>
@@ -19978,7 +19985,7 @@
       <c r="Q145"/>
       <c r="R145" s="41"/>
     </row>
-    <row r="146" spans="1:18" ht="15" thickBot="1">
+    <row r="146" spans="1:18" ht="15.75" thickBot="1">
       <c r="A146" s="1" t="s">
         <v>1299</v>
       </c>
@@ -20020,7 +20027,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15" thickBot="1">
+    <row r="147" spans="1:18" ht="15.75" thickBot="1">
       <c r="A147" s="92" t="s">
         <v>1277</v>
       </c>
@@ -20057,7 +20064,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15" thickBot="1">
+    <row r="148" spans="1:18" ht="15.75" thickBot="1">
       <c r="A148" t="s">
         <v>1280</v>
       </c>
@@ -20093,7 +20100,7 @@
       </c>
       <c r="R148" s="39"/>
     </row>
-    <row r="149" spans="1:18" ht="15" thickBot="1">
+    <row r="149" spans="1:18" ht="15.75" thickBot="1">
       <c r="A149" t="s">
         <v>1291</v>
       </c>
@@ -20129,7 +20136,7 @@
       </c>
       <c r="R149" s="40"/>
     </row>
-    <row r="150" spans="1:18" ht="15" thickBot="1">
+    <row r="150" spans="1:18" ht="15.75" thickBot="1">
       <c r="A150" t="s">
         <v>1292</v>
       </c>
@@ -20165,7 +20172,7 @@
       </c>
       <c r="R150" s="32"/>
     </row>
-    <row r="151" spans="1:18" ht="15" thickBot="1">
+    <row r="151" spans="1:18" ht="15.75" thickBot="1">
       <c r="A151" s="1" t="s">
         <v>886</v>
       </c>
@@ -20198,7 +20205,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15" thickBot="1">
+    <row r="152" spans="1:18" ht="15.75" thickBot="1">
       <c r="A152" s="1" t="s">
         <v>887</v>
       </c>
@@ -20231,7 +20238,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15" thickBot="1">
+    <row r="153" spans="1:18" ht="15.75" thickBot="1">
       <c r="A153" s="1" t="s">
         <v>888</v>
       </c>
@@ -20264,7 +20271,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15" thickBot="1">
+    <row r="154" spans="1:18" ht="15.75" thickBot="1">
       <c r="A154" s="1" t="s">
         <v>889</v>
       </c>
@@ -20299,7 +20306,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15" thickBot="1">
+    <row r="155" spans="1:18" ht="15.75" thickBot="1">
       <c r="A155" s="1" t="s">
         <v>890</v>
       </c>
@@ -20332,7 +20339,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15" thickBot="1">
+    <row r="156" spans="1:18" ht="15.75" thickBot="1">
       <c r="A156" t="s">
         <v>1270</v>
       </c>
@@ -20365,7 +20372,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15" thickBot="1">
+    <row r="157" spans="1:18" ht="15.75" thickBot="1">
       <c r="A157" s="92" t="s">
         <v>1277</v>
       </c>
@@ -20441,7 +20448,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15" thickBot="1">
+    <row r="159" spans="1:18" ht="15.75" thickBot="1">
       <c r="A159" t="s">
         <v>1291</v>
       </c>
@@ -20481,7 +20488,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15" thickBot="1">
+    <row r="160" spans="1:18" ht="15.75" thickBot="1">
       <c r="A160" t="s">
         <v>1292</v>
       </c>
@@ -20521,7 +20528,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15" thickBot="1">
+    <row r="161" spans="1:18" ht="15.75" thickBot="1">
       <c r="A161" t="s">
         <v>898</v>
       </c>
@@ -20557,7 +20564,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15" thickBot="1">
+    <row r="162" spans="1:18" ht="15.75" thickBot="1">
       <c r="A162" s="92" t="s">
         <v>1261</v>
       </c>
@@ -20593,7 +20600,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15" thickBot="1">
+    <row r="163" spans="1:18" ht="15.75" thickBot="1">
       <c r="A163" t="s">
         <v>1262</v>
       </c>
@@ -20629,7 +20636,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15" thickBot="1">
+    <row r="164" spans="1:18" ht="15.75" thickBot="1">
       <c r="A164" t="s">
         <v>1263</v>
       </c>
@@ -20665,7 +20672,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15" thickBot="1">
+    <row r="165" spans="1:18" ht="15.75" thickBot="1">
       <c r="A165" t="s">
         <v>1268</v>
       </c>
@@ -20701,7 +20708,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15" thickBot="1">
+    <row r="166" spans="1:18" ht="15.75" thickBot="1">
       <c r="A166" t="s">
         <v>1134</v>
       </c>
@@ -20737,7 +20744,7 @@
       </c>
       <c r="R166" s="41"/>
     </row>
-    <row r="167" spans="1:18" ht="15" thickBot="1">
+    <row r="167" spans="1:18" ht="15.75" thickBot="1">
       <c r="A167" t="s">
         <v>1130</v>
       </c>
@@ -20773,7 +20780,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15" thickBot="1">
+    <row r="168" spans="1:18" ht="15.75" thickBot="1">
       <c r="A168" t="s">
         <v>1145</v>
       </c>
@@ -20819,7 +20826,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" thickBot="1">
+    <row r="169" spans="1:18" ht="15.75" thickBot="1">
       <c r="A169" t="s">
         <v>1141</v>
       </c>
@@ -20860,7 +20867,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15" thickBot="1">
+    <row r="170" spans="1:18" ht="15.75" thickBot="1">
       <c r="A170" t="s">
         <v>1135</v>
       </c>
@@ -20895,7 +20902,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15" thickBot="1">
+    <row r="171" spans="1:18" ht="15.75" thickBot="1">
       <c r="A171" t="s">
         <v>1131</v>
       </c>
@@ -20931,7 +20938,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15" thickBot="1">
+    <row r="172" spans="1:18" ht="15.75" thickBot="1">
       <c r="A172" t="s">
         <v>1146</v>
       </c>
@@ -20977,7 +20984,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15" thickBot="1">
+    <row r="173" spans="1:18" ht="15.75" thickBot="1">
       <c r="A173" t="s">
         <v>1142</v>
       </c>
@@ -21018,7 +21025,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15" thickBot="1">
+    <row r="174" spans="1:18" ht="15.75" thickBot="1">
       <c r="A174" t="s">
         <v>1246</v>
       </c>
@@ -21047,7 +21054,7 @@
       <c r="P174" s="17"/>
       <c r="Q174"/>
     </row>
-    <row r="175" spans="1:18" ht="15" thickBot="1">
+    <row r="175" spans="1:18" ht="15.75" thickBot="1">
       <c r="A175" s="48" t="s">
         <v>1245</v>
       </c>
@@ -21087,7 +21094,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15" thickBot="1">
+    <row r="176" spans="1:18" ht="15.75" thickBot="1">
       <c r="A176" t="s">
         <v>1248</v>
       </c>
@@ -21116,7 +21123,7 @@
       <c r="P176" s="17"/>
       <c r="Q176" s="47"/>
     </row>
-    <row r="177" spans="1:18" ht="15" thickBot="1">
+    <row r="177" spans="1:18" ht="15.75" thickBot="1">
       <c r="A177" t="s">
         <v>1252</v>
       </c>
@@ -21147,7 +21154,7 @@
       <c r="P177" s="17"/>
       <c r="Q177" s="47"/>
     </row>
-    <row r="178" spans="1:18" ht="15" thickBot="1">
+    <row r="178" spans="1:18" ht="15.75" thickBot="1">
       <c r="A178" t="s">
         <v>1250</v>
       </c>
@@ -21185,7 +21192,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15" thickBot="1">
+    <row r="179" spans="1:18" ht="15.75" thickBot="1">
       <c r="A179" t="s">
         <v>1247</v>
       </c>
@@ -21214,7 +21221,7 @@
       <c r="P179" s="17"/>
       <c r="Q179" s="47"/>
     </row>
-    <row r="180" spans="1:18" ht="15" thickBot="1">
+    <row r="180" spans="1:18" ht="15.75" thickBot="1">
       <c r="A180" s="48" t="s">
         <v>1256</v>
       </c>
@@ -21258,7 +21265,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15" thickBot="1">
+    <row r="181" spans="1:18" ht="15.75" thickBot="1">
       <c r="A181" t="s">
         <v>1249</v>
       </c>
@@ -21288,7 +21295,7 @@
       <c r="Q181"/>
       <c r="R181" s="69"/>
     </row>
-    <row r="182" spans="1:18" ht="15" thickBot="1">
+    <row r="182" spans="1:18" ht="15.75" thickBot="1">
       <c r="A182" t="s">
         <v>1253</v>
       </c>
@@ -21320,7 +21327,7 @@
       <c r="Q182"/>
       <c r="R182" s="69"/>
     </row>
-    <row r="183" spans="1:18" ht="15" thickBot="1">
+    <row r="183" spans="1:18" ht="15.75" thickBot="1">
       <c r="A183" t="s">
         <v>1251</v>
       </c>
@@ -21358,7 +21365,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15" thickBot="1">
+    <row r="184" spans="1:18" ht="15.75" thickBot="1">
       <c r="A184" t="s">
         <v>1147</v>
       </c>
@@ -21387,7 +21394,7 @@
       <c r="P184" s="17"/>
       <c r="Q184"/>
     </row>
-    <row r="185" spans="1:18" ht="15" thickBot="1">
+    <row r="185" spans="1:18" ht="15.75" thickBot="1">
       <c r="A185" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21427,7 +21434,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15" thickBot="1">
+    <row r="186" spans="1:18" ht="15.75" thickBot="1">
       <c r="A186" s="1" t="s">
         <v>936</v>
       </c>
@@ -21465,7 +21472,7 @@
       </c>
       <c r="R186" s="69"/>
     </row>
-    <row r="187" spans="1:18" ht="15" thickBot="1">
+    <row r="187" spans="1:18" ht="15.75" thickBot="1">
       <c r="A187" s="1" t="s">
         <v>937</v>
       </c>
@@ -21503,7 +21510,7 @@
       </c>
       <c r="R187" s="69"/>
     </row>
-    <row r="188" spans="1:18" ht="15" thickBot="1">
+    <row r="188" spans="1:18" ht="15.75" thickBot="1">
       <c r="A188" s="1" t="s">
         <v>938</v>
       </c>
@@ -21536,7 +21543,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15" thickBot="1">
+    <row r="189" spans="1:18" ht="15.75" thickBot="1">
       <c r="A189" s="1" t="s">
         <v>939</v>
       </c>
@@ -21570,7 +21577,7 @@
       </c>
       <c r="R189" s="43"/>
     </row>
-    <row r="190" spans="1:18" ht="15" thickBot="1">
+    <row r="190" spans="1:18" ht="15.75" thickBot="1">
       <c r="A190" s="1" t="s">
         <v>940</v>
       </c>
@@ -21602,7 +21609,7 @@
       <c r="Q190"/>
       <c r="R190" s="73"/>
     </row>
-    <row r="191" spans="1:18" ht="15" thickBot="1">
+    <row r="191" spans="1:18" ht="15.75" thickBot="1">
       <c r="A191" s="1" t="s">
         <v>941</v>
       </c>
@@ -21638,7 +21645,7 @@
       </c>
       <c r="R191" s="44"/>
     </row>
-    <row r="192" spans="1:18" ht="15" thickBot="1">
+    <row r="192" spans="1:18" ht="15.75" thickBot="1">
       <c r="A192" s="1" t="s">
         <v>942</v>
       </c>
@@ -21672,7 +21679,7 @@
       <c r="Q192"/>
       <c r="R192" s="44"/>
     </row>
-    <row r="193" spans="1:18" ht="15" thickBot="1">
+    <row r="193" spans="1:18" ht="15.75" thickBot="1">
       <c r="A193" s="1" t="s">
         <v>943</v>
       </c>
@@ -21710,7 +21717,7 @@
       </c>
       <c r="R193" s="44"/>
     </row>
-    <row r="194" spans="1:18" ht="15" thickBot="1">
+    <row r="194" spans="1:18" ht="15.75" thickBot="1">
       <c r="A194" t="s">
         <v>1153</v>
       </c>
@@ -21743,7 +21750,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15" thickBot="1">
+    <row r="195" spans="1:18" ht="15.75" thickBot="1">
       <c r="A195" t="s">
         <v>1149</v>
       </c>
@@ -21776,7 +21783,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15" thickBot="1">
+    <row r="196" spans="1:18" ht="15.75" thickBot="1">
       <c r="A196" t="s">
         <v>1151</v>
       </c>
@@ -21809,7 +21816,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15" thickBot="1">
+    <row r="197" spans="1:18" ht="15.75" thickBot="1">
       <c r="A197" t="s">
         <v>1156</v>
       </c>
@@ -21842,7 +21849,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15" thickBot="1">
+    <row r="198" spans="1:18" ht="15.75" thickBot="1">
       <c r="A198" t="s">
         <v>1163</v>
       </c>
@@ -21880,7 +21887,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15" thickBot="1">
+    <row r="199" spans="1:18" ht="15.75" thickBot="1">
       <c r="A199" t="s">
         <v>1160</v>
       </c>
@@ -21916,7 +21923,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15" thickBot="1">
+    <row r="200" spans="1:18" ht="15.75" thickBot="1">
       <c r="A200" t="s">
         <v>1148</v>
       </c>
@@ -21945,7 +21952,7 @@
       <c r="P200" s="17"/>
       <c r="Q200" s="47"/>
     </row>
-    <row r="201" spans="1:18" ht="15" thickBot="1">
+    <row r="201" spans="1:18" ht="15.75" thickBot="1">
       <c r="A201" s="1" t="s">
         <v>1170</v>
       </c>
@@ -21985,7 +21992,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15" thickBot="1">
+    <row r="202" spans="1:18" ht="15.75" thickBot="1">
       <c r="A202" s="1" t="s">
         <v>944</v>
       </c>
@@ -22023,7 +22030,7 @@
       </c>
       <c r="R202" s="73"/>
     </row>
-    <row r="203" spans="1:18" ht="15" thickBot="1">
+    <row r="203" spans="1:18" ht="15.75" thickBot="1">
       <c r="A203" s="1" t="s">
         <v>945</v>
       </c>
@@ -22061,7 +22068,7 @@
       </c>
       <c r="R203" s="73"/>
     </row>
-    <row r="204" spans="1:18" ht="15" thickBot="1">
+    <row r="204" spans="1:18" ht="15.75" thickBot="1">
       <c r="A204" s="1" t="s">
         <v>946</v>
       </c>
@@ -22100,7 +22107,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15" thickBot="1">
+    <row r="205" spans="1:18" ht="15.75" thickBot="1">
       <c r="A205" s="1" t="s">
         <v>947</v>
       </c>
@@ -22142,7 +22149,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15" thickBot="1">
+    <row r="206" spans="1:18" ht="15.75" thickBot="1">
       <c r="A206" s="1" t="s">
         <v>948</v>
       </c>
@@ -22176,7 +22183,7 @@
       <c r="Q206"/>
       <c r="R206" s="73"/>
     </row>
-    <row r="207" spans="1:18" ht="15" thickBot="1">
+    <row r="207" spans="1:18" ht="15.75" thickBot="1">
       <c r="A207" s="1" t="s">
         <v>949</v>
       </c>
@@ -22216,7 +22223,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15" thickBot="1">
+    <row r="208" spans="1:18" ht="15.75" thickBot="1">
       <c r="A208" s="1" t="s">
         <v>950</v>
       </c>
@@ -22250,7 +22257,7 @@
       <c r="Q208"/>
       <c r="R208" s="44"/>
     </row>
-    <row r="209" spans="1:18" ht="15" thickBot="1">
+    <row r="209" spans="1:18" ht="15.75" thickBot="1">
       <c r="A209" s="1" t="s">
         <v>951</v>
       </c>
@@ -22290,7 +22297,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" thickBot="1">
+    <row r="210" spans="1:18" ht="15.75" thickBot="1">
       <c r="A210" t="s">
         <v>1154</v>
       </c>
@@ -22323,7 +22330,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15" thickBot="1">
+    <row r="211" spans="1:18" ht="15.75" thickBot="1">
       <c r="A211" t="s">
         <v>1150</v>
       </c>
@@ -22359,7 +22366,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15" thickBot="1">
+    <row r="212" spans="1:18" ht="15.75" thickBot="1">
       <c r="A212" t="s">
         <v>1152</v>
       </c>
@@ -22395,7 +22402,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15" thickBot="1">
+    <row r="213" spans="1:18" ht="15.75" thickBot="1">
       <c r="A213" t="s">
         <v>1157</v>
       </c>
@@ -22431,7 +22438,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15" thickBot="1">
+    <row r="214" spans="1:18" ht="15.75" thickBot="1">
       <c r="A214" t="s">
         <v>1164</v>
       </c>
@@ -22469,7 +22476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" thickBot="1">
+    <row r="215" spans="1:18" ht="15.75" thickBot="1">
       <c r="A215" t="s">
         <v>1161</v>
       </c>
@@ -22505,7 +22512,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15" thickBot="1">
+    <row r="216" spans="1:18" ht="15.75" thickBot="1">
       <c r="A216" t="s">
         <v>1095</v>
       </c>
@@ -22577,7 +22584,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15" thickBot="1">
+    <row r="218" spans="1:18" ht="15.75" thickBot="1">
       <c r="A218" t="s">
         <v>1100</v>
       </c>
@@ -22615,7 +22622,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15" thickBot="1">
+    <row r="219" spans="1:18" ht="15.75" thickBot="1">
       <c r="A219" t="s">
         <v>1104</v>
       </c>
@@ -22653,7 +22660,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15" thickBot="1">
+    <row r="220" spans="1:18" ht="15.75" thickBot="1">
       <c r="A220" t="s">
         <v>1102</v>
       </c>
@@ -22685,7 +22692,7 @@
       <c r="Q220" s="47"/>
       <c r="R220" s="29"/>
     </row>
-    <row r="221" spans="1:18" ht="15" thickBot="1">
+    <row r="221" spans="1:18" ht="15.75" thickBot="1">
       <c r="A221" t="s">
         <v>1096</v>
       </c>
@@ -22757,7 +22764,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15" thickBot="1">
+    <row r="223" spans="1:18" ht="15.75" thickBot="1">
       <c r="A223" t="s">
         <v>1101</v>
       </c>
@@ -22795,7 +22802,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15" thickBot="1">
+    <row r="224" spans="1:18" ht="15.75" thickBot="1">
       <c r="A224" t="s">
         <v>1105</v>
       </c>
@@ -22833,7 +22840,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15" thickBot="1">
+    <row r="225" spans="1:18" ht="15.75" thickBot="1">
       <c r="A225" t="s">
         <v>1103</v>
       </c>
@@ -22864,7 +22871,7 @@
       <c r="P225" s="17"/>
       <c r="Q225"/>
     </row>
-    <row r="226" spans="1:18" ht="15" thickBot="1">
+    <row r="226" spans="1:18" ht="15.75" thickBot="1">
       <c r="A226" t="s">
         <v>1112</v>
       </c>
@@ -22969,7 +22976,7 @@
       </c>
       <c r="Q228"/>
     </row>
-    <row r="229" spans="1:18" ht="15" thickBot="1">
+    <row r="229" spans="1:18" ht="15.75" thickBot="1">
       <c r="A229" t="s">
         <v>1122</v>
       </c>
@@ -23005,7 +23012,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15" thickBot="1">
+    <row r="230" spans="1:18" ht="15.75" thickBot="1">
       <c r="A230" t="s">
         <v>1124</v>
       </c>
@@ -23038,7 +23045,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15" thickBot="1">
+    <row r="231" spans="1:18" ht="15.75" thickBot="1">
       <c r="A231" t="s">
         <v>1118</v>
       </c>
@@ -23074,7 +23081,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15" thickBot="1">
+    <row r="232" spans="1:18" ht="15.75" thickBot="1">
       <c r="A232" t="s">
         <v>1116</v>
       </c>
@@ -23105,7 +23112,7 @@
       </c>
       <c r="Q232" s="47"/>
     </row>
-    <row r="233" spans="1:18" ht="15" thickBot="1">
+    <row r="233" spans="1:18" ht="15.75" thickBot="1">
       <c r="A233" t="s">
         <v>1120</v>
       </c>
@@ -23141,7 +23148,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15" thickBot="1">
+    <row r="234" spans="1:18" ht="15.75" thickBot="1">
       <c r="A234" t="s">
         <v>1113</v>
       </c>
@@ -23246,7 +23253,7 @@
       </c>
       <c r="Q236"/>
     </row>
-    <row r="237" spans="1:18" ht="15" thickBot="1">
+    <row r="237" spans="1:18" ht="15.75" thickBot="1">
       <c r="A237" t="s">
         <v>1123</v>
       </c>
@@ -23282,7 +23289,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15" thickBot="1">
+    <row r="238" spans="1:18" ht="15.75" thickBot="1">
       <c r="A238" t="s">
         <v>1125</v>
       </c>
@@ -23315,7 +23322,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15" thickBot="1">
+    <row r="239" spans="1:18" ht="15.75" thickBot="1">
       <c r="A239" t="s">
         <v>1119</v>
       </c>
@@ -23346,7 +23353,7 @@
       </c>
       <c r="Q239" s="48"/>
     </row>
-    <row r="240" spans="1:18" ht="15" thickBot="1">
+    <row r="240" spans="1:18" ht="15.75" thickBot="1">
       <c r="A240" t="s">
         <v>1117</v>
       </c>
@@ -23382,7 +23389,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15" thickBot="1">
+    <row r="241" spans="1:18" ht="15.75" thickBot="1">
       <c r="A241" t="s">
         <v>1121</v>
       </c>
@@ -23415,7 +23422,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15" thickBot="1">
+    <row r="242" spans="1:18" ht="15.75" thickBot="1">
       <c r="A242" t="s">
         <v>976</v>
       </c>
@@ -23444,7 +23451,7 @@
       <c r="P242" s="17"/>
       <c r="Q242"/>
     </row>
-    <row r="243" spans="1:18" ht="15" thickBot="1">
+    <row r="243" spans="1:18" ht="15.75" thickBot="1">
       <c r="A243" s="92" t="s">
         <v>977</v>
       </c>
@@ -23483,7 +23490,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15" thickBot="1">
+    <row r="244" spans="1:18" ht="15.75" thickBot="1">
       <c r="A244" t="s">
         <v>978</v>
       </c>
@@ -23512,7 +23519,7 @@
       <c r="P244" s="17"/>
       <c r="Q244" s="47"/>
     </row>
-    <row r="245" spans="1:18" ht="15" thickBot="1">
+    <row r="245" spans="1:18" ht="15.75" thickBot="1">
       <c r="A245" s="92" t="s">
         <v>979</v>
       </c>
@@ -23551,7 +23558,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15" thickBot="1">
+    <row r="246" spans="1:18" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -23578,7 +23585,7 @@
       </c>
       <c r="Q246"/>
     </row>
-    <row r="247" spans="1:18" ht="15" thickBot="1">
+    <row r="247" spans="1:18" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -23607,7 +23614,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15" thickBot="1">
+    <row r="248" spans="1:18" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -23639,7 +23646,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15" thickBot="1">
+    <row r="249" spans="1:18" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -23668,7 +23675,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15" thickBot="1">
+    <row r="250" spans="1:18" ht="15.75" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -23697,7 +23704,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15" thickBot="1">
+    <row r="251" spans="1:18" ht="15.75" thickBot="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -23724,7 +23731,7 @@
       </c>
       <c r="Q251"/>
     </row>
-    <row r="252" spans="1:18" ht="15" thickBot="1">
+    <row r="252" spans="1:18" ht="15.75" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -23753,7 +23760,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15" thickBot="1">
+    <row r="253" spans="1:18" ht="15.75" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -23785,7 +23792,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15" thickBot="1">
+    <row r="254" spans="1:18" ht="15.75" thickBot="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -24166,7 +24173,7 @@
       <c r="P264" s="19"/>
       <c r="Q264"/>
     </row>
-    <row r="265" spans="1:17" ht="15" thickBot="1">
+    <row r="265" spans="1:17" ht="15.75" thickBot="1">
       <c r="A265" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24209,7 +24216,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="266" spans="1:17" ht="15" thickBot="1">
+    <row r="266" spans="1:17" ht="15.75" thickBot="1">
       <c r="A266" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24244,7 +24251,7 @@
       <c r="P266" s="19"/>
       <c r="Q266"/>
     </row>
-    <row r="267" spans="1:17" ht="15" thickBot="1">
+    <row r="267" spans="1:17" ht="15.75" thickBot="1">
       <c r="A267" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24279,7 +24286,7 @@
       <c r="P267" s="19"/>
       <c r="Q267"/>
     </row>
-    <row r="268" spans="1:17" ht="15" thickBot="1">
+    <row r="268" spans="1:17" ht="15.75" thickBot="1">
       <c r="A268" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24314,7 +24321,7 @@
       <c r="P268" s="19"/>
       <c r="Q268"/>
     </row>
-    <row r="269" spans="1:17" ht="15" thickBot="1">
+    <row r="269" spans="1:17" ht="15.75" thickBot="1">
       <c r="A269" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24349,7 +24356,7 @@
       <c r="P269" s="19"/>
       <c r="Q269"/>
     </row>
-    <row r="270" spans="1:17" ht="15" thickBot="1">
+    <row r="270" spans="1:17" ht="15.75" thickBot="1">
       <c r="A270" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24384,7 +24391,7 @@
       <c r="P270" s="19"/>
       <c r="Q270"/>
     </row>
-    <row r="271" spans="1:17" ht="15" thickBot="1">
+    <row r="271" spans="1:17" ht="15.75" thickBot="1">
       <c r="A271" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24419,7 +24426,7 @@
       <c r="P271" s="19"/>
       <c r="Q271"/>
     </row>
-    <row r="272" spans="1:17" ht="15" thickBot="1">
+    <row r="272" spans="1:17" ht="15.75" thickBot="1">
       <c r="A272" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24454,7 +24461,7 @@
       <c r="P272" s="19"/>
       <c r="Q272"/>
     </row>
-    <row r="273" spans="1:19" ht="15" thickBot="1">
+    <row r="273" spans="1:19" ht="15.75" thickBot="1">
       <c r="A273" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24489,7 +24496,7 @@
       <c r="P273" s="19"/>
       <c r="Q273"/>
     </row>
-    <row r="274" spans="1:19" ht="15" thickBot="1">
+    <row r="274" spans="1:19" ht="15.75" thickBot="1">
       <c r="A274" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24524,7 +24531,7 @@
       <c r="P274" s="19"/>
       <c r="Q274"/>
     </row>
-    <row r="275" spans="1:19" ht="15" thickBot="1">
+    <row r="275" spans="1:19" ht="15.75" thickBot="1">
       <c r="A275" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24559,7 +24566,7 @@
       <c r="P275" s="19"/>
       <c r="Q275"/>
     </row>
-    <row r="276" spans="1:19" ht="15" thickBot="1">
+    <row r="276" spans="1:19" ht="15.75" thickBot="1">
       <c r="A276" t="s">
         <v>1005</v>
       </c>
@@ -24592,7 +24599,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="277" spans="1:19" ht="15" thickBot="1">
+    <row r="277" spans="1:19" ht="15.75" thickBot="1">
       <c r="A277" t="s">
         <v>1004</v>
       </c>
@@ -24622,7 +24629,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="16">
+    <row r="278" spans="1:19" ht="15.75">
       <c r="A278" s="1"/>
       <c r="B278" s="97" t="s">
         <v>1327</v>
@@ -24730,7 +24737,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="281" spans="1:19" ht="15" thickBot="1">
+    <row r="281" spans="1:19" ht="15.75" thickBot="1">
       <c r="A281" t="s">
         <v>1318</v>
       </c>
@@ -24767,7 +24774,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="282" spans="1:19" ht="15" thickBot="1">
+    <row r="282" spans="1:19" ht="15.75" thickBot="1">
       <c r="A282" s="1" t="s">
         <v>1324</v>
       </c>
@@ -24800,7 +24807,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="283" spans="1:19" ht="16">
+    <row r="283" spans="1:19" ht="15.75">
       <c r="A283" s="1"/>
       <c r="B283" s="97" t="s">
         <v>1328</v>
@@ -24908,7 +24915,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="286" spans="1:19" ht="15" thickBot="1">
+    <row r="286" spans="1:19" ht="15.75" thickBot="1">
       <c r="A286" t="s">
         <v>1319</v>
       </c>
@@ -24942,7 +24949,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="287" spans="1:19" ht="15" thickBot="1">
+    <row r="287" spans="1:19" ht="15.75" thickBot="1">
       <c r="A287" s="1" t="s">
         <v>1325</v>
       </c>
@@ -25446,7 +25453,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="16">
+    <row r="301" spans="1:18" ht="15.75">
       <c r="A301" t="s">
         <v>1179</v>
       </c>
@@ -25486,7 +25493,7 @@
       <c r="Q301" s="3"/>
       <c r="R301" s="3"/>
     </row>
-    <row r="302" spans="1:18" ht="16">
+    <row r="302" spans="1:18" ht="15.75">
       <c r="A302" t="s">
         <v>1181</v>
       </c>
@@ -25568,7 +25575,7 @@
       <c r="Q303" s="3"/>
       <c r="R303" s="3"/>
     </row>
-    <row r="304" spans="1:18" ht="14.5" customHeight="1">
+    <row r="304" spans="1:18" ht="14.45" customHeight="1">
       <c r="A304" t="s">
         <v>1011</v>
       </c>
@@ -25684,7 +25691,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="16">
+    <row r="307" spans="1:18" ht="15.75">
       <c r="A307" t="s">
         <v>1180</v>
       </c>
@@ -25720,7 +25727,7 @@
       <c r="Q307" s="3"/>
       <c r="R307" s="3"/>
     </row>
-    <row r="308" spans="1:18" ht="16">
+    <row r="308" spans="1:18" ht="15.75">
       <c r="A308" t="s">
         <v>1182</v>
       </c>
@@ -25802,7 +25809,7 @@
       <c r="Q309" s="3"/>
       <c r="R309" s="3"/>
     </row>
-    <row r="310" spans="1:18" ht="14.5" customHeight="1" thickBot="1">
+    <row r="310" spans="1:18" ht="14.45" customHeight="1" thickBot="1">
       <c r="A310" t="s">
         <v>1012</v>
       </c>
@@ -25840,7 +25847,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="14.5" customHeight="1" thickBot="1">
+    <row r="311" spans="1:18" ht="14.45" customHeight="1" thickBot="1">
       <c r="A311" t="s">
         <v>1192</v>
       </c>
@@ -25873,7 +25880,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="14.5" customHeight="1">
+    <row r="312" spans="1:18" ht="14.45" customHeight="1">
       <c r="A312" t="s">
         <v>1200</v>
       </c>
@@ -25902,7 +25909,7 @@
       <c r="P312" s="14"/>
       <c r="Q312" s="14"/>
     </row>
-    <row r="313" spans="1:18" ht="14.5" customHeight="1">
+    <row r="313" spans="1:18" ht="14.45" customHeight="1">
       <c r="A313" s="14" t="s">
         <v>1194</v>
       </c>
@@ -25938,7 +25945,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="14.5" customHeight="1">
+    <row r="314" spans="1:18" ht="14.45" customHeight="1">
       <c r="A314" s="14" t="s">
         <v>1202</v>
       </c>
@@ -26254,7 +26261,7 @@
       <c r="Q330" s="3"/>
       <c r="R330" s="3"/>
     </row>
-    <row r="331" spans="1:18" ht="15" thickBot="1">
+    <row r="331" spans="1:18" ht="15.75" thickBot="1">
       <c r="N331" s="14" t="s">
         <v>765</v>
       </c>
@@ -26267,7 +26274,7 @@
       <c r="Q331" s="3"/>
       <c r="R331" s="3"/>
     </row>
-    <row r="332" spans="1:18" ht="26.5" thickBot="1">
+    <row r="332" spans="1:18" ht="26.25" thickBot="1">
       <c r="N332" s="14"/>
       <c r="O332" s="58" t="s">
         <v>836</v>
@@ -26291,7 +26298,7 @@
       <c r="Q333" s="3"/>
       <c r="R333" s="3"/>
     </row>
-    <row r="334" spans="1:18" ht="15" thickBot="1">
+    <row r="334" spans="1:18" ht="15.75" thickBot="1">
       <c r="N334" s="14" t="s">
         <v>765</v>
       </c>
@@ -26304,7 +26311,7 @@
       <c r="Q334" s="3"/>
       <c r="R334" s="3"/>
     </row>
-    <row r="335" spans="1:18" ht="26.5" thickBot="1">
+    <row r="335" spans="1:18" ht="26.25" thickBot="1">
       <c r="N335" s="14"/>
       <c r="O335" s="58" t="s">
         <v>837</v>
@@ -27175,7 +27182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="15.5">
+    <row r="374" spans="1:18" ht="15.75">
       <c r="A374" s="14"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -27325,7 +27332,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="15.5">
+    <row r="379" spans="1:18" ht="15.75">
       <c r="A379" s="14"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -27382,7 +27389,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="15.5">
+    <row r="381" spans="1:18" ht="15.75">
       <c r="A381" s="14"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -27467,7 +27474,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="15.5">
+    <row r="384" spans="1:18" ht="15.75">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -27585,7 +27592,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="15.5">
+    <row r="388" spans="1:18" ht="15.75">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -27703,7 +27710,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="15.5">
+    <row r="392" spans="1:18" ht="15.75">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -27731,7 +27738,7 @@
       </c>
       <c r="R392" s="5"/>
     </row>
-    <row r="393" spans="1:18" ht="15" thickBot="1">
+    <row r="393" spans="1:18" ht="15.75" thickBot="1">
       <c r="A393" s="14"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -27761,7 +27768,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="15" thickBot="1">
+    <row r="394" spans="1:18" ht="15.75" thickBot="1">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -27787,7 +27794,7 @@
       <c r="Q394" s="46"/>
       <c r="R394" s="14"/>
     </row>
-    <row r="395" spans="1:18" ht="15" thickBot="1">
+    <row r="395" spans="1:18" ht="15.75" thickBot="1">
       <c r="A395" s="14"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -27813,7 +27820,7 @@
       <c r="Q395" s="46"/>
       <c r="R395" s="14"/>
     </row>
-    <row r="396" spans="1:18" ht="15.5">
+    <row r="396" spans="1:18" ht="15.75">
       <c r="N396" s="14" t="s">
         <v>765</v>
       </c>
@@ -27894,7 +27901,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="15.5">
+    <row r="400" spans="1:18" ht="15.75">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -27984,7 +27991,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="15" thickBot="1">
+    <row r="403" spans="1:18" ht="15.75" thickBot="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14"/>
@@ -28014,7 +28021,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="15" thickBot="1">
+    <row r="404" spans="1:18" ht="15.75" thickBot="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
@@ -28044,7 +28051,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="15" thickBot="1">
+    <row r="405" spans="1:18" ht="15.75" thickBot="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -28074,7 +28081,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="15" thickBot="1">
+    <row r="406" spans="1:18" ht="15.75" thickBot="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14"/>
@@ -28104,7 +28111,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="15" thickBot="1">
+    <row r="407" spans="1:18" ht="15.75" thickBot="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14"/>
@@ -28134,7 +28141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="15" thickBot="1">
+    <row r="408" spans="1:18" ht="15.75" thickBot="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14"/>
@@ -28164,7 +28171,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="15" thickBot="1">
+    <row r="409" spans="1:18" ht="15.75" thickBot="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -28194,7 +28201,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="15" thickBot="1">
+    <row r="410" spans="1:18" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -28224,7 +28231,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="15" thickBot="1">
+    <row r="411" spans="1:18" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -28254,7 +28261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="15" thickBot="1">
+    <row r="412" spans="1:18" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -28284,7 +28291,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="15" thickBot="1">
+    <row r="413" spans="1:18" ht="15.75" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14"/>
@@ -28314,7 +28321,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="15" thickBot="1">
+    <row r="414" spans="1:18" ht="15.75" thickBot="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -28344,7 +28351,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="15" thickBot="1">
+    <row r="415" spans="1:18" ht="15.75" thickBot="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14"/>
@@ -28371,7 +28378,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="15" thickBot="1">
+    <row r="416" spans="1:18" ht="15.75" thickBot="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14"/>
@@ -28398,7 +28405,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="15" thickBot="1">
+    <row r="417" spans="1:18" ht="15.75" thickBot="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -28425,7 +28432,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="15" thickBot="1">
+    <row r="418" spans="1:18" ht="15.75" thickBot="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14"/>
@@ -28452,7 +28459,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="15" thickBot="1">
+    <row r="419" spans="1:18" ht="15.75" thickBot="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14"/>
@@ -28479,7 +28486,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="15" thickBot="1">
+    <row r="420" spans="1:18" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -28506,7 +28513,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="15" thickBot="1">
+    <row r="421" spans="1:18" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -28533,7 +28540,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="15" thickBot="1">
+    <row r="422" spans="1:18" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -28560,7 +28567,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="15" thickBot="1">
+    <row r="423" spans="1:18" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -28588,7 +28595,7 @@
       </c>
       <c r="R423" s="41"/>
     </row>
-    <row r="424" spans="1:18" ht="15" thickBot="1">
+    <row r="424" spans="1:18" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -28618,7 +28625,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="15" thickBot="1">
+    <row r="425" spans="1:18" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -28648,7 +28655,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="15" thickBot="1">
+    <row r="426" spans="1:18" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -28678,7 +28685,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="15" thickBot="1">
+    <row r="427" spans="1:18" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -28708,7 +28715,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="15" thickBot="1">
+    <row r="428" spans="1:18" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -28738,7 +28745,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="15" thickBot="1">
+    <row r="429" spans="1:18" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -28768,7 +28775,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="15" thickBot="1">
+    <row r="430" spans="1:18" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -28798,7 +28805,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="15" thickBot="1">
+    <row r="431" spans="1:18" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -28828,7 +28835,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="15" thickBot="1">
+    <row r="432" spans="1:18" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -28858,7 +28865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="15" thickBot="1">
+    <row r="433" spans="1:18" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -28888,7 +28895,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="15" thickBot="1">
+    <row r="434" spans="1:18" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -28918,7 +28925,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="15" thickBot="1">
+    <row r="435" spans="1:18" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -28945,7 +28952,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="15" thickBot="1">
+    <row r="436" spans="1:18" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -28972,7 +28979,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="15" thickBot="1">
+    <row r="437" spans="1:18" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -28999,7 +29006,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="15" thickBot="1">
+    <row r="438" spans="1:18" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -29026,7 +29033,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="15" thickBot="1">
+    <row r="439" spans="1:18" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -29053,7 +29060,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="15" thickBot="1">
+    <row r="440" spans="1:18" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -29080,7 +29087,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="15" thickBot="1">
+    <row r="441" spans="1:18" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -29107,7 +29114,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="15" thickBot="1">
+    <row r="442" spans="1:18" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -29134,7 +29141,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="15" thickBot="1">
+    <row r="443" spans="1:18" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -29162,7 +29169,7 @@
       </c>
       <c r="R443" s="41"/>
     </row>
-    <row r="444" spans="1:18" ht="15" thickBot="1">
+    <row r="444" spans="1:18" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -29192,7 +29199,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="15" thickBot="1">
+    <row r="445" spans="1:18" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -29222,7 +29229,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="15" thickBot="1">
+    <row r="446" spans="1:18" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -29252,7 +29259,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="15" thickBot="1">
+    <row r="447" spans="1:18" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -29282,7 +29289,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="15" thickBot="1">
+    <row r="448" spans="1:18" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -29312,7 +29319,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="15" thickBot="1">
+    <row r="449" spans="1:18" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -29342,7 +29349,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="15" thickBot="1">
+    <row r="450" spans="1:18" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -29372,7 +29379,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="15" thickBot="1">
+    <row r="451" spans="1:18" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -29402,7 +29409,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="15" thickBot="1">
+    <row r="452" spans="1:18" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -29432,7 +29439,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="15" thickBot="1">
+    <row r="453" spans="1:18" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -29459,7 +29466,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="15" thickBot="1">
+    <row r="454" spans="1:18" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -29487,7 +29494,7 @@
       </c>
       <c r="R454" s="43"/>
     </row>
-    <row r="455" spans="1:18" ht="15" thickBot="1">
+    <row r="455" spans="1:18" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -29515,7 +29522,7 @@
       </c>
       <c r="R455" s="44"/>
     </row>
-    <row r="456" spans="1:18" ht="15" thickBot="1">
+    <row r="456" spans="1:18" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -29543,7 +29550,7 @@
       </c>
       <c r="R456" s="44"/>
     </row>
-    <row r="457" spans="1:18" ht="15" thickBot="1">
+    <row r="457" spans="1:18" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -29570,7 +29577,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="15" thickBot="1">
+    <row r="458" spans="1:18" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -29597,7 +29604,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="15" thickBot="1">
+    <row r="459" spans="1:18" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -29624,7 +29631,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="15" thickBot="1">
+    <row r="460" spans="1:18" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -29651,7 +29658,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="15" thickBot="1">
+    <row r="461" spans="1:18" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -29681,7 +29688,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="15" thickBot="1">
+    <row r="462" spans="1:18" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -29711,7 +29718,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="15" thickBot="1">
+    <row r="463" spans="1:18" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -29738,7 +29745,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="15" thickBot="1">
+    <row r="464" spans="1:18" ht="15.75" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -29768,7 +29775,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="15" thickBot="1">
+    <row r="465" spans="1:18" ht="15.75" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -29798,7 +29805,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="15" thickBot="1">
+    <row r="466" spans="1:18" ht="15.75" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -29828,7 +29835,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="15" thickBot="1">
+    <row r="467" spans="1:18" ht="15.75" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -29855,7 +29862,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="15" thickBot="1">
+    <row r="468" spans="1:18" ht="15.75" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -29885,7 +29892,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="15" thickBot="1">
+    <row r="469" spans="1:18" ht="15.75" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -29915,7 +29922,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="15" thickBot="1">
+    <row r="470" spans="1:18" ht="15.75" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -29945,7 +29952,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="15" thickBot="1">
+    <row r="471" spans="1:18" ht="15.75" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -29975,7 +29982,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="15" thickBot="1">
+    <row r="472" spans="1:18" ht="15.75" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -30005,7 +30012,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="15" thickBot="1">
+    <row r="473" spans="1:18" ht="15.75" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -30035,7 +30042,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="15" thickBot="1">
+    <row r="474" spans="1:18" ht="15.75" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -30065,7 +30072,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="15" thickBot="1">
+    <row r="475" spans="1:18" ht="15.75" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -30095,7 +30102,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="15" thickBot="1">
+    <row r="476" spans="1:18" ht="15.75" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -30125,7 +30132,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="15" thickBot="1">
+    <row r="477" spans="1:18" ht="15.75" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -30155,7 +30162,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="15" thickBot="1">
+    <row r="478" spans="1:18" ht="15.75" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -30182,7 +30189,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="15" thickBot="1">
+    <row r="479" spans="1:18" ht="15.75" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -30212,7 +30219,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="15" thickBot="1">
+    <row r="480" spans="1:18" ht="15.75" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -30242,7 +30249,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="15" thickBot="1">
+    <row r="481" spans="1:18" ht="15.75" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -30272,7 +30279,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="15" thickBot="1">
+    <row r="482" spans="1:18" ht="15.75" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -30299,7 +30306,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="15" thickBot="1">
+    <row r="483" spans="1:18" ht="15.75" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -30329,7 +30336,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="15" thickBot="1">
+    <row r="484" spans="1:18" ht="15.75" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -30359,7 +30366,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="15" thickBot="1">
+    <row r="485" spans="1:18" ht="15.75" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -30386,7 +30393,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="15" thickBot="1">
+    <row r="486" spans="1:18" ht="15.75" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -30413,7 +30420,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="15" thickBot="1">
+    <row r="487" spans="1:18" ht="15.75" thickBot="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14"/>
@@ -30440,7 +30447,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="15" thickBot="1">
+    <row r="488" spans="1:18" ht="15.75" thickBot="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14"/>
@@ -30467,7 +30474,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="15" thickBot="1">
+    <row r="489" spans="1:18" ht="15.75" thickBot="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14"/>
@@ -30497,7 +30504,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="15" thickBot="1">
+    <row r="490" spans="1:18" ht="15.75" thickBot="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14"/>
@@ -30524,7 +30531,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="15" thickBot="1">
+    <row r="491" spans="1:18" ht="15.75" thickBot="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14"/>
@@ -30551,7 +30558,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="15" thickBot="1">
+    <row r="492" spans="1:18" ht="15.75" thickBot="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14"/>
@@ -31110,7 +31117,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="15.5">
+    <row r="512" spans="1:18" ht="15.75">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -31519,7 +31526,7 @@
       <c r="Q529" s="37"/>
       <c r="R529" s="14"/>
     </row>
-    <row r="530" spans="1:18" ht="15.5">
+    <row r="530" spans="1:18" ht="15.75">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -31545,7 +31552,7 @@
       </c>
       <c r="R530" s="5"/>
     </row>
-    <row r="531" spans="1:18" ht="15.5">
+    <row r="531" spans="1:18" ht="15.75">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -31631,7 +31638,7 @@
       <c r="Q534" s="4"/>
       <c r="R534" s="3"/>
     </row>
-    <row r="535" spans="1:18" ht="15.5">
+    <row r="535" spans="1:18" ht="15.75">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -31651,7 +31658,7 @@
       <c r="Q535" s="4"/>
       <c r="R535" s="5"/>
     </row>
-    <row r="536" spans="1:18" ht="15.5">
+    <row r="536" spans="1:18" ht="15.75">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -31671,7 +31678,7 @@
       <c r="Q536" s="4"/>
       <c r="R536" s="5"/>
     </row>
-    <row r="537" spans="1:18" ht="15.5">
+    <row r="537" spans="1:18" ht="15.75">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -31803,7 +31810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:18">
+    <row r="542" spans="1:18" ht="26.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -31831,7 +31838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="26">
+    <row r="543" spans="1:18" ht="26.25">
       <c r="A543" s="7"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
@@ -31887,7 +31894,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="25" customHeight="1">
+    <row r="545" spans="1:18" ht="24.95" customHeight="1">
       <c r="A545" s="12"/>
       <c r="B545" s="12"/>
       <c r="C545" s="12"/>
@@ -32265,7 +32272,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="51">
+    <row r="562" spans="1:18" ht="51.75">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -32291,7 +32298,7 @@
       </c>
       <c r="R562" s="5"/>
     </row>
-    <row r="563" spans="1:18">
+    <row r="563" spans="1:18" ht="26.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -32319,7 +32326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="564" spans="1:18">
+    <row r="564" spans="1:18" ht="26.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -32347,7 +32354,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="26">
+    <row r="565" spans="1:18" ht="26.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -32519,7 +32526,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="15.5">
+    <row r="572" spans="1:18" ht="15.75">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -32545,7 +32552,7 @@
       </c>
       <c r="R572" s="5"/>
     </row>
-    <row r="573" spans="1:18" ht="15.5">
+    <row r="573" spans="1:18" ht="15.75">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -32571,7 +32578,7 @@
       </c>
       <c r="R573" s="5"/>
     </row>
-    <row r="574" spans="1:18" ht="15.5">
+    <row r="574" spans="1:18" ht="15.75">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -32597,7 +32604,7 @@
       </c>
       <c r="R574" s="5"/>
     </row>
-    <row r="575" spans="1:18" ht="15.5">
+    <row r="575" spans="1:18" ht="15.75">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -32623,7 +32630,7 @@
       </c>
       <c r="R575" s="5"/>
     </row>
-    <row r="576" spans="1:18" ht="15.5">
+    <row r="576" spans="1:18" ht="15.75">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -32649,7 +32656,7 @@
       </c>
       <c r="R576" s="5"/>
     </row>
-    <row r="577" spans="1:18" ht="15.5">
+    <row r="577" spans="1:18" ht="15.75">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -32675,7 +32682,7 @@
       </c>
       <c r="R577" s="5"/>
     </row>
-    <row r="578" spans="1:18" ht="15.5">
+    <row r="578" spans="1:18" ht="15.75">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -32701,7 +32708,7 @@
       </c>
       <c r="R578" s="5"/>
     </row>
-    <row r="579" spans="1:18" ht="15.5">
+    <row r="579" spans="1:18" ht="15.75">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -32807,7 +32814,7 @@
       <c r="Q584" s="8"/>
       <c r="R584" s="3"/>
     </row>
-    <row r="587" spans="1:18" ht="15.5">
+    <row r="587" spans="1:18" ht="15.75">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -32833,7 +32840,7 @@
       </c>
       <c r="R587" s="5"/>
     </row>
-    <row r="588" spans="1:18" ht="15.5">
+    <row r="588" spans="1:18" ht="15.75">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -32859,7 +32866,7 @@
       </c>
       <c r="R588" s="5"/>
     </row>
-    <row r="589" spans="1:18" ht="15.5">
+    <row r="589" spans="1:18" ht="15.75">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -32885,7 +32892,7 @@
       </c>
       <c r="R589" s="5"/>
     </row>
-    <row r="592" spans="1:18" ht="15.5">
+    <row r="592" spans="1:18" ht="15.75">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -32911,7 +32918,7 @@
       </c>
       <c r="R592" s="5"/>
     </row>
-    <row r="593" spans="1:18" ht="15.5">
+    <row r="593" spans="1:18" ht="15.75">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -32937,7 +32944,7 @@
       </c>
       <c r="R593" s="5"/>
     </row>
-    <row r="594" spans="1:18" ht="15.5">
+    <row r="594" spans="1:18" ht="15.75">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -33047,7 +33054,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="15.5">
+    <row r="600" spans="1:18" ht="15.75">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -33073,7 +33080,7 @@
       </c>
       <c r="R600" s="5"/>
     </row>
-    <row r="601" spans="1:18" ht="15.5">
+    <row r="601" spans="1:18" ht="15.75">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -33099,7 +33106,7 @@
       </c>
       <c r="R601" s="5"/>
     </row>
-    <row r="602" spans="1:18" ht="15.5">
+    <row r="602" spans="1:18" ht="15.75">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -33321,11 +33328,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
   <dimension ref="A1:H633"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="36.453125" customWidth="1"/>
+    <col min="1" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="87" style="10" customWidth="1"/>
   </cols>
@@ -33374,7 +33381,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.5">
+    <row r="3" spans="1:7" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>974</v>
       </c>
@@ -33435,7 +33442,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="15.5">
+    <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="1" t="s">
         <v>974</v>
       </c>
@@ -33479,7 +33486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.5">
+    <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>974</v>
       </c>
@@ -33565,7 +33572,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="14" customHeight="1">
+    <row r="12" spans="1:7" ht="14.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="114" t="s">
         <v>974</v>
@@ -33968,7 +33975,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1">
+    <row r="33" spans="1:8" ht="15.75" thickBot="1">
       <c r="A33" s="1" t="s">
         <v>974</v>
       </c>
@@ -33990,7 +33997,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1">
       <c r="A34" s="1" t="s">
         <v>974</v>
       </c>
@@ -34014,7 +34021,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1">
       <c r="A35" s="1" t="s">
         <v>974</v>
       </c>
@@ -34038,7 +34045,7 @@
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" ht="15" thickBot="1">
+    <row r="36" spans="1:8" ht="15.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="34" t="s">
@@ -34058,7 +34065,7 @@
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="15" thickBot="1">
+    <row r="37" spans="1:8" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="71" t="s">
@@ -34074,7 +34081,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="71" t="s">
@@ -34090,7 +34097,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1">
+    <row r="39" spans="1:8" ht="15.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="71" t="s">
@@ -34106,7 +34113,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="16" thickBot="1">
+    <row r="40" spans="1:8" ht="16.5" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="71" t="s">
@@ -34458,7 +34465,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1">
+    <row r="56" spans="1:7" ht="15.75" thickBot="1">
       <c r="A56" s="60" t="s">
         <v>974</v>
       </c>
@@ -34481,7 +34488,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1">
+    <row r="57" spans="1:7" ht="15.75" thickBot="1">
       <c r="A57" s="60" t="s">
         <v>974</v>
       </c>
@@ -34593,7 +34600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16" thickBot="1">
+    <row r="62" spans="1:7" ht="16.5" thickBot="1">
       <c r="A62" s="60" t="s">
         <v>974</v>
       </c>
@@ -34616,7 +34623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16" thickBot="1">
+    <row r="63" spans="1:7" ht="16.5" thickBot="1">
       <c r="A63" s="60" t="s">
         <v>974</v>
       </c>
@@ -34729,7 +34736,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.5">
+    <row r="68" spans="1:7" ht="15.75">
       <c r="A68" s="60" t="s">
         <v>974</v>
       </c>
@@ -34752,7 +34759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.5">
+    <row r="69" spans="1:7" ht="15.75">
       <c r="A69" s="60" t="s">
         <v>974</v>
       </c>
@@ -34789,7 +34796,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.5">
+    <row r="71" spans="1:7" ht="15.75">
       <c r="A71" s="60" t="s">
         <v>974</v>
       </c>
@@ -34978,7 +34985,7 @@
       <c r="F79"/>
       <c r="G79" s="31"/>
     </row>
-    <row r="80" spans="1:7" ht="16">
+    <row r="80" spans="1:7" ht="16.5">
       <c r="A80" s="60" t="s">
         <v>974</v>
       </c>
@@ -35024,7 +35031,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.5">
+    <row r="82" spans="1:7" ht="15.75">
       <c r="A82" s="60" t="s">
         <v>974</v>
       </c>
@@ -35085,7 +35092,7 @@
       <c r="F84"/>
       <c r="G84" s="31"/>
     </row>
-    <row r="85" spans="1:7" ht="15.5">
+    <row r="85" spans="1:7" ht="15.75">
       <c r="A85" s="60" t="s">
         <v>974</v>
       </c>
@@ -35106,7 +35113,7 @@
       </c>
       <c r="G85" s="5"/>
     </row>
-    <row r="86" spans="1:7" ht="15.5">
+    <row r="86" spans="1:7" ht="15.75">
       <c r="A86" s="60" t="s">
         <v>974</v>
       </c>
@@ -35150,7 +35157,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.5">
+    <row r="88" spans="1:7" ht="15.75">
       <c r="A88" s="60" t="s">
         <v>974</v>
       </c>
@@ -35171,7 +35178,7 @@
       </c>
       <c r="G88" s="5"/>
     </row>
-    <row r="89" spans="1:7" ht="15.5">
+    <row r="89" spans="1:7" ht="15.75">
       <c r="A89" s="60"/>
       <c r="B89" s="114"/>
       <c r="C89" s="70"/>
@@ -35303,7 +35310,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15" thickBot="1">
+    <row r="97" spans="1:7" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -35314,7 +35321,7 @@
       <c r="F97"/>
       <c r="G97" s="31"/>
     </row>
-    <row r="98" spans="1:7" ht="15" thickBot="1">
+    <row r="98" spans="1:7" ht="15.75" thickBot="1">
       <c r="A98" s="60" t="s">
         <v>974</v>
       </c>
@@ -35333,7 +35340,7 @@
       <c r="F98"/>
       <c r="G98" s="31"/>
     </row>
-    <row r="99" spans="1:7" ht="16" thickBot="1">
+    <row r="99" spans="1:7" ht="16.5" thickBot="1">
       <c r="A99" s="60" t="s">
         <v>974</v>
       </c>
@@ -35356,7 +35363,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15" thickBot="1">
+    <row r="100" spans="1:7" ht="15.75" thickBot="1">
       <c r="A100" s="60" t="s">
         <v>974</v>
       </c>
@@ -35376,7 +35383,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15" thickBot="1">
+    <row r="101" spans="1:7" ht="15.75" thickBot="1">
       <c r="A101" s="60" t="s">
         <v>974</v>
       </c>
@@ -35396,7 +35403,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15" thickBot="1">
+    <row r="102" spans="1:7" ht="15.75" thickBot="1">
       <c r="A102" s="60" t="s">
         <v>974</v>
       </c>
@@ -35416,7 +35423,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="16" thickBot="1">
+    <row r="103" spans="1:7" ht="16.5" thickBot="1">
       <c r="A103" s="60" t="s">
         <v>974</v>
       </c>
@@ -35437,7 +35444,7 @@
       </c>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7" ht="15" thickBot="1">
+    <row r="104" spans="1:7" ht="15.75" thickBot="1">
       <c r="A104" s="60" t="s">
         <v>974</v>
       </c>
@@ -35457,7 +35464,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15" thickBot="1">
+    <row r="105" spans="1:7" ht="15.75" thickBot="1">
       <c r="A105" s="60" t="s">
         <v>974</v>
       </c>
@@ -35475,7 +35482,7 @@
       </c>
       <c r="F105"/>
     </row>
-    <row r="106" spans="1:7" ht="15" thickBot="1">
+    <row r="106" spans="1:7" ht="15.75" thickBot="1">
       <c r="A106" s="60" t="s">
         <v>974</v>
       </c>
@@ -35498,7 +35505,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15" thickBot="1">
+    <row r="107" spans="1:7" ht="15.75" thickBot="1">
       <c r="A107" s="60" t="s">
         <v>974</v>
       </c>
@@ -35521,7 +35528,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15" thickBot="1">
+    <row r="108" spans="1:7" ht="15.75" thickBot="1">
       <c r="A108" s="60" t="s">
         <v>974</v>
       </c>
@@ -35544,7 +35551,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16" thickBot="1">
+    <row r="109" spans="1:7" ht="16.5" thickBot="1">
       <c r="A109" s="60" t="s">
         <v>974</v>
       </c>
@@ -35567,7 +35574,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16" thickBot="1">
+    <row r="110" spans="1:7" ht="16.5" thickBot="1">
       <c r="A110" s="60" t="s">
         <v>974</v>
       </c>
@@ -35590,7 +35597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15" thickBot="1">
+    <row r="111" spans="1:7" ht="15.75" thickBot="1">
       <c r="A111" s="60" t="s">
         <v>974</v>
       </c>
@@ -35652,7 +35659,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.5">
+    <row r="114" spans="1:7" ht="15.75">
       <c r="A114" s="60" t="s">
         <v>974</v>
       </c>
@@ -35673,7 +35680,7 @@
       </c>
       <c r="G114" s="5"/>
     </row>
-    <row r="115" spans="1:7" ht="15.5">
+    <row r="115" spans="1:7" ht="15.75">
       <c r="A115" s="60" t="s">
         <v>974</v>
       </c>
@@ -35694,7 +35701,7 @@
       </c>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7" ht="15.5">
+    <row r="116" spans="1:7" ht="15.75">
       <c r="A116" s="60" t="s">
         <v>974</v>
       </c>
@@ -35717,7 +35724,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.5">
+    <row r="117" spans="1:7" ht="15.75">
       <c r="A117" s="60" t="s">
         <v>974</v>
       </c>
@@ -35757,7 +35764,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.5">
+    <row r="119" spans="1:7" ht="15.75">
       <c r="A119" s="60" t="s">
         <v>974</v>
       </c>
@@ -35780,7 +35787,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.5">
+    <row r="120" spans="1:7" ht="15.75">
       <c r="A120" s="60" t="s">
         <v>974</v>
       </c>
@@ -35844,7 +35851,7 @@
       </c>
       <c r="F122"/>
     </row>
-    <row r="123" spans="1:7" ht="15.5">
+    <row r="123" spans="1:7" ht="15.75">
       <c r="A123" s="60" t="s">
         <v>974</v>
       </c>
@@ -35954,7 +35961,7 @@
       </c>
       <c r="F127"/>
     </row>
-    <row r="128" spans="1:7" ht="16">
+    <row r="128" spans="1:7" ht="16.5">
       <c r="A128" s="60" t="s">
         <v>974</v>
       </c>
@@ -36023,7 +36030,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15" thickBot="1">
+    <row r="131" spans="1:7" ht="15.75" thickBot="1">
       <c r="A131" s="60" t="s">
         <v>974</v>
       </c>
@@ -36046,7 +36053,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15" thickBot="1">
+    <row r="132" spans="1:7" ht="15.75" thickBot="1">
       <c r="A132" s="60" t="s">
         <v>974</v>
       </c>
@@ -36062,7 +36069,7 @@
       <c r="E132" s="3"/>
       <c r="F132"/>
     </row>
-    <row r="133" spans="1:7" ht="15" thickBot="1">
+    <row r="133" spans="1:7" ht="15.75" thickBot="1">
       <c r="A133" s="60" t="s">
         <v>974</v>
       </c>
@@ -36085,7 +36092,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15" thickBot="1">
+    <row r="134" spans="1:7" ht="15.75" thickBot="1">
       <c r="A134" s="60" t="s">
         <v>974</v>
       </c>
@@ -36108,7 +36115,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="16.5" thickBot="1">
+    <row r="135" spans="1:7" ht="17.25" thickBot="1">
       <c r="A135" s="60" t="s">
         <v>974</v>
       </c>
@@ -36131,7 +36138,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="16.5" thickBot="1">
+    <row r="136" spans="1:7" ht="17.25" thickBot="1">
       <c r="A136" s="60" t="s">
         <v>974</v>
       </c>
@@ -36154,7 +36161,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="16.5" thickBot="1">
+    <row r="137" spans="1:7" ht="17.25" thickBot="1">
       <c r="A137" s="60" t="s">
         <v>974</v>
       </c>
@@ -36177,7 +36184,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="16.5" thickBot="1">
+    <row r="138" spans="1:7" ht="17.25" thickBot="1">
       <c r="A138" s="60" t="s">
         <v>974</v>
       </c>
@@ -36200,7 +36207,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="16.5" thickBot="1">
+    <row r="139" spans="1:7" ht="17.25" thickBot="1">
       <c r="A139" s="60" t="s">
         <v>974</v>
       </c>
@@ -36223,7 +36230,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="16.5" thickBot="1">
+    <row r="140" spans="1:7" ht="17.25" thickBot="1">
       <c r="A140" s="60" t="s">
         <v>974</v>
       </c>
@@ -36246,7 +36253,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15" thickBot="1">
+    <row r="141" spans="1:7" ht="15.75" thickBot="1">
       <c r="A141" s="60" t="s">
         <v>974</v>
       </c>
@@ -36266,7 +36273,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="16.5" thickBot="1">
+    <row r="142" spans="1:7" ht="17.25" thickBot="1">
       <c r="A142" s="60" t="s">
         <v>974</v>
       </c>
@@ -36289,7 +36296,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="16.5" thickBot="1">
+    <row r="143" spans="1:7" ht="17.25" thickBot="1">
       <c r="A143" s="60" t="s">
         <v>974</v>
       </c>
@@ -36312,7 +36319,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="16.5" thickBot="1">
+    <row r="144" spans="1:7" ht="17.25" thickBot="1">
       <c r="A144" s="60" t="s">
         <v>974</v>
       </c>
@@ -36335,7 +36342,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="16.5" thickBot="1">
+    <row r="145" spans="1:7" ht="17.25" thickBot="1">
       <c r="A145" s="60" t="s">
         <v>974</v>
       </c>
@@ -36358,7 +36365,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15" thickBot="1">
+    <row r="146" spans="1:7" ht="15.75" thickBot="1">
       <c r="A146" s="60" t="s">
         <v>974</v>
       </c>
@@ -36379,7 +36386,7 @@
       </c>
       <c r="G146" s="41"/>
     </row>
-    <row r="147" spans="1:7" ht="15" thickBot="1">
+    <row r="147" spans="1:7" ht="15.75" thickBot="1">
       <c r="A147" s="60" t="s">
         <v>974</v>
       </c>
@@ -36396,7 +36403,7 @@
       <c r="F147"/>
       <c r="G147" s="41"/>
     </row>
-    <row r="148" spans="1:7" ht="15" thickBot="1">
+    <row r="148" spans="1:7" ht="15.75" thickBot="1">
       <c r="A148" s="60" t="s">
         <v>974</v>
       </c>
@@ -36419,7 +36426,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15" thickBot="1">
+    <row r="149" spans="1:7" ht="15.75" thickBot="1">
       <c r="A149" s="60" t="s">
         <v>974</v>
       </c>
@@ -36439,7 +36446,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="16.5" thickBot="1">
+    <row r="150" spans="1:7" ht="17.25" thickBot="1">
       <c r="A150" s="60" t="s">
         <v>974</v>
       </c>
@@ -36462,7 +36469,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="16.5" thickBot="1">
+    <row r="151" spans="1:7" ht="17.25" thickBot="1">
       <c r="A151" s="60" t="s">
         <v>974</v>
       </c>
@@ -36485,7 +36492,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="16.5" thickBot="1">
+    <row r="152" spans="1:7" ht="17.25" thickBot="1">
       <c r="A152" s="60" t="s">
         <v>974</v>
       </c>
@@ -36508,7 +36515,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="16.5" thickBot="1">
+    <row r="153" spans="1:7" ht="17.25" thickBot="1">
       <c r="A153" s="60" t="s">
         <v>974</v>
       </c>
@@ -36531,7 +36538,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="16.5" thickBot="1">
+    <row r="154" spans="1:7" ht="17.25" thickBot="1">
       <c r="A154" s="60" t="s">
         <v>974</v>
       </c>
@@ -36554,7 +36561,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="16.5" thickBot="1">
+    <row r="155" spans="1:7" ht="17.25" thickBot="1">
       <c r="A155" s="60" t="s">
         <v>974</v>
       </c>
@@ -36577,7 +36584,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15" thickBot="1">
+    <row r="156" spans="1:7" ht="15.75" thickBot="1">
       <c r="A156" s="60" t="s">
         <v>974</v>
       </c>
@@ -36600,7 +36607,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="16.5" thickBot="1">
+    <row r="157" spans="1:7" ht="17.25" thickBot="1">
       <c r="A157" s="60" t="s">
         <v>974</v>
       </c>
@@ -36623,7 +36630,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="16.5" thickBot="1">
+    <row r="158" spans="1:7" ht="17.25" thickBot="1">
       <c r="A158" s="60" t="s">
         <v>974</v>
       </c>
@@ -36646,7 +36653,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="16.5" thickBot="1">
+    <row r="159" spans="1:7" ht="17.25" thickBot="1">
       <c r="A159" s="60" t="s">
         <v>974</v>
       </c>
@@ -36669,7 +36676,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="16.5" thickBot="1">
+    <row r="160" spans="1:7" ht="17.25" thickBot="1">
       <c r="A160" s="60" t="s">
         <v>974</v>
       </c>
@@ -36692,7 +36699,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15" thickBot="1">
+    <row r="161" spans="1:7" ht="15.75" thickBot="1">
       <c r="A161" s="60" t="s">
         <v>974</v>
       </c>
@@ -36713,7 +36720,7 @@
       </c>
       <c r="G161" s="41"/>
     </row>
-    <row r="162" spans="1:7" ht="15" thickBot="1">
+    <row r="162" spans="1:7" ht="15.75" thickBot="1">
       <c r="A162" s="60" t="s">
         <v>974</v>
       </c>
@@ -36734,7 +36741,7 @@
       </c>
       <c r="G162" s="41"/>
     </row>
-    <row r="163" spans="1:7" ht="15" thickBot="1">
+    <row r="163" spans="1:7" ht="15.75" thickBot="1">
       <c r="A163" s="60" t="s">
         <v>974</v>
       </c>
@@ -36757,7 +36764,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15" thickBot="1">
+    <row r="164" spans="1:7" ht="15.75" thickBot="1">
       <c r="A164" s="60" t="s">
         <v>974</v>
       </c>
@@ -36780,7 +36787,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15" thickBot="1">
+    <row r="165" spans="1:7" ht="15.75" thickBot="1">
       <c r="A165" s="60" t="s">
         <v>974</v>
       </c>
@@ -36800,7 +36807,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15" thickBot="1">
+    <row r="166" spans="1:7" ht="15.75" thickBot="1">
       <c r="A166" s="60" t="s">
         <v>974</v>
       </c>
@@ -36823,7 +36830,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15" thickBot="1">
+    <row r="167" spans="1:7" ht="15.75" thickBot="1">
       <c r="A167" s="60" t="s">
         <v>974</v>
       </c>
@@ -36846,7 +36853,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15" thickBot="1">
+    <row r="168" spans="1:7" ht="15.75" thickBot="1">
       <c r="A168" s="1"/>
       <c r="B168" s="114" t="s">
         <v>974</v>
@@ -36862,7 +36869,7 @@
       </c>
       <c r="F168"/>
     </row>
-    <row r="169" spans="1:7" ht="15" thickBot="1">
+    <row r="169" spans="1:7" ht="15.75" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="121" t="s">
         <v>1509</v>
@@ -36883,7 +36890,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="16.5" thickBot="1">
+    <row r="170" spans="1:7" ht="17.25" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="114" t="s">
         <v>974</v>
@@ -36904,7 +36911,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15" thickBot="1">
+    <row r="171" spans="1:7" ht="15.75" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="114" t="s">
         <v>974</v>
@@ -36918,7 +36925,7 @@
       <c r="E171" s="17"/>
       <c r="F171"/>
     </row>
-    <row r="172" spans="1:7" ht="15" thickBot="1">
+    <row r="172" spans="1:7" ht="15.75" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="121" t="s">
         <v>1509</v>
@@ -36939,7 +36946,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="16.5" thickBot="1">
+    <row r="173" spans="1:7" ht="17.25" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="114" t="s">
         <v>974</v>
@@ -36960,7 +36967,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15" thickBot="1">
+    <row r="174" spans="1:7" ht="15.75" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="114" t="s">
         <v>974</v>
@@ -36974,7 +36981,7 @@
       <c r="E174" s="17"/>
       <c r="F174"/>
     </row>
-    <row r="175" spans="1:7" ht="15" thickBot="1">
+    <row r="175" spans="1:7" ht="15.75" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="114" t="s">
         <v>974</v>
@@ -36995,7 +37002,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15" thickBot="1">
+    <row r="176" spans="1:7" ht="15.75" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="114" t="s">
         <v>974</v>
@@ -37014,7 +37021,7 @@
       </c>
       <c r="G176" s="69"/>
     </row>
-    <row r="177" spans="1:7" ht="15" thickBot="1">
+    <row r="177" spans="1:7" ht="15.75" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="114" t="s">
         <v>974</v>
@@ -37033,7 +37040,7 @@
       </c>
       <c r="G177" s="43"/>
     </row>
-    <row r="178" spans="1:7" ht="15" thickBot="1">
+    <row r="178" spans="1:7" ht="15.75" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="114" t="s">
         <v>974</v>
@@ -37052,7 +37059,7 @@
       </c>
       <c r="G178" s="44"/>
     </row>
-    <row r="179" spans="1:7" ht="15" thickBot="1">
+    <row r="179" spans="1:7" ht="15.75" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="114" t="s">
         <v>974</v>
@@ -37071,7 +37078,7 @@
       </c>
       <c r="G179" s="44"/>
     </row>
-    <row r="180" spans="1:7" ht="15" thickBot="1">
+    <row r="180" spans="1:7" ht="15.75" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="114" t="s">
         <v>974</v>
@@ -37089,7 +37096,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15" thickBot="1">
+    <row r="181" spans="1:7" ht="15.75" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="114" t="s">
         <v>974</v>
@@ -37107,7 +37114,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15" thickBot="1">
+    <row r="182" spans="1:7" ht="15.75" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="114" t="s">
         <v>974</v>
@@ -37128,7 +37135,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15" thickBot="1">
+    <row r="183" spans="1:7" ht="15.75" thickBot="1">
       <c r="A183" s="108"/>
       <c r="B183" s="114" t="s">
         <v>974</v>
@@ -37146,7 +37153,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15" thickBot="1">
+    <row r="184" spans="1:7" ht="15.75" thickBot="1">
       <c r="A184" s="1"/>
       <c r="B184" s="114" t="s">
         <v>974</v>
@@ -37164,7 +37171,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15" thickBot="1">
+    <row r="185" spans="1:7" ht="15.75" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="114" t="s">
         <v>974</v>
@@ -37180,7 +37187,7 @@
       </c>
       <c r="F185"/>
     </row>
-    <row r="186" spans="1:7" ht="15" thickBot="1">
+    <row r="186" spans="1:7" ht="15.75" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="114" t="s">
         <v>974</v>
@@ -37201,7 +37208,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15" thickBot="1">
+    <row r="187" spans="1:7" ht="15.75" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="114" t="s">
         <v>974</v>
@@ -37220,7 +37227,7 @@
       </c>
       <c r="G187" s="73"/>
     </row>
-    <row r="188" spans="1:7" ht="15" thickBot="1">
+    <row r="188" spans="1:7" ht="15.75" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="114" t="s">
         <v>974</v>
@@ -37241,7 +37248,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15" thickBot="1">
+    <row r="189" spans="1:7" ht="15.75" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="114" t="s">
         <v>974</v>
@@ -37262,7 +37269,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15" thickBot="1">
+    <row r="190" spans="1:7" ht="15.75" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="114" t="s">
         <v>974</v>
@@ -37283,7 +37290,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15" thickBot="1">
+    <row r="191" spans="1:7" ht="15.75" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="114" t="s">
         <v>974</v>
@@ -37301,7 +37308,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15" thickBot="1">
+    <row r="192" spans="1:7" ht="15.75" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="114" t="s">
         <v>974</v>
@@ -37322,7 +37329,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15" thickBot="1">
+    <row r="193" spans="1:7" ht="15.75" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="114" t="s">
         <v>974</v>
@@ -37343,7 +37350,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15" thickBot="1">
+    <row r="194" spans="1:7" ht="15.75" thickBot="1">
       <c r="A194" s="108"/>
       <c r="B194" s="114" t="s">
         <v>974</v>
@@ -37364,7 +37371,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15" thickBot="1">
+    <row r="195" spans="1:7" ht="15.75" thickBot="1">
       <c r="A195" s="1"/>
       <c r="B195" s="114" t="s">
         <v>974</v>
@@ -37385,7 +37392,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15" thickBot="1">
+    <row r="196" spans="1:7" ht="15.75" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="114" t="s">
         <v>974</v>
@@ -37401,7 +37408,7 @@
       </c>
       <c r="G196" s="41"/>
     </row>
-    <row r="197" spans="1:7" ht="15" thickBot="1">
+    <row r="197" spans="1:7" ht="15.75" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="114" t="s">
         <v>974</v>
@@ -37422,7 +37429,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15" thickBot="1">
+    <row r="198" spans="1:7" ht="15.75" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="114" t="s">
         <v>974</v>
@@ -37443,7 +37450,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15" thickBot="1">
+    <row r="199" spans="1:7" ht="15.75" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="114" t="s">
         <v>974</v>
@@ -37460,7 +37467,7 @@
       <c r="F199"/>
       <c r="G199" s="29"/>
     </row>
-    <row r="200" spans="1:7" ht="15" thickBot="1">
+    <row r="200" spans="1:7" ht="15.75" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="114" t="s">
         <v>974</v>
@@ -37481,7 +37488,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1">
+    <row r="201" spans="1:7" ht="15.75" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="114" t="s">
         <v>974</v>
@@ -37502,7 +37509,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15" thickBot="1">
+    <row r="202" spans="1:7" ht="15.75" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="114" t="s">
         <v>974</v>
@@ -37518,7 +37525,7 @@
       </c>
       <c r="F202"/>
     </row>
-    <row r="203" spans="1:7" ht="15" thickBot="1">
+    <row r="203" spans="1:7" ht="15.75" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="114" t="s">
         <v>974</v>
@@ -37536,7 +37543,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15" thickBot="1">
+    <row r="204" spans="1:7" ht="15.75" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="114" t="s">
         <v>974</v>
@@ -37552,7 +37559,7 @@
       </c>
       <c r="F204"/>
     </row>
-    <row r="205" spans="1:7" ht="15" thickBot="1">
+    <row r="205" spans="1:7" ht="15.75" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="114" t="s">
         <v>974</v>
@@ -37573,7 +37580,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15" thickBot="1">
+    <row r="206" spans="1:7" ht="15.75" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="114" t="s">
         <v>974</v>
@@ -37591,7 +37598,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15" thickBot="1">
+    <row r="207" spans="1:7" ht="15.75" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="114" t="s">
         <v>974</v>
@@ -37612,7 +37619,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15" thickBot="1">
+    <row r="208" spans="1:7" ht="15.75" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="114" t="s">
         <v>974</v>
@@ -37633,7 +37640,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15" thickBot="1">
+    <row r="209" spans="1:7" ht="15.75" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="114" t="s">
         <v>974</v>
@@ -37649,7 +37656,7 @@
       </c>
       <c r="F209"/>
     </row>
-    <row r="210" spans="1:7" ht="15" thickBot="1">
+    <row r="210" spans="1:7" ht="15.75" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="114" t="s">
         <v>974</v>
@@ -37667,7 +37674,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15" thickBot="1">
+    <row r="211" spans="1:7" ht="15.75" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="114" t="s">
         <v>974</v>
@@ -37683,7 +37690,7 @@
       </c>
       <c r="F211"/>
     </row>
-    <row r="212" spans="1:7" ht="15" thickBot="1">
+    <row r="212" spans="1:7" ht="15.75" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="114" t="s">
         <v>974</v>
@@ -37704,7 +37711,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15" thickBot="1">
+    <row r="213" spans="1:7" ht="15.75" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="114" t="s">
         <v>974</v>
@@ -37722,7 +37729,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15" thickBot="1">
+    <row r="214" spans="1:7" ht="15.75" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="114" t="s">
         <v>974</v>
@@ -37743,7 +37750,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15" thickBot="1">
+    <row r="215" spans="1:7" ht="15.75" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="114" t="s">
         <v>974</v>
@@ -37761,7 +37768,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15" thickBot="1">
+    <row r="216" spans="1:7" ht="15.75" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="114" t="s">
         <v>974</v>
@@ -37775,7 +37782,7 @@
       <c r="E216" s="17"/>
       <c r="F216"/>
     </row>
-    <row r="217" spans="1:7" ht="15" thickBot="1">
+    <row r="217" spans="1:7" ht="15.75" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="114" t="s">
         <v>974</v>
@@ -37793,7 +37800,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15" thickBot="1">
+    <row r="218" spans="1:7" ht="15.75" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="114" t="s">
         <v>974</v>
@@ -37807,7 +37814,7 @@
       <c r="E218" s="17"/>
       <c r="F218"/>
     </row>
-    <row r="219" spans="1:7" ht="15" thickBot="1">
+    <row r="219" spans="1:7" ht="15.75" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="114" t="s">
         <v>974</v>
@@ -37825,7 +37832,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15" thickBot="1">
+    <row r="220" spans="1:7" ht="15.75" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="71" t="s">
@@ -37839,7 +37846,7 @@
       </c>
       <c r="F220"/>
     </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1">
+    <row r="221" spans="1:7" ht="15.75" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="71" t="s">
@@ -37855,7 +37862,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1">
+    <row r="222" spans="1:7" ht="15.75" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="71" t="s">
@@ -37874,7 +37881,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15" thickBot="1">
+    <row r="223" spans="1:7" ht="15.75" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="71" t="s">
@@ -37890,7 +37897,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15" thickBot="1">
+    <row r="224" spans="1:7" ht="15.75" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="71" t="s">
@@ -37906,7 +37913,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15" thickBot="1">
+    <row r="225" spans="1:7" ht="15.75" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="71" t="s">
@@ -37920,7 +37927,7 @@
       </c>
       <c r="F225"/>
     </row>
-    <row r="226" spans="1:7" ht="15" thickBot="1">
+    <row r="226" spans="1:7" ht="15.75" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="71" t="s">
@@ -37936,7 +37943,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15" thickBot="1">
+    <row r="227" spans="1:7" ht="15.75" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="71" t="s">
@@ -37955,7 +37962,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15" thickBot="1">
+    <row r="228" spans="1:7" ht="15.75" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="71" t="s">
@@ -38119,7 +38126,7 @@
       <c r="E238" s="19"/>
       <c r="F238"/>
     </row>
-    <row r="239" spans="1:7" ht="15" thickBot="1">
+    <row r="239" spans="1:7" ht="15.75" thickBot="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="135" t="s">
@@ -38135,7 +38142,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="15" thickBot="1">
+    <row r="240" spans="1:7" ht="15.75" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="125" t="s">
         <v>1003</v>
@@ -38149,7 +38156,7 @@
       <c r="E240" s="19"/>
       <c r="F240"/>
     </row>
-    <row r="241" spans="1:7" ht="15" thickBot="1">
+    <row r="241" spans="1:7" ht="15.75" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="125" t="s">
         <v>1003</v>
@@ -38163,7 +38170,7 @@
       <c r="E241" s="19"/>
       <c r="F241"/>
     </row>
-    <row r="242" spans="1:7" ht="15" thickBot="1">
+    <row r="242" spans="1:7" ht="15.75" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="125" t="s">
         <v>1003</v>
@@ -38177,7 +38184,7 @@
       <c r="E242" s="19"/>
       <c r="F242"/>
     </row>
-    <row r="243" spans="1:7" ht="15" thickBot="1">
+    <row r="243" spans="1:7" ht="15.75" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="125" t="s">
         <v>1003</v>
@@ -38191,7 +38198,7 @@
       <c r="E243" s="19"/>
       <c r="F243"/>
     </row>
-    <row r="244" spans="1:7" ht="15" thickBot="1">
+    <row r="244" spans="1:7" ht="15.75" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="125" t="s">
         <v>1003</v>
@@ -38205,7 +38212,7 @@
       <c r="E244" s="19"/>
       <c r="F244"/>
     </row>
-    <row r="245" spans="1:7" ht="15" thickBot="1">
+    <row r="245" spans="1:7" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="125" t="s">
         <v>1003</v>
@@ -38219,7 +38226,7 @@
       <c r="E245" s="19"/>
       <c r="F245"/>
     </row>
-    <row r="246" spans="1:7" ht="15" thickBot="1">
+    <row r="246" spans="1:7" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="125" t="s">
         <v>1003</v>
@@ -38233,7 +38240,7 @@
       <c r="E246" s="19"/>
       <c r="F246"/>
     </row>
-    <row r="247" spans="1:7" ht="15" thickBot="1">
+    <row r="247" spans="1:7" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="125" t="s">
         <v>1003</v>
@@ -38247,7 +38254,7 @@
       <c r="E247" s="19"/>
       <c r="F247"/>
     </row>
-    <row r="248" spans="1:7" ht="15" thickBot="1">
+    <row r="248" spans="1:7" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="125" t="s">
         <v>1003</v>
@@ -38261,7 +38268,7 @@
       <c r="E248" s="19"/>
       <c r="F248"/>
     </row>
-    <row r="249" spans="1:7" ht="15" thickBot="1">
+    <row r="249" spans="1:7" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="125" t="s">
         <v>1003</v>
@@ -38275,7 +38282,7 @@
       <c r="E249" s="19"/>
       <c r="F249"/>
     </row>
-    <row r="250" spans="1:7" ht="15" thickBot="1">
+    <row r="250" spans="1:7" ht="15.75" thickBot="1">
       <c r="A250" s="1" t="s">
         <v>1438</v>
       </c>
@@ -38295,7 +38302,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="15" thickBot="1">
+    <row r="251" spans="1:7" ht="15.75" thickBot="1">
       <c r="A251" s="1" t="s">
         <v>1438</v>
       </c>
@@ -38391,7 +38398,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="15" thickBot="1">
+    <row r="257" spans="1:8" ht="15.75" thickBot="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="81" t="s">
@@ -38413,7 +38420,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15" thickBot="1">
+    <row r="258" spans="1:8" ht="15.75" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="81" t="s">
@@ -38486,7 +38493,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="15" thickBot="1">
+    <row r="262" spans="1:8" ht="15.75" thickBot="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="81" t="s">
@@ -38505,7 +38512,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15" thickBot="1">
+    <row r="263" spans="1:8" ht="15.75" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="81" t="s">
@@ -38555,7 +38562,7 @@
       <c r="F265" s="4"/>
       <c r="G265" s="3"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" ht="26.25">
       <c r="A266" s="1" t="s">
         <v>974</v>
       </c>
@@ -39084,7 +39091,7 @@
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1">
+    <row r="300" spans="1:7" ht="15.75" thickBot="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="84" t="s">
@@ -39101,7 +39108,7 @@
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="1:7" ht="15" thickBot="1">
+    <row r="301" spans="1:7" ht="15.75" thickBot="1">
       <c r="A301" s="14"/>
       <c r="B301" s="14"/>
       <c r="C301" s="34" t="s">
@@ -40296,7 +40303,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="15.5">
+    <row r="391" spans="1:7" ht="15.75">
       <c r="A391" s="14"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14" t="s">
@@ -40391,7 +40398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="15.5">
+    <row r="396" spans="1:7" ht="15.75">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14" t="s">
@@ -40426,7 +40433,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="15.5">
+    <row r="398" spans="1:7" ht="15.75">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14" t="s">
@@ -40478,7 +40485,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="15.5">
+    <row r="401" spans="1:7" ht="15.75">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14" t="s">
@@ -40552,7 +40559,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="15.5">
+    <row r="405" spans="1:7" ht="15.75">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14" t="s">
@@ -40626,7 +40633,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15.5">
+    <row r="409" spans="1:7" ht="15.75">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14" t="s">
@@ -40643,7 +40650,7 @@
       </c>
       <c r="G409" s="5"/>
     </row>
-    <row r="410" spans="1:7" ht="15" thickBot="1">
+    <row r="410" spans="1:7" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14" t="s">
@@ -40662,7 +40669,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="15" thickBot="1">
+    <row r="411" spans="1:7" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14" t="s">
@@ -40677,7 +40684,7 @@
       <c r="F411" s="3"/>
       <c r="G411" s="14"/>
     </row>
-    <row r="412" spans="1:7" ht="15" thickBot="1">
+    <row r="412" spans="1:7" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14" t="s">
@@ -40692,7 +40699,7 @@
       <c r="F412" s="3"/>
       <c r="G412" s="14"/>
     </row>
-    <row r="413" spans="1:7" ht="15.5">
+    <row r="413" spans="1:7" ht="15.75">
       <c r="C413" s="14" t="s">
         <v>765</v>
       </c>
@@ -40762,7 +40769,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="15.5">
+    <row r="417" spans="1:7" ht="15.75">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14" t="s">
@@ -40819,7 +40826,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="15" thickBot="1">
+    <row r="420" spans="1:7" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14" t="s">
@@ -40838,7 +40845,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15" thickBot="1">
+    <row r="421" spans="1:7" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14" t="s">
@@ -40857,7 +40864,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15" thickBot="1">
+    <row r="422" spans="1:7" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14" t="s">
@@ -40876,7 +40883,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15" thickBot="1">
+    <row r="423" spans="1:7" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14" t="s">
@@ -40895,7 +40902,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15" thickBot="1">
+    <row r="424" spans="1:7" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14" t="s">
@@ -40914,7 +40921,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15" thickBot="1">
+    <row r="425" spans="1:7" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14" t="s">
@@ -40933,7 +40940,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="15" thickBot="1">
+    <row r="426" spans="1:7" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14" t="s">
@@ -40952,7 +40959,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="15" thickBot="1">
+    <row r="427" spans="1:7" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14" t="s">
@@ -40971,7 +40978,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="15" thickBot="1">
+    <row r="428" spans="1:7" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14" t="s">
@@ -40990,7 +40997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15" thickBot="1">
+    <row r="429" spans="1:7" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14" t="s">
@@ -41009,7 +41016,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15" thickBot="1">
+    <row r="430" spans="1:7" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14" t="s">
@@ -41028,7 +41035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15" thickBot="1">
+    <row r="431" spans="1:7" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14" t="s">
@@ -41047,7 +41054,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15" thickBot="1">
+    <row r="432" spans="1:7" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14" t="s">
@@ -41063,7 +41070,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15" thickBot="1">
+    <row r="433" spans="1:7" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14" t="s">
@@ -41079,7 +41086,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15" thickBot="1">
+    <row r="434" spans="1:7" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14" t="s">
@@ -41095,7 +41102,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15" thickBot="1">
+    <row r="435" spans="1:7" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14" t="s">
@@ -41111,7 +41118,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15" thickBot="1">
+    <row r="436" spans="1:7" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14" t="s">
@@ -41127,7 +41134,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15" thickBot="1">
+    <row r="437" spans="1:7" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14" t="s">
@@ -41143,7 +41150,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15" thickBot="1">
+    <row r="438" spans="1:7" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14" t="s">
@@ -41159,7 +41166,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15" thickBot="1">
+    <row r="439" spans="1:7" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14" t="s">
@@ -41175,7 +41182,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15" thickBot="1">
+    <row r="440" spans="1:7" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14" t="s">
@@ -41192,7 +41199,7 @@
       </c>
       <c r="G440" s="41"/>
     </row>
-    <row r="441" spans="1:7" ht="15" thickBot="1">
+    <row r="441" spans="1:7" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14" t="s">
@@ -41211,7 +41218,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="15" thickBot="1">
+    <row r="442" spans="1:7" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14" t="s">
@@ -41230,7 +41237,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15" thickBot="1">
+    <row r="443" spans="1:7" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14" t="s">
@@ -41249,7 +41256,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15" thickBot="1">
+    <row r="444" spans="1:7" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14" t="s">
@@ -41268,7 +41275,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15" thickBot="1">
+    <row r="445" spans="1:7" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14" t="s">
@@ -41287,7 +41294,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15" thickBot="1">
+    <row r="446" spans="1:7" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14" t="s">
@@ -41306,7 +41313,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15" thickBot="1">
+    <row r="447" spans="1:7" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14" t="s">
@@ -41325,7 +41332,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15" thickBot="1">
+    <row r="448" spans="1:7" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14" t="s">
@@ -41344,7 +41351,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15" thickBot="1">
+    <row r="449" spans="1:7" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14" t="s">
@@ -41363,7 +41370,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15" thickBot="1">
+    <row r="450" spans="1:7" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14" t="s">
@@ -41382,7 +41389,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15" thickBot="1">
+    <row r="451" spans="1:7" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14" t="s">
@@ -41401,7 +41408,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15" thickBot="1">
+    <row r="452" spans="1:7" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14" t="s">
@@ -41417,7 +41424,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15" thickBot="1">
+    <row r="453" spans="1:7" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14" t="s">
@@ -41433,7 +41440,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15" thickBot="1">
+    <row r="454" spans="1:7" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14" t="s">
@@ -41449,7 +41456,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15" thickBot="1">
+    <row r="455" spans="1:7" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14" t="s">
@@ -41465,7 +41472,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15" thickBot="1">
+    <row r="456" spans="1:7" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14" t="s">
@@ -41481,7 +41488,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15" thickBot="1">
+    <row r="457" spans="1:7" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14" t="s">
@@ -41497,7 +41504,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15" thickBot="1">
+    <row r="458" spans="1:7" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14" t="s">
@@ -41513,7 +41520,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15" thickBot="1">
+    <row r="459" spans="1:7" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14" t="s">
@@ -41529,7 +41536,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15" thickBot="1">
+    <row r="460" spans="1:7" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14" t="s">
@@ -41546,7 +41553,7 @@
       </c>
       <c r="G460" s="41"/>
     </row>
-    <row r="461" spans="1:7" ht="15" thickBot="1">
+    <row r="461" spans="1:7" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14" t="s">
@@ -41565,7 +41572,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="15" thickBot="1">
+    <row r="462" spans="1:7" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14" t="s">
@@ -41584,7 +41591,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15" thickBot="1">
+    <row r="463" spans="1:7" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14" t="s">
@@ -41603,7 +41610,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="15" thickBot="1">
+    <row r="464" spans="1:7" ht="15.75" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14" t="s">
@@ -41622,7 +41629,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="15" thickBot="1">
+    <row r="465" spans="1:7" ht="15.75" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14" t="s">
@@ -41641,7 +41648,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="15" thickBot="1">
+    <row r="466" spans="1:7" ht="15.75" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14" t="s">
@@ -41660,7 +41667,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="15" thickBot="1">
+    <row r="467" spans="1:7" ht="15.75" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14" t="s">
@@ -41679,7 +41686,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="15" thickBot="1">
+    <row r="468" spans="1:7" ht="15.75" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14" t="s">
@@ -41698,7 +41705,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="15" thickBot="1">
+    <row r="469" spans="1:7" ht="15.75" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14" t="s">
@@ -41717,7 +41724,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="15" thickBot="1">
+    <row r="470" spans="1:7" ht="15.75" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14" t="s">
@@ -41733,7 +41740,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="15" thickBot="1">
+    <row r="471" spans="1:7" ht="15.75" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14" t="s">
@@ -41750,7 +41757,7 @@
       </c>
       <c r="G471" s="43"/>
     </row>
-    <row r="472" spans="1:7" ht="15" thickBot="1">
+    <row r="472" spans="1:7" ht="15.75" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14" t="s">
@@ -41767,7 +41774,7 @@
       </c>
       <c r="G472" s="44"/>
     </row>
-    <row r="473" spans="1:7" ht="15" thickBot="1">
+    <row r="473" spans="1:7" ht="15.75" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14" t="s">
@@ -41784,7 +41791,7 @@
       </c>
       <c r="G473" s="44"/>
     </row>
-    <row r="474" spans="1:7" ht="15" thickBot="1">
+    <row r="474" spans="1:7" ht="15.75" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14" t="s">
@@ -41800,7 +41807,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="15" thickBot="1">
+    <row r="475" spans="1:7" ht="15.75" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14" t="s">
@@ -41816,7 +41823,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="15" thickBot="1">
+    <row r="476" spans="1:7" ht="15.75" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14" t="s">
@@ -41832,7 +41839,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="15" thickBot="1">
+    <row r="477" spans="1:7" ht="15.75" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14" t="s">
@@ -41848,7 +41855,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="15" thickBot="1">
+    <row r="478" spans="1:7" ht="15.75" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14" t="s">
@@ -41867,7 +41874,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="15" thickBot="1">
+    <row r="479" spans="1:7" ht="15.75" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14" t="s">
@@ -41886,7 +41893,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="15" thickBot="1">
+    <row r="480" spans="1:7" ht="15.75" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14" t="s">
@@ -41902,7 +41909,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="15" thickBot="1">
+    <row r="481" spans="1:7" ht="15.75" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14" t="s">
@@ -41921,7 +41928,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="15" thickBot="1">
+    <row r="482" spans="1:7" ht="15.75" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14" t="s">
@@ -41940,7 +41947,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15" thickBot="1">
+    <row r="483" spans="1:7" ht="15.75" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14" t="s">
@@ -41959,7 +41966,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="15" thickBot="1">
+    <row r="484" spans="1:7" ht="15.75" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14" t="s">
@@ -41975,7 +41982,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15" thickBot="1">
+    <row r="485" spans="1:7" ht="15.75" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14" t="s">
@@ -41994,7 +42001,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15" thickBot="1">
+    <row r="486" spans="1:7" ht="15.75" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14" t="s">
@@ -42013,7 +42020,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15" thickBot="1">
+    <row r="487" spans="1:7" ht="15.75" thickBot="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14" t="s">
@@ -42032,7 +42039,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15" thickBot="1">
+    <row r="488" spans="1:7" ht="15.75" thickBot="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14" t="s">
@@ -42051,7 +42058,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15" thickBot="1">
+    <row r="489" spans="1:7" ht="15.75" thickBot="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14" t="s">
@@ -42070,7 +42077,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15" thickBot="1">
+    <row r="490" spans="1:7" ht="15.75" thickBot="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14" t="s">
@@ -42089,7 +42096,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15" thickBot="1">
+    <row r="491" spans="1:7" ht="15.75" thickBot="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14" t="s">
@@ -42108,7 +42115,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15" thickBot="1">
+    <row r="492" spans="1:7" ht="15.75" thickBot="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14" t="s">
@@ -42127,7 +42134,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15" thickBot="1">
+    <row r="493" spans="1:7" ht="15.75" thickBot="1">
       <c r="A493" s="14"/>
       <c r="B493" s="14"/>
       <c r="C493" s="14" t="s">
@@ -42146,7 +42153,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15" thickBot="1">
+    <row r="494" spans="1:7" ht="15.75" thickBot="1">
       <c r="A494" s="14"/>
       <c r="B494" s="14"/>
       <c r="C494" s="14" t="s">
@@ -42165,7 +42172,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15" thickBot="1">
+    <row r="495" spans="1:7" ht="15.75" thickBot="1">
       <c r="A495" s="14"/>
       <c r="B495" s="14"/>
       <c r="C495" s="14" t="s">
@@ -42181,7 +42188,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15" thickBot="1">
+    <row r="496" spans="1:7" ht="15.75" thickBot="1">
       <c r="A496" s="14"/>
       <c r="B496" s="14"/>
       <c r="C496" s="14" t="s">
@@ -42200,7 +42207,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15" thickBot="1">
+    <row r="497" spans="1:7" ht="15.75" thickBot="1">
       <c r="A497" s="14"/>
       <c r="B497" s="14"/>
       <c r="C497" s="14" t="s">
@@ -42219,7 +42226,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="15" thickBot="1">
+    <row r="498" spans="1:7" ht="15.75" thickBot="1">
       <c r="A498" s="14"/>
       <c r="B498" s="14"/>
       <c r="C498" s="14" t="s">
@@ -42238,7 +42245,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="15" thickBot="1">
+    <row r="499" spans="1:7" ht="15.75" thickBot="1">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14" t="s">
@@ -42254,7 +42261,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15" thickBot="1">
+    <row r="500" spans="1:7" ht="15.75" thickBot="1">
       <c r="A500" s="14"/>
       <c r="B500" s="14"/>
       <c r="C500" s="14" t="s">
@@ -42273,7 +42280,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15" thickBot="1">
+    <row r="501" spans="1:7" ht="15.75" thickBot="1">
       <c r="A501" s="14"/>
       <c r="B501" s="14"/>
       <c r="C501" s="14" t="s">
@@ -42292,7 +42299,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15" thickBot="1">
+    <row r="502" spans="1:7" ht="15.75" thickBot="1">
       <c r="A502" s="14"/>
       <c r="B502" s="14"/>
       <c r="C502" s="14" t="s">
@@ -42308,7 +42315,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15" thickBot="1">
+    <row r="503" spans="1:7" ht="15.75" thickBot="1">
       <c r="A503" s="14"/>
       <c r="B503" s="14"/>
       <c r="C503" s="14" t="s">
@@ -42324,7 +42331,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15" thickBot="1">
+    <row r="504" spans="1:7" ht="15.75" thickBot="1">
       <c r="A504" s="14"/>
       <c r="B504" s="14"/>
       <c r="C504" s="14" t="s">
@@ -42340,7 +42347,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15" thickBot="1">
+    <row r="505" spans="1:7" ht="15.75" thickBot="1">
       <c r="A505" s="14"/>
       <c r="B505" s="14"/>
       <c r="C505" s="14" t="s">
@@ -42356,7 +42363,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15" thickBot="1">
+    <row r="506" spans="1:7" ht="15.75" thickBot="1">
       <c r="A506" s="14"/>
       <c r="B506" s="14"/>
       <c r="C506" s="14" t="s">
@@ -42375,7 +42382,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15" thickBot="1">
+    <row r="507" spans="1:7" ht="15.75" thickBot="1">
       <c r="A507" s="14"/>
       <c r="B507" s="14"/>
       <c r="C507" s="14" t="s">
@@ -42391,7 +42398,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15" thickBot="1">
+    <row r="508" spans="1:7" ht="15.75" thickBot="1">
       <c r="A508" s="14"/>
       <c r="B508" s="14"/>
       <c r="C508" s="14" t="s">
@@ -42407,7 +42414,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15" thickBot="1">
+    <row r="509" spans="1:7" ht="15.75" thickBot="1">
       <c r="A509" s="14"/>
       <c r="B509" s="14"/>
       <c r="C509" s="14" t="s">
@@ -42746,7 +42753,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="15.5">
+    <row r="529" spans="1:7" ht="15.75">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="16" t="s">
@@ -42968,7 +42975,7 @@
       <c r="F546" s="13"/>
       <c r="G546" s="14"/>
     </row>
-    <row r="547" spans="1:7" ht="15.5">
+    <row r="547" spans="1:7" ht="15.75">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -42983,7 +42990,7 @@
       </c>
       <c r="G547" s="5"/>
     </row>
-    <row r="548" spans="1:7" ht="15.5">
+    <row r="548" spans="1:7" ht="15.75">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -43025,7 +43032,7 @@
       <c r="F551" s="4"/>
       <c r="G551" s="3"/>
     </row>
-    <row r="552" spans="1:7" ht="15.5">
+    <row r="552" spans="1:7" ht="15.75">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -43034,7 +43041,7 @@
       <c r="F552" s="4"/>
       <c r="G552" s="5"/>
     </row>
-    <row r="553" spans="1:7" ht="15.5">
+    <row r="553" spans="1:7" ht="15.75">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -43043,7 +43050,7 @@
       <c r="F553" s="4"/>
       <c r="G553" s="5"/>
     </row>
-    <row r="554" spans="1:7" ht="15.5">
+    <row r="554" spans="1:7" ht="15.75">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -43120,7 +43127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="559" spans="1:7" ht="26">
+    <row r="559" spans="1:7" ht="26.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -43137,7 +43144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="26">
+    <row r="560" spans="1:7" ht="26.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="7"/>
@@ -43384,7 +43391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="579" spans="1:7" ht="63.5">
+    <row r="579" spans="1:7" ht="64.5">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -43399,7 +43406,7 @@
       </c>
       <c r="G579" s="5"/>
     </row>
-    <row r="580" spans="1:7" ht="26">
+    <row r="580" spans="1:7" ht="26.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -43416,7 +43423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="581" spans="1:7" ht="26">
+    <row r="581" spans="1:7" ht="26.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -43433,7 +43440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="38.5">
+    <row r="582" spans="1:7" ht="39">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -43528,7 +43535,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="589" spans="1:7" ht="15.5">
+    <row r="589" spans="1:7" ht="15.75">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -43543,7 +43550,7 @@
       </c>
       <c r="G589" s="5"/>
     </row>
-    <row r="590" spans="1:7" ht="15.5">
+    <row r="590" spans="1:7" ht="15.75">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -43558,7 +43565,7 @@
       </c>
       <c r="G590" s="5"/>
     </row>
-    <row r="591" spans="1:7" ht="15.5">
+    <row r="591" spans="1:7" ht="15.75">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -43573,7 +43580,7 @@
       </c>
       <c r="G591" s="5"/>
     </row>
-    <row r="592" spans="1:7" ht="15.5">
+    <row r="592" spans="1:7" ht="15.75">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -43588,7 +43595,7 @@
       </c>
       <c r="G592" s="5"/>
     </row>
-    <row r="593" spans="1:7" ht="15.5">
+    <row r="593" spans="1:7" ht="15.75">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -43603,7 +43610,7 @@
       </c>
       <c r="G593" s="5"/>
     </row>
-    <row r="594" spans="1:7" ht="15.5">
+    <row r="594" spans="1:7" ht="15.75">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -43618,7 +43625,7 @@
       </c>
       <c r="G594" s="5"/>
     </row>
-    <row r="595" spans="1:7" ht="15.5">
+    <row r="595" spans="1:7" ht="15.75">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -43633,7 +43640,7 @@
       </c>
       <c r="G595" s="5"/>
     </row>
-    <row r="596" spans="1:7" ht="15.5">
+    <row r="596" spans="1:7" ht="15.75">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -43684,7 +43691,7 @@
       <c r="F601" s="4"/>
       <c r="G601" s="3"/>
     </row>
-    <row r="604" spans="1:7" ht="15.5">
+    <row r="604" spans="1:7" ht="15.75">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -43699,7 +43706,7 @@
       </c>
       <c r="G604" s="5"/>
     </row>
-    <row r="605" spans="1:7" ht="15.5">
+    <row r="605" spans="1:7" ht="15.75">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -43714,7 +43721,7 @@
       </c>
       <c r="G605" s="5"/>
     </row>
-    <row r="606" spans="1:7" ht="15.5">
+    <row r="606" spans="1:7" ht="15.75">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -43729,7 +43736,7 @@
       </c>
       <c r="G606" s="5"/>
     </row>
-    <row r="609" spans="1:7" ht="15.5">
+    <row r="609" spans="1:7" ht="15.75">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -43744,7 +43751,7 @@
       </c>
       <c r="G609" s="5"/>
     </row>
-    <row r="610" spans="1:7" ht="15.5">
+    <row r="610" spans="1:7" ht="15.75">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -43759,7 +43766,7 @@
       </c>
       <c r="G610" s="5"/>
     </row>
-    <row r="611" spans="1:7" ht="15.5">
+    <row r="611" spans="1:7" ht="15.75">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -43825,7 +43832,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="617" spans="1:7" ht="15.5">
+    <row r="617" spans="1:7" ht="15.75">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -43840,7 +43847,7 @@
       </c>
       <c r="G617" s="5"/>
     </row>
-    <row r="618" spans="1:7" ht="15.5">
+    <row r="618" spans="1:7" ht="15.75">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -43855,7 +43862,7 @@
       </c>
       <c r="G618" s="5"/>
     </row>
-    <row r="619" spans="1:7" ht="15.5">
+    <row r="619" spans="1:7" ht="15.75">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -43864,7 +43871,7 @@
       <c r="F619" s="4"/>
       <c r="G619" s="5"/>
     </row>
-    <row r="620" spans="1:7" ht="26">
+    <row r="620" spans="1:7" ht="26.25">
       <c r="A620" s="27"/>
       <c r="B620" s="27"/>
       <c r="C620" s="27"/>
@@ -43988,11 +43995,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3CE29B-B7F7-4B7E-8D51-80E542FD86A4}">
   <dimension ref="A1:I633"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="32.81640625" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="1" max="3" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="87" style="10" customWidth="1"/>
   </cols>
@@ -44028,7 +44035,9 @@
       <c r="B2" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C2" s="114"/>
+      <c r="C2" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D2" s="85" t="s">
         <v>615</v>
       </c>
@@ -44045,14 +44054,16 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5">
+    <row r="3" spans="1:8" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>974</v>
       </c>
       <c r="B3" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C3" s="114"/>
+      <c r="C3" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D3" s="85" t="s">
         <v>615</v>
       </c>
@@ -44074,7 +44085,9 @@
       <c r="B4" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C4" s="114"/>
+      <c r="C4" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D4" s="85" t="s">
         <v>615</v>
       </c>
@@ -44113,14 +44126,16 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="15.5">
+    <row r="6" spans="1:8" ht="15.75">
       <c r="A6" s="1" t="s">
         <v>974</v>
       </c>
       <c r="B6" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C6" s="114"/>
+      <c r="C6" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D6" s="85" t="s">
         <v>615</v>
       </c>
@@ -44142,7 +44157,9 @@
       <c r="B7" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C7" s="114"/>
+      <c r="C7" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D7" s="85" t="s">
         <v>615</v>
       </c>
@@ -44159,14 +44176,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.5">
+    <row r="8" spans="1:8" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>974</v>
       </c>
       <c r="B8" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C8" s="114"/>
+      <c r="C8" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D8" s="85" t="s">
         <v>615</v>
       </c>
@@ -44188,7 +44207,7 @@
       <c r="B9" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C9" s="114"/>
+      <c r="C9" s="161"/>
       <c r="D9" s="35" t="s">
         <v>616</v>
       </c>
@@ -44212,7 +44231,7 @@
       <c r="B10" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C10" s="114"/>
+      <c r="C10" s="161"/>
       <c r="D10" s="35" t="s">
         <v>616</v>
       </c>
@@ -44249,7 +44268,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="14" customHeight="1">
+    <row r="12" spans="1:8" ht="14.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="114" t="s">
         <v>974</v>
@@ -44677,7 +44696,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="15" thickBot="1">
+    <row r="33" spans="1:9" ht="15.75" thickBot="1">
       <c r="A33" s="1" t="s">
         <v>974</v>
       </c>
@@ -44700,7 +44719,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1">
+    <row r="34" spans="1:9" ht="15.75" thickBot="1">
       <c r="A34" s="1" t="s">
         <v>974</v>
       </c>
@@ -44727,7 +44746,7 @@
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="15" thickBot="1">
+    <row r="35" spans="1:9" ht="15.75" thickBot="1">
       <c r="A35" s="1" t="s">
         <v>974</v>
       </c>
@@ -44754,7 +44773,7 @@
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1">
+    <row r="36" spans="1:9" ht="15.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -44777,7 +44796,7 @@
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="15" thickBot="1">
+    <row r="37" spans="1:9" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="125" t="s">
@@ -44796,7 +44815,7 @@
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" ht="15" thickBot="1">
+    <row r="38" spans="1:9" ht="15.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -44815,7 +44834,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="15" thickBot="1">
+    <row r="39" spans="1:9" ht="15.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="9" t="s">
@@ -44834,7 +44853,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" ht="16" thickBot="1">
+    <row r="40" spans="1:9" ht="16.5" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -45204,7 +45223,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1">
+    <row r="56" spans="1:8" ht="15.75" thickBot="1">
       <c r="A56" s="60" t="s">
         <v>974</v>
       </c>
@@ -45228,7 +45247,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" thickBot="1">
+    <row r="57" spans="1:8" ht="15.75" thickBot="1">
       <c r="A57" s="60" t="s">
         <v>974</v>
       </c>
@@ -45345,7 +45364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="16" thickBot="1">
+    <row r="62" spans="1:8" ht="16.5" thickBot="1">
       <c r="A62" s="60" t="s">
         <v>974</v>
       </c>
@@ -45369,7 +45388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="16" thickBot="1">
+    <row r="63" spans="1:8" ht="16.5" thickBot="1">
       <c r="A63" s="60" t="s">
         <v>974</v>
       </c>
@@ -45487,7 +45506,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.5">
+    <row r="68" spans="1:8" ht="15.75">
       <c r="A68" s="60" t="s">
         <v>974</v>
       </c>
@@ -45511,7 +45530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.5">
+    <row r="69" spans="1:8" ht="15.75">
       <c r="A69" s="60" t="s">
         <v>974</v>
       </c>
@@ -45550,7 +45569,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.5">
+    <row r="71" spans="1:8" ht="15.75">
       <c r="A71" s="60" t="s">
         <v>974</v>
       </c>
@@ -45748,7 +45767,7 @@
       <c r="G79"/>
       <c r="H79" s="31"/>
     </row>
-    <row r="80" spans="1:8" ht="16">
+    <row r="80" spans="1:8" ht="16.5">
       <c r="A80" s="60" t="s">
         <v>974</v>
       </c>
@@ -45796,7 +45815,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.5">
+    <row r="82" spans="1:8" ht="15.75">
       <c r="A82" s="60" t="s">
         <v>974</v>
       </c>
@@ -45860,7 +45879,7 @@
       <c r="G84"/>
       <c r="H84" s="31"/>
     </row>
-    <row r="85" spans="1:8" ht="15.5">
+    <row r="85" spans="1:8" ht="15.75">
       <c r="A85" s="60" t="s">
         <v>974</v>
       </c>
@@ -45882,7 +45901,7 @@
       </c>
       <c r="H85" s="5"/>
     </row>
-    <row r="86" spans="1:8" ht="15.5">
+    <row r="86" spans="1:8" ht="15.75">
       <c r="A86" s="60" t="s">
         <v>974</v>
       </c>
@@ -45928,7 +45947,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.5">
+    <row r="88" spans="1:8" ht="15.75">
       <c r="A88" s="60" t="s">
         <v>974</v>
       </c>
@@ -45950,7 +45969,7 @@
       </c>
       <c r="H88" s="5"/>
     </row>
-    <row r="89" spans="1:8" ht="15.5">
+    <row r="89" spans="1:8" ht="15.75">
       <c r="A89" s="60"/>
       <c r="B89" s="114"/>
       <c r="C89" s="114"/>
@@ -46090,7 +46109,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" thickBot="1">
+    <row r="97" spans="1:8" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -46102,7 +46121,7 @@
       <c r="G97"/>
       <c r="H97" s="31"/>
     </row>
-    <row r="98" spans="1:8" ht="15" thickBot="1">
+    <row r="98" spans="1:8" ht="15.75" thickBot="1">
       <c r="A98" s="60" t="s">
         <v>974</v>
       </c>
@@ -46122,7 +46141,7 @@
       <c r="G98"/>
       <c r="H98" s="31"/>
     </row>
-    <row r="99" spans="1:8" ht="16" thickBot="1">
+    <row r="99" spans="1:8" ht="16.5" thickBot="1">
       <c r="A99" s="60" t="s">
         <v>974</v>
       </c>
@@ -46146,7 +46165,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" thickBot="1">
+    <row r="100" spans="1:8" ht="15.75" thickBot="1">
       <c r="A100" s="60" t="s">
         <v>974</v>
       </c>
@@ -46167,7 +46186,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" thickBot="1">
+    <row r="101" spans="1:8" ht="15.75" thickBot="1">
       <c r="A101" s="60" t="s">
         <v>974</v>
       </c>
@@ -46188,7 +46207,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" thickBot="1">
+    <row r="102" spans="1:8" ht="15.75" thickBot="1">
       <c r="A102" s="60" t="s">
         <v>974</v>
       </c>
@@ -46209,7 +46228,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="16" thickBot="1">
+    <row r="103" spans="1:8" ht="16.5" thickBot="1">
       <c r="A103" s="60" t="s">
         <v>974</v>
       </c>
@@ -46231,7 +46250,7 @@
       </c>
       <c r="H103" s="5"/>
     </row>
-    <row r="104" spans="1:8" ht="15" thickBot="1">
+    <row r="104" spans="1:8" ht="15.75" thickBot="1">
       <c r="A104" s="60" t="s">
         <v>974</v>
       </c>
@@ -46252,7 +46271,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" thickBot="1">
+    <row r="105" spans="1:8" ht="15.75" thickBot="1">
       <c r="A105" s="60" t="s">
         <v>974</v>
       </c>
@@ -46271,7 +46290,7 @@
       </c>
       <c r="G105"/>
     </row>
-    <row r="106" spans="1:8" ht="15" thickBot="1">
+    <row r="106" spans="1:8" ht="15.75" thickBot="1">
       <c r="A106" s="60" t="s">
         <v>974</v>
       </c>
@@ -46295,7 +46314,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15" thickBot="1">
+    <row r="107" spans="1:8" ht="15.75" thickBot="1">
       <c r="A107" s="60" t="s">
         <v>974</v>
       </c>
@@ -46319,7 +46338,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15" thickBot="1">
+    <row r="108" spans="1:8" ht="15.75" thickBot="1">
       <c r="A108" s="60" t="s">
         <v>974</v>
       </c>
@@ -46343,7 +46362,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="16" thickBot="1">
+    <row r="109" spans="1:8" ht="16.5" thickBot="1">
       <c r="A109" s="60" t="s">
         <v>974</v>
       </c>
@@ -46367,7 +46386,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="16" thickBot="1">
+    <row r="110" spans="1:8" ht="16.5" thickBot="1">
       <c r="A110" s="60" t="s">
         <v>974</v>
       </c>
@@ -46391,7 +46410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15" thickBot="1">
+    <row r="111" spans="1:8" ht="15.75" thickBot="1">
       <c r="A111" s="60" t="s">
         <v>974</v>
       </c>
@@ -46456,7 +46475,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.5">
+    <row r="114" spans="1:8" ht="15.75">
       <c r="A114" s="60" t="s">
         <v>974</v>
       </c>
@@ -46478,7 +46497,7 @@
       </c>
       <c r="H114" s="5"/>
     </row>
-    <row r="115" spans="1:8" ht="15.5">
+    <row r="115" spans="1:8" ht="15.75">
       <c r="A115" s="60" t="s">
         <v>974</v>
       </c>
@@ -46500,7 +46519,7 @@
       </c>
       <c r="H115" s="5"/>
     </row>
-    <row r="116" spans="1:8" ht="15.5">
+    <row r="116" spans="1:8" ht="15.75">
       <c r="A116" s="60" t="s">
         <v>974</v>
       </c>
@@ -46524,7 +46543,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.5">
+    <row r="117" spans="1:8" ht="15.75">
       <c r="A117" s="60" t="s">
         <v>974</v>
       </c>
@@ -46566,7 +46585,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.5">
+    <row r="119" spans="1:8" ht="15.75">
       <c r="A119" s="60" t="s">
         <v>974</v>
       </c>
@@ -46590,7 +46609,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.5">
+    <row r="120" spans="1:8" ht="15.75">
       <c r="A120" s="60" t="s">
         <v>974</v>
       </c>
@@ -46657,7 +46676,7 @@
       </c>
       <c r="G122"/>
     </row>
-    <row r="123" spans="1:8" ht="15.5">
+    <row r="123" spans="1:8" ht="15.75">
       <c r="A123" s="60" t="s">
         <v>974</v>
       </c>
@@ -46772,7 +46791,7 @@
       </c>
       <c r="G127"/>
     </row>
-    <row r="128" spans="1:8" ht="16">
+    <row r="128" spans="1:8" ht="16.5">
       <c r="A128" s="60" t="s">
         <v>974</v>
       </c>
@@ -46844,7 +46863,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15" thickBot="1">
+    <row r="131" spans="1:8" ht="15.75" thickBot="1">
       <c r="A131" s="60" t="s">
         <v>974</v>
       </c>
@@ -46868,7 +46887,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15" thickBot="1">
+    <row r="132" spans="1:8" ht="15.75" thickBot="1">
       <c r="A132" s="60" t="s">
         <v>974</v>
       </c>
@@ -46885,7 +46904,7 @@
       <c r="F132" s="3"/>
       <c r="G132"/>
     </row>
-    <row r="133" spans="1:8" ht="15" thickBot="1">
+    <row r="133" spans="1:8" ht="15.75" thickBot="1">
       <c r="A133" s="60" t="s">
         <v>974</v>
       </c>
@@ -46909,7 +46928,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" thickBot="1">
+    <row r="134" spans="1:8" ht="15.75" thickBot="1">
       <c r="A134" s="60" t="s">
         <v>974</v>
       </c>
@@ -46933,7 +46952,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="16.5" thickBot="1">
+    <row r="135" spans="1:8" ht="17.25" thickBot="1">
       <c r="A135" s="60" t="s">
         <v>974</v>
       </c>
@@ -46957,7 +46976,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="16.5" thickBot="1">
+    <row r="136" spans="1:8" ht="17.25" thickBot="1">
       <c r="A136" s="60" t="s">
         <v>974</v>
       </c>
@@ -46981,7 +47000,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="16.5" thickBot="1">
+    <row r="137" spans="1:8" ht="17.25" thickBot="1">
       <c r="A137" s="60" t="s">
         <v>974</v>
       </c>
@@ -47005,7 +47024,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="16.5" thickBot="1">
+    <row r="138" spans="1:8" ht="17.25" thickBot="1">
       <c r="A138" s="60" t="s">
         <v>974</v>
       </c>
@@ -47029,7 +47048,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="16.5" thickBot="1">
+    <row r="139" spans="1:8" ht="17.25" thickBot="1">
       <c r="A139" s="60" t="s">
         <v>974</v>
       </c>
@@ -47053,7 +47072,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="16.5" thickBot="1">
+    <row r="140" spans="1:8" ht="17.25" thickBot="1">
       <c r="A140" s="60" t="s">
         <v>974</v>
       </c>
@@ -47077,7 +47096,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15" thickBot="1">
+    <row r="141" spans="1:8" ht="15.75" thickBot="1">
       <c r="A141" s="60" t="s">
         <v>974</v>
       </c>
@@ -47098,7 +47117,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="16.5" thickBot="1">
+    <row r="142" spans="1:8" ht="17.25" thickBot="1">
       <c r="A142" s="60" t="s">
         <v>974</v>
       </c>
@@ -47122,7 +47141,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="16.5" thickBot="1">
+    <row r="143" spans="1:8" ht="17.25" thickBot="1">
       <c r="A143" s="60" t="s">
         <v>974</v>
       </c>
@@ -47146,7 +47165,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="16.5" thickBot="1">
+    <row r="144" spans="1:8" ht="17.25" thickBot="1">
       <c r="A144" s="60" t="s">
         <v>974</v>
       </c>
@@ -47170,7 +47189,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="16.5" thickBot="1">
+    <row r="145" spans="1:8" ht="17.25" thickBot="1">
       <c r="A145" s="60" t="s">
         <v>974</v>
       </c>
@@ -47194,7 +47213,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" thickBot="1">
+    <row r="146" spans="1:8" ht="15.75" thickBot="1">
       <c r="A146" s="60" t="s">
         <v>974</v>
       </c>
@@ -47216,7 +47235,7 @@
       </c>
       <c r="H146" s="41"/>
     </row>
-    <row r="147" spans="1:8" ht="15" thickBot="1">
+    <row r="147" spans="1:8" ht="15.75" thickBot="1">
       <c r="A147" s="60" t="s">
         <v>974</v>
       </c>
@@ -47234,7 +47253,7 @@
       <c r="G147"/>
       <c r="H147" s="41"/>
     </row>
-    <row r="148" spans="1:8" ht="15" thickBot="1">
+    <row r="148" spans="1:8" ht="15.75" thickBot="1">
       <c r="A148" s="60" t="s">
         <v>974</v>
       </c>
@@ -47258,7 +47277,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" thickBot="1">
+    <row r="149" spans="1:8" ht="15.75" thickBot="1">
       <c r="A149" s="60" t="s">
         <v>974</v>
       </c>
@@ -47279,7 +47298,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="16.5" thickBot="1">
+    <row r="150" spans="1:8" ht="17.25" thickBot="1">
       <c r="A150" s="60" t="s">
         <v>974</v>
       </c>
@@ -47303,7 +47322,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="16.5" thickBot="1">
+    <row r="151" spans="1:8" ht="17.25" thickBot="1">
       <c r="A151" s="60" t="s">
         <v>974</v>
       </c>
@@ -47327,7 +47346,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="16.5" thickBot="1">
+    <row r="152" spans="1:8" ht="17.25" thickBot="1">
       <c r="A152" s="60" t="s">
         <v>974</v>
       </c>
@@ -47351,7 +47370,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="16.5" thickBot="1">
+    <row r="153" spans="1:8" ht="17.25" thickBot="1">
       <c r="A153" s="60" t="s">
         <v>974</v>
       </c>
@@ -47375,7 +47394,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="16.5" thickBot="1">
+    <row r="154" spans="1:8" ht="17.25" thickBot="1">
       <c r="A154" s="60" t="s">
         <v>974</v>
       </c>
@@ -47399,7 +47418,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="16.5" thickBot="1">
+    <row r="155" spans="1:8" ht="17.25" thickBot="1">
       <c r="A155" s="60" t="s">
         <v>974</v>
       </c>
@@ -47423,7 +47442,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15" thickBot="1">
+    <row r="156" spans="1:8" ht="15.75" thickBot="1">
       <c r="A156" s="60" t="s">
         <v>974</v>
       </c>
@@ -47447,7 +47466,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="16.5" thickBot="1">
+    <row r="157" spans="1:8" ht="17.25" thickBot="1">
       <c r="A157" s="60" t="s">
         <v>974</v>
       </c>
@@ -47471,7 +47490,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="16.5" thickBot="1">
+    <row r="158" spans="1:8" ht="17.25" thickBot="1">
       <c r="A158" s="60" t="s">
         <v>974</v>
       </c>
@@ -47495,7 +47514,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="16.5" thickBot="1">
+    <row r="159" spans="1:8" ht="17.25" thickBot="1">
       <c r="A159" s="60" t="s">
         <v>974</v>
       </c>
@@ -47519,7 +47538,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="16.5" thickBot="1">
+    <row r="160" spans="1:8" ht="17.25" thickBot="1">
       <c r="A160" s="60" t="s">
         <v>974</v>
       </c>
@@ -47543,7 +47562,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15" thickBot="1">
+    <row r="161" spans="1:8" ht="15.75" thickBot="1">
       <c r="A161" s="60" t="s">
         <v>974</v>
       </c>
@@ -47565,7 +47584,7 @@
       </c>
       <c r="H161" s="41"/>
     </row>
-    <row r="162" spans="1:8" ht="15" thickBot="1">
+    <row r="162" spans="1:8" ht="15.75" thickBot="1">
       <c r="A162" s="60" t="s">
         <v>974</v>
       </c>
@@ -47587,7 +47606,7 @@
       </c>
       <c r="H162" s="41"/>
     </row>
-    <row r="163" spans="1:8" ht="15" thickBot="1">
+    <row r="163" spans="1:8" ht="15.75" thickBot="1">
       <c r="A163" s="60" t="s">
         <v>974</v>
       </c>
@@ -47611,7 +47630,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15" thickBot="1">
+    <row r="164" spans="1:8" ht="15.75" thickBot="1">
       <c r="A164" s="60" t="s">
         <v>974</v>
       </c>
@@ -47635,7 +47654,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" thickBot="1">
+    <row r="165" spans="1:8" ht="15.75" thickBot="1">
       <c r="A165" s="60" t="s">
         <v>974</v>
       </c>
@@ -47656,7 +47675,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" thickBot="1">
+    <row r="166" spans="1:8" ht="15.75" thickBot="1">
       <c r="A166" s="60" t="s">
         <v>974</v>
       </c>
@@ -47680,7 +47699,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" thickBot="1">
+    <row r="167" spans="1:8" ht="15.75" thickBot="1">
       <c r="A167" s="60" t="s">
         <v>974</v>
       </c>
@@ -47704,7 +47723,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15" thickBot="1">
+    <row r="168" spans="1:8" ht="15.75" thickBot="1">
       <c r="A168" s="1"/>
       <c r="B168" s="114" t="s">
         <v>974</v>
@@ -47721,7 +47740,7 @@
       </c>
       <c r="G168"/>
     </row>
-    <row r="169" spans="1:8" ht="15" thickBot="1">
+    <row r="169" spans="1:8" ht="15.75" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="121" t="s">
         <v>1509</v>
@@ -47743,7 +47762,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="16.5" thickBot="1">
+    <row r="170" spans="1:8" ht="17.25" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="114" t="s">
         <v>974</v>
@@ -47765,7 +47784,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15" thickBot="1">
+    <row r="171" spans="1:8" ht="15.75" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="114" t="s">
         <v>974</v>
@@ -47780,7 +47799,7 @@
       <c r="F171" s="17"/>
       <c r="G171"/>
     </row>
-    <row r="172" spans="1:8" ht="15" thickBot="1">
+    <row r="172" spans="1:8" ht="15.75" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="121" t="s">
         <v>1509</v>
@@ -47802,7 +47821,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="16.5" thickBot="1">
+    <row r="173" spans="1:8" ht="17.25" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="114" t="s">
         <v>974</v>
@@ -47824,7 +47843,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="15" thickBot="1">
+    <row r="174" spans="1:8" ht="15.75" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="114" t="s">
         <v>974</v>
@@ -47839,7 +47858,7 @@
       <c r="F174" s="17"/>
       <c r="G174"/>
     </row>
-    <row r="175" spans="1:8" ht="15" thickBot="1">
+    <row r="175" spans="1:8" ht="15.75" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="114" t="s">
         <v>974</v>
@@ -47861,7 +47880,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15" thickBot="1">
+    <row r="176" spans="1:8" ht="15.75" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="114" t="s">
         <v>974</v>
@@ -47881,7 +47900,7 @@
       </c>
       <c r="H176" s="69"/>
     </row>
-    <row r="177" spans="1:8" ht="15" thickBot="1">
+    <row r="177" spans="1:8" ht="15.75" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="114" t="s">
         <v>974</v>
@@ -47901,7 +47920,7 @@
       </c>
       <c r="H177" s="43"/>
     </row>
-    <row r="178" spans="1:8" ht="15" thickBot="1">
+    <row r="178" spans="1:8" ht="15.75" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="114" t="s">
         <v>974</v>
@@ -47921,7 +47940,7 @@
       </c>
       <c r="H178" s="44"/>
     </row>
-    <row r="179" spans="1:8" ht="15" thickBot="1">
+    <row r="179" spans="1:8" ht="15.75" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="114" t="s">
         <v>974</v>
@@ -47941,7 +47960,7 @@
       </c>
       <c r="H179" s="44"/>
     </row>
-    <row r="180" spans="1:8" ht="15" thickBot="1">
+    <row r="180" spans="1:8" ht="15.75" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="114" t="s">
         <v>974</v>
@@ -47960,7 +47979,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15" thickBot="1">
+    <row r="181" spans="1:8" ht="15.75" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="114" t="s">
         <v>974</v>
@@ -47979,7 +47998,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15" thickBot="1">
+    <row r="182" spans="1:8" ht="15.75" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="114" t="s">
         <v>974</v>
@@ -48001,7 +48020,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" thickBot="1">
+    <row r="183" spans="1:8" ht="15.75" thickBot="1">
       <c r="A183" s="108"/>
       <c r="B183" s="114" t="s">
         <v>974</v>
@@ -48020,7 +48039,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15" thickBot="1">
+    <row r="184" spans="1:8" ht="15.75" thickBot="1">
       <c r="A184" s="1"/>
       <c r="B184" s="114" t="s">
         <v>974</v>
@@ -48039,7 +48058,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15" thickBot="1">
+    <row r="185" spans="1:8" ht="15.75" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="114" t="s">
         <v>974</v>
@@ -48056,7 +48075,7 @@
       </c>
       <c r="G185"/>
     </row>
-    <row r="186" spans="1:8" ht="15" thickBot="1">
+    <row r="186" spans="1:8" ht="15.75" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="114" t="s">
         <v>974</v>
@@ -48078,7 +48097,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15" thickBot="1">
+    <row r="187" spans="1:8" ht="15.75" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="114" t="s">
         <v>974</v>
@@ -48098,7 +48117,7 @@
       </c>
       <c r="H187" s="73"/>
     </row>
-    <row r="188" spans="1:8" ht="15" thickBot="1">
+    <row r="188" spans="1:8" ht="15.75" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="114" t="s">
         <v>974</v>
@@ -48120,7 +48139,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15" thickBot="1">
+    <row r="189" spans="1:8" ht="15.75" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="114" t="s">
         <v>974</v>
@@ -48142,7 +48161,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15" thickBot="1">
+    <row r="190" spans="1:8" ht="15.75" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="114" t="s">
         <v>974</v>
@@ -48164,7 +48183,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15" thickBot="1">
+    <row r="191" spans="1:8" ht="15.75" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="114" t="s">
         <v>974</v>
@@ -48183,7 +48202,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15" thickBot="1">
+    <row r="192" spans="1:8" ht="15.75" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="114" t="s">
         <v>974</v>
@@ -48205,7 +48224,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15" thickBot="1">
+    <row r="193" spans="1:8" ht="15.75" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="114" t="s">
         <v>974</v>
@@ -48227,7 +48246,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15" thickBot="1">
+    <row r="194" spans="1:8" ht="15.75" thickBot="1">
       <c r="A194" s="108"/>
       <c r="B194" s="114" t="s">
         <v>974</v>
@@ -48249,7 +48268,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15" thickBot="1">
+    <row r="195" spans="1:8" ht="15.75" thickBot="1">
       <c r="A195" s="1"/>
       <c r="B195" s="114" t="s">
         <v>974</v>
@@ -48271,7 +48290,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15" thickBot="1">
+    <row r="196" spans="1:8" ht="15.75" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="114" t="s">
         <v>974</v>
@@ -48288,7 +48307,7 @@
       </c>
       <c r="H196" s="41"/>
     </row>
-    <row r="197" spans="1:8" ht="15" thickBot="1">
+    <row r="197" spans="1:8" ht="15.75" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="114" t="s">
         <v>974</v>
@@ -48310,7 +48329,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15" thickBot="1">
+    <row r="198" spans="1:8" ht="15.75" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="114" t="s">
         <v>974</v>
@@ -48332,7 +48351,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15" thickBot="1">
+    <row r="199" spans="1:8" ht="15.75" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="114" t="s">
         <v>974</v>
@@ -48350,7 +48369,7 @@
       <c r="G199"/>
       <c r="H199" s="29"/>
     </row>
-    <row r="200" spans="1:8" ht="15" thickBot="1">
+    <row r="200" spans="1:8" ht="15.75" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="114" t="s">
         <v>974</v>
@@ -48372,7 +48391,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15" thickBot="1">
+    <row r="201" spans="1:8" ht="15.75" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="114" t="s">
         <v>974</v>
@@ -48394,7 +48413,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15" thickBot="1">
+    <row r="202" spans="1:8" ht="15.75" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="114" t="s">
         <v>974</v>
@@ -48411,7 +48430,7 @@
       </c>
       <c r="G202"/>
     </row>
-    <row r="203" spans="1:8" ht="15" thickBot="1">
+    <row r="203" spans="1:8" ht="15.75" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="114" t="s">
         <v>974</v>
@@ -48430,7 +48449,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="15" thickBot="1">
+    <row r="204" spans="1:8" ht="15.75" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="114" t="s">
         <v>974</v>
@@ -48447,7 +48466,7 @@
       </c>
       <c r="G204"/>
     </row>
-    <row r="205" spans="1:8" ht="15" thickBot="1">
+    <row r="205" spans="1:8" ht="15.75" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="114" t="s">
         <v>974</v>
@@ -48469,7 +48488,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15" thickBot="1">
+    <row r="206" spans="1:8" ht="15.75" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="114" t="s">
         <v>974</v>
@@ -48488,7 +48507,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15" thickBot="1">
+    <row r="207" spans="1:8" ht="15.75" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="114" t="s">
         <v>974</v>
@@ -48510,7 +48529,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15" thickBot="1">
+    <row r="208" spans="1:8" ht="15.75" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="114" t="s">
         <v>974</v>
@@ -48532,7 +48551,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15" thickBot="1">
+    <row r="209" spans="1:8" ht="15.75" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="114" t="s">
         <v>974</v>
@@ -48549,7 +48568,7 @@
       </c>
       <c r="G209"/>
     </row>
-    <row r="210" spans="1:8" ht="15" thickBot="1">
+    <row r="210" spans="1:8" ht="15.75" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="114" t="s">
         <v>974</v>
@@ -48568,7 +48587,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="15" thickBot="1">
+    <row r="211" spans="1:8" ht="15.75" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="114" t="s">
         <v>974</v>
@@ -48585,7 +48604,7 @@
       </c>
       <c r="G211"/>
     </row>
-    <row r="212" spans="1:8" ht="15" thickBot="1">
+    <row r="212" spans="1:8" ht="15.75" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="114" t="s">
         <v>974</v>
@@ -48607,7 +48626,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15" thickBot="1">
+    <row r="213" spans="1:8" ht="15.75" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="114" t="s">
         <v>974</v>
@@ -48626,7 +48645,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15" thickBot="1">
+    <row r="214" spans="1:8" ht="15.75" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="114" t="s">
         <v>974</v>
@@ -48648,7 +48667,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15" thickBot="1">
+    <row r="215" spans="1:8" ht="15.75" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="114" t="s">
         <v>974</v>
@@ -48667,7 +48686,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15" thickBot="1">
+    <row r="216" spans="1:8" ht="15.75" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="114" t="s">
         <v>974</v>
@@ -48682,7 +48701,7 @@
       <c r="F216" s="17"/>
       <c r="G216"/>
     </row>
-    <row r="217" spans="1:8" ht="15" thickBot="1">
+    <row r="217" spans="1:8" ht="15.75" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="114" t="s">
         <v>974</v>
@@ -48701,7 +48720,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15" thickBot="1">
+    <row r="218" spans="1:8" ht="15.75" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="114" t="s">
         <v>974</v>
@@ -48716,7 +48735,7 @@
       <c r="F218" s="17"/>
       <c r="G218"/>
     </row>
-    <row r="219" spans="1:8" ht="15" thickBot="1">
+    <row r="219" spans="1:8" ht="15.75" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="114" t="s">
         <v>974</v>
@@ -48735,7 +48754,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="15" thickBot="1">
+    <row r="220" spans="1:8" ht="15.75" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -48750,7 +48769,7 @@
       </c>
       <c r="G220"/>
     </row>
-    <row r="221" spans="1:8" ht="15" thickBot="1">
+    <row r="221" spans="1:8" ht="15.75" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -48767,7 +48786,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15" thickBot="1">
+    <row r="222" spans="1:8" ht="15.75" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -48787,7 +48806,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15" thickBot="1">
+    <row r="223" spans="1:8" ht="15.75" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -48804,7 +48823,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15" thickBot="1">
+    <row r="224" spans="1:8" ht="15.75" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -48821,7 +48840,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15" thickBot="1">
+    <row r="225" spans="1:8" ht="15.75" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -48836,7 +48855,7 @@
       </c>
       <c r="G225"/>
     </row>
-    <row r="226" spans="1:8" ht="15" thickBot="1">
+    <row r="226" spans="1:8" ht="15.75" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -48853,7 +48872,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15" thickBot="1">
+    <row r="227" spans="1:8" ht="15.75" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -48873,7 +48892,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15" thickBot="1">
+    <row r="228" spans="1:8" ht="15.75" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -49048,7 +49067,7 @@
       <c r="F238" s="19"/>
       <c r="G238"/>
     </row>
-    <row r="239" spans="1:8" ht="15" thickBot="1">
+    <row r="239" spans="1:8" ht="15.75" thickBot="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -49065,7 +49084,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="15" thickBot="1">
+    <row r="240" spans="1:8" ht="15.75" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="125" t="s">
         <v>1003</v>
@@ -49080,7 +49099,7 @@
       <c r="F240" s="19"/>
       <c r="G240"/>
     </row>
-    <row r="241" spans="1:8" ht="15" thickBot="1">
+    <row r="241" spans="1:8" ht="15.75" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="125" t="s">
         <v>1003</v>
@@ -49095,7 +49114,7 @@
       <c r="F241" s="19"/>
       <c r="G241"/>
     </row>
-    <row r="242" spans="1:8" ht="15" thickBot="1">
+    <row r="242" spans="1:8" ht="15.75" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="125" t="s">
         <v>1003</v>
@@ -49110,7 +49129,7 @@
       <c r="F242" s="19"/>
       <c r="G242"/>
     </row>
-    <row r="243" spans="1:8" ht="15" thickBot="1">
+    <row r="243" spans="1:8" ht="15.75" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="125" t="s">
         <v>1003</v>
@@ -49125,7 +49144,7 @@
       <c r="F243" s="19"/>
       <c r="G243"/>
     </row>
-    <row r="244" spans="1:8" ht="15" thickBot="1">
+    <row r="244" spans="1:8" ht="15.75" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="125" t="s">
         <v>1003</v>
@@ -49140,7 +49159,7 @@
       <c r="F244" s="19"/>
       <c r="G244"/>
     </row>
-    <row r="245" spans="1:8" ht="15" thickBot="1">
+    <row r="245" spans="1:8" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="125" t="s">
         <v>1003</v>
@@ -49155,7 +49174,7 @@
       <c r="F245" s="19"/>
       <c r="G245"/>
     </row>
-    <row r="246" spans="1:8" ht="15" thickBot="1">
+    <row r="246" spans="1:8" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="125" t="s">
         <v>1003</v>
@@ -49170,7 +49189,7 @@
       <c r="F246" s="19"/>
       <c r="G246"/>
     </row>
-    <row r="247" spans="1:8" ht="15" thickBot="1">
+    <row r="247" spans="1:8" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="125" t="s">
         <v>1003</v>
@@ -49185,7 +49204,7 @@
       <c r="F247" s="19"/>
       <c r="G247"/>
     </row>
-    <row r="248" spans="1:8" ht="15" thickBot="1">
+    <row r="248" spans="1:8" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="125" t="s">
         <v>1003</v>
@@ -49200,7 +49219,7 @@
       <c r="F248" s="19"/>
       <c r="G248"/>
     </row>
-    <row r="249" spans="1:8" ht="15" thickBot="1">
+    <row r="249" spans="1:8" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="125" t="s">
         <v>1003</v>
@@ -49215,7 +49234,7 @@
       <c r="F249" s="19"/>
       <c r="G249"/>
     </row>
-    <row r="250" spans="1:8" ht="15" thickBot="1">
+    <row r="250" spans="1:8" ht="15.75" thickBot="1">
       <c r="A250" s="1" t="s">
         <v>1438</v>
       </c>
@@ -49236,7 +49255,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="15" thickBot="1">
+    <row r="251" spans="1:8" ht="15.75" thickBot="1">
       <c r="A251" s="1" t="s">
         <v>1438</v>
       </c>
@@ -49338,7 +49357,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15" thickBot="1">
+    <row r="257" spans="1:9" ht="15.75" thickBot="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -49361,7 +49380,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15" thickBot="1">
+    <row r="258" spans="1:9" ht="15.75" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -49438,7 +49457,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15" thickBot="1">
+    <row r="262" spans="1:9" ht="15.75" thickBot="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -49458,7 +49477,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15" thickBot="1">
+    <row r="263" spans="1:9" ht="15.75" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -49511,7 +49530,7 @@
       <c r="G265" s="4"/>
       <c r="H265" s="3"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" ht="26.25">
       <c r="A266" s="1" t="s">
         <v>974</v>
       </c>
@@ -50066,7 +50085,7 @@
       </c>
       <c r="H299" s="14"/>
     </row>
-    <row r="300" spans="1:8" ht="15" thickBot="1">
+    <row r="300" spans="1:8" ht="15.75" thickBot="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -50084,7 +50103,7 @@
       </c>
       <c r="H300" s="14"/>
     </row>
-    <row r="301" spans="1:8" ht="15" thickBot="1">
+    <row r="301" spans="1:8" ht="15.75" thickBot="1">
       <c r="A301" s="14"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -51323,7 +51342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="15.5">
+    <row r="391" spans="1:8" ht="15.75">
       <c r="A391" s="14"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -51423,7 +51442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="15.5">
+    <row r="396" spans="1:8" ht="15.75">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -51460,7 +51479,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="15.5">
+    <row r="398" spans="1:8" ht="15.75">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -51515,7 +51534,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="15.5">
+    <row r="401" spans="1:8" ht="15.75">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -51593,7 +51612,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="15.5">
+    <row r="405" spans="1:8" ht="15.75">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -51671,7 +51690,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="15.5">
+    <row r="409" spans="1:8" ht="15.75">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -51689,7 +51708,7 @@
       </c>
       <c r="H409" s="5"/>
     </row>
-    <row r="410" spans="1:8" ht="15" thickBot="1">
+    <row r="410" spans="1:8" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -51709,7 +51728,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="15" thickBot="1">
+    <row r="411" spans="1:8" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -51725,7 +51744,7 @@
       <c r="G411" s="3"/>
       <c r="H411" s="14"/>
     </row>
-    <row r="412" spans="1:8" ht="15" thickBot="1">
+    <row r="412" spans="1:8" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -51741,7 +51760,7 @@
       <c r="G412" s="3"/>
       <c r="H412" s="14"/>
     </row>
-    <row r="413" spans="1:8" ht="15.5">
+    <row r="413" spans="1:8" ht="15.75">
       <c r="D413" s="14" t="s">
         <v>765</v>
       </c>
@@ -51812,7 +51831,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="15.5">
+    <row r="417" spans="1:8" ht="15.75">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -51872,7 +51891,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="420" spans="1:8" ht="15" thickBot="1">
+    <row r="420" spans="1:8" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -51892,7 +51911,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="15" thickBot="1">
+    <row r="421" spans="1:8" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -51912,7 +51931,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="15" thickBot="1">
+    <row r="422" spans="1:8" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -51932,7 +51951,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="15" thickBot="1">
+    <row r="423" spans="1:8" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -51952,7 +51971,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="15" thickBot="1">
+    <row r="424" spans="1:8" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -51972,7 +51991,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="15" thickBot="1">
+    <row r="425" spans="1:8" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -51992,7 +52011,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="15" thickBot="1">
+    <row r="426" spans="1:8" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -52012,7 +52031,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="15" thickBot="1">
+    <row r="427" spans="1:8" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -52032,7 +52051,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="428" spans="1:8" ht="15" thickBot="1">
+    <row r="428" spans="1:8" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -52052,7 +52071,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:8" ht="15" thickBot="1">
+    <row r="429" spans="1:8" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -52072,7 +52091,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="15" thickBot="1">
+    <row r="430" spans="1:8" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -52092,7 +52111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="15" thickBot="1">
+    <row r="431" spans="1:8" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -52112,7 +52131,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="432" spans="1:8" ht="15" thickBot="1">
+    <row r="432" spans="1:8" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -52129,7 +52148,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="433" spans="1:8" ht="15" thickBot="1">
+    <row r="433" spans="1:8" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -52146,7 +52165,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="434" spans="1:8" ht="15" thickBot="1">
+    <row r="434" spans="1:8" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -52163,7 +52182,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="15" thickBot="1">
+    <row r="435" spans="1:8" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -52180,7 +52199,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="436" spans="1:8" ht="15" thickBot="1">
+    <row r="436" spans="1:8" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -52197,7 +52216,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="15" thickBot="1">
+    <row r="437" spans="1:8" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -52214,7 +52233,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="438" spans="1:8" ht="15" thickBot="1">
+    <row r="438" spans="1:8" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -52231,7 +52250,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="15" thickBot="1">
+    <row r="439" spans="1:8" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -52248,7 +52267,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="440" spans="1:8" ht="15" thickBot="1">
+    <row r="440" spans="1:8" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -52266,7 +52285,7 @@
       </c>
       <c r="H440" s="41"/>
     </row>
-    <row r="441" spans="1:8" ht="15" thickBot="1">
+    <row r="441" spans="1:8" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -52286,7 +52305,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="442" spans="1:8" ht="15" thickBot="1">
+    <row r="442" spans="1:8" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -52306,7 +52325,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="443" spans="1:8" ht="15" thickBot="1">
+    <row r="443" spans="1:8" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -52326,7 +52345,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="15" thickBot="1">
+    <row r="444" spans="1:8" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -52346,7 +52365,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="445" spans="1:8" ht="15" thickBot="1">
+    <row r="445" spans="1:8" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -52366,7 +52385,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="446" spans="1:8" ht="15" thickBot="1">
+    <row r="446" spans="1:8" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -52386,7 +52405,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="15" thickBot="1">
+    <row r="447" spans="1:8" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -52406,7 +52425,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="448" spans="1:8" ht="15" thickBot="1">
+    <row r="448" spans="1:8" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -52426,7 +52445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="449" spans="1:8" ht="15" thickBot="1">
+    <row r="449" spans="1:8" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -52446,7 +52465,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="450" spans="1:8" ht="15" thickBot="1">
+    <row r="450" spans="1:8" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -52466,7 +52485,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="451" spans="1:8" ht="15" thickBot="1">
+    <row r="451" spans="1:8" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -52486,7 +52505,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="15" thickBot="1">
+    <row r="452" spans="1:8" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -52503,7 +52522,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="15" thickBot="1">
+    <row r="453" spans="1:8" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -52520,7 +52539,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="454" spans="1:8" ht="15" thickBot="1">
+    <row r="454" spans="1:8" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -52537,7 +52556,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="455" spans="1:8" ht="15" thickBot="1">
+    <row r="455" spans="1:8" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -52554,7 +52573,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="456" spans="1:8" ht="15" thickBot="1">
+    <row r="456" spans="1:8" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -52571,7 +52590,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="15" thickBot="1">
+    <row r="457" spans="1:8" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -52588,7 +52607,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="15" thickBot="1">
+    <row r="458" spans="1:8" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -52605,7 +52624,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="15" thickBot="1">
+    <row r="459" spans="1:8" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -52622,7 +52641,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="15" thickBot="1">
+    <row r="460" spans="1:8" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -52640,7 +52659,7 @@
       </c>
       <c r="H460" s="41"/>
     </row>
-    <row r="461" spans="1:8" ht="15" thickBot="1">
+    <row r="461" spans="1:8" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -52660,7 +52679,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="462" spans="1:8" ht="15" thickBot="1">
+    <row r="462" spans="1:8" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -52680,7 +52699,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="15" thickBot="1">
+    <row r="463" spans="1:8" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -52700,7 +52719,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="15" thickBot="1">
+    <row r="464" spans="1:8" ht="15.75" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -52720,7 +52739,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="15" thickBot="1">
+    <row r="465" spans="1:8" ht="15.75" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -52740,7 +52759,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="15" thickBot="1">
+    <row r="466" spans="1:8" ht="15.75" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -52760,7 +52779,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="15" thickBot="1">
+    <row r="467" spans="1:8" ht="15.75" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -52780,7 +52799,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="15" thickBot="1">
+    <row r="468" spans="1:8" ht="15.75" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -52800,7 +52819,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="469" spans="1:8" ht="15" thickBot="1">
+    <row r="469" spans="1:8" ht="15.75" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -52820,7 +52839,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="470" spans="1:8" ht="15" thickBot="1">
+    <row r="470" spans="1:8" ht="15.75" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -52837,7 +52856,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="471" spans="1:8" ht="15" thickBot="1">
+    <row r="471" spans="1:8" ht="15.75" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -52855,7 +52874,7 @@
       </c>
       <c r="H471" s="43"/>
     </row>
-    <row r="472" spans="1:8" ht="15" thickBot="1">
+    <row r="472" spans="1:8" ht="15.75" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -52873,7 +52892,7 @@
       </c>
       <c r="H472" s="44"/>
     </row>
-    <row r="473" spans="1:8" ht="15" thickBot="1">
+    <row r="473" spans="1:8" ht="15.75" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -52891,7 +52910,7 @@
       </c>
       <c r="H473" s="44"/>
     </row>
-    <row r="474" spans="1:8" ht="15" thickBot="1">
+    <row r="474" spans="1:8" ht="15.75" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -52908,7 +52927,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="475" spans="1:8" ht="15" thickBot="1">
+    <row r="475" spans="1:8" ht="15.75" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -52925,7 +52944,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="476" spans="1:8" ht="15" thickBot="1">
+    <row r="476" spans="1:8" ht="15.75" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -52942,7 +52961,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="15" thickBot="1">
+    <row r="477" spans="1:8" ht="15.75" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -52959,7 +52978,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="478" spans="1:8" ht="15" thickBot="1">
+    <row r="478" spans="1:8" ht="15.75" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -52979,7 +52998,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="15" thickBot="1">
+    <row r="479" spans="1:8" ht="15.75" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -52999,7 +53018,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="480" spans="1:8" ht="15" thickBot="1">
+    <row r="480" spans="1:8" ht="15.75" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -53016,7 +53035,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="15" thickBot="1">
+    <row r="481" spans="1:8" ht="15.75" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -53036,7 +53055,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="15" thickBot="1">
+    <row r="482" spans="1:8" ht="15.75" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -53056,7 +53075,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="483" spans="1:8" ht="15" thickBot="1">
+    <row r="483" spans="1:8" ht="15.75" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -53076,7 +53095,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="15" thickBot="1">
+    <row r="484" spans="1:8" ht="15.75" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -53093,7 +53112,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="15" thickBot="1">
+    <row r="485" spans="1:8" ht="15.75" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -53113,7 +53132,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="15" thickBot="1">
+    <row r="486" spans="1:8" ht="15.75" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -53133,7 +53152,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="487" spans="1:8" ht="15" thickBot="1">
+    <row r="487" spans="1:8" ht="15.75" thickBot="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14"/>
@@ -53153,7 +53172,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="15" thickBot="1">
+    <row r="488" spans="1:8" ht="15.75" thickBot="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14"/>
@@ -53173,7 +53192,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="15" thickBot="1">
+    <row r="489" spans="1:8" ht="15.75" thickBot="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14"/>
@@ -53193,7 +53212,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="490" spans="1:8" ht="15" thickBot="1">
+    <row r="490" spans="1:8" ht="15.75" thickBot="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14"/>
@@ -53213,7 +53232,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="15" thickBot="1">
+    <row r="491" spans="1:8" ht="15.75" thickBot="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14"/>
@@ -53233,7 +53252,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="15" thickBot="1">
+    <row r="492" spans="1:8" ht="15.75" thickBot="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14"/>
@@ -53253,7 +53272,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="493" spans="1:8" ht="15" thickBot="1">
+    <row r="493" spans="1:8" ht="15.75" thickBot="1">
       <c r="A493" s="14"/>
       <c r="B493" s="14"/>
       <c r="C493" s="14"/>
@@ -53273,7 +53292,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="494" spans="1:8" ht="15" thickBot="1">
+    <row r="494" spans="1:8" ht="15.75" thickBot="1">
       <c r="A494" s="14"/>
       <c r="B494" s="14"/>
       <c r="C494" s="14"/>
@@ -53293,7 +53312,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="15" thickBot="1">
+    <row r="495" spans="1:8" ht="15.75" thickBot="1">
       <c r="A495" s="14"/>
       <c r="B495" s="14"/>
       <c r="C495" s="14"/>
@@ -53310,7 +53329,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="15" thickBot="1">
+    <row r="496" spans="1:8" ht="15.75" thickBot="1">
       <c r="A496" s="14"/>
       <c r="B496" s="14"/>
       <c r="C496" s="14"/>
@@ -53330,7 +53349,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="497" spans="1:8" ht="15" thickBot="1">
+    <row r="497" spans="1:8" ht="15.75" thickBot="1">
       <c r="A497" s="14"/>
       <c r="B497" s="14"/>
       <c r="C497" s="14"/>
@@ -53350,7 +53369,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="498" spans="1:8" ht="15" thickBot="1">
+    <row r="498" spans="1:8" ht="15.75" thickBot="1">
       <c r="A498" s="14"/>
       <c r="B498" s="14"/>
       <c r="C498" s="14"/>
@@ -53370,7 +53389,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="15" thickBot="1">
+    <row r="499" spans="1:8" ht="15.75" thickBot="1">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
@@ -53387,7 +53406,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="500" spans="1:8" ht="15" thickBot="1">
+    <row r="500" spans="1:8" ht="15.75" thickBot="1">
       <c r="A500" s="14"/>
       <c r="B500" s="14"/>
       <c r="C500" s="14"/>
@@ -53407,7 +53426,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="15" thickBot="1">
+    <row r="501" spans="1:8" ht="15.75" thickBot="1">
       <c r="A501" s="14"/>
       <c r="B501" s="14"/>
       <c r="C501" s="14"/>
@@ -53427,7 +53446,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="15" thickBot="1">
+    <row r="502" spans="1:8" ht="15.75" thickBot="1">
       <c r="A502" s="14"/>
       <c r="B502" s="14"/>
       <c r="C502" s="14"/>
@@ -53444,7 +53463,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="503" spans="1:8" ht="15" thickBot="1">
+    <row r="503" spans="1:8" ht="15.75" thickBot="1">
       <c r="A503" s="14"/>
       <c r="B503" s="14"/>
       <c r="C503" s="14"/>
@@ -53461,7 +53480,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="504" spans="1:8" ht="15" thickBot="1">
+    <row r="504" spans="1:8" ht="15.75" thickBot="1">
       <c r="A504" s="14"/>
       <c r="B504" s="14"/>
       <c r="C504" s="14"/>
@@ -53478,7 +53497,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="505" spans="1:8" ht="15" thickBot="1">
+    <row r="505" spans="1:8" ht="15.75" thickBot="1">
       <c r="A505" s="14"/>
       <c r="B505" s="14"/>
       <c r="C505" s="14"/>
@@ -53495,7 +53514,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="15" thickBot="1">
+    <row r="506" spans="1:8" ht="15.75" thickBot="1">
       <c r="A506" s="14"/>
       <c r="B506" s="14"/>
       <c r="C506" s="14"/>
@@ -53515,7 +53534,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="507" spans="1:8" ht="15" thickBot="1">
+    <row r="507" spans="1:8" ht="15.75" thickBot="1">
       <c r="A507" s="14"/>
       <c r="B507" s="14"/>
       <c r="C507" s="14"/>
@@ -53532,7 +53551,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="508" spans="1:8" ht="15" thickBot="1">
+    <row r="508" spans="1:8" ht="15.75" thickBot="1">
       <c r="A508" s="14"/>
       <c r="B508" s="14"/>
       <c r="C508" s="14"/>
@@ -53549,7 +53568,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="509" spans="1:8" ht="15" thickBot="1">
+    <row r="509" spans="1:8" ht="15.75" thickBot="1">
       <c r="A509" s="14"/>
       <c r="B509" s="14"/>
       <c r="C509" s="14"/>
@@ -53908,7 +53927,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="529" spans="1:8" ht="15.5">
+    <row r="529" spans="1:8" ht="15.75">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -54147,7 +54166,7 @@
       <c r="G546" s="13"/>
       <c r="H546" s="14"/>
     </row>
-    <row r="547" spans="1:8" ht="15.5">
+    <row r="547" spans="1:8" ht="15.75">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -54163,7 +54182,7 @@
       </c>
       <c r="H547" s="5"/>
     </row>
-    <row r="548" spans="1:8" ht="15.5">
+    <row r="548" spans="1:8" ht="15.75">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -54209,7 +54228,7 @@
       <c r="G551" s="4"/>
       <c r="H551" s="3"/>
     </row>
-    <row r="552" spans="1:8" ht="15.5">
+    <row r="552" spans="1:8" ht="15.75">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -54219,7 +54238,7 @@
       <c r="G552" s="4"/>
       <c r="H552" s="5"/>
     </row>
-    <row r="553" spans="1:8" ht="15.5">
+    <row r="553" spans="1:8" ht="15.75">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -54229,7 +54248,7 @@
       <c r="G553" s="4"/>
       <c r="H553" s="5"/>
     </row>
-    <row r="554" spans="1:8" ht="15.5">
+    <row r="554" spans="1:8" ht="15.75">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -54311,7 +54330,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="559" spans="1:8" ht="26">
+    <row r="559" spans="1:8" ht="26.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -54329,7 +54348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:8" ht="26">
+    <row r="560" spans="1:8" ht="26.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -54593,7 +54612,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="579" spans="1:8" ht="63.5">
+    <row r="579" spans="1:8" ht="64.5">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -54609,7 +54628,7 @@
       </c>
       <c r="H579" s="5"/>
     </row>
-    <row r="580" spans="1:8" ht="26">
+    <row r="580" spans="1:8" ht="26.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -54627,7 +54646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="581" spans="1:8" ht="26">
+    <row r="581" spans="1:8" ht="26.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -54645,7 +54664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="582" spans="1:8" ht="38.5">
+    <row r="582" spans="1:8" ht="39">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -54747,7 +54766,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="589" spans="1:8" ht="15.5">
+    <row r="589" spans="1:8" ht="15.75">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -54763,7 +54782,7 @@
       </c>
       <c r="H589" s="5"/>
     </row>
-    <row r="590" spans="1:8" ht="15.5">
+    <row r="590" spans="1:8" ht="15.75">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -54779,7 +54798,7 @@
       </c>
       <c r="H590" s="5"/>
     </row>
-    <row r="591" spans="1:8" ht="15.5">
+    <row r="591" spans="1:8" ht="15.75">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -54795,7 +54814,7 @@
       </c>
       <c r="H591" s="5"/>
     </row>
-    <row r="592" spans="1:8" ht="15.5">
+    <row r="592" spans="1:8" ht="15.75">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -54811,7 +54830,7 @@
       </c>
       <c r="H592" s="5"/>
     </row>
-    <row r="593" spans="1:8" ht="15.5">
+    <row r="593" spans="1:8" ht="15.75">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -54827,7 +54846,7 @@
       </c>
       <c r="H593" s="5"/>
     </row>
-    <row r="594" spans="1:8" ht="15.5">
+    <row r="594" spans="1:8" ht="15.75">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -54843,7 +54862,7 @@
       </c>
       <c r="H594" s="5"/>
     </row>
-    <row r="595" spans="1:8" ht="15.5">
+    <row r="595" spans="1:8" ht="15.75">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -54859,7 +54878,7 @@
       </c>
       <c r="H595" s="5"/>
     </row>
-    <row r="596" spans="1:8" ht="15.5">
+    <row r="596" spans="1:8" ht="15.75">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -54915,7 +54934,7 @@
       <c r="G601" s="4"/>
       <c r="H601" s="3"/>
     </row>
-    <row r="604" spans="1:8" ht="15.5">
+    <row r="604" spans="1:8" ht="15.75">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -54931,7 +54950,7 @@
       </c>
       <c r="H604" s="5"/>
     </row>
-    <row r="605" spans="1:8" ht="15.5">
+    <row r="605" spans="1:8" ht="15.75">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -54947,7 +54966,7 @@
       </c>
       <c r="H605" s="5"/>
     </row>
-    <row r="606" spans="1:8" ht="15.5">
+    <row r="606" spans="1:8" ht="15.75">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -54963,7 +54982,7 @@
       </c>
       <c r="H606" s="5"/>
     </row>
-    <row r="609" spans="1:8" ht="15.5">
+    <row r="609" spans="1:8" ht="15.75">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -54979,7 +54998,7 @@
       </c>
       <c r="H609" s="5"/>
     </row>
-    <row r="610" spans="1:8" ht="15.5">
+    <row r="610" spans="1:8" ht="15.75">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -54995,7 +55014,7 @@
       </c>
       <c r="H610" s="5"/>
     </row>
-    <row r="611" spans="1:8" ht="15.5">
+    <row r="611" spans="1:8" ht="15.75">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -55065,7 +55084,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="617" spans="1:8" ht="15.5">
+    <row r="617" spans="1:8" ht="15.75">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -55081,7 +55100,7 @@
       </c>
       <c r="H617" s="5"/>
     </row>
-    <row r="618" spans="1:8" ht="15.5">
+    <row r="618" spans="1:8" ht="15.75">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -55097,7 +55116,7 @@
       </c>
       <c r="H618" s="5"/>
     </row>
-    <row r="619" spans="1:8" ht="15.5">
+    <row r="619" spans="1:8" ht="15.75">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -55107,7 +55126,7 @@
       <c r="G619" s="4"/>
       <c r="H619" s="5"/>
     </row>
-    <row r="620" spans="1:8" ht="26">
+    <row r="620" spans="1:8" ht="26.25">
       <c r="A620" s="27"/>
       <c r="B620" s="27"/>
       <c r="C620" s="27"/>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3205" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52567F8F-BC62-4A65-8287-D6DB8C524A64}"/>
+  <xr:revisionPtr revIDLastSave="3225" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A50586-65B9-4B8E-B299-E1099556587E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" firstSheet="1" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'10_FOMD_ERA_readme_OLD'!$A$1:$S$321</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -413,7 +414,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8404" uniqueCount="1654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8468" uniqueCount="1654">
   <si>
     <t>Example</t>
   </si>
@@ -13424,14 +13425,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487E46BC-52D3-4EF1-8B98-2DA697255E52}">
   <dimension ref="A1:PS2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="5" width="23.140625" customWidth="1"/>
+    <col min="1" max="2" width="23.1796875" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
+    <col min="4" max="5" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:435" s="149" customFormat="1" ht="60.75" thickBot="1">
+    <row r="1" spans="1:435" s="149" customFormat="1" ht="58.5" thickBot="1">
       <c r="A1" s="62" t="s">
         <v>157</v>
       </c>
@@ -14524,7 +14525,7 @@
       <c r="PR1" s="144"/>
       <c r="PS1" s="144"/>
     </row>
-    <row r="2" spans="1:435" ht="15.75">
+    <row r="2" spans="1:435" ht="15.5">
       <c r="A2" s="60"/>
       <c r="B2" s="1"/>
       <c r="C2" s="60"/>
@@ -14543,19 +14544,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}">
   <dimension ref="A1:S616"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" customWidth="1"/>
-    <col min="7" max="13" width="25.42578125" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" customWidth="1"/>
-    <col min="15" max="15" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="34.453125" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="6" max="6" width="32.81640625" customWidth="1"/>
+    <col min="7" max="13" width="25.453125" customWidth="1"/>
+    <col min="14" max="14" width="20.54296875" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="121.85546875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="121.81640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -14608,7 +14609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="24.95" customHeight="1">
+    <row r="2" spans="1:18" ht="25" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>902</v>
       </c>
@@ -14646,7 +14647,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75">
+    <row r="3" spans="1:18" ht="15.5">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14751,7 +14752,7 @@
       <c r="Q5" s="46"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75">
+    <row r="6" spans="1:18" ht="15.5">
       <c r="A6" s="3" t="s">
         <v>903</v>
       </c>
@@ -14825,7 +14826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75">
+    <row r="8" spans="1:18" ht="15.5">
       <c r="A8" s="3" t="s">
         <v>905</v>
       </c>
@@ -14861,7 +14862,7 @@
       </c>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75">
+    <row r="9" spans="1:18" ht="16">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -15127,7 +15128,7 @@
       </c>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75">
+    <row r="16" spans="1:18" ht="15.5">
       <c r="A16" s="3" t="s">
         <v>909</v>
       </c>
@@ -15163,7 +15164,7 @@
       </c>
       <c r="R16" s="5"/>
     </row>
-    <row r="17" spans="1:19" ht="15.75">
+    <row r="17" spans="1:19" ht="15.5">
       <c r="A17" s="3" t="s">
         <v>910</v>
       </c>
@@ -15199,7 +15200,7 @@
       </c>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75">
+    <row r="18" spans="1:19" ht="15.5">
       <c r="A18" s="3" t="s">
         <v>911</v>
       </c>
@@ -15310,7 +15311,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" thickBot="1">
+    <row r="21" spans="1:19" ht="15" thickBot="1">
       <c r="A21" s="3" t="s">
         <v>913</v>
       </c>
@@ -15345,7 +15346,7 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1">
+    <row r="22" spans="1:19" ht="15" thickBot="1">
       <c r="A22" s="75" t="s">
         <v>1003</v>
       </c>
@@ -15425,7 +15426,7 @@
       </c>
       <c r="S23" s="4"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1">
+    <row r="24" spans="1:19" ht="15" thickBot="1">
       <c r="A24" s="75" t="s">
         <v>1003</v>
       </c>
@@ -15464,7 +15465,7 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" thickBot="1">
+    <row r="25" spans="1:19" ht="15" thickBot="1">
       <c r="A25" s="3" t="s">
         <v>915</v>
       </c>
@@ -15497,7 +15498,7 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" thickBot="1">
+    <row r="26" spans="1:19" ht="15" thickBot="1">
       <c r="A26" s="3" t="s">
         <v>916</v>
       </c>
@@ -15530,7 +15531,7 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:19" ht="16.5" thickBot="1">
+    <row r="27" spans="1:19" ht="16" thickBot="1">
       <c r="A27" t="s">
         <v>1044</v>
       </c>
@@ -15762,7 +15763,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15.75">
+    <row r="33" spans="1:18" ht="16">
       <c r="A33" t="s">
         <v>1045</v>
       </c>
@@ -15906,7 +15907,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15.75">
+    <row r="36" spans="1:18" ht="16">
       <c r="A36" t="s">
         <v>1046</v>
       </c>
@@ -16191,7 +16192,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15.75">
+    <row r="43" spans="1:18" ht="16">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -16293,7 +16294,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15.75">
+    <row r="46" spans="1:18" ht="16">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -16329,7 +16330,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15.75" thickBot="1">
+    <row r="47" spans="1:18" ht="15" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -16361,7 +16362,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15.75" thickBot="1">
+    <row r="48" spans="1:18" ht="15" thickBot="1">
       <c r="A48" s="3" t="s">
         <v>1062</v>
       </c>
@@ -16398,7 +16399,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15.75">
+    <row r="49" spans="1:18" ht="16">
       <c r="A49" s="3"/>
       <c r="B49" s="87" t="s">
         <v>1070</v>
@@ -16552,7 +16553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="16.5" thickBot="1">
+    <row r="53" spans="1:18" ht="16" thickBot="1">
       <c r="A53" s="3" t="s">
         <v>1018</v>
       </c>
@@ -16590,7 +16591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="16.5" thickBot="1">
+    <row r="54" spans="1:18" ht="16" thickBot="1">
       <c r="A54" s="3" t="s">
         <v>1063</v>
       </c>
@@ -16628,7 +16629,7 @@
       </c>
       <c r="R54" s="5"/>
     </row>
-    <row r="55" spans="1:18" ht="15.75">
+    <row r="55" spans="1:18" ht="16">
       <c r="A55" s="3"/>
       <c r="B55" s="87" t="s">
         <v>1070</v>
@@ -16782,7 +16783,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15.75">
+    <row r="59" spans="1:18" ht="15.5">
       <c r="A59" s="3" t="s">
         <v>1022</v>
       </c>
@@ -16820,7 +16821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15.75">
+    <row r="60" spans="1:18" ht="15.5">
       <c r="A60" t="s">
         <v>1068</v>
       </c>
@@ -16885,7 +16886,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15.75">
+    <row r="62" spans="1:18" ht="16">
       <c r="A62" t="s">
         <v>1066</v>
       </c>
@@ -17069,7 +17070,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15.75">
+    <row r="67" spans="1:18" ht="16">
       <c r="A67" t="s">
         <v>1067</v>
       </c>
@@ -17287,7 +17288,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15.75">
+    <row r="73" spans="1:18" ht="15.5">
       <c r="A73" s="3" t="s">
         <v>1024</v>
       </c>
@@ -17385,7 +17386,7 @@
       <c r="Q75"/>
       <c r="R75" s="31"/>
     </row>
-    <row r="76" spans="1:18" ht="15.75">
+    <row r="76" spans="1:18" ht="15.5">
       <c r="A76" t="s">
         <v>1046</v>
       </c>
@@ -17419,7 +17420,7 @@
       </c>
       <c r="R76" s="5"/>
     </row>
-    <row r="77" spans="1:18" ht="15.75">
+    <row r="77" spans="1:18" ht="15.5">
       <c r="A77" s="3" t="s">
         <v>1025</v>
       </c>
@@ -17491,7 +17492,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15.75">
+    <row r="79" spans="1:18" ht="15.5">
       <c r="A79" s="3" t="s">
         <v>1061</v>
       </c>
@@ -17527,7 +17528,7 @@
       </c>
       <c r="R79" s="5"/>
     </row>
-    <row r="80" spans="1:18" ht="15.75">
+    <row r="80" spans="1:18" ht="15.5">
       <c r="A80" s="3"/>
       <c r="B80" s="93"/>
       <c r="C80" s="93"/>
@@ -17822,7 +17823,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1">
+    <row r="89" spans="1:18" ht="15" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -17850,7 +17851,7 @@
       <c r="Q89"/>
       <c r="R89" s="31"/>
     </row>
-    <row r="90" spans="1:18" ht="15.75" thickBot="1">
+    <row r="90" spans="1:18" ht="15" thickBot="1">
       <c r="A90" t="s">
         <v>1084</v>
       </c>
@@ -17923,7 +17924,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15.75" thickBot="1">
+    <row r="92" spans="1:18" ht="15" thickBot="1">
       <c r="A92" s="75" t="s">
         <v>1003</v>
       </c>
@@ -17960,7 +17961,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15.75" thickBot="1">
+    <row r="93" spans="1:18" ht="15" thickBot="1">
       <c r="A93" s="75" t="s">
         <v>1003</v>
       </c>
@@ -17997,7 +17998,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15.75" thickBot="1">
+    <row r="94" spans="1:18" ht="15" thickBot="1">
       <c r="A94" s="3" t="s">
         <v>896</v>
       </c>
@@ -18032,7 +18033,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="16.5" thickBot="1">
+    <row r="95" spans="1:18" ht="16" thickBot="1">
       <c r="A95" t="s">
         <v>1086</v>
       </c>
@@ -18068,7 +18069,7 @@
       </c>
       <c r="R95" s="5"/>
     </row>
-    <row r="96" spans="1:18" ht="15.75" thickBot="1">
+    <row r="96" spans="1:18" ht="15" thickBot="1">
       <c r="A96" s="3" t="s">
         <v>895</v>
       </c>
@@ -18103,7 +18104,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15.75" thickBot="1">
+    <row r="97" spans="1:18" ht="15" thickBot="1">
       <c r="A97" t="s">
         <v>1085</v>
       </c>
@@ -18136,7 +18137,7 @@
       </c>
       <c r="Q97"/>
     </row>
-    <row r="98" spans="1:18" ht="16.5" thickBot="1">
+    <row r="98" spans="1:18" ht="16" thickBot="1">
       <c r="A98" s="3"/>
       <c r="B98" s="89" t="s">
         <v>1089</v>
@@ -18174,7 +18175,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15.75" thickBot="1">
+    <row r="99" spans="1:18" ht="15" thickBot="1">
       <c r="A99" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18214,7 +18215,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15.75" thickBot="1">
+    <row r="100" spans="1:18" ht="15" thickBot="1">
       <c r="A100" s="75" t="s">
         <v>1003</v>
       </c>
@@ -18254,7 +18255,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="16.5" thickBot="1">
+    <row r="101" spans="1:18" ht="16" thickBot="1">
       <c r="A101" s="3" t="s">
         <v>894</v>
       </c>
@@ -18292,7 +18293,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="16.5" thickBot="1">
+    <row r="102" spans="1:18" ht="16" thickBot="1">
       <c r="A102" t="s">
         <v>1087</v>
       </c>
@@ -18330,7 +18331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15.75" thickBot="1">
+    <row r="103" spans="1:18" ht="15" thickBot="1">
       <c r="A103" s="3" t="s">
         <v>893</v>
       </c>
@@ -18399,7 +18400,7 @@
       <c r="P104" s="3"/>
       <c r="Q104"/>
     </row>
-    <row r="105" spans="1:18" ht="15.75">
+    <row r="105" spans="1:18" ht="16">
       <c r="A105" t="s">
         <v>1227</v>
       </c>
@@ -18439,7 +18440,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15.75">
+    <row r="106" spans="1:18" ht="15.5">
       <c r="A106" t="s">
         <v>1091</v>
       </c>
@@ -18475,7 +18476,7 @@
       </c>
       <c r="R106" s="5"/>
     </row>
-    <row r="107" spans="1:18" ht="15.75">
+    <row r="107" spans="1:18" ht="15.5">
       <c r="A107" t="s">
         <v>1093</v>
       </c>
@@ -18510,7 +18511,7 @@
       </c>
       <c r="R107" s="5"/>
     </row>
-    <row r="108" spans="1:18" ht="15.75">
+    <row r="108" spans="1:18" ht="15.5">
       <c r="A108" s="1"/>
       <c r="B108" s="97" t="s">
         <v>1232</v>
@@ -18546,7 +18547,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15.75">
+    <row r="109" spans="1:18" ht="15.5">
       <c r="A109" s="92" t="s">
         <v>891</v>
       </c>
@@ -18578,7 +18579,7 @@
       <c r="Q109"/>
       <c r="R109" s="5"/>
     </row>
-    <row r="110" spans="1:18" ht="15.75">
+    <row r="110" spans="1:18" ht="16">
       <c r="A110" t="s">
         <v>1227</v>
       </c>
@@ -18618,7 +18619,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15.75">
+    <row r="111" spans="1:18" ht="15.5">
       <c r="A111" t="s">
         <v>1092</v>
       </c>
@@ -18656,7 +18657,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15.75">
+    <row r="112" spans="1:18" ht="15.5">
       <c r="A112" t="s">
         <v>1094</v>
       </c>
@@ -18763,7 +18764,7 @@
       </c>
       <c r="Q114"/>
     </row>
-    <row r="115" spans="1:18" ht="15.75">
+    <row r="115" spans="1:18" ht="16">
       <c r="A115" s="1" t="s">
         <v>1301</v>
       </c>
@@ -18931,7 +18932,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15.75" thickBot="1">
+    <row r="119" spans="1:18" ht="15" thickBot="1">
       <c r="A119" s="1" t="s">
         <v>1237</v>
       </c>
@@ -19084,7 +19085,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15.75" thickBot="1">
+    <row r="123" spans="1:18" ht="15" thickBot="1">
       <c r="A123" s="75" t="s">
         <v>1003</v>
       </c>
@@ -19124,7 +19125,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15.75" thickBot="1">
+    <row r="124" spans="1:18" ht="15" thickBot="1">
       <c r="A124" t="s">
         <v>1257</v>
       </c>
@@ -19153,7 +19154,7 @@
       <c r="P124" s="3"/>
       <c r="Q124"/>
     </row>
-    <row r="125" spans="1:18" ht="15.75" thickBot="1">
+    <row r="125" spans="1:18" ht="15" thickBot="1">
       <c r="A125" s="1" t="s">
         <v>1298</v>
       </c>
@@ -19195,7 +19196,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15.75" thickBot="1">
+    <row r="126" spans="1:18" ht="15" thickBot="1">
       <c r="A126" s="92" t="s">
         <v>1274</v>
       </c>
@@ -19235,7 +19236,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15.75" thickBot="1">
+    <row r="127" spans="1:18" ht="15" thickBot="1">
       <c r="A127" t="s">
         <v>1279</v>
       </c>
@@ -19273,7 +19274,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15.75" thickBot="1">
+    <row r="128" spans="1:18" ht="15" thickBot="1">
       <c r="A128" t="s">
         <v>1283</v>
       </c>
@@ -19311,7 +19312,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15.75" thickBot="1">
+    <row r="129" spans="1:18" ht="15" thickBot="1">
       <c r="A129" t="s">
         <v>1284</v>
       </c>
@@ -19349,7 +19350,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15.75" thickBot="1">
+    <row r="130" spans="1:18" ht="15" thickBot="1">
       <c r="A130" s="1" t="s">
         <v>881</v>
       </c>
@@ -19385,7 +19386,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15.75" thickBot="1">
+    <row r="131" spans="1:18" ht="15" thickBot="1">
       <c r="A131" t="s">
         <v>882</v>
       </c>
@@ -19421,7 +19422,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15.75" thickBot="1">
+    <row r="132" spans="1:18" ht="15" thickBot="1">
       <c r="A132" s="1" t="s">
         <v>883</v>
       </c>
@@ -19457,7 +19458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" thickBot="1">
+    <row r="133" spans="1:18" ht="15" thickBot="1">
       <c r="A133" s="1" t="s">
         <v>884</v>
       </c>
@@ -19493,7 +19494,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" thickBot="1">
+    <row r="134" spans="1:18" ht="15" thickBot="1">
       <c r="A134" s="1" t="s">
         <v>885</v>
       </c>
@@ -19529,7 +19530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15.75" thickBot="1">
+    <row r="135" spans="1:18" ht="15" thickBot="1">
       <c r="A135" t="s">
         <v>1269</v>
       </c>
@@ -19565,7 +19566,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15.75" thickBot="1">
+    <row r="136" spans="1:18" ht="15" thickBot="1">
       <c r="A136" s="92" t="s">
         <v>1274</v>
       </c>
@@ -19635,7 +19636,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" thickBot="1">
+    <row r="138" spans="1:18" ht="15" thickBot="1">
       <c r="A138" t="s">
         <v>1283</v>
       </c>
@@ -19672,7 +19673,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15.75" thickBot="1">
+    <row r="139" spans="1:18" ht="15" thickBot="1">
       <c r="A139" t="s">
         <v>1284</v>
       </c>
@@ -19709,7 +19710,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15.75" thickBot="1">
+    <row r="140" spans="1:18" ht="15" thickBot="1">
       <c r="A140" t="s">
         <v>897</v>
       </c>
@@ -19742,7 +19743,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15.75" thickBot="1">
+    <row r="141" spans="1:18" ht="15" thickBot="1">
       <c r="A141" s="92" t="s">
         <v>1259</v>
       </c>
@@ -19775,7 +19776,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15.75" thickBot="1">
+    <row r="142" spans="1:18" ht="15" thickBot="1">
       <c r="A142" t="s">
         <v>1260</v>
       </c>
@@ -19808,7 +19809,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15.75" thickBot="1">
+    <row r="143" spans="1:18" ht="15" thickBot="1">
       <c r="A143" t="s">
         <v>1264</v>
       </c>
@@ -19841,7 +19842,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15.75" thickBot="1">
+    <row r="144" spans="1:18" ht="15" thickBot="1">
       <c r="A144" t="s">
         <v>1267</v>
       </c>
@@ -19875,7 +19876,7 @@
       </c>
       <c r="R144" s="41"/>
     </row>
-    <row r="145" spans="1:18" ht="15.75" thickBot="1">
+    <row r="145" spans="1:18" ht="15" thickBot="1">
       <c r="A145" t="s">
         <v>1258</v>
       </c>
@@ -19905,7 +19906,7 @@
       <c r="Q145"/>
       <c r="R145" s="41"/>
     </row>
-    <row r="146" spans="1:18" ht="15.75" thickBot="1">
+    <row r="146" spans="1:18" ht="15" thickBot="1">
       <c r="A146" s="1" t="s">
         <v>1299</v>
       </c>
@@ -19947,7 +19948,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15.75" thickBot="1">
+    <row r="147" spans="1:18" ht="15" thickBot="1">
       <c r="A147" s="92" t="s">
         <v>1277</v>
       </c>
@@ -19984,7 +19985,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15.75" thickBot="1">
+    <row r="148" spans="1:18" ht="15" thickBot="1">
       <c r="A148" t="s">
         <v>1280</v>
       </c>
@@ -20020,7 +20021,7 @@
       </c>
       <c r="R148" s="39"/>
     </row>
-    <row r="149" spans="1:18" ht="15.75" thickBot="1">
+    <row r="149" spans="1:18" ht="15" thickBot="1">
       <c r="A149" t="s">
         <v>1291</v>
       </c>
@@ -20056,7 +20057,7 @@
       </c>
       <c r="R149" s="40"/>
     </row>
-    <row r="150" spans="1:18" ht="15.75" thickBot="1">
+    <row r="150" spans="1:18" ht="15" thickBot="1">
       <c r="A150" t="s">
         <v>1292</v>
       </c>
@@ -20092,7 +20093,7 @@
       </c>
       <c r="R150" s="32"/>
     </row>
-    <row r="151" spans="1:18" ht="15.75" thickBot="1">
+    <row r="151" spans="1:18" ht="15" thickBot="1">
       <c r="A151" s="1" t="s">
         <v>886</v>
       </c>
@@ -20125,7 +20126,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15.75" thickBot="1">
+    <row r="152" spans="1:18" ht="15" thickBot="1">
       <c r="A152" s="1" t="s">
         <v>887</v>
       </c>
@@ -20158,7 +20159,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15.75" thickBot="1">
+    <row r="153" spans="1:18" ht="15" thickBot="1">
       <c r="A153" s="1" t="s">
         <v>888</v>
       </c>
@@ -20191,7 +20192,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15.75" thickBot="1">
+    <row r="154" spans="1:18" ht="15" thickBot="1">
       <c r="A154" s="1" t="s">
         <v>889</v>
       </c>
@@ -20226,7 +20227,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15.75" thickBot="1">
+    <row r="155" spans="1:18" ht="15" thickBot="1">
       <c r="A155" s="1" t="s">
         <v>890</v>
       </c>
@@ -20259,7 +20260,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15.75" thickBot="1">
+    <row r="156" spans="1:18" ht="15" thickBot="1">
       <c r="A156" t="s">
         <v>1270</v>
       </c>
@@ -20292,7 +20293,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15.75" thickBot="1">
+    <row r="157" spans="1:18" ht="15" thickBot="1">
       <c r="A157" s="92" t="s">
         <v>1277</v>
       </c>
@@ -20368,7 +20369,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15.75" thickBot="1">
+    <row r="159" spans="1:18" ht="15" thickBot="1">
       <c r="A159" t="s">
         <v>1291</v>
       </c>
@@ -20408,7 +20409,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15.75" thickBot="1">
+    <row r="160" spans="1:18" ht="15" thickBot="1">
       <c r="A160" t="s">
         <v>1292</v>
       </c>
@@ -20448,7 +20449,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15.75" thickBot="1">
+    <row r="161" spans="1:18" ht="15" thickBot="1">
       <c r="A161" t="s">
         <v>898</v>
       </c>
@@ -20484,7 +20485,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15.75" thickBot="1">
+    <row r="162" spans="1:18" ht="15" thickBot="1">
       <c r="A162" s="92" t="s">
         <v>1261</v>
       </c>
@@ -20520,7 +20521,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15.75" thickBot="1">
+    <row r="163" spans="1:18" ht="15" thickBot="1">
       <c r="A163" t="s">
         <v>1262</v>
       </c>
@@ -20556,7 +20557,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15.75" thickBot="1">
+    <row r="164" spans="1:18" ht="15" thickBot="1">
       <c r="A164" t="s">
         <v>1263</v>
       </c>
@@ -20592,7 +20593,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15.75" thickBot="1">
+    <row r="165" spans="1:18" ht="15" thickBot="1">
       <c r="A165" t="s">
         <v>1268</v>
       </c>
@@ -20628,7 +20629,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15.75" thickBot="1">
+    <row r="166" spans="1:18" ht="15" thickBot="1">
       <c r="A166" t="s">
         <v>1134</v>
       </c>
@@ -20664,7 +20665,7 @@
       </c>
       <c r="R166" s="41"/>
     </row>
-    <row r="167" spans="1:18" ht="15.75" thickBot="1">
+    <row r="167" spans="1:18" ht="15" thickBot="1">
       <c r="A167" t="s">
         <v>1130</v>
       </c>
@@ -20700,7 +20701,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15.75" thickBot="1">
+    <row r="168" spans="1:18" ht="15" thickBot="1">
       <c r="A168" t="s">
         <v>1145</v>
       </c>
@@ -20746,7 +20747,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15.75" thickBot="1">
+    <row r="169" spans="1:18" ht="15" thickBot="1">
       <c r="A169" t="s">
         <v>1141</v>
       </c>
@@ -20787,7 +20788,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15.75" thickBot="1">
+    <row r="170" spans="1:18" ht="15" thickBot="1">
       <c r="A170" t="s">
         <v>1135</v>
       </c>
@@ -20822,7 +20823,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15.75" thickBot="1">
+    <row r="171" spans="1:18" ht="15" thickBot="1">
       <c r="A171" t="s">
         <v>1131</v>
       </c>
@@ -20858,7 +20859,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15.75" thickBot="1">
+    <row r="172" spans="1:18" ht="15" thickBot="1">
       <c r="A172" t="s">
         <v>1146</v>
       </c>
@@ -20904,7 +20905,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15.75" thickBot="1">
+    <row r="173" spans="1:18" ht="15" thickBot="1">
       <c r="A173" t="s">
         <v>1142</v>
       </c>
@@ -20945,7 +20946,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15.75" thickBot="1">
+    <row r="174" spans="1:18" ht="15" thickBot="1">
       <c r="A174" t="s">
         <v>1246</v>
       </c>
@@ -20974,7 +20975,7 @@
       <c r="P174" s="17"/>
       <c r="Q174"/>
     </row>
-    <row r="175" spans="1:18" ht="15.75" thickBot="1">
+    <row r="175" spans="1:18" ht="15" thickBot="1">
       <c r="A175" s="48" t="s">
         <v>1245</v>
       </c>
@@ -21014,7 +21015,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15.75" thickBot="1">
+    <row r="176" spans="1:18" ht="15" thickBot="1">
       <c r="A176" t="s">
         <v>1248</v>
       </c>
@@ -21043,7 +21044,7 @@
       <c r="P176" s="17"/>
       <c r="Q176" s="47"/>
     </row>
-    <row r="177" spans="1:18" ht="15.75" thickBot="1">
+    <row r="177" spans="1:18" ht="15" thickBot="1">
       <c r="A177" t="s">
         <v>1252</v>
       </c>
@@ -21074,7 +21075,7 @@
       <c r="P177" s="17"/>
       <c r="Q177" s="47"/>
     </row>
-    <row r="178" spans="1:18" ht="15.75" thickBot="1">
+    <row r="178" spans="1:18" ht="15" thickBot="1">
       <c r="A178" t="s">
         <v>1250</v>
       </c>
@@ -21112,7 +21113,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15.75" thickBot="1">
+    <row r="179" spans="1:18" ht="15" thickBot="1">
       <c r="A179" t="s">
         <v>1247</v>
       </c>
@@ -21141,7 +21142,7 @@
       <c r="P179" s="17"/>
       <c r="Q179" s="47"/>
     </row>
-    <row r="180" spans="1:18" ht="15.75" thickBot="1">
+    <row r="180" spans="1:18" ht="15" thickBot="1">
       <c r="A180" s="48" t="s">
         <v>1256</v>
       </c>
@@ -21185,7 +21186,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15.75" thickBot="1">
+    <row r="181" spans="1:18" ht="15" thickBot="1">
       <c r="A181" t="s">
         <v>1249</v>
       </c>
@@ -21215,7 +21216,7 @@
       <c r="Q181"/>
       <c r="R181" s="69"/>
     </row>
-    <row r="182" spans="1:18" ht="15.75" thickBot="1">
+    <row r="182" spans="1:18" ht="15" thickBot="1">
       <c r="A182" t="s">
         <v>1253</v>
       </c>
@@ -21247,7 +21248,7 @@
       <c r="Q182"/>
       <c r="R182" s="69"/>
     </row>
-    <row r="183" spans="1:18" ht="15.75" thickBot="1">
+    <row r="183" spans="1:18" ht="15" thickBot="1">
       <c r="A183" t="s">
         <v>1251</v>
       </c>
@@ -21285,7 +21286,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15.75" thickBot="1">
+    <row r="184" spans="1:18" ht="15" thickBot="1">
       <c r="A184" t="s">
         <v>1147</v>
       </c>
@@ -21314,7 +21315,7 @@
       <c r="P184" s="17"/>
       <c r="Q184"/>
     </row>
-    <row r="185" spans="1:18" ht="15.75" thickBot="1">
+    <row r="185" spans="1:18" ht="15" thickBot="1">
       <c r="A185" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21354,7 +21355,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15.75" thickBot="1">
+    <row r="186" spans="1:18" ht="15" thickBot="1">
       <c r="A186" s="1" t="s">
         <v>936</v>
       </c>
@@ -21392,7 +21393,7 @@
       </c>
       <c r="R186" s="69"/>
     </row>
-    <row r="187" spans="1:18" ht="15.75" thickBot="1">
+    <row r="187" spans="1:18" ht="15" thickBot="1">
       <c r="A187" s="1" t="s">
         <v>937</v>
       </c>
@@ -21430,7 +21431,7 @@
       </c>
       <c r="R187" s="69"/>
     </row>
-    <row r="188" spans="1:18" ht="15.75" thickBot="1">
+    <row r="188" spans="1:18" ht="15" thickBot="1">
       <c r="A188" s="1" t="s">
         <v>938</v>
       </c>
@@ -21463,7 +21464,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15.75" thickBot="1">
+    <row r="189" spans="1:18" ht="15" thickBot="1">
       <c r="A189" s="1" t="s">
         <v>939</v>
       </c>
@@ -21497,7 +21498,7 @@
       </c>
       <c r="R189" s="43"/>
     </row>
-    <row r="190" spans="1:18" ht="15.75" thickBot="1">
+    <row r="190" spans="1:18" ht="15" thickBot="1">
       <c r="A190" s="1" t="s">
         <v>940</v>
       </c>
@@ -21529,7 +21530,7 @@
       <c r="Q190"/>
       <c r="R190" s="73"/>
     </row>
-    <row r="191" spans="1:18" ht="15.75" thickBot="1">
+    <row r="191" spans="1:18" ht="15" thickBot="1">
       <c r="A191" s="1" t="s">
         <v>941</v>
       </c>
@@ -21565,7 +21566,7 @@
       </c>
       <c r="R191" s="44"/>
     </row>
-    <row r="192" spans="1:18" ht="15.75" thickBot="1">
+    <row r="192" spans="1:18" ht="15" thickBot="1">
       <c r="A192" s="1" t="s">
         <v>942</v>
       </c>
@@ -21599,7 +21600,7 @@
       <c r="Q192"/>
       <c r="R192" s="44"/>
     </row>
-    <row r="193" spans="1:18" ht="15.75" thickBot="1">
+    <row r="193" spans="1:18" ht="15" thickBot="1">
       <c r="A193" s="1" t="s">
         <v>943</v>
       </c>
@@ -21637,7 +21638,7 @@
       </c>
       <c r="R193" s="44"/>
     </row>
-    <row r="194" spans="1:18" ht="15.75" thickBot="1">
+    <row r="194" spans="1:18" ht="15" thickBot="1">
       <c r="A194" t="s">
         <v>1153</v>
       </c>
@@ -21670,7 +21671,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15.75" thickBot="1">
+    <row r="195" spans="1:18" ht="15" thickBot="1">
       <c r="A195" t="s">
         <v>1149</v>
       </c>
@@ -21703,7 +21704,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15.75" thickBot="1">
+    <row r="196" spans="1:18" ht="15" thickBot="1">
       <c r="A196" t="s">
         <v>1151</v>
       </c>
@@ -21736,7 +21737,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15.75" thickBot="1">
+    <row r="197" spans="1:18" ht="15" thickBot="1">
       <c r="A197" t="s">
         <v>1156</v>
       </c>
@@ -21769,7 +21770,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15.75" thickBot="1">
+    <row r="198" spans="1:18" ht="15" thickBot="1">
       <c r="A198" t="s">
         <v>1163</v>
       </c>
@@ -21807,7 +21808,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15.75" thickBot="1">
+    <row r="199" spans="1:18" ht="15" thickBot="1">
       <c r="A199" t="s">
         <v>1160</v>
       </c>
@@ -21843,7 +21844,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15.75" thickBot="1">
+    <row r="200" spans="1:18" ht="15" thickBot="1">
       <c r="A200" t="s">
         <v>1148</v>
       </c>
@@ -21872,7 +21873,7 @@
       <c r="P200" s="17"/>
       <c r="Q200" s="47"/>
     </row>
-    <row r="201" spans="1:18" ht="15.75" thickBot="1">
+    <row r="201" spans="1:18" ht="15" thickBot="1">
       <c r="A201" s="1" t="s">
         <v>1170</v>
       </c>
@@ -21912,7 +21913,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15.75" thickBot="1">
+    <row r="202" spans="1:18" ht="15" thickBot="1">
       <c r="A202" s="1" t="s">
         <v>944</v>
       </c>
@@ -21950,7 +21951,7 @@
       </c>
       <c r="R202" s="73"/>
     </row>
-    <row r="203" spans="1:18" ht="15.75" thickBot="1">
+    <row r="203" spans="1:18" ht="15" thickBot="1">
       <c r="A203" s="1" t="s">
         <v>945</v>
       </c>
@@ -21988,7 +21989,7 @@
       </c>
       <c r="R203" s="73"/>
     </row>
-    <row r="204" spans="1:18" ht="15.75" thickBot="1">
+    <row r="204" spans="1:18" ht="15" thickBot="1">
       <c r="A204" s="1" t="s">
         <v>946</v>
       </c>
@@ -22027,7 +22028,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15.75" thickBot="1">
+    <row r="205" spans="1:18" ht="15" thickBot="1">
       <c r="A205" s="1" t="s">
         <v>947</v>
       </c>
@@ -22069,7 +22070,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15.75" thickBot="1">
+    <row r="206" spans="1:18" ht="15" thickBot="1">
       <c r="A206" s="1" t="s">
         <v>948</v>
       </c>
@@ -22103,7 +22104,7 @@
       <c r="Q206"/>
       <c r="R206" s="73"/>
     </row>
-    <row r="207" spans="1:18" ht="15.75" thickBot="1">
+    <row r="207" spans="1:18" ht="15" thickBot="1">
       <c r="A207" s="1" t="s">
         <v>949</v>
       </c>
@@ -22143,7 +22144,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15.75" thickBot="1">
+    <row r="208" spans="1:18" ht="15" thickBot="1">
       <c r="A208" s="1" t="s">
         <v>950</v>
       </c>
@@ -22177,7 +22178,7 @@
       <c r="Q208"/>
       <c r="R208" s="44"/>
     </row>
-    <row r="209" spans="1:18" ht="15.75" thickBot="1">
+    <row r="209" spans="1:18" ht="15" thickBot="1">
       <c r="A209" s="1" t="s">
         <v>951</v>
       </c>
@@ -22217,7 +22218,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15.75" thickBot="1">
+    <row r="210" spans="1:18" ht="15" thickBot="1">
       <c r="A210" t="s">
         <v>1154</v>
       </c>
@@ -22250,7 +22251,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15.75" thickBot="1">
+    <row r="211" spans="1:18" ht="15" thickBot="1">
       <c r="A211" t="s">
         <v>1150</v>
       </c>
@@ -22286,7 +22287,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15.75" thickBot="1">
+    <row r="212" spans="1:18" ht="15" thickBot="1">
       <c r="A212" t="s">
         <v>1152</v>
       </c>
@@ -22322,7 +22323,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15.75" thickBot="1">
+    <row r="213" spans="1:18" ht="15" thickBot="1">
       <c r="A213" t="s">
         <v>1157</v>
       </c>
@@ -22358,7 +22359,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15.75" thickBot="1">
+    <row r="214" spans="1:18" ht="15" thickBot="1">
       <c r="A214" t="s">
         <v>1164</v>
       </c>
@@ -22396,7 +22397,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15.75" thickBot="1">
+    <row r="215" spans="1:18" ht="15" thickBot="1">
       <c r="A215" t="s">
         <v>1161</v>
       </c>
@@ -22432,7 +22433,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15.75" thickBot="1">
+    <row r="216" spans="1:18" ht="15" thickBot="1">
       <c r="A216" t="s">
         <v>1095</v>
       </c>
@@ -22504,7 +22505,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15.75" thickBot="1">
+    <row r="218" spans="1:18" ht="15" thickBot="1">
       <c r="A218" t="s">
         <v>1100</v>
       </c>
@@ -22542,7 +22543,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15.75" thickBot="1">
+    <row r="219" spans="1:18" ht="15" thickBot="1">
       <c r="A219" t="s">
         <v>1104</v>
       </c>
@@ -22580,7 +22581,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15.75" thickBot="1">
+    <row r="220" spans="1:18" ht="15" thickBot="1">
       <c r="A220" t="s">
         <v>1102</v>
       </c>
@@ -22612,7 +22613,7 @@
       <c r="Q220" s="47"/>
       <c r="R220" s="29"/>
     </row>
-    <row r="221" spans="1:18" ht="15.75" thickBot="1">
+    <row r="221" spans="1:18" ht="15" thickBot="1">
       <c r="A221" t="s">
         <v>1096</v>
       </c>
@@ -22684,7 +22685,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15.75" thickBot="1">
+    <row r="223" spans="1:18" ht="15" thickBot="1">
       <c r="A223" t="s">
         <v>1101</v>
       </c>
@@ -22722,7 +22723,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15.75" thickBot="1">
+    <row r="224" spans="1:18" ht="15" thickBot="1">
       <c r="A224" t="s">
         <v>1105</v>
       </c>
@@ -22760,7 +22761,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15.75" thickBot="1">
+    <row r="225" spans="1:18" ht="15" thickBot="1">
       <c r="A225" t="s">
         <v>1103</v>
       </c>
@@ -22791,7 +22792,7 @@
       <c r="P225" s="17"/>
       <c r="Q225"/>
     </row>
-    <row r="226" spans="1:18" ht="15.75" thickBot="1">
+    <row r="226" spans="1:18" ht="15" thickBot="1">
       <c r="A226" t="s">
         <v>1112</v>
       </c>
@@ -22896,7 +22897,7 @@
       </c>
       <c r="Q228"/>
     </row>
-    <row r="229" spans="1:18" ht="15.75" thickBot="1">
+    <row r="229" spans="1:18" ht="15" thickBot="1">
       <c r="A229" t="s">
         <v>1122</v>
       </c>
@@ -22932,7 +22933,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15.75" thickBot="1">
+    <row r="230" spans="1:18" ht="15" thickBot="1">
       <c r="A230" t="s">
         <v>1124</v>
       </c>
@@ -22965,7 +22966,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15.75" thickBot="1">
+    <row r="231" spans="1:18" ht="15" thickBot="1">
       <c r="A231" t="s">
         <v>1118</v>
       </c>
@@ -23001,7 +23002,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15.75" thickBot="1">
+    <row r="232" spans="1:18" ht="15" thickBot="1">
       <c r="A232" t="s">
         <v>1116</v>
       </c>
@@ -23032,7 +23033,7 @@
       </c>
       <c r="Q232" s="47"/>
     </row>
-    <row r="233" spans="1:18" ht="15.75" thickBot="1">
+    <row r="233" spans="1:18" ht="15" thickBot="1">
       <c r="A233" t="s">
         <v>1120</v>
       </c>
@@ -23068,7 +23069,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15.75" thickBot="1">
+    <row r="234" spans="1:18" ht="15" thickBot="1">
       <c r="A234" t="s">
         <v>1113</v>
       </c>
@@ -23173,7 +23174,7 @@
       </c>
       <c r="Q236"/>
     </row>
-    <row r="237" spans="1:18" ht="15.75" thickBot="1">
+    <row r="237" spans="1:18" ht="15" thickBot="1">
       <c r="A237" t="s">
         <v>1123</v>
       </c>
@@ -23209,7 +23210,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15.75" thickBot="1">
+    <row r="238" spans="1:18" ht="15" thickBot="1">
       <c r="A238" t="s">
         <v>1125</v>
       </c>
@@ -23242,7 +23243,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15.75" thickBot="1">
+    <row r="239" spans="1:18" ht="15" thickBot="1">
       <c r="A239" t="s">
         <v>1119</v>
       </c>
@@ -23273,7 +23274,7 @@
       </c>
       <c r="Q239" s="48"/>
     </row>
-    <row r="240" spans="1:18" ht="15.75" thickBot="1">
+    <row r="240" spans="1:18" ht="15" thickBot="1">
       <c r="A240" t="s">
         <v>1117</v>
       </c>
@@ -23309,7 +23310,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15.75" thickBot="1">
+    <row r="241" spans="1:18" ht="15" thickBot="1">
       <c r="A241" t="s">
         <v>1121</v>
       </c>
@@ -23342,7 +23343,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15.75" thickBot="1">
+    <row r="242" spans="1:18" ht="15" thickBot="1">
       <c r="A242" t="s">
         <v>976</v>
       </c>
@@ -23371,7 +23372,7 @@
       <c r="P242" s="17"/>
       <c r="Q242"/>
     </row>
-    <row r="243" spans="1:18" ht="15.75" thickBot="1">
+    <row r="243" spans="1:18" ht="15" thickBot="1">
       <c r="A243" s="92" t="s">
         <v>977</v>
       </c>
@@ -23410,7 +23411,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15.75" thickBot="1">
+    <row r="244" spans="1:18" ht="15" thickBot="1">
       <c r="A244" t="s">
         <v>978</v>
       </c>
@@ -23439,7 +23440,7 @@
       <c r="P244" s="17"/>
       <c r="Q244" s="47"/>
     </row>
-    <row r="245" spans="1:18" ht="15.75" thickBot="1">
+    <row r="245" spans="1:18" ht="15" thickBot="1">
       <c r="A245" s="92" t="s">
         <v>979</v>
       </c>
@@ -23478,7 +23479,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15.75" thickBot="1">
+    <row r="246" spans="1:18" ht="15" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -23505,7 +23506,7 @@
       </c>
       <c r="Q246"/>
     </row>
-    <row r="247" spans="1:18" ht="15.75" thickBot="1">
+    <row r="247" spans="1:18" ht="15" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -23534,7 +23535,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15.75" thickBot="1">
+    <row r="248" spans="1:18" ht="15" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -23566,7 +23567,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15.75" thickBot="1">
+    <row r="249" spans="1:18" ht="15" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -23595,7 +23596,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15.75" thickBot="1">
+    <row r="250" spans="1:18" ht="15" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -23624,7 +23625,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15.75" thickBot="1">
+    <row r="251" spans="1:18" ht="15" thickBot="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -23651,7 +23652,7 @@
       </c>
       <c r="Q251"/>
     </row>
-    <row r="252" spans="1:18" ht="15.75" thickBot="1">
+    <row r="252" spans="1:18" ht="15" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -23680,7 +23681,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15.75" thickBot="1">
+    <row r="253" spans="1:18" ht="15" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -23712,7 +23713,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15.75" thickBot="1">
+    <row r="254" spans="1:18" ht="15" thickBot="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -24093,7 +24094,7 @@
       <c r="P264" s="19"/>
       <c r="Q264"/>
     </row>
-    <row r="265" spans="1:17" ht="15.75" thickBot="1">
+    <row r="265" spans="1:17" ht="15" thickBot="1">
       <c r="A265" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24136,7 +24137,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="266" spans="1:17" ht="15.75" thickBot="1">
+    <row r="266" spans="1:17" ht="15" thickBot="1">
       <c r="A266" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24171,7 +24172,7 @@
       <c r="P266" s="19"/>
       <c r="Q266"/>
     </row>
-    <row r="267" spans="1:17" ht="15.75" thickBot="1">
+    <row r="267" spans="1:17" ht="15" thickBot="1">
       <c r="A267" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24206,7 +24207,7 @@
       <c r="P267" s="19"/>
       <c r="Q267"/>
     </row>
-    <row r="268" spans="1:17" ht="15.75" thickBot="1">
+    <row r="268" spans="1:17" ht="15" thickBot="1">
       <c r="A268" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24241,7 +24242,7 @@
       <c r="P268" s="19"/>
       <c r="Q268"/>
     </row>
-    <row r="269" spans="1:17" ht="15.75" thickBot="1">
+    <row r="269" spans="1:17" ht="15" thickBot="1">
       <c r="A269" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24276,7 +24277,7 @@
       <c r="P269" s="19"/>
       <c r="Q269"/>
     </row>
-    <row r="270" spans="1:17" ht="15.75" thickBot="1">
+    <row r="270" spans="1:17" ht="15" thickBot="1">
       <c r="A270" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24311,7 +24312,7 @@
       <c r="P270" s="19"/>
       <c r="Q270"/>
     </row>
-    <row r="271" spans="1:17" ht="15.75" thickBot="1">
+    <row r="271" spans="1:17" ht="15" thickBot="1">
       <c r="A271" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24346,7 +24347,7 @@
       <c r="P271" s="19"/>
       <c r="Q271"/>
     </row>
-    <row r="272" spans="1:17" ht="15.75" thickBot="1">
+    <row r="272" spans="1:17" ht="15" thickBot="1">
       <c r="A272" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24381,7 +24382,7 @@
       <c r="P272" s="19"/>
       <c r="Q272"/>
     </row>
-    <row r="273" spans="1:19" ht="15.75" thickBot="1">
+    <row r="273" spans="1:19" ht="15" thickBot="1">
       <c r="A273" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24416,7 +24417,7 @@
       <c r="P273" s="19"/>
       <c r="Q273"/>
     </row>
-    <row r="274" spans="1:19" ht="15.75" thickBot="1">
+    <row r="274" spans="1:19" ht="15" thickBot="1">
       <c r="A274" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24451,7 +24452,7 @@
       <c r="P274" s="19"/>
       <c r="Q274"/>
     </row>
-    <row r="275" spans="1:19" ht="15.75" thickBot="1">
+    <row r="275" spans="1:19" ht="15" thickBot="1">
       <c r="A275" s="9" t="s">
         <v>1003</v>
       </c>
@@ -24486,7 +24487,7 @@
       <c r="P275" s="19"/>
       <c r="Q275"/>
     </row>
-    <row r="276" spans="1:19" ht="15.75" thickBot="1">
+    <row r="276" spans="1:19" ht="15" thickBot="1">
       <c r="A276" t="s">
         <v>1005</v>
       </c>
@@ -24519,7 +24520,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="277" spans="1:19" ht="15.75" thickBot="1">
+    <row r="277" spans="1:19" ht="15" thickBot="1">
       <c r="A277" t="s">
         <v>1004</v>
       </c>
@@ -24549,7 +24550,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="15.75">
+    <row r="278" spans="1:19" ht="16">
       <c r="A278" s="1"/>
       <c r="B278" s="97" t="s">
         <v>1327</v>
@@ -24657,7 +24658,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="281" spans="1:19" ht="15.75" thickBot="1">
+    <row r="281" spans="1:19" ht="15" thickBot="1">
       <c r="A281" t="s">
         <v>1318</v>
       </c>
@@ -24694,7 +24695,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="282" spans="1:19" ht="15.75" thickBot="1">
+    <row r="282" spans="1:19" ht="15" thickBot="1">
       <c r="A282" s="1" t="s">
         <v>1324</v>
       </c>
@@ -24727,7 +24728,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="283" spans="1:19" ht="15.75">
+    <row r="283" spans="1:19" ht="16">
       <c r="A283" s="1"/>
       <c r="B283" s="97" t="s">
         <v>1328</v>
@@ -24835,7 +24836,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="286" spans="1:19" ht="15.75" thickBot="1">
+    <row r="286" spans="1:19" ht="15" thickBot="1">
       <c r="A286" t="s">
         <v>1319</v>
       </c>
@@ -24869,7 +24870,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="287" spans="1:19" ht="15.75" thickBot="1">
+    <row r="287" spans="1:19" ht="15" thickBot="1">
       <c r="A287" s="1" t="s">
         <v>1325</v>
       </c>
@@ -25373,7 +25374,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="15.75">
+    <row r="301" spans="1:18" ht="16">
       <c r="A301" t="s">
         <v>1179</v>
       </c>
@@ -25413,7 +25414,7 @@
       <c r="Q301" s="3"/>
       <c r="R301" s="3"/>
     </row>
-    <row r="302" spans="1:18" ht="15.75">
+    <row r="302" spans="1:18" ht="16">
       <c r="A302" t="s">
         <v>1181</v>
       </c>
@@ -25495,7 +25496,7 @@
       <c r="Q303" s="3"/>
       <c r="R303" s="3"/>
     </row>
-    <row r="304" spans="1:18" ht="14.45" customHeight="1">
+    <row r="304" spans="1:18" ht="14.5" customHeight="1">
       <c r="A304" t="s">
         <v>1011</v>
       </c>
@@ -25611,7 +25612,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="15.75">
+    <row r="307" spans="1:18" ht="16">
       <c r="A307" t="s">
         <v>1180</v>
       </c>
@@ -25647,7 +25648,7 @@
       <c r="Q307" s="3"/>
       <c r="R307" s="3"/>
     </row>
-    <row r="308" spans="1:18" ht="15.75">
+    <row r="308" spans="1:18" ht="16">
       <c r="A308" t="s">
         <v>1182</v>
       </c>
@@ -25729,7 +25730,7 @@
       <c r="Q309" s="3"/>
       <c r="R309" s="3"/>
     </row>
-    <row r="310" spans="1:18" ht="14.45" customHeight="1" thickBot="1">
+    <row r="310" spans="1:18" ht="14.5" customHeight="1" thickBot="1">
       <c r="A310" t="s">
         <v>1012</v>
       </c>
@@ -25767,7 +25768,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="14.45" customHeight="1" thickBot="1">
+    <row r="311" spans="1:18" ht="14.5" customHeight="1" thickBot="1">
       <c r="A311" t="s">
         <v>1192</v>
       </c>
@@ -25800,7 +25801,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="14.45" customHeight="1">
+    <row r="312" spans="1:18" ht="14.5" customHeight="1">
       <c r="A312" t="s">
         <v>1200</v>
       </c>
@@ -25829,7 +25830,7 @@
       <c r="P312" s="14"/>
       <c r="Q312" s="14"/>
     </row>
-    <row r="313" spans="1:18" ht="14.45" customHeight="1">
+    <row r="313" spans="1:18" ht="14.5" customHeight="1">
       <c r="A313" s="14" t="s">
         <v>1194</v>
       </c>
@@ -25865,7 +25866,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="14.45" customHeight="1">
+    <row r="314" spans="1:18" ht="14.5" customHeight="1">
       <c r="A314" s="14" t="s">
         <v>1202</v>
       </c>
@@ -26181,7 +26182,7 @@
       <c r="Q330" s="3"/>
       <c r="R330" s="3"/>
     </row>
-    <row r="331" spans="1:18" ht="15.75" thickBot="1">
+    <row r="331" spans="1:18" ht="15" thickBot="1">
       <c r="N331" s="14" t="s">
         <v>765</v>
       </c>
@@ -26194,7 +26195,7 @@
       <c r="Q331" s="3"/>
       <c r="R331" s="3"/>
     </row>
-    <row r="332" spans="1:18" ht="26.25" thickBot="1">
+    <row r="332" spans="1:18" ht="26.5" thickBot="1">
       <c r="N332" s="14"/>
       <c r="O332" s="58" t="s">
         <v>836</v>
@@ -26218,7 +26219,7 @@
       <c r="Q333" s="3"/>
       <c r="R333" s="3"/>
     </row>
-    <row r="334" spans="1:18" ht="15.75" thickBot="1">
+    <row r="334" spans="1:18" ht="15" thickBot="1">
       <c r="N334" s="14" t="s">
         <v>765</v>
       </c>
@@ -26231,7 +26232,7 @@
       <c r="Q334" s="3"/>
       <c r="R334" s="3"/>
     </row>
-    <row r="335" spans="1:18" ht="26.25" thickBot="1">
+    <row r="335" spans="1:18" ht="26.5" thickBot="1">
       <c r="N335" s="14"/>
       <c r="O335" s="58" t="s">
         <v>837</v>
@@ -27102,7 +27103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="15.75">
+    <row r="374" spans="1:18" ht="15.5">
       <c r="A374" s="14"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -27252,7 +27253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="15.75">
+    <row r="379" spans="1:18" ht="15.5">
       <c r="A379" s="14"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -27309,7 +27310,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="15.75">
+    <row r="381" spans="1:18" ht="15.5">
       <c r="A381" s="14"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -27394,7 +27395,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="15.75">
+    <row r="384" spans="1:18" ht="15.5">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -27512,7 +27513,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="15.75">
+    <row r="388" spans="1:18" ht="15.5">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -27630,7 +27631,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="15.75">
+    <row r="392" spans="1:18" ht="15.5">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -27658,7 +27659,7 @@
       </c>
       <c r="R392" s="5"/>
     </row>
-    <row r="393" spans="1:18" ht="15.75" thickBot="1">
+    <row r="393" spans="1:18" ht="15" thickBot="1">
       <c r="A393" s="14"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -27688,7 +27689,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="15.75" thickBot="1">
+    <row r="394" spans="1:18" ht="15" thickBot="1">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -27714,7 +27715,7 @@
       <c r="Q394" s="46"/>
       <c r="R394" s="14"/>
     </row>
-    <row r="395" spans="1:18" ht="15.75" thickBot="1">
+    <row r="395" spans="1:18" ht="15" thickBot="1">
       <c r="A395" s="14"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -27740,7 +27741,7 @@
       <c r="Q395" s="46"/>
       <c r="R395" s="14"/>
     </row>
-    <row r="396" spans="1:18" ht="15.75">
+    <row r="396" spans="1:18" ht="15.5">
       <c r="N396" s="14" t="s">
         <v>765</v>
       </c>
@@ -27821,7 +27822,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="15.75">
+    <row r="400" spans="1:18" ht="15.5">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -27911,7 +27912,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="15.75" thickBot="1">
+    <row r="403" spans="1:18" ht="15" thickBot="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14"/>
@@ -27941,7 +27942,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="15.75" thickBot="1">
+    <row r="404" spans="1:18" ht="15" thickBot="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
@@ -27971,7 +27972,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="15.75" thickBot="1">
+    <row r="405" spans="1:18" ht="15" thickBot="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -28001,7 +28002,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="15.75" thickBot="1">
+    <row r="406" spans="1:18" ht="15" thickBot="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14"/>
@@ -28031,7 +28032,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="15.75" thickBot="1">
+    <row r="407" spans="1:18" ht="15" thickBot="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14"/>
@@ -28061,7 +28062,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="15.75" thickBot="1">
+    <row r="408" spans="1:18" ht="15" thickBot="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14"/>
@@ -28091,7 +28092,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="15.75" thickBot="1">
+    <row r="409" spans="1:18" ht="15" thickBot="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -28121,7 +28122,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="15.75" thickBot="1">
+    <row r="410" spans="1:18" ht="15" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -28151,7 +28152,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="15.75" thickBot="1">
+    <row r="411" spans="1:18" ht="15" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -28181,7 +28182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="15.75" thickBot="1">
+    <row r="412" spans="1:18" ht="15" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -28211,7 +28212,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="15.75" thickBot="1">
+    <row r="413" spans="1:18" ht="15" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14"/>
@@ -28241,7 +28242,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="15.75" thickBot="1">
+    <row r="414" spans="1:18" ht="15" thickBot="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -28271,7 +28272,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="15.75" thickBot="1">
+    <row r="415" spans="1:18" ht="15" thickBot="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14"/>
@@ -28298,7 +28299,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="15.75" thickBot="1">
+    <row r="416" spans="1:18" ht="15" thickBot="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14"/>
@@ -28325,7 +28326,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="15.75" thickBot="1">
+    <row r="417" spans="1:18" ht="15" thickBot="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -28352,7 +28353,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="15.75" thickBot="1">
+    <row r="418" spans="1:18" ht="15" thickBot="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14"/>
@@ -28379,7 +28380,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="15.75" thickBot="1">
+    <row r="419" spans="1:18" ht="15" thickBot="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14"/>
@@ -28406,7 +28407,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="15.75" thickBot="1">
+    <row r="420" spans="1:18" ht="15" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -28433,7 +28434,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="15.75" thickBot="1">
+    <row r="421" spans="1:18" ht="15" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -28460,7 +28461,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="15.75" thickBot="1">
+    <row r="422" spans="1:18" ht="15" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -28487,7 +28488,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="15.75" thickBot="1">
+    <row r="423" spans="1:18" ht="15" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -28515,7 +28516,7 @@
       </c>
       <c r="R423" s="41"/>
     </row>
-    <row r="424" spans="1:18" ht="15.75" thickBot="1">
+    <row r="424" spans="1:18" ht="15" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -28545,7 +28546,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="15.75" thickBot="1">
+    <row r="425" spans="1:18" ht="15" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -28575,7 +28576,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="15.75" thickBot="1">
+    <row r="426" spans="1:18" ht="15" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -28605,7 +28606,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="15.75" thickBot="1">
+    <row r="427" spans="1:18" ht="15" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -28635,7 +28636,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="15.75" thickBot="1">
+    <row r="428" spans="1:18" ht="15" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -28665,7 +28666,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="15.75" thickBot="1">
+    <row r="429" spans="1:18" ht="15" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -28695,7 +28696,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="15.75" thickBot="1">
+    <row r="430" spans="1:18" ht="15" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -28725,7 +28726,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="15.75" thickBot="1">
+    <row r="431" spans="1:18" ht="15" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -28755,7 +28756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="15.75" thickBot="1">
+    <row r="432" spans="1:18" ht="15" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -28785,7 +28786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="15.75" thickBot="1">
+    <row r="433" spans="1:18" ht="15" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -28815,7 +28816,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="15.75" thickBot="1">
+    <row r="434" spans="1:18" ht="15" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -28845,7 +28846,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="15.75" thickBot="1">
+    <row r="435" spans="1:18" ht="15" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -28872,7 +28873,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="15.75" thickBot="1">
+    <row r="436" spans="1:18" ht="15" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -28899,7 +28900,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="15.75" thickBot="1">
+    <row r="437" spans="1:18" ht="15" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -28926,7 +28927,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="15.75" thickBot="1">
+    <row r="438" spans="1:18" ht="15" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -28953,7 +28954,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="15.75" thickBot="1">
+    <row r="439" spans="1:18" ht="15" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -28980,7 +28981,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="15.75" thickBot="1">
+    <row r="440" spans="1:18" ht="15" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -29007,7 +29008,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="15.75" thickBot="1">
+    <row r="441" spans="1:18" ht="15" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -29034,7 +29035,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="15.75" thickBot="1">
+    <row r="442" spans="1:18" ht="15" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -29061,7 +29062,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="15.75" thickBot="1">
+    <row r="443" spans="1:18" ht="15" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -29089,7 +29090,7 @@
       </c>
       <c r="R443" s="41"/>
     </row>
-    <row r="444" spans="1:18" ht="15.75" thickBot="1">
+    <row r="444" spans="1:18" ht="15" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -29119,7 +29120,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="15.75" thickBot="1">
+    <row r="445" spans="1:18" ht="15" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -29149,7 +29150,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="15.75" thickBot="1">
+    <row r="446" spans="1:18" ht="15" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -29179,7 +29180,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="15.75" thickBot="1">
+    <row r="447" spans="1:18" ht="15" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -29209,7 +29210,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="15.75" thickBot="1">
+    <row r="448" spans="1:18" ht="15" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -29239,7 +29240,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="15.75" thickBot="1">
+    <row r="449" spans="1:18" ht="15" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -29269,7 +29270,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="15.75" thickBot="1">
+    <row r="450" spans="1:18" ht="15" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -29299,7 +29300,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="15.75" thickBot="1">
+    <row r="451" spans="1:18" ht="15" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -29329,7 +29330,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="15.75" thickBot="1">
+    <row r="452" spans="1:18" ht="15" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -29359,7 +29360,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="15.75" thickBot="1">
+    <row r="453" spans="1:18" ht="15" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -29386,7 +29387,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="15.75" thickBot="1">
+    <row r="454" spans="1:18" ht="15" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -29414,7 +29415,7 @@
       </c>
       <c r="R454" s="43"/>
     </row>
-    <row r="455" spans="1:18" ht="15.75" thickBot="1">
+    <row r="455" spans="1:18" ht="15" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -29442,7 +29443,7 @@
       </c>
       <c r="R455" s="44"/>
     </row>
-    <row r="456" spans="1:18" ht="15.75" thickBot="1">
+    <row r="456" spans="1:18" ht="15" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -29470,7 +29471,7 @@
       </c>
       <c r="R456" s="44"/>
     </row>
-    <row r="457" spans="1:18" ht="15.75" thickBot="1">
+    <row r="457" spans="1:18" ht="15" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -29497,7 +29498,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="15.75" thickBot="1">
+    <row r="458" spans="1:18" ht="15" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -29524,7 +29525,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="15.75" thickBot="1">
+    <row r="459" spans="1:18" ht="15" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -29551,7 +29552,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="15.75" thickBot="1">
+    <row r="460" spans="1:18" ht="15" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -29578,7 +29579,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="15.75" thickBot="1">
+    <row r="461" spans="1:18" ht="15" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -29608,7 +29609,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="15.75" thickBot="1">
+    <row r="462" spans="1:18" ht="15" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -29638,7 +29639,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="15.75" thickBot="1">
+    <row r="463" spans="1:18" ht="15" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -29665,7 +29666,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="15.75" thickBot="1">
+    <row r="464" spans="1:18" ht="15" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -29695,7 +29696,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="15.75" thickBot="1">
+    <row r="465" spans="1:18" ht="15" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -29725,7 +29726,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="15.75" thickBot="1">
+    <row r="466" spans="1:18" ht="15" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -29755,7 +29756,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="15.75" thickBot="1">
+    <row r="467" spans="1:18" ht="15" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -29782,7 +29783,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="15.75" thickBot="1">
+    <row r="468" spans="1:18" ht="15" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -29812,7 +29813,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="15.75" thickBot="1">
+    <row r="469" spans="1:18" ht="15" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -29842,7 +29843,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="15.75" thickBot="1">
+    <row r="470" spans="1:18" ht="15" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -29872,7 +29873,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="15.75" thickBot="1">
+    <row r="471" spans="1:18" ht="15" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -29902,7 +29903,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="15.75" thickBot="1">
+    <row r="472" spans="1:18" ht="15" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -29932,7 +29933,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="15.75" thickBot="1">
+    <row r="473" spans="1:18" ht="15" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -29962,7 +29963,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="15.75" thickBot="1">
+    <row r="474" spans="1:18" ht="15" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -29992,7 +29993,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="15.75" thickBot="1">
+    <row r="475" spans="1:18" ht="15" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -30022,7 +30023,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="15.75" thickBot="1">
+    <row r="476" spans="1:18" ht="15" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -30052,7 +30053,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="15.75" thickBot="1">
+    <row r="477" spans="1:18" ht="15" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -30082,7 +30083,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="15.75" thickBot="1">
+    <row r="478" spans="1:18" ht="15" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -30109,7 +30110,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="15.75" thickBot="1">
+    <row r="479" spans="1:18" ht="15" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -30139,7 +30140,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="15.75" thickBot="1">
+    <row r="480" spans="1:18" ht="15" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -30169,7 +30170,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="15.75" thickBot="1">
+    <row r="481" spans="1:18" ht="15" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -30199,7 +30200,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="15.75" thickBot="1">
+    <row r="482" spans="1:18" ht="15" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -30226,7 +30227,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="15.75" thickBot="1">
+    <row r="483" spans="1:18" ht="15" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -30256,7 +30257,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="15.75" thickBot="1">
+    <row r="484" spans="1:18" ht="15" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -30286,7 +30287,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="15.75" thickBot="1">
+    <row r="485" spans="1:18" ht="15" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -30313,7 +30314,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="15.75" thickBot="1">
+    <row r="486" spans="1:18" ht="15" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -30340,7 +30341,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="15.75" thickBot="1">
+    <row r="487" spans="1:18" ht="15" thickBot="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14"/>
@@ -30367,7 +30368,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="15.75" thickBot="1">
+    <row r="488" spans="1:18" ht="15" thickBot="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14"/>
@@ -30394,7 +30395,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="15.75" thickBot="1">
+    <row r="489" spans="1:18" ht="15" thickBot="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14"/>
@@ -30424,7 +30425,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="15.75" thickBot="1">
+    <row r="490" spans="1:18" ht="15" thickBot="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14"/>
@@ -30451,7 +30452,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="15.75" thickBot="1">
+    <row r="491" spans="1:18" ht="15" thickBot="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14"/>
@@ -30478,7 +30479,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="15.75" thickBot="1">
+    <row r="492" spans="1:18" ht="15" thickBot="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14"/>
@@ -31037,7 +31038,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="15.75">
+    <row r="512" spans="1:18" ht="15.5">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -31446,7 +31447,7 @@
       <c r="Q529" s="37"/>
       <c r="R529" s="14"/>
     </row>
-    <row r="530" spans="1:18" ht="15.75">
+    <row r="530" spans="1:18" ht="15.5">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -31472,7 +31473,7 @@
       </c>
       <c r="R530" s="5"/>
     </row>
-    <row r="531" spans="1:18" ht="15.75">
+    <row r="531" spans="1:18" ht="15.5">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -31558,7 +31559,7 @@
       <c r="Q534" s="4"/>
       <c r="R534" s="3"/>
     </row>
-    <row r="535" spans="1:18" ht="15.75">
+    <row r="535" spans="1:18" ht="15.5">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -31578,7 +31579,7 @@
       <c r="Q535" s="4"/>
       <c r="R535" s="5"/>
     </row>
-    <row r="536" spans="1:18" ht="15.75">
+    <row r="536" spans="1:18" ht="15.5">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -31598,7 +31599,7 @@
       <c r="Q536" s="4"/>
       <c r="R536" s="5"/>
     </row>
-    <row r="537" spans="1:18" ht="15.75">
+    <row r="537" spans="1:18" ht="15.5">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -31730,7 +31731,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="26.25">
+    <row r="542" spans="1:18">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -31758,7 +31759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="26.25">
+    <row r="543" spans="1:18" ht="26">
       <c r="A543" s="7"/>
       <c r="B543" s="7"/>
       <c r="C543" s="7"/>
@@ -31814,7 +31815,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="24.95" customHeight="1">
+    <row r="545" spans="1:18" ht="25" customHeight="1">
       <c r="A545" s="12"/>
       <c r="B545" s="12"/>
       <c r="C545" s="12"/>
@@ -32192,7 +32193,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="51.75">
+    <row r="562" spans="1:18" ht="51">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -32218,7 +32219,7 @@
       </c>
       <c r="R562" s="5"/>
     </row>
-    <row r="563" spans="1:18" ht="26.25">
+    <row r="563" spans="1:18">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -32246,7 +32247,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="26.25">
+    <row r="564" spans="1:18">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -32274,7 +32275,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="26.25">
+    <row r="565" spans="1:18" ht="26">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -32446,7 +32447,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="15.75">
+    <row r="572" spans="1:18" ht="15.5">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -32472,7 +32473,7 @@
       </c>
       <c r="R572" s="5"/>
     </row>
-    <row r="573" spans="1:18" ht="15.75">
+    <row r="573" spans="1:18" ht="15.5">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -32498,7 +32499,7 @@
       </c>
       <c r="R573" s="5"/>
     </row>
-    <row r="574" spans="1:18" ht="15.75">
+    <row r="574" spans="1:18" ht="15.5">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -32524,7 +32525,7 @@
       </c>
       <c r="R574" s="5"/>
     </row>
-    <row r="575" spans="1:18" ht="15.75">
+    <row r="575" spans="1:18" ht="15.5">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -32550,7 +32551,7 @@
       </c>
       <c r="R575" s="5"/>
     </row>
-    <row r="576" spans="1:18" ht="15.75">
+    <row r="576" spans="1:18" ht="15.5">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -32576,7 +32577,7 @@
       </c>
       <c r="R576" s="5"/>
     </row>
-    <row r="577" spans="1:18" ht="15.75">
+    <row r="577" spans="1:18" ht="15.5">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -32602,7 +32603,7 @@
       </c>
       <c r="R577" s="5"/>
     </row>
-    <row r="578" spans="1:18" ht="15.75">
+    <row r="578" spans="1:18" ht="15.5">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -32628,7 +32629,7 @@
       </c>
       <c r="R578" s="5"/>
     </row>
-    <row r="579" spans="1:18" ht="15.75">
+    <row r="579" spans="1:18" ht="15.5">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -32734,7 +32735,7 @@
       <c r="Q584" s="8"/>
       <c r="R584" s="3"/>
     </row>
-    <row r="587" spans="1:18" ht="15.75">
+    <row r="587" spans="1:18" ht="15.5">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -32760,7 +32761,7 @@
       </c>
       <c r="R587" s="5"/>
     </row>
-    <row r="588" spans="1:18" ht="15.75">
+    <row r="588" spans="1:18" ht="15.5">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -32786,7 +32787,7 @@
       </c>
       <c r="R588" s="5"/>
     </row>
-    <row r="589" spans="1:18" ht="15.75">
+    <row r="589" spans="1:18" ht="15.5">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -32812,7 +32813,7 @@
       </c>
       <c r="R589" s="5"/>
     </row>
-    <row r="592" spans="1:18" ht="15.75">
+    <row r="592" spans="1:18" ht="15.5">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -32838,7 +32839,7 @@
       </c>
       <c r="R592" s="5"/>
     </row>
-    <row r="593" spans="1:18" ht="15.75">
+    <row r="593" spans="1:18" ht="15.5">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -32864,7 +32865,7 @@
       </c>
       <c r="R593" s="5"/>
     </row>
-    <row r="594" spans="1:18" ht="15.75">
+    <row r="594" spans="1:18" ht="15.5">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -32974,7 +32975,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="15.75">
+    <row r="600" spans="1:18" ht="15.5">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -33000,7 +33001,7 @@
       </c>
       <c r="R600" s="5"/>
     </row>
-    <row r="601" spans="1:18" ht="15.75">
+    <row r="601" spans="1:18" ht="15.5">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -33026,7 +33027,7 @@
       </c>
       <c r="R601" s="5"/>
     </row>
-    <row r="602" spans="1:18" ht="15.75">
+    <row r="602" spans="1:18" ht="15.5">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -33248,11 +33249,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
   <dimension ref="A1:H634"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="1" max="2" width="32.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" customWidth="1"/>
+    <col min="4" max="4" width="36.453125" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="87" style="10" customWidth="1"/>
   </cols>
@@ -33301,7 +33302,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" s="1" t="s">
         <v>974</v>
       </c>
@@ -33362,7 +33363,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" s="1" t="s">
         <v>974</v>
       </c>
@@ -33406,7 +33407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" s="1" t="s">
         <v>974</v>
       </c>
@@ -33492,7 +33493,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="14.1" customHeight="1">
+    <row r="12" spans="1:7" ht="14.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="114" t="s">
         <v>974</v>
@@ -33895,7 +33896,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1">
+    <row r="33" spans="1:8" ht="15" thickBot="1">
       <c r="A33" s="1" t="s">
         <v>974</v>
       </c>
@@ -33917,7 +33918,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1">
+    <row r="34" spans="1:8" ht="15" thickBot="1">
       <c r="A34" s="1" t="s">
         <v>974</v>
       </c>
@@ -33941,7 +33942,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1">
+    <row r="35" spans="1:8" ht="15" thickBot="1">
       <c r="A35" s="1" t="s">
         <v>974</v>
       </c>
@@ -33965,7 +33966,7 @@
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1">
+    <row r="36" spans="1:8" ht="15" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="34" t="s">
@@ -33985,7 +33986,7 @@
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1">
+    <row r="37" spans="1:8" ht="15" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="71" t="s">
@@ -34001,7 +34002,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1">
+    <row r="38" spans="1:8" ht="15" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="71" t="s">
@@ -34017,7 +34018,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1">
+    <row r="39" spans="1:8" ht="15" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="71" t="s">
@@ -34033,7 +34034,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="16.5" thickBot="1">
+    <row r="40" spans="1:8" ht="16" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="71" t="s">
@@ -34385,7 +34386,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" thickBot="1">
+    <row r="56" spans="1:7" ht="15" thickBot="1">
       <c r="A56" s="60" t="s">
         <v>974</v>
       </c>
@@ -34408,7 +34409,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1">
+    <row r="57" spans="1:7" ht="15" thickBot="1">
       <c r="A57" s="60" t="s">
         <v>974</v>
       </c>
@@ -34520,7 +34521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.5" thickBot="1">
+    <row r="62" spans="1:7" ht="16" thickBot="1">
       <c r="A62" s="60" t="s">
         <v>974</v>
       </c>
@@ -34543,7 +34544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.5" thickBot="1">
+    <row r="63" spans="1:7" ht="16" thickBot="1">
       <c r="A63" s="60" t="s">
         <v>974</v>
       </c>
@@ -34656,7 +34657,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75">
+    <row r="68" spans="1:7" ht="15.5">
       <c r="A68" s="60" t="s">
         <v>974</v>
       </c>
@@ -34679,7 +34680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75">
+    <row r="69" spans="1:7" ht="15.5">
       <c r="A69" s="60" t="s">
         <v>974</v>
       </c>
@@ -34716,7 +34717,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75">
+    <row r="71" spans="1:7" ht="15.5">
       <c r="A71" s="60" t="s">
         <v>974</v>
       </c>
@@ -34905,7 +34906,7 @@
       <c r="F79"/>
       <c r="G79" s="31"/>
     </row>
-    <row r="80" spans="1:7" ht="16.5">
+    <row r="80" spans="1:7" ht="16">
       <c r="A80" s="60" t="s">
         <v>974</v>
       </c>
@@ -34951,7 +34952,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.75">
+    <row r="82" spans="1:7" ht="15.5">
       <c r="A82" s="60" t="s">
         <v>974</v>
       </c>
@@ -35012,7 +35013,7 @@
       <c r="F84"/>
       <c r="G84" s="31"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75">
+    <row r="85" spans="1:7" ht="15.5">
       <c r="A85" s="60" t="s">
         <v>974</v>
       </c>
@@ -35033,7 +35034,7 @@
       </c>
       <c r="G85" s="5"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75">
+    <row r="86" spans="1:7" ht="15.5">
       <c r="A86" s="60" t="s">
         <v>974</v>
       </c>
@@ -35077,7 +35078,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.75">
+    <row r="88" spans="1:7" ht="15.5">
       <c r="A88" s="60" t="s">
         <v>974</v>
       </c>
@@ -35098,7 +35099,7 @@
       </c>
       <c r="G88" s="5"/>
     </row>
-    <row r="89" spans="1:7" ht="15.75">
+    <row r="89" spans="1:7" ht="15.5">
       <c r="A89" s="60"/>
       <c r="B89" s="114"/>
       <c r="C89" s="70"/>
@@ -35241,7 +35242,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.75" thickBot="1">
+    <row r="98" spans="1:7" ht="15" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -35252,7 +35253,7 @@
       <c r="F98"/>
       <c r="G98" s="31"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" thickBot="1">
+    <row r="99" spans="1:7" ht="15" thickBot="1">
       <c r="A99" s="60" t="s">
         <v>974</v>
       </c>
@@ -35271,7 +35272,7 @@
       <c r="F99"/>
       <c r="G99" s="31"/>
     </row>
-    <row r="100" spans="1:7" ht="16.5" thickBot="1">
+    <row r="100" spans="1:7" ht="16" thickBot="1">
       <c r="A100" s="60" t="s">
         <v>974</v>
       </c>
@@ -35294,7 +35295,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.75" thickBot="1">
+    <row r="101" spans="1:7" ht="15" thickBot="1">
       <c r="A101" s="60" t="s">
         <v>974</v>
       </c>
@@ -35314,7 +35315,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.75" thickBot="1">
+    <row r="102" spans="1:7" ht="15" thickBot="1">
       <c r="A102" s="60" t="s">
         <v>974</v>
       </c>
@@ -35334,7 +35335,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.75" thickBot="1">
+    <row r="103" spans="1:7" ht="15" thickBot="1">
       <c r="A103" s="60" t="s">
         <v>974</v>
       </c>
@@ -35354,7 +35355,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="16.5" thickBot="1">
+    <row r="104" spans="1:7" ht="16" thickBot="1">
       <c r="A104" s="60" t="s">
         <v>974</v>
       </c>
@@ -35375,7 +35376,7 @@
       </c>
       <c r="G104" s="5"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" thickBot="1">
+    <row r="105" spans="1:7" ht="15" thickBot="1">
       <c r="A105" s="60" t="s">
         <v>974</v>
       </c>
@@ -35395,7 +35396,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.75" thickBot="1">
+    <row r="106" spans="1:7" ht="15" thickBot="1">
       <c r="A106" s="60" t="s">
         <v>974</v>
       </c>
@@ -35413,7 +35414,7 @@
       </c>
       <c r="F106"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" thickBot="1">
+    <row r="107" spans="1:7" ht="15" thickBot="1">
       <c r="A107" s="60" t="s">
         <v>974</v>
       </c>
@@ -35436,7 +35437,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" thickBot="1">
+    <row r="108" spans="1:7" ht="15" thickBot="1">
       <c r="A108" s="60" t="s">
         <v>974</v>
       </c>
@@ -35459,7 +35460,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.75" thickBot="1">
+    <row r="109" spans="1:7" ht="15" thickBot="1">
       <c r="A109" s="60" t="s">
         <v>974</v>
       </c>
@@ -35482,7 +35483,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16.5" thickBot="1">
+    <row r="110" spans="1:7" ht="16" thickBot="1">
       <c r="A110" s="60" t="s">
         <v>974</v>
       </c>
@@ -35505,7 +35506,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="16.5" thickBot="1">
+    <row r="111" spans="1:7" ht="16" thickBot="1">
       <c r="A111" s="60" t="s">
         <v>974</v>
       </c>
@@ -35528,7 +35529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.75" thickBot="1">
+    <row r="112" spans="1:7" ht="15" thickBot="1">
       <c r="A112" s="60" t="s">
         <v>974</v>
       </c>
@@ -35590,7 +35591,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.75">
+    <row r="115" spans="1:7" ht="15.5">
       <c r="A115" s="60" t="s">
         <v>974</v>
       </c>
@@ -35611,7 +35612,7 @@
       </c>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7" ht="15.75">
+    <row r="116" spans="1:7" ht="15.5">
       <c r="A116" s="60" t="s">
         <v>974</v>
       </c>
@@ -35632,7 +35633,7 @@
       </c>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7" ht="15.75">
+    <row r="117" spans="1:7" ht="15.5">
       <c r="A117" s="60" t="s">
         <v>974</v>
       </c>
@@ -35655,7 +35656,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.75">
+    <row r="118" spans="1:7" ht="15.5">
       <c r="A118" s="60" t="s">
         <v>974</v>
       </c>
@@ -35695,7 +35696,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75">
+    <row r="120" spans="1:7" ht="15.5">
       <c r="A120" s="60" t="s">
         <v>974</v>
       </c>
@@ -35718,7 +35719,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.75">
+    <row r="121" spans="1:7" ht="15.5">
       <c r="A121" s="60" t="s">
         <v>974</v>
       </c>
@@ -35782,7 +35783,7 @@
       </c>
       <c r="F123"/>
     </row>
-    <row r="124" spans="1:7" ht="15.75">
+    <row r="124" spans="1:7" ht="15.5">
       <c r="A124" s="60" t="s">
         <v>974</v>
       </c>
@@ -35892,7 +35893,7 @@
       </c>
       <c r="F128"/>
     </row>
-    <row r="129" spans="1:7" ht="16.5">
+    <row r="129" spans="1:7" ht="16">
       <c r="A129" s="60" t="s">
         <v>974</v>
       </c>
@@ -35961,7 +35962,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.75" thickBot="1">
+    <row r="132" spans="1:7" ht="15" thickBot="1">
       <c r="A132" s="60" t="s">
         <v>974</v>
       </c>
@@ -35984,7 +35985,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.75" thickBot="1">
+    <row r="133" spans="1:7" ht="15" thickBot="1">
       <c r="A133" s="60" t="s">
         <v>974</v>
       </c>
@@ -36000,7 +36001,7 @@
       <c r="E133" s="3"/>
       <c r="F133"/>
     </row>
-    <row r="134" spans="1:7" ht="15.75" thickBot="1">
+    <row r="134" spans="1:7" ht="15" thickBot="1">
       <c r="A134" s="60" t="s">
         <v>974</v>
       </c>
@@ -36023,7 +36024,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.75" thickBot="1">
+    <row r="135" spans="1:7" ht="15" thickBot="1">
       <c r="A135" s="60" t="s">
         <v>974</v>
       </c>
@@ -36046,7 +36047,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="17.25" thickBot="1">
+    <row r="136" spans="1:7" ht="16.5" thickBot="1">
       <c r="A136" s="60" t="s">
         <v>974</v>
       </c>
@@ -36069,7 +36070,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="17.25" thickBot="1">
+    <row r="137" spans="1:7" ht="16.5" thickBot="1">
       <c r="A137" s="60" t="s">
         <v>974</v>
       </c>
@@ -36092,7 +36093,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="17.25" thickBot="1">
+    <row r="138" spans="1:7" ht="16.5" thickBot="1">
       <c r="A138" s="60" t="s">
         <v>974</v>
       </c>
@@ -36115,7 +36116,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="17.25" thickBot="1">
+    <row r="139" spans="1:7" ht="16.5" thickBot="1">
       <c r="A139" s="60" t="s">
         <v>974</v>
       </c>
@@ -36138,7 +36139,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="17.25" thickBot="1">
+    <row r="140" spans="1:7" ht="16.5" thickBot="1">
       <c r="A140" s="60" t="s">
         <v>974</v>
       </c>
@@ -36161,7 +36162,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="17.25" thickBot="1">
+    <row r="141" spans="1:7" ht="16.5" thickBot="1">
       <c r="A141" s="60" t="s">
         <v>974</v>
       </c>
@@ -36184,7 +36185,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.75" thickBot="1">
+    <row r="142" spans="1:7" ht="15" thickBot="1">
       <c r="A142" s="60" t="s">
         <v>974</v>
       </c>
@@ -36204,7 +36205,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="17.25" thickBot="1">
+    <row r="143" spans="1:7" ht="16.5" thickBot="1">
       <c r="A143" s="60" t="s">
         <v>974</v>
       </c>
@@ -36227,7 +36228,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="17.25" thickBot="1">
+    <row r="144" spans="1:7" ht="16.5" thickBot="1">
       <c r="A144" s="60" t="s">
         <v>974</v>
       </c>
@@ -36250,7 +36251,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="17.25" thickBot="1">
+    <row r="145" spans="1:7" ht="16.5" thickBot="1">
       <c r="A145" s="60" t="s">
         <v>974</v>
       </c>
@@ -36273,7 +36274,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="17.25" thickBot="1">
+    <row r="146" spans="1:7" ht="16.5" thickBot="1">
       <c r="A146" s="60" t="s">
         <v>974</v>
       </c>
@@ -36296,7 +36297,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.75" thickBot="1">
+    <row r="147" spans="1:7" ht="15" thickBot="1">
       <c r="A147" s="60" t="s">
         <v>974</v>
       </c>
@@ -36317,7 +36318,7 @@
       </c>
       <c r="G147" s="41"/>
     </row>
-    <row r="148" spans="1:7" ht="15.75" thickBot="1">
+    <row r="148" spans="1:7" ht="15" thickBot="1">
       <c r="A148" s="60" t="s">
         <v>974</v>
       </c>
@@ -36334,7 +36335,7 @@
       <c r="F148"/>
       <c r="G148" s="41"/>
     </row>
-    <row r="149" spans="1:7" ht="15.75" thickBot="1">
+    <row r="149" spans="1:7" ht="15" thickBot="1">
       <c r="A149" s="60" t="s">
         <v>974</v>
       </c>
@@ -36357,7 +36358,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15.75" thickBot="1">
+    <row r="150" spans="1:7" ht="15" thickBot="1">
       <c r="A150" s="60" t="s">
         <v>974</v>
       </c>
@@ -36377,7 +36378,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="17.25" thickBot="1">
+    <row r="151" spans="1:7" ht="16.5" thickBot="1">
       <c r="A151" s="60" t="s">
         <v>974</v>
       </c>
@@ -36400,7 +36401,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="17.25" thickBot="1">
+    <row r="152" spans="1:7" ht="16.5" thickBot="1">
       <c r="A152" s="60" t="s">
         <v>974</v>
       </c>
@@ -36423,7 +36424,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="17.25" thickBot="1">
+    <row r="153" spans="1:7" ht="16.5" thickBot="1">
       <c r="A153" s="60" t="s">
         <v>974</v>
       </c>
@@ -36446,7 +36447,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="17.25" thickBot="1">
+    <row r="154" spans="1:7" ht="16.5" thickBot="1">
       <c r="A154" s="60" t="s">
         <v>974</v>
       </c>
@@ -36469,7 +36470,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="17.25" thickBot="1">
+    <row r="155" spans="1:7" ht="16.5" thickBot="1">
       <c r="A155" s="60" t="s">
         <v>974</v>
       </c>
@@ -36492,7 +36493,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="17.25" thickBot="1">
+    <row r="156" spans="1:7" ht="16.5" thickBot="1">
       <c r="A156" s="60" t="s">
         <v>974</v>
       </c>
@@ -36515,7 +36516,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15.75" thickBot="1">
+    <row r="157" spans="1:7" ht="15" thickBot="1">
       <c r="A157" s="60" t="s">
         <v>974</v>
       </c>
@@ -36538,7 +36539,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="17.25" thickBot="1">
+    <row r="158" spans="1:7" ht="16.5" thickBot="1">
       <c r="A158" s="60" t="s">
         <v>974</v>
       </c>
@@ -36561,7 +36562,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="17.25" thickBot="1">
+    <row r="159" spans="1:7" ht="16.5" thickBot="1">
       <c r="A159" s="60" t="s">
         <v>974</v>
       </c>
@@ -36584,7 +36585,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="17.25" thickBot="1">
+    <row r="160" spans="1:7" ht="16.5" thickBot="1">
       <c r="A160" s="60" t="s">
         <v>974</v>
       </c>
@@ -36607,7 +36608,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="17.25" thickBot="1">
+    <row r="161" spans="1:7" ht="16.5" thickBot="1">
       <c r="A161" s="60" t="s">
         <v>974</v>
       </c>
@@ -36630,7 +36631,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.75" thickBot="1">
+    <row r="162" spans="1:7" ht="15" thickBot="1">
       <c r="A162" s="60" t="s">
         <v>974</v>
       </c>
@@ -36651,7 +36652,7 @@
       </c>
       <c r="G162" s="41"/>
     </row>
-    <row r="163" spans="1:7" ht="15.75" thickBot="1">
+    <row r="163" spans="1:7" ht="15" thickBot="1">
       <c r="A163" s="60" t="s">
         <v>974</v>
       </c>
@@ -36672,7 +36673,7 @@
       </c>
       <c r="G163" s="41"/>
     </row>
-    <row r="164" spans="1:7" ht="15.75" thickBot="1">
+    <row r="164" spans="1:7" ht="15" thickBot="1">
       <c r="A164" s="60" t="s">
         <v>974</v>
       </c>
@@ -36695,7 +36696,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15.75" thickBot="1">
+    <row r="165" spans="1:7" ht="15" thickBot="1">
       <c r="A165" s="60" t="s">
         <v>974</v>
       </c>
@@ -36718,7 +36719,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15.75" thickBot="1">
+    <row r="166" spans="1:7" ht="15" thickBot="1">
       <c r="A166" s="60" t="s">
         <v>974</v>
       </c>
@@ -36738,7 +36739,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15.75" thickBot="1">
+    <row r="167" spans="1:7" ht="15" thickBot="1">
       <c r="A167" s="60" t="s">
         <v>974</v>
       </c>
@@ -36761,7 +36762,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15.75" thickBot="1">
+    <row r="168" spans="1:7" ht="15" thickBot="1">
       <c r="A168" s="60" t="s">
         <v>974</v>
       </c>
@@ -36784,7 +36785,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15.75" thickBot="1">
+    <row r="169" spans="1:7" ht="15" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="114" t="s">
         <v>974</v>
@@ -36800,7 +36801,7 @@
       </c>
       <c r="F169"/>
     </row>
-    <row r="170" spans="1:7" ht="15.75" thickBot="1">
+    <row r="170" spans="1:7" ht="15" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="121" t="s">
         <v>1509</v>
@@ -36821,7 +36822,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="17.25" thickBot="1">
+    <row r="171" spans="1:7" ht="16.5" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="114" t="s">
         <v>974</v>
@@ -36842,7 +36843,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.75" thickBot="1">
+    <row r="172" spans="1:7" ht="15" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="114" t="s">
         <v>974</v>
@@ -36856,7 +36857,7 @@
       <c r="E172" s="17"/>
       <c r="F172"/>
     </row>
-    <row r="173" spans="1:7" ht="15.75" thickBot="1">
+    <row r="173" spans="1:7" ht="15" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="121" t="s">
         <v>1509</v>
@@ -36877,7 +36878,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="17.25" thickBot="1">
+    <row r="174" spans="1:7" ht="16.5" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="114" t="s">
         <v>974</v>
@@ -36898,7 +36899,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15.75" thickBot="1">
+    <row r="175" spans="1:7" ht="15" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="114" t="s">
         <v>974</v>
@@ -36912,7 +36913,7 @@
       <c r="E175" s="17"/>
       <c r="F175"/>
     </row>
-    <row r="176" spans="1:7" ht="15.75" thickBot="1">
+    <row r="176" spans="1:7" ht="15" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="114" t="s">
         <v>974</v>
@@ -36933,7 +36934,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.75" thickBot="1">
+    <row r="177" spans="1:7" ht="15" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="114" t="s">
         <v>974</v>
@@ -36952,7 +36953,7 @@
       </c>
       <c r="G177" s="69"/>
     </row>
-    <row r="178" spans="1:7" ht="15.75" thickBot="1">
+    <row r="178" spans="1:7" ht="15" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="114" t="s">
         <v>974</v>
@@ -36971,7 +36972,7 @@
       </c>
       <c r="G178" s="43"/>
     </row>
-    <row r="179" spans="1:7" ht="15.75" thickBot="1">
+    <row r="179" spans="1:7" ht="15" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="114" t="s">
         <v>974</v>
@@ -36990,7 +36991,7 @@
       </c>
       <c r="G179" s="44"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" thickBot="1">
+    <row r="180" spans="1:7" ht="15" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="114" t="s">
         <v>974</v>
@@ -37009,7 +37010,7 @@
       </c>
       <c r="G180" s="44"/>
     </row>
-    <row r="181" spans="1:7" ht="15.75" thickBot="1">
+    <row r="181" spans="1:7" ht="15" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="114" t="s">
         <v>974</v>
@@ -37027,7 +37028,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15.75" thickBot="1">
+    <row r="182" spans="1:7" ht="15" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="114" t="s">
         <v>974</v>
@@ -37045,7 +37046,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15.75" thickBot="1">
+    <row r="183" spans="1:7" ht="15" thickBot="1">
       <c r="A183" s="1"/>
       <c r="B183" s="114" t="s">
         <v>974</v>
@@ -37066,7 +37067,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15.75" thickBot="1">
+    <row r="184" spans="1:7" ht="15" thickBot="1">
       <c r="A184" s="108"/>
       <c r="B184" s="114" t="s">
         <v>974</v>
@@ -37084,7 +37085,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15.75" thickBot="1">
+    <row r="185" spans="1:7" ht="15" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="114" t="s">
         <v>974</v>
@@ -37102,7 +37103,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.75" thickBot="1">
+    <row r="186" spans="1:7" ht="15" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="114" t="s">
         <v>974</v>
@@ -37118,7 +37119,7 @@
       </c>
       <c r="F186"/>
     </row>
-    <row r="187" spans="1:7" ht="15.75" thickBot="1">
+    <row r="187" spans="1:7" ht="15" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="114" t="s">
         <v>974</v>
@@ -37139,7 +37140,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15.75" thickBot="1">
+    <row r="188" spans="1:7" ht="15" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="114" t="s">
         <v>974</v>
@@ -37158,7 +37159,7 @@
       </c>
       <c r="G188" s="73"/>
     </row>
-    <row r="189" spans="1:7" ht="15.75" thickBot="1">
+    <row r="189" spans="1:7" ht="15" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="114" t="s">
         <v>974</v>
@@ -37179,7 +37180,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15.75" thickBot="1">
+    <row r="190" spans="1:7" ht="15" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="114" t="s">
         <v>974</v>
@@ -37200,7 +37201,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15.75" thickBot="1">
+    <row r="191" spans="1:7" ht="15" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="114" t="s">
         <v>974</v>
@@ -37221,7 +37222,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15.75" thickBot="1">
+    <row r="192" spans="1:7" ht="15" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="114" t="s">
         <v>974</v>
@@ -37239,7 +37240,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15.75" thickBot="1">
+    <row r="193" spans="1:7" ht="15" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="114" t="s">
         <v>974</v>
@@ -37260,7 +37261,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15.75" thickBot="1">
+    <row r="194" spans="1:7" ht="15" thickBot="1">
       <c r="A194" s="1"/>
       <c r="B194" s="114" t="s">
         <v>974</v>
@@ -37281,7 +37282,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15.75" thickBot="1">
+    <row r="195" spans="1:7" ht="15" thickBot="1">
       <c r="A195" s="108"/>
       <c r="B195" s="114" t="s">
         <v>974</v>
@@ -37302,7 +37303,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15.75" thickBot="1">
+    <row r="196" spans="1:7" ht="15" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="114" t="s">
         <v>974</v>
@@ -37323,7 +37324,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15.75" thickBot="1">
+    <row r="197" spans="1:7" ht="15" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="114" t="s">
         <v>974</v>
@@ -37339,7 +37340,7 @@
       </c>
       <c r="G197" s="41"/>
     </row>
-    <row r="198" spans="1:7" ht="15.75" thickBot="1">
+    <row r="198" spans="1:7" ht="15" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="114" t="s">
         <v>974</v>
@@ -37360,7 +37361,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15.75" thickBot="1">
+    <row r="199" spans="1:7" ht="15" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="114" t="s">
         <v>974</v>
@@ -37381,7 +37382,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15.75" thickBot="1">
+    <row r="200" spans="1:7" ht="15" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="114" t="s">
         <v>974</v>
@@ -37398,7 +37399,7 @@
       <c r="F200"/>
       <c r="G200" s="29"/>
     </row>
-    <row r="201" spans="1:7" ht="15.75" thickBot="1">
+    <row r="201" spans="1:7" ht="15" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="114" t="s">
         <v>974</v>
@@ -37419,7 +37420,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15.75" thickBot="1">
+    <row r="202" spans="1:7" ht="15" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="114" t="s">
         <v>974</v>
@@ -37440,7 +37441,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="15.75" thickBot="1">
+    <row r="203" spans="1:7" ht="15" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="114" t="s">
         <v>974</v>
@@ -37456,7 +37457,7 @@
       </c>
       <c r="F203"/>
     </row>
-    <row r="204" spans="1:7" ht="15.75" thickBot="1">
+    <row r="204" spans="1:7" ht="15" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="114" t="s">
         <v>974</v>
@@ -37474,7 +37475,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15.75" thickBot="1">
+    <row r="205" spans="1:7" ht="15" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="114" t="s">
         <v>974</v>
@@ -37490,7 +37491,7 @@
       </c>
       <c r="F205"/>
     </row>
-    <row r="206" spans="1:7" ht="15.75" thickBot="1">
+    <row r="206" spans="1:7" ht="15" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="114" t="s">
         <v>974</v>
@@ -37511,7 +37512,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15.75" thickBot="1">
+    <row r="207" spans="1:7" ht="15" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="114" t="s">
         <v>974</v>
@@ -37529,7 +37530,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15.75" thickBot="1">
+    <row r="208" spans="1:7" ht="15" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="114" t="s">
         <v>974</v>
@@ -37550,7 +37551,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15.75" thickBot="1">
+    <row r="209" spans="1:7" ht="15" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="114" t="s">
         <v>974</v>
@@ -37571,7 +37572,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.75" thickBot="1">
+    <row r="210" spans="1:7" ht="15" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="114" t="s">
         <v>974</v>
@@ -37587,7 +37588,7 @@
       </c>
       <c r="F210"/>
     </row>
-    <row r="211" spans="1:7" ht="15.75" thickBot="1">
+    <row r="211" spans="1:7" ht="15" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="114" t="s">
         <v>974</v>
@@ -37605,7 +37606,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.75" thickBot="1">
+    <row r="212" spans="1:7" ht="15" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="114" t="s">
         <v>974</v>
@@ -37621,7 +37622,7 @@
       </c>
       <c r="F212"/>
     </row>
-    <row r="213" spans="1:7" ht="15.75" thickBot="1">
+    <row r="213" spans="1:7" ht="15" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="114" t="s">
         <v>974</v>
@@ -37642,7 +37643,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.75" thickBot="1">
+    <row r="214" spans="1:7" ht="15" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="114" t="s">
         <v>974</v>
@@ -37660,7 +37661,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.75" thickBot="1">
+    <row r="215" spans="1:7" ht="15" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="114" t="s">
         <v>974</v>
@@ -37681,7 +37682,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15.75" thickBot="1">
+    <row r="216" spans="1:7" ht="15" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="114" t="s">
         <v>974</v>
@@ -37699,7 +37700,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.75" thickBot="1">
+    <row r="217" spans="1:7" ht="15" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="114" t="s">
         <v>974</v>
@@ -37713,7 +37714,7 @@
       <c r="E217" s="17"/>
       <c r="F217"/>
     </row>
-    <row r="218" spans="1:7" ht="15.75" thickBot="1">
+    <row r="218" spans="1:7" ht="15" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="114" t="s">
         <v>974</v>
@@ -37731,7 +37732,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15.75" thickBot="1">
+    <row r="219" spans="1:7" ht="15" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="114" t="s">
         <v>974</v>
@@ -37745,7 +37746,7 @@
       <c r="E219" s="17"/>
       <c r="F219"/>
     </row>
-    <row r="220" spans="1:7" ht="15.75" thickBot="1">
+    <row r="220" spans="1:7" ht="15" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="114" t="s">
         <v>974</v>
@@ -37763,7 +37764,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15.75" thickBot="1">
+    <row r="221" spans="1:7" ht="15" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="71" t="s">
@@ -37777,7 +37778,7 @@
       </c>
       <c r="F221"/>
     </row>
-    <row r="222" spans="1:7" ht="15.75" thickBot="1">
+    <row r="222" spans="1:7" ht="15" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="71" t="s">
@@ -37793,7 +37794,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15.75" thickBot="1">
+    <row r="223" spans="1:7" ht="15" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="71" t="s">
@@ -37812,7 +37813,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15.75" thickBot="1">
+    <row r="224" spans="1:7" ht="15" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="71" t="s">
@@ -37828,7 +37829,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15.75" thickBot="1">
+    <row r="225" spans="1:7" ht="15" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="71" t="s">
@@ -37844,7 +37845,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.75" thickBot="1">
+    <row r="226" spans="1:7" ht="15" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="71" t="s">
@@ -37858,7 +37859,7 @@
       </c>
       <c r="F226"/>
     </row>
-    <row r="227" spans="1:7" ht="15.75" thickBot="1">
+    <row r="227" spans="1:7" ht="15" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="71" t="s">
@@ -37874,7 +37875,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15.75" thickBot="1">
+    <row r="228" spans="1:7" ht="15" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="71" t="s">
@@ -37893,7 +37894,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15.75" thickBot="1">
+    <row r="229" spans="1:7" ht="15" thickBot="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="71" t="s">
@@ -38057,7 +38058,7 @@
       <c r="E239" s="19"/>
       <c r="F239"/>
     </row>
-    <row r="240" spans="1:7" ht="15.75" thickBot="1">
+    <row r="240" spans="1:7" ht="15" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="135" t="s">
@@ -38073,7 +38074,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="15.75" thickBot="1">
+    <row r="241" spans="1:7" ht="15" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="125" t="s">
         <v>1003</v>
@@ -38087,7 +38088,7 @@
       <c r="E241" s="19"/>
       <c r="F241"/>
     </row>
-    <row r="242" spans="1:7" ht="15.75" thickBot="1">
+    <row r="242" spans="1:7" ht="15" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="125" t="s">
         <v>1003</v>
@@ -38101,7 +38102,7 @@
       <c r="E242" s="19"/>
       <c r="F242"/>
     </row>
-    <row r="243" spans="1:7" ht="15.75" thickBot="1">
+    <row r="243" spans="1:7" ht="15" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="125" t="s">
         <v>1003</v>
@@ -38115,7 +38116,7 @@
       <c r="E243" s="19"/>
       <c r="F243"/>
     </row>
-    <row r="244" spans="1:7" ht="15.75" thickBot="1">
+    <row r="244" spans="1:7" ht="15" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="125" t="s">
         <v>1003</v>
@@ -38129,7 +38130,7 @@
       <c r="E244" s="19"/>
       <c r="F244"/>
     </row>
-    <row r="245" spans="1:7" ht="15.75" thickBot="1">
+    <row r="245" spans="1:7" ht="15" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="125" t="s">
         <v>1003</v>
@@ -38143,7 +38144,7 @@
       <c r="E245" s="19"/>
       <c r="F245"/>
     </row>
-    <row r="246" spans="1:7" ht="15.75" thickBot="1">
+    <row r="246" spans="1:7" ht="15" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="125" t="s">
         <v>1003</v>
@@ -38157,7 +38158,7 @@
       <c r="E246" s="19"/>
       <c r="F246"/>
     </row>
-    <row r="247" spans="1:7" ht="15.75" thickBot="1">
+    <row r="247" spans="1:7" ht="15" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="125" t="s">
         <v>1003</v>
@@ -38171,7 +38172,7 @@
       <c r="E247" s="19"/>
       <c r="F247"/>
     </row>
-    <row r="248" spans="1:7" ht="15.75" thickBot="1">
+    <row r="248" spans="1:7" ht="15" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="125" t="s">
         <v>1003</v>
@@ -38185,7 +38186,7 @@
       <c r="E248" s="19"/>
       <c r="F248"/>
     </row>
-    <row r="249" spans="1:7" ht="15.75" thickBot="1">
+    <row r="249" spans="1:7" ht="15" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="125" t="s">
         <v>1003</v>
@@ -38199,7 +38200,7 @@
       <c r="E249" s="19"/>
       <c r="F249"/>
     </row>
-    <row r="250" spans="1:7" ht="15.75" thickBot="1">
+    <row r="250" spans="1:7" ht="15" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="125" t="s">
         <v>1003</v>
@@ -38213,7 +38214,7 @@
       <c r="E250" s="19"/>
       <c r="F250"/>
     </row>
-    <row r="251" spans="1:7" ht="15.75" thickBot="1">
+    <row r="251" spans="1:7" ht="15" thickBot="1">
       <c r="A251" s="1" t="s">
         <v>1438</v>
       </c>
@@ -38233,7 +38234,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="15.75" thickBot="1">
+    <row r="252" spans="1:7" ht="15" thickBot="1">
       <c r="A252" s="1" t="s">
         <v>1438</v>
       </c>
@@ -38329,7 +38330,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="15.75" thickBot="1">
+    <row r="258" spans="1:8" ht="15" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="81" t="s">
@@ -38351,7 +38352,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="15.75" thickBot="1">
+    <row r="259" spans="1:8" ht="15" thickBot="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="81" t="s">
@@ -38424,7 +38425,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="15.75" thickBot="1">
+    <row r="263" spans="1:8" ht="15" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="81" t="s">
@@ -38443,7 +38444,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="15.75" thickBot="1">
+    <row r="264" spans="1:8" ht="15" thickBot="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="81" t="s">
@@ -38493,7 +38494,7 @@
       <c r="F266" s="4"/>
       <c r="G266" s="3"/>
     </row>
-    <row r="267" spans="1:8" ht="26.25">
+    <row r="267" spans="1:8">
       <c r="A267" s="1" t="s">
         <v>974</v>
       </c>
@@ -39022,7 +39023,7 @@
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="1:7" ht="15.75" thickBot="1">
+    <row r="301" spans="1:7" ht="15" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="84" t="s">
@@ -39039,7 +39040,7 @@
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="1:7" ht="15.75" thickBot="1">
+    <row r="302" spans="1:7" ht="15" thickBot="1">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="34" t="s">
@@ -40234,7 +40235,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="15.75">
+    <row r="392" spans="1:7" ht="15.5">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14" t="s">
@@ -40329,7 +40330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="15.75">
+    <row r="397" spans="1:7" ht="15.5">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14" t="s">
@@ -40364,7 +40365,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="15.75">
+    <row r="399" spans="1:7" ht="15.5">
       <c r="A399" s="14"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14" t="s">
@@ -40416,7 +40417,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="15.75">
+    <row r="402" spans="1:7" ht="15.5">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14" t="s">
@@ -40490,7 +40491,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="15.75">
+    <row r="406" spans="1:7" ht="15.5">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14" t="s">
@@ -40564,7 +40565,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15.75">
+    <row r="410" spans="1:7" ht="15.5">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14" t="s">
@@ -40581,7 +40582,7 @@
       </c>
       <c r="G410" s="5"/>
     </row>
-    <row r="411" spans="1:7" ht="15.75" thickBot="1">
+    <row r="411" spans="1:7" ht="15" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14" t="s">
@@ -40600,7 +40601,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15.75" thickBot="1">
+    <row r="412" spans="1:7" ht="15" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14" t="s">
@@ -40615,7 +40616,7 @@
       <c r="F412" s="3"/>
       <c r="G412" s="14"/>
     </row>
-    <row r="413" spans="1:7" ht="15.75" thickBot="1">
+    <row r="413" spans="1:7" ht="15" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14" t="s">
@@ -40630,7 +40631,7 @@
       <c r="F413" s="3"/>
       <c r="G413" s="14"/>
     </row>
-    <row r="414" spans="1:7" ht="15.75">
+    <row r="414" spans="1:7" ht="15.5">
       <c r="C414" s="14" t="s">
         <v>765</v>
       </c>
@@ -40700,7 +40701,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="15.75">
+    <row r="418" spans="1:7" ht="15.5">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14" t="s">
@@ -40757,7 +40758,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15.75" thickBot="1">
+    <row r="421" spans="1:7" ht="15" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14" t="s">
@@ -40776,7 +40777,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15.75" thickBot="1">
+    <row r="422" spans="1:7" ht="15" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14" t="s">
@@ -40795,7 +40796,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15.75" thickBot="1">
+    <row r="423" spans="1:7" ht="15" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14" t="s">
@@ -40814,7 +40815,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15.75" thickBot="1">
+    <row r="424" spans="1:7" ht="15" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14" t="s">
@@ -40833,7 +40834,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15.75" thickBot="1">
+    <row r="425" spans="1:7" ht="15" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14" t="s">
@@ -40852,7 +40853,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="15.75" thickBot="1">
+    <row r="426" spans="1:7" ht="15" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14" t="s">
@@ -40871,7 +40872,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="15.75" thickBot="1">
+    <row r="427" spans="1:7" ht="15" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14" t="s">
@@ -40890,7 +40891,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="15.75" thickBot="1">
+    <row r="428" spans="1:7" ht="15" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14" t="s">
@@ -40909,7 +40910,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15.75" thickBot="1">
+    <row r="429" spans="1:7" ht="15" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14" t="s">
@@ -40928,7 +40929,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15.75" thickBot="1">
+    <row r="430" spans="1:7" ht="15" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14" t="s">
@@ -40947,7 +40948,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15.75" thickBot="1">
+    <row r="431" spans="1:7" ht="15" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14" t="s">
@@ -40966,7 +40967,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15.75" thickBot="1">
+    <row r="432" spans="1:7" ht="15" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14" t="s">
@@ -40985,7 +40986,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15.75" thickBot="1">
+    <row r="433" spans="1:7" ht="15" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14" t="s">
@@ -41001,7 +41002,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15.75" thickBot="1">
+    <row r="434" spans="1:7" ht="15" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14" t="s">
@@ -41017,7 +41018,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15.75" thickBot="1">
+    <row r="435" spans="1:7" ht="15" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14" t="s">
@@ -41033,7 +41034,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15.75" thickBot="1">
+    <row r="436" spans="1:7" ht="15" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14" t="s">
@@ -41049,7 +41050,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15.75" thickBot="1">
+    <row r="437" spans="1:7" ht="15" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14" t="s">
@@ -41065,7 +41066,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15.75" thickBot="1">
+    <row r="438" spans="1:7" ht="15" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14" t="s">
@@ -41081,7 +41082,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15.75" thickBot="1">
+    <row r="439" spans="1:7" ht="15" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14" t="s">
@@ -41097,7 +41098,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15.75" thickBot="1">
+    <row r="440" spans="1:7" ht="15" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14" t="s">
@@ -41113,7 +41114,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="15.75" thickBot="1">
+    <row r="441" spans="1:7" ht="15" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14" t="s">
@@ -41130,7 +41131,7 @@
       </c>
       <c r="G441" s="41"/>
     </row>
-    <row r="442" spans="1:7" ht="15.75" thickBot="1">
+    <row r="442" spans="1:7" ht="15" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14" t="s">
@@ -41149,7 +41150,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15.75" thickBot="1">
+    <row r="443" spans="1:7" ht="15" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14" t="s">
@@ -41168,7 +41169,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15.75" thickBot="1">
+    <row r="444" spans="1:7" ht="15" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14" t="s">
@@ -41187,7 +41188,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15.75" thickBot="1">
+    <row r="445" spans="1:7" ht="15" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14" t="s">
@@ -41206,7 +41207,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15.75" thickBot="1">
+    <row r="446" spans="1:7" ht="15" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14" t="s">
@@ -41225,7 +41226,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15.75" thickBot="1">
+    <row r="447" spans="1:7" ht="15" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14" t="s">
@@ -41244,7 +41245,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15.75" thickBot="1">
+    <row r="448" spans="1:7" ht="15" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14" t="s">
@@ -41263,7 +41264,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15.75" thickBot="1">
+    <row r="449" spans="1:7" ht="15" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14" t="s">
@@ -41282,7 +41283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15.75" thickBot="1">
+    <row r="450" spans="1:7" ht="15" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14" t="s">
@@ -41301,7 +41302,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15.75" thickBot="1">
+    <row r="451" spans="1:7" ht="15" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14" t="s">
@@ -41320,7 +41321,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15.75" thickBot="1">
+    <row r="452" spans="1:7" ht="15" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14" t="s">
@@ -41339,7 +41340,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15.75" thickBot="1">
+    <row r="453" spans="1:7" ht="15" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14" t="s">
@@ -41355,7 +41356,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15.75" thickBot="1">
+    <row r="454" spans="1:7" ht="15" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14" t="s">
@@ -41371,7 +41372,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15.75" thickBot="1">
+    <row r="455" spans="1:7" ht="15" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14" t="s">
@@ -41387,7 +41388,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15.75" thickBot="1">
+    <row r="456" spans="1:7" ht="15" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14" t="s">
@@ -41403,7 +41404,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15.75" thickBot="1">
+    <row r="457" spans="1:7" ht="15" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14" t="s">
@@ -41419,7 +41420,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15.75" thickBot="1">
+    <row r="458" spans="1:7" ht="15" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14" t="s">
@@ -41435,7 +41436,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15.75" thickBot="1">
+    <row r="459" spans="1:7" ht="15" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14" t="s">
@@ -41451,7 +41452,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15.75" thickBot="1">
+    <row r="460" spans="1:7" ht="15" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14" t="s">
@@ -41467,7 +41468,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="15.75" thickBot="1">
+    <row r="461" spans="1:7" ht="15" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14" t="s">
@@ -41484,7 +41485,7 @@
       </c>
       <c r="G461" s="41"/>
     </row>
-    <row r="462" spans="1:7" ht="15.75" thickBot="1">
+    <row r="462" spans="1:7" ht="15" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14" t="s">
@@ -41503,7 +41504,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15.75" thickBot="1">
+    <row r="463" spans="1:7" ht="15" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14" t="s">
@@ -41522,7 +41523,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="15.75" thickBot="1">
+    <row r="464" spans="1:7" ht="15" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14" t="s">
@@ -41541,7 +41542,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="15.75" thickBot="1">
+    <row r="465" spans="1:7" ht="15" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14" t="s">
@@ -41560,7 +41561,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="15.75" thickBot="1">
+    <row r="466" spans="1:7" ht="15" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14" t="s">
@@ -41579,7 +41580,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="15.75" thickBot="1">
+    <row r="467" spans="1:7" ht="15" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14" t="s">
@@ -41598,7 +41599,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="15.75" thickBot="1">
+    <row r="468" spans="1:7" ht="15" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14" t="s">
@@ -41617,7 +41618,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="15.75" thickBot="1">
+    <row r="469" spans="1:7" ht="15" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14" t="s">
@@ -41636,7 +41637,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="15.75" thickBot="1">
+    <row r="470" spans="1:7" ht="15" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14" t="s">
@@ -41655,7 +41656,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="15.75" thickBot="1">
+    <row r="471" spans="1:7" ht="15" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14" t="s">
@@ -41671,7 +41672,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="15.75" thickBot="1">
+    <row r="472" spans="1:7" ht="15" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14" t="s">
@@ -41688,7 +41689,7 @@
       </c>
       <c r="G472" s="43"/>
     </row>
-    <row r="473" spans="1:7" ht="15.75" thickBot="1">
+    <row r="473" spans="1:7" ht="15" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14" t="s">
@@ -41705,7 +41706,7 @@
       </c>
       <c r="G473" s="44"/>
     </row>
-    <row r="474" spans="1:7" ht="15.75" thickBot="1">
+    <row r="474" spans="1:7" ht="15" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14" t="s">
@@ -41722,7 +41723,7 @@
       </c>
       <c r="G474" s="44"/>
     </row>
-    <row r="475" spans="1:7" ht="15.75" thickBot="1">
+    <row r="475" spans="1:7" ht="15" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14" t="s">
@@ -41738,7 +41739,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="15.75" thickBot="1">
+    <row r="476" spans="1:7" ht="15" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14" t="s">
@@ -41754,7 +41755,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="15.75" thickBot="1">
+    <row r="477" spans="1:7" ht="15" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14" t="s">
@@ -41770,7 +41771,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="15.75" thickBot="1">
+    <row r="478" spans="1:7" ht="15" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14" t="s">
@@ -41786,7 +41787,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="15.75" thickBot="1">
+    <row r="479" spans="1:7" ht="15" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14" t="s">
@@ -41805,7 +41806,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="15.75" thickBot="1">
+    <row r="480" spans="1:7" ht="15" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14" t="s">
@@ -41824,7 +41825,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="15.75" thickBot="1">
+    <row r="481" spans="1:7" ht="15" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14" t="s">
@@ -41840,7 +41841,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="15.75" thickBot="1">
+    <row r="482" spans="1:7" ht="15" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14" t="s">
@@ -41859,7 +41860,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15.75" thickBot="1">
+    <row r="483" spans="1:7" ht="15" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14" t="s">
@@ -41878,7 +41879,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="15.75" thickBot="1">
+    <row r="484" spans="1:7" ht="15" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14" t="s">
@@ -41897,7 +41898,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15.75" thickBot="1">
+    <row r="485" spans="1:7" ht="15" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14" t="s">
@@ -41913,7 +41914,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15.75" thickBot="1">
+    <row r="486" spans="1:7" ht="15" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14" t="s">
@@ -41932,7 +41933,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15.75" thickBot="1">
+    <row r="487" spans="1:7" ht="15" thickBot="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14" t="s">
@@ -41951,7 +41952,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15.75" thickBot="1">
+    <row r="488" spans="1:7" ht="15" thickBot="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14" t="s">
@@ -41970,7 +41971,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15.75" thickBot="1">
+    <row r="489" spans="1:7" ht="15" thickBot="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14" t="s">
@@ -41989,7 +41990,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15.75" thickBot="1">
+    <row r="490" spans="1:7" ht="15" thickBot="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14" t="s">
@@ -42008,7 +42009,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15.75" thickBot="1">
+    <row r="491" spans="1:7" ht="15" thickBot="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14" t="s">
@@ -42027,7 +42028,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15.75" thickBot="1">
+    <row r="492" spans="1:7" ht="15" thickBot="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14" t="s">
@@ -42046,7 +42047,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15.75" thickBot="1">
+    <row r="493" spans="1:7" ht="15" thickBot="1">
       <c r="A493" s="14"/>
       <c r="B493" s="14"/>
       <c r="C493" s="14" t="s">
@@ -42065,7 +42066,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15.75" thickBot="1">
+    <row r="494" spans="1:7" ht="15" thickBot="1">
       <c r="A494" s="14"/>
       <c r="B494" s="14"/>
       <c r="C494" s="14" t="s">
@@ -42084,7 +42085,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15.75" thickBot="1">
+    <row r="495" spans="1:7" ht="15" thickBot="1">
       <c r="A495" s="14"/>
       <c r="B495" s="14"/>
       <c r="C495" s="14" t="s">
@@ -42103,7 +42104,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15.75" thickBot="1">
+    <row r="496" spans="1:7" ht="15" thickBot="1">
       <c r="A496" s="14"/>
       <c r="B496" s="14"/>
       <c r="C496" s="14" t="s">
@@ -42119,7 +42120,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15.75" thickBot="1">
+    <row r="497" spans="1:7" ht="15" thickBot="1">
       <c r="A497" s="14"/>
       <c r="B497" s="14"/>
       <c r="C497" s="14" t="s">
@@ -42138,7 +42139,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="15.75" thickBot="1">
+    <row r="498" spans="1:7" ht="15" thickBot="1">
       <c r="A498" s="14"/>
       <c r="B498" s="14"/>
       <c r="C498" s="14" t="s">
@@ -42157,7 +42158,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="15.75" thickBot="1">
+    <row r="499" spans="1:7" ht="15" thickBot="1">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14" t="s">
@@ -42176,7 +42177,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15.75" thickBot="1">
+    <row r="500" spans="1:7" ht="15" thickBot="1">
       <c r="A500" s="14"/>
       <c r="B500" s="14"/>
       <c r="C500" s="14" t="s">
@@ -42192,7 +42193,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15.75" thickBot="1">
+    <row r="501" spans="1:7" ht="15" thickBot="1">
       <c r="A501" s="14"/>
       <c r="B501" s="14"/>
       <c r="C501" s="14" t="s">
@@ -42211,7 +42212,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15.75" thickBot="1">
+    <row r="502" spans="1:7" ht="15" thickBot="1">
       <c r="A502" s="14"/>
       <c r="B502" s="14"/>
       <c r="C502" s="14" t="s">
@@ -42230,7 +42231,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15.75" thickBot="1">
+    <row r="503" spans="1:7" ht="15" thickBot="1">
       <c r="A503" s="14"/>
       <c r="B503" s="14"/>
       <c r="C503" s="14" t="s">
@@ -42246,7 +42247,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15.75" thickBot="1">
+    <row r="504" spans="1:7" ht="15" thickBot="1">
       <c r="A504" s="14"/>
       <c r="B504" s="14"/>
       <c r="C504" s="14" t="s">
@@ -42262,7 +42263,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15.75" thickBot="1">
+    <row r="505" spans="1:7" ht="15" thickBot="1">
       <c r="A505" s="14"/>
       <c r="B505" s="14"/>
       <c r="C505" s="14" t="s">
@@ -42278,7 +42279,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15.75" thickBot="1">
+    <row r="506" spans="1:7" ht="15" thickBot="1">
       <c r="A506" s="14"/>
       <c r="B506" s="14"/>
       <c r="C506" s="14" t="s">
@@ -42294,7 +42295,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15.75" thickBot="1">
+    <row r="507" spans="1:7" ht="15" thickBot="1">
       <c r="A507" s="14"/>
       <c r="B507" s="14"/>
       <c r="C507" s="14" t="s">
@@ -42313,7 +42314,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15.75" thickBot="1">
+    <row r="508" spans="1:7" ht="15" thickBot="1">
       <c r="A508" s="14"/>
       <c r="B508" s="14"/>
       <c r="C508" s="14" t="s">
@@ -42329,7 +42330,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15.75" thickBot="1">
+    <row r="509" spans="1:7" ht="15" thickBot="1">
       <c r="A509" s="14"/>
       <c r="B509" s="14"/>
       <c r="C509" s="14" t="s">
@@ -42345,7 +42346,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="15.75" thickBot="1">
+    <row r="510" spans="1:7" ht="15" thickBot="1">
       <c r="A510" s="14"/>
       <c r="B510" s="14"/>
       <c r="C510" s="14" t="s">
@@ -42684,7 +42685,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="15.75">
+    <row r="530" spans="1:7" ht="15.5">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="16" t="s">
@@ -42906,7 +42907,7 @@
       <c r="F547" s="13"/>
       <c r="G547" s="14"/>
     </row>
-    <row r="548" spans="1:7" ht="15.75">
+    <row r="548" spans="1:7" ht="15.5">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -42921,7 +42922,7 @@
       </c>
       <c r="G548" s="5"/>
     </row>
-    <row r="549" spans="1:7" ht="15.75">
+    <row r="549" spans="1:7" ht="15.5">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -42963,7 +42964,7 @@
       <c r="F552" s="4"/>
       <c r="G552" s="3"/>
     </row>
-    <row r="553" spans="1:7" ht="15.75">
+    <row r="553" spans="1:7" ht="15.5">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -42972,7 +42973,7 @@
       <c r="F553" s="4"/>
       <c r="G553" s="5"/>
     </row>
-    <row r="554" spans="1:7" ht="15.75">
+    <row r="554" spans="1:7" ht="15.5">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -42981,7 +42982,7 @@
       <c r="F554" s="4"/>
       <c r="G554" s="5"/>
     </row>
-    <row r="555" spans="1:7" ht="15.75">
+    <row r="555" spans="1:7" ht="15.5">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -43058,7 +43059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="26.25">
+    <row r="560" spans="1:7" ht="26">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -43075,7 +43076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:7" ht="26.25">
+    <row r="561" spans="1:7" ht="26">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="7"/>
@@ -43322,7 +43323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="580" spans="1:7" ht="64.5">
+    <row r="580" spans="1:7" ht="63.5">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -43337,7 +43338,7 @@
       </c>
       <c r="G580" s="5"/>
     </row>
-    <row r="581" spans="1:7" ht="26.25">
+    <row r="581" spans="1:7" ht="26">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -43354,7 +43355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="26.25">
+    <row r="582" spans="1:7" ht="26">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -43371,7 +43372,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="583" spans="1:7" ht="39">
+    <row r="583" spans="1:7" ht="38.5">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -43466,7 +43467,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="590" spans="1:7" ht="15.75">
+    <row r="590" spans="1:7" ht="15.5">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -43481,7 +43482,7 @@
       </c>
       <c r="G590" s="5"/>
     </row>
-    <row r="591" spans="1:7" ht="15.75">
+    <row r="591" spans="1:7" ht="15.5">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -43496,7 +43497,7 @@
       </c>
       <c r="G591" s="5"/>
     </row>
-    <row r="592" spans="1:7" ht="15.75">
+    <row r="592" spans="1:7" ht="15.5">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -43511,7 +43512,7 @@
       </c>
       <c r="G592" s="5"/>
     </row>
-    <row r="593" spans="1:7" ht="15.75">
+    <row r="593" spans="1:7" ht="15.5">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -43526,7 +43527,7 @@
       </c>
       <c r="G593" s="5"/>
     </row>
-    <row r="594" spans="1:7" ht="15.75">
+    <row r="594" spans="1:7" ht="15.5">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -43541,7 +43542,7 @@
       </c>
       <c r="G594" s="5"/>
     </row>
-    <row r="595" spans="1:7" ht="15.75">
+    <row r="595" spans="1:7" ht="15.5">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -43556,7 +43557,7 @@
       </c>
       <c r="G595" s="5"/>
     </row>
-    <row r="596" spans="1:7" ht="15.75">
+    <row r="596" spans="1:7" ht="15.5">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -43571,7 +43572,7 @@
       </c>
       <c r="G596" s="5"/>
     </row>
-    <row r="597" spans="1:7" ht="15.75">
+    <row r="597" spans="1:7" ht="15.5">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -43622,7 +43623,7 @@
       <c r="F602" s="4"/>
       <c r="G602" s="3"/>
     </row>
-    <row r="605" spans="1:7" ht="15.75">
+    <row r="605" spans="1:7" ht="15.5">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -43637,7 +43638,7 @@
       </c>
       <c r="G605" s="5"/>
     </row>
-    <row r="606" spans="1:7" ht="15.75">
+    <row r="606" spans="1:7" ht="15.5">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -43652,7 +43653,7 @@
       </c>
       <c r="G606" s="5"/>
     </row>
-    <row r="607" spans="1:7" ht="15.75">
+    <row r="607" spans="1:7" ht="15.5">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -43667,7 +43668,7 @@
       </c>
       <c r="G607" s="5"/>
     </row>
-    <row r="610" spans="1:7" ht="15.75">
+    <row r="610" spans="1:7" ht="15.5">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -43682,7 +43683,7 @@
       </c>
       <c r="G610" s="5"/>
     </row>
-    <row r="611" spans="1:7" ht="15.75">
+    <row r="611" spans="1:7" ht="15.5">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -43697,7 +43698,7 @@
       </c>
       <c r="G611" s="5"/>
     </row>
-    <row r="612" spans="1:7" ht="15.75">
+    <row r="612" spans="1:7" ht="15.5">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -43763,7 +43764,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="15.75">
+    <row r="618" spans="1:7" ht="15.5">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -43778,7 +43779,7 @@
       </c>
       <c r="G618" s="5"/>
     </row>
-    <row r="619" spans="1:7" ht="15.75">
+    <row r="619" spans="1:7" ht="15.5">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -43793,7 +43794,7 @@
       </c>
       <c r="G619" s="5"/>
     </row>
-    <row r="620" spans="1:7" ht="15.75">
+    <row r="620" spans="1:7" ht="15.5">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -43802,7 +43803,7 @@
       <c r="F620" s="4"/>
       <c r="G620" s="5"/>
     </row>
-    <row r="621" spans="1:7" ht="26.25">
+    <row r="621" spans="1:7" ht="26">
       <c r="A621" s="27"/>
       <c r="B621" s="27"/>
       <c r="C621" s="27"/>
@@ -43926,11 +43927,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3CE29B-B7F7-4B7E-8D51-80E542FD86A4}">
   <dimension ref="A1:I338"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="3" width="32.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" customWidth="1"/>
+    <col min="1" max="3" width="32.81640625" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="87" style="10" customWidth="1"/>
   </cols>
@@ -43985,7 +43986,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
+    <row r="3" spans="1:8" ht="15.5">
       <c r="A3" s="1" t="s">
         <v>974</v>
       </c>
@@ -44057,7 +44058,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75">
+    <row r="6" spans="1:8" ht="15.5">
       <c r="A6" s="1" t="s">
         <v>974</v>
       </c>
@@ -44107,7 +44108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
+    <row r="8" spans="1:8" ht="15.5">
       <c r="A8" s="1" t="s">
         <v>974</v>
       </c>
@@ -44205,7 +44206,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="14.1" customHeight="1">
+    <row r="12" spans="1:8" ht="14.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="114" t="s">
         <v>974</v>
@@ -44671,7 +44672,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1">
+    <row r="33" spans="1:9" ht="15" thickBot="1">
       <c r="A33" s="1" t="s">
         <v>974</v>
       </c>
@@ -44696,7 +44697,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" ht="15.75" thickBot="1">
+    <row r="34" spans="1:9" ht="15" thickBot="1">
       <c r="A34" s="1" t="s">
         <v>974</v>
       </c>
@@ -44723,7 +44724,7 @@
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="15.75" thickBot="1">
+    <row r="35" spans="1:9" ht="15" thickBot="1">
       <c r="A35" s="1" t="s">
         <v>974</v>
       </c>
@@ -44750,7 +44751,7 @@
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" thickBot="1">
+    <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="114" t="s">
@@ -44773,7 +44774,7 @@
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="15.75" thickBot="1">
+    <row r="37" spans="1:9" ht="15" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="125" t="s">
@@ -44792,7 +44793,7 @@
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" ht="15.75" thickBot="1">
+    <row r="38" spans="1:9" ht="15" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="11" t="s">
@@ -44811,7 +44812,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="15.75" thickBot="1">
+    <row r="39" spans="1:9" ht="15" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="11" t="s">
@@ -44830,7 +44831,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" ht="16.5" thickBot="1">
+    <row r="40" spans="1:9" ht="16" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="11" t="s">
@@ -45230,7 +45231,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1">
+    <row r="56" spans="1:8" ht="15" thickBot="1">
       <c r="A56" s="60" t="s">
         <v>974</v>
       </c>
@@ -45256,7 +45257,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1">
+    <row r="57" spans="1:8" ht="15" thickBot="1">
       <c r="A57" s="60" t="s">
         <v>974</v>
       </c>
@@ -45383,7 +45384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="16.5" thickBot="1">
+    <row r="62" spans="1:8" ht="16" thickBot="1">
       <c r="A62" s="60" t="s">
         <v>974</v>
       </c>
@@ -45409,7 +45410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="16.5" thickBot="1">
+    <row r="63" spans="1:8" ht="16" thickBot="1">
       <c r="A63" s="60" t="s">
         <v>974</v>
       </c>
@@ -45537,7 +45538,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75">
+    <row r="68" spans="1:8" ht="15.5">
       <c r="A68" s="60" t="s">
         <v>974</v>
       </c>
@@ -45563,7 +45564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75">
+    <row r="69" spans="1:8" ht="15.5">
       <c r="A69" s="60" t="s">
         <v>974</v>
       </c>
@@ -45606,7 +45607,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75">
+    <row r="71" spans="1:8" ht="15.5">
       <c r="A71" s="60" t="s">
         <v>974</v>
       </c>
@@ -45822,7 +45823,7 @@
       <c r="G79"/>
       <c r="H79" s="31"/>
     </row>
-    <row r="80" spans="1:8" ht="16.5">
+    <row r="80" spans="1:8" ht="16">
       <c r="A80" s="60" t="s">
         <v>974</v>
       </c>
@@ -45874,7 +45875,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75">
+    <row r="82" spans="1:8" ht="15.5">
       <c r="A82" s="60" t="s">
         <v>974</v>
       </c>
@@ -45944,7 +45945,7 @@
       <c r="G84"/>
       <c r="H84" s="31"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75">
+    <row r="85" spans="1:8" ht="15.5">
       <c r="A85" s="60" t="s">
         <v>974</v>
       </c>
@@ -45968,7 +45969,7 @@
       </c>
       <c r="H85" s="5"/>
     </row>
-    <row r="86" spans="1:8" ht="15.75">
+    <row r="86" spans="1:8" ht="15.5">
       <c r="A86" s="60" t="s">
         <v>974</v>
       </c>
@@ -46018,7 +46019,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75">
+    <row r="88" spans="1:8" ht="15.5">
       <c r="A88" s="60" t="s">
         <v>974</v>
       </c>
@@ -46042,7 +46043,7 @@
       </c>
       <c r="H88" s="5"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75">
+    <row r="89" spans="1:8" ht="15.5">
       <c r="A89" s="60"/>
       <c r="B89" s="114"/>
       <c r="C89" s="11" t="s">
@@ -46212,7 +46213,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1">
+    <row r="98" spans="1:8" ht="15" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="123" t="s">
@@ -46226,7 +46227,7 @@
       <c r="G98"/>
       <c r="H98" s="31"/>
     </row>
-    <row r="99" spans="1:8" ht="15.75" thickBot="1">
+    <row r="99" spans="1:8" ht="15" thickBot="1">
       <c r="A99" s="60" t="s">
         <v>974</v>
       </c>
@@ -46248,7 +46249,7 @@
       <c r="G99"/>
       <c r="H99" s="31"/>
     </row>
-    <row r="100" spans="1:8" ht="16.5" thickBot="1">
+    <row r="100" spans="1:8" ht="16" thickBot="1">
       <c r="A100" s="60" t="s">
         <v>974</v>
       </c>
@@ -46274,7 +46275,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" thickBot="1">
+    <row r="101" spans="1:8" ht="15" thickBot="1">
       <c r="A101" s="60" t="s">
         <v>974</v>
       </c>
@@ -46297,7 +46298,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" thickBot="1">
+    <row r="102" spans="1:8" ht="15" thickBot="1">
       <c r="A102" s="60" t="s">
         <v>974</v>
       </c>
@@ -46320,7 +46321,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.75" thickBot="1">
+    <row r="103" spans="1:8" ht="15" thickBot="1">
       <c r="A103" s="60" t="s">
         <v>974</v>
       </c>
@@ -46343,7 +46344,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="16.5" thickBot="1">
+    <row r="104" spans="1:8" ht="16" thickBot="1">
       <c r="A104" s="60" t="s">
         <v>974</v>
       </c>
@@ -46367,7 +46368,7 @@
       </c>
       <c r="H104" s="5"/>
     </row>
-    <row r="105" spans="1:8" ht="15.75" thickBot="1">
+    <row r="105" spans="1:8" ht="15" thickBot="1">
       <c r="A105" s="60" t="s">
         <v>974</v>
       </c>
@@ -46390,7 +46391,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" thickBot="1">
+    <row r="106" spans="1:8" ht="15" thickBot="1">
       <c r="A106" s="60" t="s">
         <v>974</v>
       </c>
@@ -46411,7 +46412,7 @@
       </c>
       <c r="G106"/>
     </row>
-    <row r="107" spans="1:8" ht="15.75" thickBot="1">
+    <row r="107" spans="1:8" ht="15" thickBot="1">
       <c r="A107" s="60" t="s">
         <v>974</v>
       </c>
@@ -46437,7 +46438,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" thickBot="1">
+    <row r="108" spans="1:8" ht="15" thickBot="1">
       <c r="A108" s="60" t="s">
         <v>974</v>
       </c>
@@ -46463,7 +46464,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" thickBot="1">
+    <row r="109" spans="1:8" ht="15" thickBot="1">
       <c r="A109" s="60" t="s">
         <v>974</v>
       </c>
@@ -46489,7 +46490,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="16.5" thickBot="1">
+    <row r="110" spans="1:8" ht="16" thickBot="1">
       <c r="A110" s="60" t="s">
         <v>974</v>
       </c>
@@ -46515,7 +46516,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="16.5" thickBot="1">
+    <row r="111" spans="1:8" ht="16" thickBot="1">
       <c r="A111" s="60" t="s">
         <v>974</v>
       </c>
@@ -46541,7 +46542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" thickBot="1">
+    <row r="112" spans="1:8" ht="15" thickBot="1">
       <c r="A112" s="60" t="s">
         <v>974</v>
       </c>
@@ -46612,7 +46613,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.75">
+    <row r="115" spans="1:8" ht="15.5">
       <c r="A115" s="60" t="s">
         <v>974</v>
       </c>
@@ -46636,7 +46637,7 @@
       </c>
       <c r="H115" s="5"/>
     </row>
-    <row r="116" spans="1:8" ht="15.75">
+    <row r="116" spans="1:8" ht="15.5">
       <c r="A116" s="60" t="s">
         <v>974</v>
       </c>
@@ -46660,7 +46661,7 @@
       </c>
       <c r="H116" s="5"/>
     </row>
-    <row r="117" spans="1:8" ht="15.75">
+    <row r="117" spans="1:8" ht="15.5">
       <c r="A117" s="60" t="s">
         <v>974</v>
       </c>
@@ -46686,7 +46687,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75">
+    <row r="118" spans="1:8" ht="15.5">
       <c r="A118" s="60" t="s">
         <v>974</v>
       </c>
@@ -46732,7 +46733,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75">
+    <row r="120" spans="1:8" ht="15.5">
       <c r="A120" s="60" t="s">
         <v>974</v>
       </c>
@@ -46758,7 +46759,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75">
+    <row r="121" spans="1:8" ht="15.5">
       <c r="A121" s="60" t="s">
         <v>974</v>
       </c>
@@ -46831,7 +46832,7 @@
       </c>
       <c r="G123"/>
     </row>
-    <row r="124" spans="1:8" ht="15.75">
+    <row r="124" spans="1:8" ht="15.5">
       <c r="A124" s="60" t="s">
         <v>974</v>
       </c>
@@ -46956,7 +46957,7 @@
       </c>
       <c r="G128"/>
     </row>
-    <row r="129" spans="1:8" ht="16.5">
+    <row r="129" spans="1:8" ht="16">
       <c r="A129" s="60" t="s">
         <v>974</v>
       </c>
@@ -47034,7 +47035,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" thickBot="1">
+    <row r="132" spans="1:8" ht="15" thickBot="1">
       <c r="A132" s="60" t="s">
         <v>974</v>
       </c>
@@ -47060,7 +47061,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" thickBot="1">
+    <row r="133" spans="1:8" ht="15" thickBot="1">
       <c r="A133" s="60" t="s">
         <v>974</v>
       </c>
@@ -47079,7 +47080,7 @@
       <c r="F133" s="3"/>
       <c r="G133"/>
     </row>
-    <row r="134" spans="1:8" ht="15.75" thickBot="1">
+    <row r="134" spans="1:8" ht="15" thickBot="1">
       <c r="A134" s="60" t="s">
         <v>974</v>
       </c>
@@ -47105,7 +47106,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" thickBot="1">
+    <row r="135" spans="1:8" ht="15" thickBot="1">
       <c r="A135" s="60" t="s">
         <v>974</v>
       </c>
@@ -47131,7 +47132,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="17.25" thickBot="1">
+    <row r="136" spans="1:8" ht="16.5" thickBot="1">
       <c r="A136" s="60" t="s">
         <v>974</v>
       </c>
@@ -47157,7 +47158,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="17.25" thickBot="1">
+    <row r="137" spans="1:8" ht="16.5" thickBot="1">
       <c r="A137" s="60" t="s">
         <v>974</v>
       </c>
@@ -47183,7 +47184,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="17.25" thickBot="1">
+    <row r="138" spans="1:8" ht="16.5" thickBot="1">
       <c r="A138" s="60" t="s">
         <v>974</v>
       </c>
@@ -47209,7 +47210,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="17.25" thickBot="1">
+    <row r="139" spans="1:8" ht="16.5" thickBot="1">
       <c r="A139" s="60" t="s">
         <v>974</v>
       </c>
@@ -47235,7 +47236,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="17.25" thickBot="1">
+    <row r="140" spans="1:8" ht="16.5" thickBot="1">
       <c r="A140" s="60" t="s">
         <v>974</v>
       </c>
@@ -47261,7 +47262,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="17.25" thickBot="1">
+    <row r="141" spans="1:8" ht="16.5" thickBot="1">
       <c r="A141" s="60" t="s">
         <v>974</v>
       </c>
@@ -47287,7 +47288,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" thickBot="1">
+    <row r="142" spans="1:8" ht="15" thickBot="1">
       <c r="A142" s="60" t="s">
         <v>974</v>
       </c>
@@ -47310,7 +47311,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="17.25" thickBot="1">
+    <row r="143" spans="1:8" ht="16.5" thickBot="1">
       <c r="A143" s="60" t="s">
         <v>974</v>
       </c>
@@ -47336,7 +47337,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="17.25" thickBot="1">
+    <row r="144" spans="1:8" ht="16.5" thickBot="1">
       <c r="A144" s="60" t="s">
         <v>974</v>
       </c>
@@ -47362,7 +47363,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="17.25" thickBot="1">
+    <row r="145" spans="1:8" ht="16.5" thickBot="1">
       <c r="A145" s="60" t="s">
         <v>974</v>
       </c>
@@ -47388,7 +47389,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="17.25" thickBot="1">
+    <row r="146" spans="1:8" ht="16.5" thickBot="1">
       <c r="A146" s="60" t="s">
         <v>974</v>
       </c>
@@ -47414,7 +47415,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" thickBot="1">
+    <row r="147" spans="1:8" ht="15" thickBot="1">
       <c r="A147" s="60" t="s">
         <v>974</v>
       </c>
@@ -47438,7 +47439,7 @@
       </c>
       <c r="H147" s="41"/>
     </row>
-    <row r="148" spans="1:8" ht="15.75" thickBot="1">
+    <row r="148" spans="1:8" ht="15" thickBot="1">
       <c r="A148" s="60" t="s">
         <v>974</v>
       </c>
@@ -47458,7 +47459,7 @@
       <c r="G148"/>
       <c r="H148" s="41"/>
     </row>
-    <row r="149" spans="1:8" ht="15.75" thickBot="1">
+    <row r="149" spans="1:8" ht="15" thickBot="1">
       <c r="A149" s="60" t="s">
         <v>974</v>
       </c>
@@ -47484,7 +47485,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" thickBot="1">
+    <row r="150" spans="1:8" ht="15" thickBot="1">
       <c r="A150" s="60" t="s">
         <v>974</v>
       </c>
@@ -47507,7 +47508,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="17.25" thickBot="1">
+    <row r="151" spans="1:8" ht="16.5" thickBot="1">
       <c r="A151" s="60" t="s">
         <v>974</v>
       </c>
@@ -47533,7 +47534,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="17.25" thickBot="1">
+    <row r="152" spans="1:8" ht="16.5" thickBot="1">
       <c r="A152" s="60" t="s">
         <v>974</v>
       </c>
@@ -47559,7 +47560,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="17.25" thickBot="1">
+    <row r="153" spans="1:8" ht="16.5" thickBot="1">
       <c r="A153" s="60" t="s">
         <v>974</v>
       </c>
@@ -47585,7 +47586,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="17.25" thickBot="1">
+    <row r="154" spans="1:8" ht="16.5" thickBot="1">
       <c r="A154" s="60" t="s">
         <v>974</v>
       </c>
@@ -47611,7 +47612,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="17.25" thickBot="1">
+    <row r="155" spans="1:8" ht="16.5" thickBot="1">
       <c r="A155" s="60" t="s">
         <v>974</v>
       </c>
@@ -47637,7 +47638,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="17.25" thickBot="1">
+    <row r="156" spans="1:8" ht="16.5" thickBot="1">
       <c r="A156" s="60" t="s">
         <v>974</v>
       </c>
@@ -47663,7 +47664,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" thickBot="1">
+    <row r="157" spans="1:8" ht="15" thickBot="1">
       <c r="A157" s="60" t="s">
         <v>974</v>
       </c>
@@ -47689,7 +47690,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="17.25" thickBot="1">
+    <row r="158" spans="1:8" ht="16.5" thickBot="1">
       <c r="A158" s="60" t="s">
         <v>974</v>
       </c>
@@ -47715,7 +47716,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="17.25" thickBot="1">
+    <row r="159" spans="1:8" ht="16.5" thickBot="1">
       <c r="A159" s="60" t="s">
         <v>974</v>
       </c>
@@ -47741,7 +47742,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="17.25" thickBot="1">
+    <row r="160" spans="1:8" ht="16.5" thickBot="1">
       <c r="A160" s="60" t="s">
         <v>974</v>
       </c>
@@ -47767,7 +47768,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="17.25" thickBot="1">
+    <row r="161" spans="1:8" ht="16.5" thickBot="1">
       <c r="A161" s="60" t="s">
         <v>974</v>
       </c>
@@ -47793,7 +47794,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" thickBot="1">
+    <row r="162" spans="1:8" ht="15" thickBot="1">
       <c r="A162" s="60" t="s">
         <v>974</v>
       </c>
@@ -47817,7 +47818,7 @@
       </c>
       <c r="H162" s="41"/>
     </row>
-    <row r="163" spans="1:8" ht="15.75" thickBot="1">
+    <row r="163" spans="1:8" ht="15" thickBot="1">
       <c r="A163" s="60" t="s">
         <v>974</v>
       </c>
@@ -47841,7 +47842,7 @@
       </c>
       <c r="H163" s="41"/>
     </row>
-    <row r="164" spans="1:8" ht="15.75" thickBot="1">
+    <row r="164" spans="1:8" ht="15" thickBot="1">
       <c r="A164" s="60" t="s">
         <v>974</v>
       </c>
@@ -47867,7 +47868,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" thickBot="1">
+    <row r="165" spans="1:8" ht="15" thickBot="1">
       <c r="A165" s="60" t="s">
         <v>974</v>
       </c>
@@ -47893,7 +47894,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" thickBot="1">
+    <row r="166" spans="1:8" ht="15" thickBot="1">
       <c r="A166" s="60" t="s">
         <v>974</v>
       </c>
@@ -47916,7 +47917,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" thickBot="1">
+    <row r="167" spans="1:8" ht="15" thickBot="1">
       <c r="A167" s="60" t="s">
         <v>974</v>
       </c>
@@ -47942,7 +47943,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" thickBot="1">
+    <row r="168" spans="1:8" ht="15" thickBot="1">
       <c r="A168" s="60" t="s">
         <v>974</v>
       </c>
@@ -47968,12 +47969,14 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" thickBot="1">
+    <row r="169" spans="1:8" ht="15" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C169" s="114"/>
+      <c r="C169" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D169" s="71" t="s">
         <v>924</v>
       </c>
@@ -47985,7 +47988,7 @@
       </c>
       <c r="G169"/>
     </row>
-    <row r="170" spans="1:8" ht="15.75" thickBot="1">
+    <row r="170" spans="1:8" ht="15" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="121" t="s">
         <v>1509</v>
@@ -48007,12 +48010,14 @@
         <v>490</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="17.25" thickBot="1">
+    <row r="171" spans="1:8" ht="16.5" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C171" s="114"/>
+      <c r="C171" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D171" s="71" t="s">
         <v>924</v>
       </c>
@@ -48029,12 +48034,14 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" thickBot="1">
+    <row r="172" spans="1:8" ht="15" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C172" s="114"/>
+      <c r="C172" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D172" s="71" t="s">
         <v>924</v>
       </c>
@@ -48044,7 +48051,7 @@
       <c r="F172" s="17"/>
       <c r="G172"/>
     </row>
-    <row r="173" spans="1:8" ht="15.75" thickBot="1">
+    <row r="173" spans="1:8" ht="15" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="121" t="s">
         <v>1509</v>
@@ -48066,12 +48073,14 @@
         <v>493</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="17.25" thickBot="1">
+    <row r="174" spans="1:8" ht="16.5" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C174" s="114"/>
+      <c r="C174" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D174" s="71" t="s">
         <v>924</v>
       </c>
@@ -48088,12 +48097,14 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" thickBot="1">
+    <row r="175" spans="1:8" ht="15" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C175" s="114"/>
+      <c r="C175" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D175" s="72" t="s">
         <v>925</v>
       </c>
@@ -48103,12 +48114,14 @@
       <c r="F175" s="17"/>
       <c r="G175"/>
     </row>
-    <row r="176" spans="1:8" ht="15.75" thickBot="1">
+    <row r="176" spans="1:8" ht="15" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C176" s="114"/>
+      <c r="C176" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D176" s="72" t="s">
         <v>925</v>
       </c>
@@ -48125,12 +48138,14 @@
         <v>501</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" thickBot="1">
+    <row r="177" spans="1:8" ht="15" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C177" s="114"/>
+      <c r="C177" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D177" s="72" t="s">
         <v>925</v>
       </c>
@@ -48145,12 +48160,14 @@
       </c>
       <c r="H177" s="69"/>
     </row>
-    <row r="178" spans="1:8" ht="15.75" thickBot="1">
+    <row r="178" spans="1:8" ht="15" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C178" s="114"/>
+      <c r="C178" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D178" s="72" t="s">
         <v>925</v>
       </c>
@@ -48165,12 +48182,14 @@
       </c>
       <c r="H178" s="43"/>
     </row>
-    <row r="179" spans="1:8" ht="15.75" thickBot="1">
+    <row r="179" spans="1:8" ht="15" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C179" s="114"/>
+      <c r="C179" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D179" s="72" t="s">
         <v>925</v>
       </c>
@@ -48185,12 +48204,14 @@
       </c>
       <c r="H179" s="44"/>
     </row>
-    <row r="180" spans="1:8" ht="15.75" thickBot="1">
+    <row r="180" spans="1:8" ht="15" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C180" s="114"/>
+      <c r="C180" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D180" s="72" t="s">
         <v>925</v>
       </c>
@@ -48205,12 +48226,14 @@
       </c>
       <c r="H180" s="44"/>
     </row>
-    <row r="181" spans="1:8" ht="15.75" thickBot="1">
+    <row r="181" spans="1:8" ht="15" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C181" s="114"/>
+      <c r="C181" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D181" s="72" t="s">
         <v>925</v>
       </c>
@@ -48224,12 +48247,14 @@
         <v>529</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" thickBot="1">
+    <row r="182" spans="1:8" ht="15" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C182" s="114"/>
+      <c r="C182" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D182" s="72" t="s">
         <v>925</v>
       </c>
@@ -48243,12 +48268,14 @@
         <v>530</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" thickBot="1">
+    <row r="183" spans="1:8" ht="15" thickBot="1">
       <c r="A183" s="1"/>
       <c r="B183" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C183" s="114"/>
+      <c r="C183" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D183" s="72" t="s">
         <v>925</v>
       </c>
@@ -48265,12 +48292,14 @@
         <v>523</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" thickBot="1">
+    <row r="184" spans="1:8" ht="15" thickBot="1">
       <c r="A184" s="108"/>
       <c r="B184" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C184" s="114"/>
+      <c r="C184" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D184" s="72" t="s">
         <v>925</v>
       </c>
@@ -48284,12 +48313,14 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" thickBot="1">
+    <row r="185" spans="1:8" ht="15" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C185" s="114"/>
+      <c r="C185" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D185" s="72" t="s">
         <v>925</v>
       </c>
@@ -48303,12 +48334,14 @@
         <v>531</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" thickBot="1">
+    <row r="186" spans="1:8" ht="15" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C186" s="114"/>
+      <c r="C186" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D186" s="72" t="s">
         <v>925</v>
       </c>
@@ -48320,12 +48353,14 @@
       </c>
       <c r="G186"/>
     </row>
-    <row r="187" spans="1:8" ht="15.75" thickBot="1">
+    <row r="187" spans="1:8" ht="15" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C187" s="114"/>
+      <c r="C187" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D187" s="72" t="s">
         <v>925</v>
       </c>
@@ -48342,12 +48377,14 @@
         <v>520</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" thickBot="1">
+    <row r="188" spans="1:8" ht="15" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C188" s="114"/>
+      <c r="C188" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D188" s="72" t="s">
         <v>925</v>
       </c>
@@ -48362,12 +48399,14 @@
       </c>
       <c r="H188" s="73"/>
     </row>
-    <row r="189" spans="1:8" ht="15.75" thickBot="1">
+    <row r="189" spans="1:8" ht="15" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C189" s="114"/>
+      <c r="C189" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D189" s="72" t="s">
         <v>925</v>
       </c>
@@ -48384,12 +48423,14 @@
         <v>511</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" thickBot="1">
+    <row r="190" spans="1:8" ht="15" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C190" s="114"/>
+      <c r="C190" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D190" s="72" t="s">
         <v>925</v>
       </c>
@@ -48406,12 +48447,14 @@
         <v>511</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" thickBot="1">
+    <row r="191" spans="1:8" ht="15" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C191" s="114"/>
+      <c r="C191" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D191" s="72" t="s">
         <v>925</v>
       </c>
@@ -48428,12 +48471,14 @@
         <v>511</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" thickBot="1">
+    <row r="192" spans="1:8" ht="15" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C192" s="114"/>
+      <c r="C192" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D192" s="72" t="s">
         <v>925</v>
       </c>
@@ -48447,12 +48492,14 @@
         <v>529</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" thickBot="1">
+    <row r="193" spans="1:8" ht="15" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C193" s="114"/>
+      <c r="C193" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D193" s="72" t="s">
         <v>925</v>
       </c>
@@ -48469,12 +48516,14 @@
         <v>521</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" thickBot="1">
+    <row r="194" spans="1:8" ht="15" thickBot="1">
       <c r="A194" s="1"/>
       <c r="B194" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C194" s="114"/>
+      <c r="C194" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D194" s="72" t="s">
         <v>925</v>
       </c>
@@ -48491,12 +48540,14 @@
         <v>523</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" thickBot="1">
+    <row r="195" spans="1:8" ht="15" thickBot="1">
       <c r="A195" s="108"/>
       <c r="B195" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C195" s="114"/>
+      <c r="C195" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D195" s="72" t="s">
         <v>925</v>
       </c>
@@ -48513,12 +48564,14 @@
         <v>511</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" thickBot="1">
+    <row r="196" spans="1:8" ht="15" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C196" s="114"/>
+      <c r="C196" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D196" s="72" t="s">
         <v>925</v>
       </c>
@@ -48535,12 +48588,14 @@
         <v>511</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" thickBot="1">
+    <row r="197" spans="1:8" ht="15" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C197" s="114"/>
+      <c r="C197" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D197" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48552,12 +48607,14 @@
       </c>
       <c r="H197" s="41"/>
     </row>
-    <row r="198" spans="1:8" ht="15.75" thickBot="1">
+    <row r="198" spans="1:8" ht="15" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C198" s="114"/>
+      <c r="C198" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D198" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48574,12 +48631,14 @@
         <v>548</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" thickBot="1">
+    <row r="199" spans="1:8" ht="15" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C199" s="114"/>
+      <c r="C199" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D199" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48596,12 +48655,14 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" thickBot="1">
+    <row r="200" spans="1:8" ht="15" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C200" s="114"/>
+      <c r="C200" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D200" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48614,12 +48675,14 @@
       <c r="G200"/>
       <c r="H200" s="29"/>
     </row>
-    <row r="201" spans="1:8" ht="15.75" thickBot="1">
+    <row r="201" spans="1:8" ht="15" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C201" s="114"/>
+      <c r="C201" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D201" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48636,12 +48699,14 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" thickBot="1">
+    <row r="202" spans="1:8" ht="15" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C202" s="114"/>
+      <c r="C202" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D202" s="91" t="s">
         <v>1097</v>
       </c>
@@ -48658,12 +48723,14 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" thickBot="1">
+    <row r="203" spans="1:8" ht="15" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C203" s="114"/>
+      <c r="C203" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D203" s="76" t="s">
         <v>975</v>
       </c>
@@ -48675,12 +48742,14 @@
       </c>
       <c r="G203"/>
     </row>
-    <row r="204" spans="1:8" ht="15.75" thickBot="1">
+    <row r="204" spans="1:8" ht="15" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C204" s="114"/>
+      <c r="C204" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D204" s="76" t="s">
         <v>975</v>
       </c>
@@ -48694,12 +48763,14 @@
         <v>563</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" thickBot="1">
+    <row r="205" spans="1:8" ht="15" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C205" s="114"/>
+      <c r="C205" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D205" s="76" t="s">
         <v>975</v>
       </c>
@@ -48711,12 +48782,14 @@
       </c>
       <c r="G205"/>
     </row>
-    <row r="206" spans="1:8" ht="15.75" thickBot="1">
+    <row r="206" spans="1:8" ht="15" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C206" s="114"/>
+      <c r="C206" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D206" s="76" t="s">
         <v>975</v>
       </c>
@@ -48733,12 +48806,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" thickBot="1">
+    <row r="207" spans="1:8" ht="15" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C207" s="114"/>
+      <c r="C207" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D207" s="76" t="s">
         <v>975</v>
       </c>
@@ -48752,12 +48827,14 @@
         <v>967</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" thickBot="1">
+    <row r="208" spans="1:8" ht="15" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C208" s="114"/>
+      <c r="C208" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D208" s="76" t="s">
         <v>975</v>
       </c>
@@ -48774,12 +48851,14 @@
         <v>565</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15.75" thickBot="1">
+    <row r="209" spans="1:8" ht="15" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C209" s="114"/>
+      <c r="C209" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D209" s="76" t="s">
         <v>975</v>
       </c>
@@ -48796,12 +48875,14 @@
         <v>567</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" thickBot="1">
+    <row r="210" spans="1:8" ht="15" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C210" s="114"/>
+      <c r="C210" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D210" s="76" t="s">
         <v>975</v>
       </c>
@@ -48813,12 +48894,14 @@
       </c>
       <c r="G210"/>
     </row>
-    <row r="211" spans="1:8" ht="15.75" thickBot="1">
+    <row r="211" spans="1:8" ht="15" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C211" s="114"/>
+      <c r="C211" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D211" s="76" t="s">
         <v>975</v>
       </c>
@@ -48832,12 +48915,14 @@
         <v>568</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="15.75" thickBot="1">
+    <row r="212" spans="1:8" ht="15" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C212" s="114"/>
+      <c r="C212" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D212" s="76" t="s">
         <v>975</v>
       </c>
@@ -48849,12 +48934,14 @@
       </c>
       <c r="G212"/>
     </row>
-    <row r="213" spans="1:8" ht="15.75" thickBot="1">
+    <row r="213" spans="1:8" ht="15" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C213" s="114"/>
+      <c r="C213" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D213" s="76" t="s">
         <v>975</v>
       </c>
@@ -48871,12 +48958,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75" thickBot="1">
+    <row r="214" spans="1:8" ht="15" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C214" s="114"/>
+      <c r="C214" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D214" s="76" t="s">
         <v>975</v>
       </c>
@@ -48890,12 +48979,14 @@
         <v>962</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75" thickBot="1">
+    <row r="215" spans="1:8" ht="15" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C215" s="114"/>
+      <c r="C215" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D215" s="76" t="s">
         <v>975</v>
       </c>
@@ -48912,12 +49003,14 @@
         <v>565</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75" thickBot="1">
+    <row r="216" spans="1:8" ht="15" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C216" s="114"/>
+      <c r="C216" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D216" s="76" t="s">
         <v>975</v>
       </c>
@@ -48931,12 +49024,14 @@
         <v>570</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" thickBot="1">
+    <row r="217" spans="1:8" ht="15" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C217" s="114"/>
+      <c r="C217" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D217" s="77" t="s">
         <v>1437</v>
       </c>
@@ -48946,12 +49041,14 @@
       <c r="F217" s="17"/>
       <c r="G217"/>
     </row>
-    <row r="218" spans="1:8" ht="15.75" thickBot="1">
+    <row r="218" spans="1:8" ht="15" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C218" s="114"/>
+      <c r="C218" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D218" s="77" t="s">
         <v>1437</v>
       </c>
@@ -48965,12 +49062,14 @@
         <v>585</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15.75" thickBot="1">
+    <row r="219" spans="1:8" ht="15" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C219" s="114"/>
+      <c r="C219" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D219" s="77" t="s">
         <v>1437</v>
       </c>
@@ -48980,12 +49079,14 @@
       <c r="F219" s="17"/>
       <c r="G219"/>
     </row>
-    <row r="220" spans="1:8" ht="15.75" thickBot="1">
+    <row r="220" spans="1:8" ht="15" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C220" s="114"/>
+      <c r="C220" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D220" s="77" t="s">
         <v>1437</v>
       </c>
@@ -48999,12 +49100,14 @@
         <v>575</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" thickBot="1">
+    <row r="221" spans="1:8" ht="15" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C221" s="1"/>
+      <c r="C221" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D221" s="71" t="s">
         <v>990</v>
       </c>
@@ -49016,7 +49119,7 @@
       </c>
       <c r="G221"/>
     </row>
-    <row r="222" spans="1:8" ht="15.75" thickBot="1">
+    <row r="222" spans="1:8" ht="15" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="121" t="s">
         <v>1550</v>
@@ -49035,12 +49138,14 @@
         <v>580</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" thickBot="1">
+    <row r="223" spans="1:8" ht="15" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C223" s="1"/>
+      <c r="C223" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D223" s="71" t="s">
         <v>990</v>
       </c>
@@ -49057,12 +49162,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" thickBot="1">
+    <row r="224" spans="1:8" ht="15" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C224" s="1"/>
+      <c r="C224" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D224" s="71" t="s">
         <v>990</v>
       </c>
@@ -49076,12 +49183,14 @@
         <v>985</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75" thickBot="1">
+    <row r="225" spans="1:8" ht="15" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C225" s="1"/>
+      <c r="C225" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D225" s="71" t="s">
         <v>990</v>
       </c>
@@ -49095,12 +49204,14 @@
         <v>581</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15.75" thickBot="1">
+    <row r="226" spans="1:8" ht="15" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C226" s="1"/>
+      <c r="C226" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D226" s="71" t="s">
         <v>990</v>
       </c>
@@ -49112,7 +49223,7 @@
       </c>
       <c r="G226"/>
     </row>
-    <row r="227" spans="1:8" ht="15.75" thickBot="1">
+    <row r="227" spans="1:8" ht="15" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="121" t="s">
         <v>1550</v>
@@ -49131,12 +49242,14 @@
         <v>582</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" thickBot="1">
+    <row r="228" spans="1:8" ht="15" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C228" s="1"/>
+      <c r="C228" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D228" s="71" t="s">
         <v>990</v>
       </c>
@@ -49153,12 +49266,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" thickBot="1">
+    <row r="229" spans="1:8" ht="15" thickBot="1">
       <c r="A229" s="1"/>
       <c r="B229" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C229" s="1"/>
+      <c r="C229" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D229" s="71" t="s">
         <v>990</v>
       </c>
@@ -49177,7 +49292,9 @@
       <c r="B230" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C230" s="1"/>
+      <c r="C230" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D230" s="71" t="s">
         <v>990</v>
       </c>
@@ -49196,7 +49313,9 @@
       <c r="B231" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C231" s="1"/>
+      <c r="C231" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D231" s="135" t="s">
         <v>1577</v>
       </c>
@@ -49293,7 +49412,9 @@
       <c r="B236" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C236" s="1"/>
+      <c r="C236" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D236" s="135" t="s">
         <v>1577</v>
       </c>
@@ -49360,7 +49481,7 @@
       <c r="F239" s="19"/>
       <c r="G239"/>
     </row>
-    <row r="240" spans="1:8" ht="15.75" thickBot="1">
+    <row r="240" spans="1:8" ht="15" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="123" t="s">
         <v>1412</v>
@@ -49381,7 +49502,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15.75" thickBot="1">
+    <row r="241" spans="1:8" ht="15" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="125" t="s">
         <v>1003</v>
@@ -49398,7 +49519,7 @@
       <c r="F241" s="19"/>
       <c r="G241"/>
     </row>
-    <row r="242" spans="1:8" ht="15.75" thickBot="1">
+    <row r="242" spans="1:8" ht="15" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="125" t="s">
         <v>1003</v>
@@ -49415,7 +49536,7 @@
       <c r="F242" s="19"/>
       <c r="G242"/>
     </row>
-    <row r="243" spans="1:8" ht="15.75" thickBot="1">
+    <row r="243" spans="1:8" ht="15" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="125" t="s">
         <v>1003</v>
@@ -49432,7 +49553,7 @@
       <c r="F243" s="19"/>
       <c r="G243"/>
     </row>
-    <row r="244" spans="1:8" ht="15.75" thickBot="1">
+    <row r="244" spans="1:8" ht="15" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="125" t="s">
         <v>1003</v>
@@ -49449,7 +49570,7 @@
       <c r="F244" s="19"/>
       <c r="G244"/>
     </row>
-    <row r="245" spans="1:8" ht="15.75" thickBot="1">
+    <row r="245" spans="1:8" ht="15" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="125" t="s">
         <v>1003</v>
@@ -49466,7 +49587,7 @@
       <c r="F245" s="19"/>
       <c r="G245"/>
     </row>
-    <row r="246" spans="1:8" ht="15.75" thickBot="1">
+    <row r="246" spans="1:8" ht="15" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="125" t="s">
         <v>1003</v>
@@ -49483,7 +49604,7 @@
       <c r="F246" s="19"/>
       <c r="G246"/>
     </row>
-    <row r="247" spans="1:8" ht="15.75" thickBot="1">
+    <row r="247" spans="1:8" ht="15" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="125" t="s">
         <v>1003</v>
@@ -49500,7 +49621,7 @@
       <c r="F247" s="19"/>
       <c r="G247"/>
     </row>
-    <row r="248" spans="1:8" ht="15.75" thickBot="1">
+    <row r="248" spans="1:8" ht="15" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="125" t="s">
         <v>1003</v>
@@ -49517,7 +49638,7 @@
       <c r="F248" s="19"/>
       <c r="G248"/>
     </row>
-    <row r="249" spans="1:8" ht="15.75" thickBot="1">
+    <row r="249" spans="1:8" ht="15" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="125" t="s">
         <v>1003</v>
@@ -49534,7 +49655,7 @@
       <c r="F249" s="19"/>
       <c r="G249"/>
     </row>
-    <row r="250" spans="1:8" ht="15.75" thickBot="1">
+    <row r="250" spans="1:8" ht="15" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="125" t="s">
         <v>1003</v>
@@ -49551,14 +49672,16 @@
       <c r="F250" s="19"/>
       <c r="G250"/>
     </row>
-    <row r="251" spans="1:8" ht="15.75" thickBot="1">
+    <row r="251" spans="1:8" ht="15" thickBot="1">
       <c r="A251" s="1" t="s">
         <v>1438</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="C251" s="1"/>
+      <c r="C251" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D251" s="79" t="s">
         <v>1002</v>
       </c>
@@ -49572,14 +49695,16 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15.75" thickBot="1">
+    <row r="252" spans="1:8" ht="15" thickBot="1">
       <c r="A252" s="1" t="s">
         <v>1438</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="C252" s="1"/>
+      <c r="C252" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D252" s="79" t="s">
         <v>1002</v>
       </c>
@@ -49593,7 +49718,9 @@
     <row r="253" spans="1:8">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
+      <c r="C253" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D253" s="79" t="s">
         <v>1002</v>
       </c>
@@ -49605,7 +49732,9 @@
     <row r="254" spans="1:8">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
+      <c r="C254" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D254" s="79" t="s">
         <v>1002</v>
       </c>
@@ -49674,7 +49803,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" thickBot="1">
+    <row r="258" spans="1:9" ht="15" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -49697,7 +49826,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" thickBot="1">
+    <row r="259" spans="1:9" ht="15" thickBot="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -49774,7 +49903,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" thickBot="1">
+    <row r="263" spans="1:9" ht="15" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -49794,7 +49923,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" thickBot="1">
+    <row r="264" spans="1:9" ht="15" thickBot="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -50414,7 +50543,7 @@
       </c>
       <c r="H300" s="14"/>
     </row>
-    <row r="301" spans="1:8" ht="15.75" thickBot="1">
+    <row r="301" spans="1:8" ht="15" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -50432,7 +50561,7 @@
       </c>
       <c r="H301" s="14"/>
     </row>
-    <row r="302" spans="1:8" ht="15.75" thickBot="1">
+    <row r="302" spans="1:8" ht="15" thickBot="1">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -50895,26 +51024,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -51115,26 +51224,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -51151,4 +51261,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3225" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A50586-65B9-4B8E-B299-E1099556587E}"/>
+  <xr:revisionPtr revIDLastSave="3316" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38A4DB2-4DA8-4F7D-A8C2-19E4E4FBE17F}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" firstSheet="1" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'10_FOMD_ERA_readme_OLD'!$A$1:$S$321</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,10 +44,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={70416B9F-A49B-4976-AD74-7ABC1D157763}</author>
+    <author>tc={5E1778F3-5314-4E36-9058-282C0A5FC15F}</author>
   </authors>
   <commentList>
-    <comment ref="JL1" authorId="0" shapeId="0" xr:uid="{70416B9F-A49B-4976-AD74-7ABC1D157763}">
+    <comment ref="JL1" authorId="0" shapeId="0" xr:uid="{5E1778F3-5314-4E36-9058-282C0A5FC15F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -414,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8468" uniqueCount="1654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8509" uniqueCount="1656">
   <si>
     <t>Example</t>
   </si>
@@ -11203,6 +11202,12 @@
   </si>
   <si>
     <t>it is missing</t>
+  </si>
+  <si>
+    <t>PENDING FIXING FROM LOLITA</t>
+  </si>
+  <si>
+    <t>PENDING NEED TO FIND AN STRATEGY</t>
   </si>
 </sst>
 </file>
@@ -12194,7 +12199,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12468,6 +12473,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="56" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -13304,7 +13310,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="JL1" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{70416B9F-A49B-4976-AD74-7ABC1D157763}">
+  <threadedComment ref="JL1" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{5E1778F3-5314-4E36-9058-282C0A5FC15F}">
     <text>Should be the same for C and T, to check!</text>
   </threadedComment>
 </ThreadedComments>
@@ -33209,24 +33215,6 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33236,6 +33224,24 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -43887,6 +43893,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D562:D563"/>
+    <mergeCell ref="E562:E563"/>
+    <mergeCell ref="F562:F563"/>
+    <mergeCell ref="D566:D567"/>
+    <mergeCell ref="E566:E567"/>
+    <mergeCell ref="F566:F567"/>
+    <mergeCell ref="D568:D569"/>
+    <mergeCell ref="E568:E569"/>
+    <mergeCell ref="F568:F569"/>
+    <mergeCell ref="D572:D573"/>
+    <mergeCell ref="E572:E573"/>
+    <mergeCell ref="F572:F573"/>
+    <mergeCell ref="D574:D575"/>
+    <mergeCell ref="E574:E575"/>
+    <mergeCell ref="F574:F575"/>
+    <mergeCell ref="D576:D577"/>
+    <mergeCell ref="E576:E577"/>
+    <mergeCell ref="F576:F577"/>
     <mergeCell ref="D587:D589"/>
     <mergeCell ref="E587:E589"/>
     <mergeCell ref="F587:F589"/>
@@ -43896,24 +43920,6 @@
     <mergeCell ref="D584:D586"/>
     <mergeCell ref="E584:E586"/>
     <mergeCell ref="F584:F586"/>
-    <mergeCell ref="D574:D575"/>
-    <mergeCell ref="E574:E575"/>
-    <mergeCell ref="F574:F575"/>
-    <mergeCell ref="D576:D577"/>
-    <mergeCell ref="E576:E577"/>
-    <mergeCell ref="F576:F577"/>
-    <mergeCell ref="D568:D569"/>
-    <mergeCell ref="E568:E569"/>
-    <mergeCell ref="F568:F569"/>
-    <mergeCell ref="D572:D573"/>
-    <mergeCell ref="E572:E573"/>
-    <mergeCell ref="F572:F573"/>
-    <mergeCell ref="D562:D563"/>
-    <mergeCell ref="E562:E563"/>
-    <mergeCell ref="F562:F563"/>
-    <mergeCell ref="D566:D567"/>
-    <mergeCell ref="E566:E567"/>
-    <mergeCell ref="F566:F567"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -46124,7 +46130,7 @@
     <row r="93" spans="1:8">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="123" t="s">
+      <c r="C93" s="161" t="s">
         <v>1653</v>
       </c>
       <c r="D93" s="1"/>
@@ -46216,7 +46222,7 @@
     <row r="98" spans="1:8" ht="15" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
-      <c r="C98" s="123" t="s">
+      <c r="C98" s="161" t="s">
         <v>1653</v>
       </c>
       <c r="D98" s="1"/>
@@ -49746,7 +49752,9 @@
     <row r="255" spans="1:8">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
+      <c r="C255" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D255" s="81" t="s">
         <v>620</v>
       </c>
@@ -49846,7 +49854,9 @@
     <row r="260" spans="1:9">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
+      <c r="C260" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D260" s="81" t="s">
         <v>620</v>
       </c>
@@ -49945,7 +49955,7 @@
       <c r="B265" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C265" s="125"/>
+      <c r="C265" s="1"/>
       <c r="D265" s="81" t="s">
         <v>620</v>
       </c>
@@ -49963,7 +49973,9 @@
       <c r="B266" s="125" t="s">
         <v>1003</v>
       </c>
-      <c r="C266" s="125"/>
+      <c r="C266" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D266" s="81" t="s">
         <v>620</v>
       </c>
@@ -49980,6 +49992,9 @@
       <c r="A267" s="1" t="s">
         <v>974</v>
       </c>
+      <c r="C267" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D267" s="82" t="s">
         <v>621</v>
       </c>
@@ -50003,7 +50018,7 @@
       <c r="B268" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C268" s="114"/>
+      <c r="C268" s="1"/>
       <c r="D268" s="82" t="s">
         <v>621</v>
       </c>
@@ -50027,7 +50042,7 @@
       <c r="B269" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C269" s="114"/>
+      <c r="C269" s="1"/>
       <c r="D269" s="82" t="s">
         <v>621</v>
       </c>
@@ -50045,7 +50060,7 @@
       <c r="B270" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C270" s="114"/>
+      <c r="C270" s="1"/>
       <c r="D270" s="82" t="s">
         <v>621</v>
       </c>
@@ -50065,7 +50080,9 @@
     <row r="271" spans="1:9">
       <c r="A271" s="1"/>
       <c r="B271" s="114"/>
-      <c r="C271" s="114"/>
+      <c r="C271" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D271" s="82" t="s">
         <v>621</v>
       </c>
@@ -50079,7 +50096,9 @@
     <row r="272" spans="1:9">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
+      <c r="C272" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D272" s="82" t="s">
         <v>621</v>
       </c>
@@ -50097,6 +50116,9 @@
       </c>
     </row>
     <row r="273" spans="1:8">
+      <c r="C273" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D273" s="82" t="s">
         <v>621</v>
       </c>
@@ -50114,6 +50136,9 @@
       </c>
     </row>
     <row r="274" spans="1:8">
+      <c r="C274" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D274" s="82" t="s">
         <v>621</v>
       </c>
@@ -50131,6 +50156,9 @@
       </c>
     </row>
     <row r="275" spans="1:8">
+      <c r="C275" s="161" t="s">
+        <v>1412</v>
+      </c>
       <c r="D275" s="82" t="s">
         <v>621</v>
       </c>
@@ -50142,6 +50170,9 @@
       <c r="H275" s="3"/>
     </row>
     <row r="276" spans="1:8">
+      <c r="C276" s="161" t="s">
+        <v>1412</v>
+      </c>
       <c r="D276" s="82" t="s">
         <v>621</v>
       </c>
@@ -50153,6 +50184,9 @@
       <c r="H276" s="3"/>
     </row>
     <row r="277" spans="1:8">
+      <c r="C277" s="161" t="s">
+        <v>1412</v>
+      </c>
       <c r="D277" s="82" t="s">
         <v>621</v>
       </c>
@@ -50164,6 +50198,9 @@
       <c r="H277" s="3"/>
     </row>
     <row r="278" spans="1:8">
+      <c r="C278" s="161" t="s">
+        <v>1412</v>
+      </c>
       <c r="D278" s="82" t="s">
         <v>621</v>
       </c>
@@ -50175,6 +50212,9 @@
       <c r="H278" s="3"/>
     </row>
     <row r="279" spans="1:8">
+      <c r="C279" s="161" t="s">
+        <v>1412</v>
+      </c>
       <c r="D279" s="82" t="s">
         <v>621</v>
       </c>
@@ -50188,7 +50228,9 @@
     <row r="280" spans="1:8">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
+      <c r="C280" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D280" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50204,7 +50246,9 @@
     <row r="281" spans="1:8">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
+      <c r="C281" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D281" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50224,7 +50268,9 @@
     <row r="282" spans="1:8">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
+      <c r="C282" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D282" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50240,7 +50286,9 @@
     <row r="283" spans="1:8">
       <c r="A283" s="60"/>
       <c r="B283" s="60"/>
-      <c r="C283" s="60"/>
+      <c r="C283" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D283" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50256,7 +50304,9 @@
     <row r="284" spans="1:8">
       <c r="A284" s="60"/>
       <c r="B284" s="60"/>
-      <c r="C284" s="60"/>
+      <c r="C284" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D284" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50272,7 +50322,9 @@
     <row r="285" spans="1:8">
       <c r="A285" s="60"/>
       <c r="B285" s="60"/>
-      <c r="C285" s="60"/>
+      <c r="C285" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D285" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50288,7 +50340,9 @@
     <row r="286" spans="1:8">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
+      <c r="C286" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D286" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50304,7 +50358,9 @@
     <row r="287" spans="1:8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
+      <c r="C287" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D287" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50324,7 +50380,9 @@
     <row r="288" spans="1:8">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
-      <c r="C288" s="1"/>
+      <c r="C288" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D288" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50340,7 +50398,9 @@
     <row r="289" spans="1:8">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
-      <c r="C289" s="1"/>
+      <c r="C289" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D289" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50360,7 +50420,9 @@
     <row r="290" spans="1:8">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
-      <c r="C290" s="1"/>
+      <c r="C290" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D290" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50376,7 +50438,9 @@
     <row r="291" spans="1:8">
       <c r="A291" s="60"/>
       <c r="B291" s="60"/>
-      <c r="C291" s="60"/>
+      <c r="C291" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D291" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50392,7 +50456,9 @@
     <row r="292" spans="1:8">
       <c r="A292" s="60"/>
       <c r="B292" s="60"/>
-      <c r="C292" s="60"/>
+      <c r="C292" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D292" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50408,7 +50474,9 @@
     <row r="293" spans="1:8">
       <c r="A293" s="60"/>
       <c r="B293" s="60"/>
-      <c r="C293" s="60"/>
+      <c r="C293" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D293" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50424,7 +50492,9 @@
     <row r="294" spans="1:8">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
+      <c r="C294" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D294" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50440,7 +50510,9 @@
     <row r="295" spans="1:8">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
+      <c r="C295" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D295" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50460,7 +50532,9 @@
     <row r="296" spans="1:8">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
+      <c r="C296" s="161" t="s">
+        <v>1654</v>
+      </c>
       <c r="D296" s="84" t="s">
         <v>1008</v>
       </c>
@@ -50474,7 +50548,9 @@
     <row r="297" spans="1:8">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
+      <c r="C297" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D297" s="84" t="s">
         <v>1630</v>
       </c>
@@ -50492,7 +50568,9 @@
     <row r="298" spans="1:8">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
-      <c r="C298" s="1"/>
+      <c r="C298" s="125" t="s">
+        <v>1003</v>
+      </c>
       <c r="D298" s="84" t="s">
         <v>1630</v>
       </c>
@@ -50510,7 +50588,9 @@
     <row r="299" spans="1:8">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
+      <c r="C299" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D299" s="84" t="s">
         <v>1630</v>
       </c>
@@ -50528,7 +50608,9 @@
     <row r="300" spans="1:8">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
-      <c r="C300" s="1"/>
+      <c r="C300" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D300" s="84" t="s">
         <v>1630</v>
       </c>
@@ -50546,7 +50628,9 @@
     <row r="301" spans="1:8" ht="15" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
-      <c r="C301" s="1"/>
+      <c r="C301" s="161" t="s">
+        <v>1655</v>
+      </c>
       <c r="D301" s="84" t="s">
         <v>1630</v>
       </c>
@@ -50564,7 +50648,9 @@
     <row r="302" spans="1:8" ht="15" thickBot="1">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
-      <c r="C302" s="14"/>
+      <c r="C302" s="161" t="s">
+        <v>1654</v>
+      </c>
       <c r="D302" s="34" t="s">
         <v>1014</v>
       </c>
@@ -50581,7 +50667,9 @@
     <row r="303" spans="1:8">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
-      <c r="C303" s="14"/>
+      <c r="C303" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D303" s="34" t="s">
         <v>1014</v>
       </c>
@@ -50599,6 +50687,9 @@
       </c>
     </row>
     <row r="304" spans="1:8">
+      <c r="C304" s="123" t="s">
+        <v>1654</v>
+      </c>
       <c r="D304" s="34" t="s">
         <v>1014</v>
       </c>
@@ -50614,6 +50705,9 @@
       <c r="H304" s="14"/>
     </row>
     <row r="305" spans="1:8">
+      <c r="C305" s="123" t="s">
+        <v>1654</v>
+      </c>
       <c r="D305" s="34" t="s">
         <v>1014</v>
       </c>
@@ -50631,7 +50725,9 @@
     <row r="306" spans="1:8">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
-      <c r="C306" s="14"/>
+      <c r="C306" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D306" s="34" t="s">
         <v>1014</v>
       </c>
@@ -50649,7 +50745,9 @@
     <row r="307" spans="1:8">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
-      <c r="C307" s="14"/>
+      <c r="C307" s="114" t="s">
+        <v>974</v>
+      </c>
       <c r="D307" s="34" t="s">
         <v>1014</v>
       </c>
@@ -51024,6 +51122,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -51224,27 +51342,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -51261,23 +51378,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3316" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38A4DB2-4DA8-4F7D-A8C2-19E4E4FBE17F}"/>
+  <xr:revisionPtr revIDLastSave="3318" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D429055-5F48-4944-8A27-FDB09B430026}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -12467,13 +12467,13 @@
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="56" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="56" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31808,13 +31808,13 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="157" t="s">
+      <c r="O544" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="P544" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q544" s="159" t="s">
+      <c r="P544" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q544" s="160" t="s">
         <v>36</v>
       </c>
       <c r="R544" s="3" t="s">
@@ -31836,9 +31836,9 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="157"/>
-      <c r="P545" s="158"/>
-      <c r="Q545" s="159"/>
+      <c r="O545" s="158"/>
+      <c r="P545" s="159"/>
+      <c r="Q545" s="160"/>
       <c r="R545" s="3" t="s">
         <v>38</v>
       </c>
@@ -31886,13 +31886,13 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="160" t="s">
+      <c r="O548" s="161" t="s">
         <v>42</v>
       </c>
-      <c r="P548" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q548" s="159" t="s">
+      <c r="P548" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q548" s="160" t="s">
         <v>43</v>
       </c>
       <c r="R548" s="3">
@@ -31914,9 +31914,9 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="160"/>
-      <c r="P549" s="158"/>
-      <c r="Q549" s="159"/>
+      <c r="O549" s="161"/>
+      <c r="P549" s="159"/>
+      <c r="Q549" s="160"/>
       <c r="R549" s="3" t="s">
         <v>44</v>
       </c>
@@ -31936,13 +31936,13 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="157" t="s">
+      <c r="O550" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="P550" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q550" s="159" t="s">
+      <c r="P550" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q550" s="160" t="s">
         <v>46</v>
       </c>
       <c r="R550" s="3" t="s">
@@ -31964,9 +31964,9 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="157"/>
-      <c r="P551" s="158"/>
-      <c r="Q551" s="159"/>
+      <c r="O551" s="158"/>
+      <c r="P551" s="159"/>
+      <c r="Q551" s="160"/>
       <c r="R551" s="3" t="s">
         <v>48</v>
       </c>
@@ -32014,13 +32014,13 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="160" t="s">
+      <c r="O554" s="161" t="s">
         <v>52</v>
       </c>
-      <c r="P554" s="158" t="s">
+      <c r="P554" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="Q554" s="159" t="s">
+      <c r="Q554" s="160" t="s">
         <v>53</v>
       </c>
       <c r="R554" s="3">
@@ -32042,9 +32042,9 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="160"/>
-      <c r="P555" s="158"/>
-      <c r="Q555" s="159"/>
+      <c r="O555" s="161"/>
+      <c r="P555" s="159"/>
+      <c r="Q555" s="160"/>
       <c r="R555" s="3" t="s">
         <v>44</v>
       </c>
@@ -32064,13 +32064,13 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="157" t="s">
+      <c r="O556" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="P556" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q556" s="159" t="s">
+      <c r="P556" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q556" s="160" t="s">
         <v>55</v>
       </c>
       <c r="R556" s="3" t="s">
@@ -32092,9 +32092,9 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="157"/>
-      <c r="P557" s="158"/>
-      <c r="Q557" s="159"/>
+      <c r="O557" s="158"/>
+      <c r="P557" s="159"/>
+      <c r="Q557" s="160"/>
       <c r="R557" s="3" t="s">
         <v>57</v>
       </c>
@@ -32114,13 +32114,13 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="157" t="s">
+      <c r="O558" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="P558" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q558" s="159" t="s">
+      <c r="P558" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q558" s="160" t="s">
         <v>59</v>
       </c>
       <c r="R558" s="3" t="s">
@@ -32142,9 +32142,9 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="157"/>
-      <c r="P559" s="158"/>
-      <c r="Q559" s="159"/>
+      <c r="O559" s="158"/>
+      <c r="P559" s="159"/>
+      <c r="Q559" s="160"/>
       <c r="R559" s="3" t="s">
         <v>61</v>
       </c>
@@ -32164,13 +32164,13 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="157" t="s">
+      <c r="O560" s="158" t="s">
         <v>62</v>
       </c>
-      <c r="P560" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q560" s="159" t="s">
+      <c r="P560" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q560" s="160" t="s">
         <v>63</v>
       </c>
       <c r="R560" s="3" t="s">
@@ -32192,9 +32192,9 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="157"/>
-      <c r="P561" s="158"/>
-      <c r="Q561" s="159"/>
+      <c r="O561" s="158"/>
+      <c r="P561" s="159"/>
+      <c r="Q561" s="160"/>
       <c r="R561" s="3" t="s">
         <v>65</v>
       </c>
@@ -32324,13 +32324,13 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="160" t="s">
+      <c r="O566" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="P566" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q566" s="159" t="s">
+      <c r="P566" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q566" s="160" t="s">
         <v>87</v>
       </c>
       <c r="R566" s="3" t="s">
@@ -32352,9 +32352,9 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="160"/>
-      <c r="P567" s="158"/>
-      <c r="Q567" s="159"/>
+      <c r="O567" s="161"/>
+      <c r="P567" s="159"/>
+      <c r="Q567" s="160"/>
       <c r="R567" s="3" t="s">
         <v>89</v>
       </c>
@@ -32374,9 +32374,9 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="160"/>
-      <c r="P568" s="158"/>
-      <c r="Q568" s="159"/>
+      <c r="O568" s="161"/>
+      <c r="P568" s="159"/>
+      <c r="Q568" s="160"/>
       <c r="R568" s="3" t="s">
         <v>90</v>
       </c>
@@ -32396,13 +32396,13 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="160" t="s">
+      <c r="O569" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="P569" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q569" s="159" t="s">
+      <c r="P569" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q569" s="160" t="s">
         <v>92</v>
       </c>
       <c r="R569" s="3" t="s">
@@ -32424,9 +32424,9 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="160"/>
-      <c r="P570" s="158"/>
-      <c r="Q570" s="159"/>
+      <c r="O570" s="161"/>
+      <c r="P570" s="159"/>
+      <c r="Q570" s="160"/>
       <c r="R570" s="3" t="s">
         <v>89</v>
       </c>
@@ -32446,9 +32446,9 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="160"/>
-      <c r="P571" s="158"/>
-      <c r="Q571" s="159"/>
+      <c r="O571" s="161"/>
+      <c r="P571" s="159"/>
+      <c r="Q571" s="160"/>
       <c r="R571" s="3" t="s">
         <v>90</v>
       </c>
@@ -33215,6 +33215,24 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33224,24 +33242,6 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -43103,13 +43103,13 @@
       <c r="A562" s="12"/>
       <c r="B562" s="12"/>
       <c r="C562" s="12"/>
-      <c r="D562" s="157" t="s">
+      <c r="D562" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="E562" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F562" s="159" t="s">
+      <c r="E562" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F562" s="160" t="s">
         <v>36</v>
       </c>
       <c r="G562" s="3" t="s">
@@ -43120,9 +43120,9 @@
       <c r="A563" s="12"/>
       <c r="B563" s="12"/>
       <c r="C563" s="12"/>
-      <c r="D563" s="157"/>
-      <c r="E563" s="158"/>
-      <c r="F563" s="159"/>
+      <c r="D563" s="158"/>
+      <c r="E563" s="159"/>
+      <c r="F563" s="160"/>
       <c r="G563" s="3" t="s">
         <v>38</v>
       </c>
@@ -43148,13 +43148,13 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="160" t="s">
+      <c r="D566" s="161" t="s">
         <v>42</v>
       </c>
-      <c r="E566" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F566" s="159" t="s">
+      <c r="E566" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F566" s="160" t="s">
         <v>43</v>
       </c>
       <c r="G566" s="3">
@@ -43165,9 +43165,9 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="160"/>
-      <c r="E567" s="158"/>
-      <c r="F567" s="159"/>
+      <c r="D567" s="161"/>
+      <c r="E567" s="159"/>
+      <c r="F567" s="160"/>
       <c r="G567" s="3" t="s">
         <v>44</v>
       </c>
@@ -43176,13 +43176,13 @@
       <c r="A568" s="12"/>
       <c r="B568" s="12"/>
       <c r="C568" s="12"/>
-      <c r="D568" s="157" t="s">
+      <c r="D568" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="E568" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F568" s="159" t="s">
+      <c r="E568" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F568" s="160" t="s">
         <v>46</v>
       </c>
       <c r="G568" s="3" t="s">
@@ -43193,9 +43193,9 @@
       <c r="A569" s="12"/>
       <c r="B569" s="12"/>
       <c r="C569" s="12"/>
-      <c r="D569" s="157"/>
-      <c r="E569" s="158"/>
-      <c r="F569" s="159"/>
+      <c r="D569" s="158"/>
+      <c r="E569" s="159"/>
+      <c r="F569" s="160"/>
       <c r="G569" s="3" t="s">
         <v>48</v>
       </c>
@@ -43221,13 +43221,13 @@
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
-      <c r="D572" s="160" t="s">
+      <c r="D572" s="161" t="s">
         <v>52</v>
       </c>
-      <c r="E572" s="158" t="s">
+      <c r="E572" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="F572" s="159" t="s">
+      <c r="F572" s="160" t="s">
         <v>53</v>
       </c>
       <c r="G572" s="3">
@@ -43238,9 +43238,9 @@
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
-      <c r="D573" s="160"/>
-      <c r="E573" s="158"/>
-      <c r="F573" s="159"/>
+      <c r="D573" s="161"/>
+      <c r="E573" s="159"/>
+      <c r="F573" s="160"/>
       <c r="G573" s="3" t="s">
         <v>44</v>
       </c>
@@ -43249,13 +43249,13 @@
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
-      <c r="D574" s="157" t="s">
+      <c r="D574" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="E574" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F574" s="159" t="s">
+      <c r="E574" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F574" s="160" t="s">
         <v>55</v>
       </c>
       <c r="G574" s="3" t="s">
@@ -43266,9 +43266,9 @@
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="157"/>
-      <c r="E575" s="158"/>
-      <c r="F575" s="159"/>
+      <c r="D575" s="158"/>
+      <c r="E575" s="159"/>
+      <c r="F575" s="160"/>
       <c r="G575" s="3" t="s">
         <v>57</v>
       </c>
@@ -43277,13 +43277,13 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="157" t="s">
+      <c r="D576" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="E576" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F576" s="159" t="s">
+      <c r="E576" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F576" s="160" t="s">
         <v>59</v>
       </c>
       <c r="G576" s="3" t="s">
@@ -43294,9 +43294,9 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="157"/>
-      <c r="E577" s="158"/>
-      <c r="F577" s="159"/>
+      <c r="D577" s="158"/>
+      <c r="E577" s="159"/>
+      <c r="F577" s="160"/>
       <c r="G577" s="3" t="s">
         <v>61</v>
       </c>
@@ -43305,13 +43305,13 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="157" t="s">
+      <c r="D578" s="158" t="s">
         <v>62</v>
       </c>
-      <c r="E578" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F578" s="159" t="s">
+      <c r="E578" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F578" s="160" t="s">
         <v>63</v>
       </c>
       <c r="G578" s="3" t="s">
@@ -43322,9 +43322,9 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="157"/>
-      <c r="E579" s="158"/>
-      <c r="F579" s="159"/>
+      <c r="D579" s="158"/>
+      <c r="E579" s="159"/>
+      <c r="F579" s="160"/>
       <c r="G579" s="3" t="s">
         <v>65</v>
       </c>
@@ -43399,13 +43399,13 @@
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
-      <c r="D584" s="160" t="s">
+      <c r="D584" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="E584" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F584" s="159" t="s">
+      <c r="E584" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F584" s="160" t="s">
         <v>87</v>
       </c>
       <c r="G584" s="3" t="s">
@@ -43416,9 +43416,9 @@
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
-      <c r="D585" s="160"/>
-      <c r="E585" s="158"/>
-      <c r="F585" s="159"/>
+      <c r="D585" s="161"/>
+      <c r="E585" s="159"/>
+      <c r="F585" s="160"/>
       <c r="G585" s="3" t="s">
         <v>89</v>
       </c>
@@ -43427,9 +43427,9 @@
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
-      <c r="D586" s="160"/>
-      <c r="E586" s="158"/>
-      <c r="F586" s="159"/>
+      <c r="D586" s="161"/>
+      <c r="E586" s="159"/>
+      <c r="F586" s="160"/>
       <c r="G586" s="3" t="s">
         <v>90</v>
       </c>
@@ -43438,13 +43438,13 @@
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
-      <c r="D587" s="160" t="s">
+      <c r="D587" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="E587" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F587" s="159" t="s">
+      <c r="E587" s="159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F587" s="160" t="s">
         <v>92</v>
       </c>
       <c r="G587" s="3" t="s">
@@ -43455,9 +43455,9 @@
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
-      <c r="D588" s="160"/>
-      <c r="E588" s="158"/>
-      <c r="F588" s="159"/>
+      <c r="D588" s="161"/>
+      <c r="E588" s="159"/>
+      <c r="F588" s="160"/>
       <c r="G588" s="3" t="s">
         <v>89</v>
       </c>
@@ -43466,9 +43466,9 @@
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
-      <c r="D589" s="160"/>
-      <c r="E589" s="158"/>
-      <c r="F589" s="159"/>
+      <c r="D589" s="161"/>
+      <c r="E589" s="159"/>
+      <c r="F589" s="160"/>
       <c r="G589" s="3" t="s">
         <v>90</v>
       </c>
@@ -43893,24 +43893,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D562:D563"/>
-    <mergeCell ref="E562:E563"/>
-    <mergeCell ref="F562:F563"/>
-    <mergeCell ref="D566:D567"/>
-    <mergeCell ref="E566:E567"/>
-    <mergeCell ref="F566:F567"/>
-    <mergeCell ref="D568:D569"/>
-    <mergeCell ref="E568:E569"/>
-    <mergeCell ref="F568:F569"/>
-    <mergeCell ref="D572:D573"/>
-    <mergeCell ref="E572:E573"/>
-    <mergeCell ref="F572:F573"/>
-    <mergeCell ref="D574:D575"/>
-    <mergeCell ref="E574:E575"/>
-    <mergeCell ref="F574:F575"/>
-    <mergeCell ref="D576:D577"/>
-    <mergeCell ref="E576:E577"/>
-    <mergeCell ref="F576:F577"/>
     <mergeCell ref="D587:D589"/>
     <mergeCell ref="E587:E589"/>
     <mergeCell ref="F587:F589"/>
@@ -43920,6 +43902,24 @@
     <mergeCell ref="D584:D586"/>
     <mergeCell ref="E584:E586"/>
     <mergeCell ref="F584:F586"/>
+    <mergeCell ref="D574:D575"/>
+    <mergeCell ref="E574:E575"/>
+    <mergeCell ref="F574:F575"/>
+    <mergeCell ref="D576:D577"/>
+    <mergeCell ref="E576:E577"/>
+    <mergeCell ref="F576:F577"/>
+    <mergeCell ref="D568:D569"/>
+    <mergeCell ref="E568:E569"/>
+    <mergeCell ref="F568:F569"/>
+    <mergeCell ref="D572:D573"/>
+    <mergeCell ref="E572:E573"/>
+    <mergeCell ref="F572:F573"/>
+    <mergeCell ref="D562:D563"/>
+    <mergeCell ref="E562:E563"/>
+    <mergeCell ref="F562:F563"/>
+    <mergeCell ref="D566:D567"/>
+    <mergeCell ref="E566:E567"/>
+    <mergeCell ref="F566:F567"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -45166,8 +45166,8 @@
       <c r="B53" s="123" t="s">
         <v>1420</v>
       </c>
-      <c r="C53" s="123" t="s">
-        <v>1420</v>
+      <c r="C53" s="125" t="s">
+        <v>1003</v>
       </c>
       <c r="D53" s="35" t="s">
         <v>619</v>
@@ -45244,8 +45244,8 @@
       <c r="B56" s="123" t="s">
         <v>1420</v>
       </c>
-      <c r="C56" s="123" t="s">
-        <v>1420</v>
+      <c r="C56" s="125" t="s">
+        <v>1003</v>
       </c>
       <c r="D56" s="35" t="s">
         <v>619</v>
@@ -46130,7 +46130,7 @@
     <row r="93" spans="1:8">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="161" t="s">
+      <c r="C93" s="157" t="s">
         <v>1653</v>
       </c>
       <c r="D93" s="1"/>
@@ -46222,7 +46222,7 @@
     <row r="98" spans="1:8" ht="15" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
-      <c r="C98" s="161" t="s">
+      <c r="C98" s="157" t="s">
         <v>1653</v>
       </c>
       <c r="D98" s="1"/>
@@ -50156,7 +50156,7 @@
       </c>
     </row>
     <row r="275" spans="1:8">
-      <c r="C275" s="161" t="s">
+      <c r="C275" s="157" t="s">
         <v>1412</v>
       </c>
       <c r="D275" s="82" t="s">
@@ -50170,7 +50170,7 @@
       <c r="H275" s="3"/>
     </row>
     <row r="276" spans="1:8">
-      <c r="C276" s="161" t="s">
+      <c r="C276" s="157" t="s">
         <v>1412</v>
       </c>
       <c r="D276" s="82" t="s">
@@ -50184,7 +50184,7 @@
       <c r="H276" s="3"/>
     </row>
     <row r="277" spans="1:8">
-      <c r="C277" s="161" t="s">
+      <c r="C277" s="157" t="s">
         <v>1412</v>
       </c>
       <c r="D277" s="82" t="s">
@@ -50198,7 +50198,7 @@
       <c r="H277" s="3"/>
     </row>
     <row r="278" spans="1:8">
-      <c r="C278" s="161" t="s">
+      <c r="C278" s="157" t="s">
         <v>1412</v>
       </c>
       <c r="D278" s="82" t="s">
@@ -50212,7 +50212,7 @@
       <c r="H278" s="3"/>
     </row>
     <row r="279" spans="1:8">
-      <c r="C279" s="161" t="s">
+      <c r="C279" s="157" t="s">
         <v>1412</v>
       </c>
       <c r="D279" s="82" t="s">
@@ -50532,7 +50532,7 @@
     <row r="296" spans="1:8">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
-      <c r="C296" s="161" t="s">
+      <c r="C296" s="157" t="s">
         <v>1654</v>
       </c>
       <c r="D296" s="84" t="s">
@@ -50628,7 +50628,7 @@
     <row r="301" spans="1:8" ht="15" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
-      <c r="C301" s="161" t="s">
+      <c r="C301" s="157" t="s">
         <v>1655</v>
       </c>
       <c r="D301" s="84" t="s">
@@ -50648,7 +50648,7 @@
     <row r="302" spans="1:8" ht="15" thickBot="1">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
-      <c r="C302" s="161" t="s">
+      <c r="C302" s="157" t="s">
         <v>1654</v>
       </c>
       <c r="D302" s="34" t="s">
@@ -51131,17 +51131,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -51342,6 +51331,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
   <ds:schemaRefs>
@@ -51351,17 +51351,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -51378,4 +51367,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3318" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D429055-5F48-4944-8A27-FDB09B430026}"/>
+  <xr:revisionPtr revIDLastSave="3319" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD701D76-2E94-4D36-8EF4-F8DE9E2FEA54}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -33215,24 +33215,6 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33242,6 +33224,24 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -43893,6 +43893,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D562:D563"/>
+    <mergeCell ref="E562:E563"/>
+    <mergeCell ref="F562:F563"/>
+    <mergeCell ref="D566:D567"/>
+    <mergeCell ref="E566:E567"/>
+    <mergeCell ref="F566:F567"/>
+    <mergeCell ref="D568:D569"/>
+    <mergeCell ref="E568:E569"/>
+    <mergeCell ref="F568:F569"/>
+    <mergeCell ref="D572:D573"/>
+    <mergeCell ref="E572:E573"/>
+    <mergeCell ref="F572:F573"/>
+    <mergeCell ref="D574:D575"/>
+    <mergeCell ref="E574:E575"/>
+    <mergeCell ref="F574:F575"/>
+    <mergeCell ref="D576:D577"/>
+    <mergeCell ref="E576:E577"/>
+    <mergeCell ref="F576:F577"/>
     <mergeCell ref="D587:D589"/>
     <mergeCell ref="E587:E589"/>
     <mergeCell ref="F587:F589"/>
@@ -43902,24 +43920,6 @@
     <mergeCell ref="D584:D586"/>
     <mergeCell ref="E584:E586"/>
     <mergeCell ref="F584:F586"/>
-    <mergeCell ref="D574:D575"/>
-    <mergeCell ref="E574:E575"/>
-    <mergeCell ref="F574:F575"/>
-    <mergeCell ref="D576:D577"/>
-    <mergeCell ref="E576:E577"/>
-    <mergeCell ref="F576:F577"/>
-    <mergeCell ref="D568:D569"/>
-    <mergeCell ref="E568:E569"/>
-    <mergeCell ref="F568:F569"/>
-    <mergeCell ref="D572:D573"/>
-    <mergeCell ref="E572:E573"/>
-    <mergeCell ref="F572:F573"/>
-    <mergeCell ref="D562:D563"/>
-    <mergeCell ref="E562:E563"/>
-    <mergeCell ref="F562:F563"/>
-    <mergeCell ref="D566:D567"/>
-    <mergeCell ref="E566:E567"/>
-    <mergeCell ref="F566:F567"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -44145,8 +44145,8 @@
       <c r="B9" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C9" s="123" t="s">
-        <v>1420</v>
+      <c r="C9" s="114" t="s">
+        <v>974</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>616</v>
@@ -44171,8 +44171,8 @@
       <c r="B10" s="114" t="s">
         <v>974</v>
       </c>
-      <c r="C10" s="123" t="s">
-        <v>1420</v>
+      <c r="C10" s="114" t="s">
+        <v>974</v>
       </c>
       <c r="D10" s="35" t="s">
         <v>616</v>
@@ -51122,12 +51122,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -51332,20 +51334,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -51370,12 +51373,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>